--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\github_corrigido_dashboard_obrasRev1\github\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D3F51D-200A-4500-8FFE-9E4651753B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D805BD9-6DCB-4FAA-87EB-09E91707409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2879,7 +2879,7 @@
         <v>207.5</v>
       </c>
       <c r="F72" s="5">
-        <v>485.52</v>
+        <v>276.38</v>
       </c>
       <c r="I72">
         <v>1801</v>
@@ -2898,7 +2898,7 @@
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
       <c r="X72">
-        <v>485.52</v>
+        <v>276.38</v>
       </c>
       <c r="AG72" t="s">
         <v>114</v>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D805BD9-6DCB-4FAA-87EB-09E91707409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE97603-A5C3-4271-951A-6B91FEF1BAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,7 +403,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,13 +432,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -453,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -466,12 +485,309 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -501,33 +817,33 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bloco"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo_Extensao"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Extensao_Planejada_m"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Extensao_Executada_m" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Extensao_Executada_m" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{6BB83A0A-92EF-4D0A-89EF-C6F503D3B7CB}" name="PV"/>
     <tableColumn id="7" xr3:uid="{16D84CF1-E783-4000-847C-89A0C712ADDD}" name="Profundidade_PV_m"/>
     <tableColumn id="8" xr3:uid="{CCC7E282-906C-4070-A05D-0C12B88259D5}" name="Economias prevista"/>
     <tableColumn id="9" xr3:uid="{141F879B-3CB0-49C0-B696-841DCF5BEDB4}" name="Economias Recebidas"/>
     <tableColumn id="10" xr3:uid="{C0195FBC-3466-4999-8402-DBEE3F7978C5}" name="produção março 2025"/>
-    <tableColumn id="11" xr3:uid="{9560D17C-B2DC-4B87-9E68-8B0334D1A5F1}" name="produção Abril 2025"/>
-    <tableColumn id="12" xr3:uid="{2CC935E5-AE57-401D-B0B9-16AA7CE547C9}" name="produção Maio 2025"/>
-    <tableColumn id="13" xr3:uid="{D4A32E48-58F4-4347-A22F-3EC617F115ED}" name="produção Junho 2025"/>
-    <tableColumn id="14" xr3:uid="{FD08EE1C-24D6-435D-BFB5-DE8525365C0B}" name="produção Julho 2025"/>
-    <tableColumn id="15" xr3:uid="{0E3143BC-7DD4-42C2-9632-F4C84435B02B}" name="produção Agosto 2025"/>
-    <tableColumn id="16" xr3:uid="{1A595E00-BFE2-4CB2-88ED-7BAD72BCDC1D}" name="produção Setembro 2025"/>
-    <tableColumn id="17" xr3:uid="{8A59EA87-2170-4E3A-8757-7A5746B89A12}" name="produção Outubro 2025"/>
-    <tableColumn id="18" xr3:uid="{E9DBE3BD-B4AB-4971-9574-0FF7FA5803DD}" name="produção Novembro 2025"/>
-    <tableColumn id="19" xr3:uid="{1D73A10C-A301-48D5-96BD-32A1DB452BFA}" name="produção Dezembro 2025"/>
-    <tableColumn id="20" xr3:uid="{D518955F-FB3C-479D-B0A0-C858B4EE0CF2}" name="produção Janeiro 2026"/>
-    <tableColumn id="21" xr3:uid="{2643BDE6-67AE-4701-982B-BBA15C7E24D7}" name="produção Fevereiro 2026"/>
-    <tableColumn id="22" xr3:uid="{25EDB414-06AF-467B-BEAF-CBFA34B0E3FE}" name="produção Março 2026"/>
-    <tableColumn id="23" xr3:uid="{ACC94B2B-3C05-4E69-BC1D-31E6BC6BF41F}" name="produção Abril 2026"/>
-    <tableColumn id="24" xr3:uid="{434478D3-9DE1-40FA-BAE2-5B310B23261F}" name="produção Maio 2026"/>
-    <tableColumn id="25" xr3:uid="{F969BF45-8403-448D-ADFE-D1E4B359F4FC}" name="produção Junho 2026"/>
-    <tableColumn id="26" xr3:uid="{3190B8C0-F461-4D5F-9042-D3DA4392D852}" name="produção Julho 2026"/>
-    <tableColumn id="27" xr3:uid="{1296E3F8-3AB4-4A3B-8378-6F3E29C9E2CA}" name="produção Agosto 2026"/>
-    <tableColumn id="28" xr3:uid="{8DDEDC24-3476-4DA6-AF25-63FF4B848894}" name="produção Setembro 2026"/>
-    <tableColumn id="29" xr3:uid="{CCF3E2AD-2E1F-42BE-8A16-B57AE967B62C}" name="produção Outubro 2026"/>
-    <tableColumn id="30" xr3:uid="{AEDAF9C8-4CB3-46E6-9E05-502560E49621}" name="produção Novembro 2026"/>
-    <tableColumn id="31" xr3:uid="{224F4735-9E51-4718-AB11-1FC679A00B87}" name="produção Dezembro 2026"/>
+    <tableColumn id="11" xr3:uid="{9560D17C-B2DC-4B87-9E68-8B0334D1A5F1}" name="produção Abril 2025" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{2CC935E5-AE57-401D-B0B9-16AA7CE547C9}" name="produção Maio 2025" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{D4A32E48-58F4-4347-A22F-3EC617F115ED}" name="produção Junho 2025" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{FD08EE1C-24D6-435D-BFB5-DE8525365C0B}" name="produção Julho 2025" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{0E3143BC-7DD4-42C2-9632-F4C84435B02B}" name="produção Agosto 2025" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{1A595E00-BFE2-4CB2-88ED-7BAD72BCDC1D}" name="produção Setembro 2025" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{8A59EA87-2170-4E3A-8757-7A5746B89A12}" name="produção Outubro 2025" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{E9DBE3BD-B4AB-4971-9574-0FF7FA5803DD}" name="produção Novembro 2025" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{1D73A10C-A301-48D5-96BD-32A1DB452BFA}" name="produção Dezembro 2025" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{D518955F-FB3C-479D-B0A0-C858B4EE0CF2}" name="produção Janeiro 2026" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{2643BDE6-67AE-4701-982B-BBA15C7E24D7}" name="produção Fevereiro 2026" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{25EDB414-06AF-467B-BEAF-CBFA34B0E3FE}" name="produção Março 2026" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{ACC94B2B-3C05-4E69-BC1D-31E6BC6BF41F}" name="produção Abril 2026" dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{434478D3-9DE1-40FA-BAE2-5B310B23261F}" name="produção Maio 2026" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{F969BF45-8403-448D-ADFE-D1E4B359F4FC}" name="produção Junho 2026" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{3190B8C0-F461-4D5F-9042-D3DA4392D852}" name="produção Julho 2026" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{1296E3F8-3AB4-4A3B-8378-6F3E29C9E2CA}" name="produção Agosto 2026" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{8DDEDC24-3476-4DA6-AF25-63FF4B848894}" name="produção Setembro 2026" dataDxfId="3"/>
+    <tableColumn id="29" xr3:uid="{CCF3E2AD-2E1F-42BE-8A16-B57AE967B62C}" name="produção Outubro 2026" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{AEDAF9C8-4CB3-46E6-9E05-502560E49621}" name="produção Novembro 2026" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{224F4735-9E51-4718-AB11-1FC679A00B87}" name="produção Dezembro 2026" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -831,7 +1147,11 @@
     <col min="8" max="8" width="8.88671875" customWidth="1"/>
     <col min="9" max="9" width="26.5546875" customWidth="1"/>
     <col min="10" max="10" width="10.44140625" customWidth="1"/>
-    <col min="11" max="32" width="7.6640625" customWidth="1"/>
+    <col min="11" max="12" width="7.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="15" width="7.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" customWidth="1"/>
+    <col min="17" max="32" width="7.6640625" customWidth="1"/>
     <col min="33" max="33" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -955,17 +1275,29 @@
       <c r="G2">
         <v>10</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4">
+      <c r="L2" s="6"/>
+      <c r="M2" s="8">
         <v>162.59</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
       <c r="AG2" t="s">
         <v>114</v>
       </c>
@@ -986,17 +1318,29 @@
       <c r="F3" s="5">
         <v>6.19</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4">
+      <c r="L3" s="6"/>
+      <c r="M3" s="8">
         <v>6.19</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
       <c r="AG3" t="s">
         <v>114</v>
       </c>
@@ -1017,19 +1361,31 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4">
+      <c r="L4" s="6"/>
+      <c r="M4" s="8">
         <v>47.94</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="8">
         <v>11.7</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
       <c r="AG4" t="s">
         <v>114</v>
       </c>
@@ -1050,17 +1406,29 @@
       <c r="F5" s="5">
         <v>47.5</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="8">
         <v>47.5</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
       <c r="AG5" t="s">
         <v>114</v>
       </c>
@@ -1081,17 +1449,29 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4">
+      <c r="L6" s="6"/>
+      <c r="M6" s="8">
         <v>105.6</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
       <c r="AG6" t="s">
         <v>114</v>
       </c>
@@ -1112,17 +1492,29 @@
       <c r="F7" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4">
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
       <c r="AG7" t="s">
         <v>114</v>
       </c>
@@ -1146,19 +1538,31 @@
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4">
+      <c r="L8" s="6"/>
+      <c r="M8" s="8">
         <v>66.83</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="8">
         <v>64.599999999999994</v>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
       <c r="AG8" t="s">
         <v>114</v>
       </c>
@@ -1182,15 +1586,27 @@
       <c r="J9">
         <v>2706</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
       <c r="AG9" t="s">
         <v>114</v>
       </c>
@@ -1209,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="5">
-        <v>523.63</v>
+        <v>523.65499999999997</v>
       </c>
       <c r="G10">
         <v>47</v>
@@ -1223,19 +1639,31 @@
       <c r="J10">
         <v>599</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4">
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="8">
         <v>217.93</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="8">
         <v>305.72500000000002</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
       <c r="AG10" t="s">
         <v>114</v>
       </c>
@@ -1253,15 +1681,27 @@
       <c r="E11">
         <v>469.7</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
       <c r="AG11" t="s">
         <v>114</v>
       </c>
@@ -1288,19 +1728,31 @@
       <c r="J12">
         <v>595</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4">
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="8">
         <v>134.10499999999999</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="8">
         <v>208.60499999999999</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
       <c r="AG12" t="s">
         <v>114</v>
       </c>
@@ -1321,15 +1773,27 @@
       <c r="F13" s="5">
         <v>0</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
       <c r="AG13" t="s">
         <v>114</v>
       </c>
@@ -1356,17 +1820,29 @@
       <c r="J14">
         <v>109</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4">
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="8">
         <v>231.85</v>
       </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
       <c r="AG14" t="s">
         <v>114</v>
       </c>
@@ -1387,17 +1863,29 @@
       <c r="F15" s="5">
         <v>4.0599999999999996</v>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4">
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="8">
         <v>4.0599999999999996</v>
       </c>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
       <c r="AG15" t="s">
         <v>114</v>
       </c>
@@ -1424,19 +1912,31 @@
       <c r="J16">
         <v>3229</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4">
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="8">
         <v>132.27000000000001</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="8">
         <v>235.44</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
       <c r="AG16" t="s">
         <v>114</v>
       </c>
@@ -1454,17 +1954,29 @@
       <c r="E17">
         <v>232.1</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4">
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="9">
         <v>154.93</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
       <c r="AG17" t="s">
         <v>114</v>
       </c>
@@ -1491,17 +2003,29 @@
       <c r="J18">
         <v>42</v>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4">
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6">
         <v>253.94</v>
       </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
       <c r="AG18" t="s">
         <v>114</v>
       </c>
@@ -1522,21 +2046,33 @@
       <c r="F19" s="5">
         <v>445.46</v>
       </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4">
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6">
         <v>242.97</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="Q19" s="6">
         <v>148.49</v>
       </c>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4">
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6">
         <v>54</v>
       </c>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
       <c r="AG19" t="s">
         <v>114</v>
       </c>
@@ -1569,17 +2105,29 @@
       <c r="J20">
         <v>661</v>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4">
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6">
         <v>192.04</v>
       </c>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
       <c r="AG20" t="s">
         <v>114</v>
       </c>
@@ -1600,17 +2148,29 @@
       <c r="F21" s="5">
         <v>19.91</v>
       </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4">
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6">
         <v>19.91</v>
       </c>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
       <c r="AG21" t="s">
         <v>114</v>
       </c>
@@ -1637,17 +2197,29 @@
       <c r="J22">
         <v>270</v>
       </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4">
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6">
         <v>259.3</v>
       </c>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
       <c r="AG22" t="s">
         <v>114</v>
       </c>
@@ -1668,17 +2240,29 @@
       <c r="F23" s="5">
         <v>39.75</v>
       </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4">
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6">
         <v>39.75</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
       <c r="AG23" t="s">
         <v>114</v>
       </c>
@@ -1699,15 +2283,27 @@
       <c r="I24">
         <v>43</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
       <c r="AG24" t="s">
         <v>115</v>
       </c>
@@ -1722,6 +2318,27 @@
       <c r="D25" t="s">
         <v>7</v>
       </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
       <c r="AG25" t="s">
         <v>115</v>
       </c>
@@ -1739,6 +2356,27 @@
       <c r="E26">
         <v>137</v>
       </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
@@ -1753,6 +2391,27 @@
       <c r="E27">
         <v>636</v>
       </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
@@ -1767,6 +2426,27 @@
       <c r="E28">
         <v>20</v>
       </c>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
     </row>
     <row r="29" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
@@ -1778,6 +2458,27 @@
       <c r="D29" t="s">
         <v>7</v>
       </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="6"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
@@ -1789,6 +2490,27 @@
       <c r="D30" t="s">
         <v>6</v>
       </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
@@ -1803,6 +2525,27 @@
       <c r="E31">
         <v>110</v>
       </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
     </row>
     <row r="32" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
@@ -1814,8 +2557,29 @@
       <c r="D32" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>29</v>
       </c>
@@ -1828,8 +2592,29 @@
       <c r="E33">
         <v>55</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6"/>
+      <c r="AE33" s="6"/>
+      <c r="AF33" s="6"/>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>30</v>
       </c>
@@ -1839,8 +2624,29 @@
       <c r="D34" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>30</v>
       </c>
@@ -1853,8 +2659,29 @@
       <c r="E35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
+      <c r="U35" s="6"/>
+      <c r="V35" s="6"/>
+      <c r="W35" s="6"/>
+      <c r="X35" s="6"/>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="6"/>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="6"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6"/>
+      <c r="AF35" s="6"/>
+    </row>
+    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>31</v>
       </c>
@@ -1864,8 +2691,29 @@
       <c r="D36" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>31</v>
       </c>
@@ -1878,8 +2726,29 @@
       <c r="E37">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="6"/>
+      <c r="W37" s="6"/>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="6"/>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="6"/>
+      <c r="AF37" s="6"/>
+    </row>
+    <row r="38" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>32</v>
       </c>
@@ -1892,8 +2761,29 @@
       <c r="I38">
         <v>11130</v>
       </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+      <c r="U38" s="6"/>
+      <c r="V38" s="6"/>
+      <c r="W38" s="6"/>
+      <c r="X38" s="6"/>
+      <c r="Y38" s="6"/>
+      <c r="Z38" s="6"/>
+      <c r="AA38" s="6"/>
+      <c r="AB38" s="6"/>
+      <c r="AC38" s="6"/>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="6"/>
+      <c r="AF38" s="6"/>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>32</v>
       </c>
@@ -1903,8 +2793,29 @@
       <c r="D39" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="6"/>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="6"/>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="6"/>
+      <c r="AF39" s="6"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>33</v>
       </c>
@@ -1917,8 +2828,29 @@
       <c r="E40">
         <v>1787.905</v>
       </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
+      <c r="X40" s="6"/>
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="6"/>
+      <c r="AB40" s="6"/>
+      <c r="AC40" s="6"/>
+      <c r="AD40" s="6"/>
+      <c r="AE40" s="6"/>
+      <c r="AF40" s="6"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>33</v>
       </c>
@@ -1928,8 +2860,29 @@
       <c r="D41" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="6"/>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="6"/>
+      <c r="AD41" s="6"/>
+      <c r="AE41" s="6"/>
+      <c r="AF41" s="6"/>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>117</v>
       </c>
@@ -1942,8 +2895,29 @@
       <c r="E42">
         <v>1583.28</v>
       </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>117</v>
       </c>
@@ -1953,8 +2927,29 @@
       <c r="D43" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="6"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="6"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="6"/>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6"/>
+      <c r="AF43" s="6"/>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>34</v>
       </c>
@@ -1967,8 +2962,29 @@
       <c r="E44">
         <v>699.23500000000001</v>
       </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="6"/>
+      <c r="W44" s="6"/>
+      <c r="X44" s="6"/>
+      <c r="Y44" s="6"/>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6"/>
+      <c r="AF44" s="6"/>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>34</v>
       </c>
@@ -1981,8 +2997,29 @@
       <c r="E45">
         <v>166.2</v>
       </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="6"/>
+      <c r="S45" s="6"/>
+      <c r="T45" s="6"/>
+      <c r="U45" s="6"/>
+      <c r="V45" s="6"/>
+      <c r="W45" s="6"/>
+      <c r="X45" s="6"/>
+      <c r="Y45" s="6"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="6"/>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="6"/>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>35</v>
       </c>
@@ -1995,8 +3032,29 @@
       <c r="E46">
         <v>820.2</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6"/>
+      <c r="U46" s="6"/>
+      <c r="V46" s="6"/>
+      <c r="W46" s="6"/>
+      <c r="X46" s="6"/>
+      <c r="Y46" s="6"/>
+      <c r="Z46" s="6"/>
+      <c r="AA46" s="6"/>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="6"/>
+      <c r="AD46" s="6"/>
+      <c r="AE46" s="6"/>
+      <c r="AF46" s="6"/>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>35</v>
       </c>
@@ -2009,8 +3067,29 @@
       <c r="E47">
         <v>191.4</v>
       </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6"/>
+      <c r="T47" s="6"/>
+      <c r="U47" s="6"/>
+      <c r="V47" s="6"/>
+      <c r="W47" s="6"/>
+      <c r="X47" s="6"/>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="6"/>
+      <c r="AF47" s="6"/>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>36</v>
       </c>
@@ -2023,6 +3102,27 @@
       <c r="E48">
         <v>165</v>
       </c>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
+      <c r="V48" s="6"/>
+      <c r="W48" s="6"/>
+      <c r="X48" s="6"/>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="6"/>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="6"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="6"/>
+      <c r="AF48" s="6"/>
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
@@ -2037,6 +3137,27 @@
       <c r="E49">
         <v>43.5</v>
       </c>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="6"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="6"/>
+      <c r="T49" s="6"/>
+      <c r="U49" s="6"/>
+      <c r="V49" s="6"/>
+      <c r="W49" s="6"/>
+      <c r="X49" s="6"/>
+      <c r="Y49" s="6"/>
+      <c r="Z49" s="6"/>
+      <c r="AA49" s="6"/>
+      <c r="AB49" s="6"/>
+      <c r="AC49" s="6"/>
+      <c r="AD49" s="6"/>
+      <c r="AE49" s="6"/>
+      <c r="AF49" s="6"/>
     </row>
     <row r="50" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
@@ -2048,6 +3169,27 @@
       <c r="D50" t="s">
         <v>6</v>
       </c>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="6"/>
+      <c r="Y50" s="6"/>
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="6"/>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="6"/>
+      <c r="AD50" s="6"/>
+      <c r="AE50" s="6"/>
+      <c r="AF50" s="6"/>
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
@@ -2063,18 +3205,27 @@
         <v>201.5</v>
       </c>
       <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="6"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="6"/>
+      <c r="T51" s="6"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6"/>
+      <c r="X51" s="6"/>
+      <c r="Y51" s="6"/>
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="6"/>
+      <c r="AF51" s="6"/>
     </row>
     <row r="52" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B52" s="5" t="s">
@@ -2099,22 +3250,31 @@
         <v>39</v>
       </c>
       <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4">
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6">
         <v>75</v>
       </c>
-      <c r="S52" s="4">
+      <c r="S52" s="6">
         <v>325</v>
       </c>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="6"/>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6"/>
+      <c r="AF52" s="6"/>
       <c r="AG52" t="s">
         <v>114</v>
       </c>
@@ -2136,18 +3296,27 @@
         <v>0</v>
       </c>
       <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6"/>
+      <c r="Q53" s="6"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6"/>
+      <c r="T53" s="6"/>
+      <c r="U53" s="6"/>
+      <c r="V53" s="6"/>
+      <c r="W53" s="6"/>
+      <c r="X53" s="6"/>
+      <c r="Y53" s="6"/>
+      <c r="Z53" s="6"/>
+      <c r="AA53" s="6"/>
+      <c r="AB53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AD53" s="6"/>
+      <c r="AE53" s="6"/>
+      <c r="AF53" s="6"/>
       <c r="AG53" t="s">
         <v>114</v>
       </c>
@@ -2175,22 +3344,31 @@
         <v>523</v>
       </c>
       <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4">
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="6"/>
+      <c r="T54" s="6">
         <v>35</v>
       </c>
-      <c r="U54" s="4">
+      <c r="U54" s="6">
         <v>122.7</v>
       </c>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
+      <c r="V54" s="6"/>
+      <c r="W54" s="6"/>
+      <c r="X54" s="6"/>
+      <c r="Y54" s="6"/>
+      <c r="Z54" s="6"/>
+      <c r="AA54" s="6"/>
+      <c r="AB54" s="6"/>
+      <c r="AC54" s="6"/>
+      <c r="AD54" s="6"/>
+      <c r="AE54" s="6"/>
+      <c r="AF54" s="6"/>
       <c r="AG54" t="s">
         <v>114</v>
       </c>
@@ -2212,18 +3390,27 @@
         <v>0</v>
       </c>
       <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="6"/>
+      <c r="T55" s="6"/>
+      <c r="U55" s="6"/>
+      <c r="V55" s="6"/>
+      <c r="W55" s="6"/>
+      <c r="X55" s="6"/>
+      <c r="Y55" s="6"/>
+      <c r="Z55" s="6"/>
+      <c r="AA55" s="6"/>
+      <c r="AB55" s="6"/>
+      <c r="AC55" s="6"/>
+      <c r="AD55" s="6"/>
+      <c r="AE55" s="6"/>
+      <c r="AF55" s="6"/>
       <c r="AG55" t="s">
         <v>114</v>
       </c>
@@ -2251,22 +3438,31 @@
         <v>2126</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4">
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6">
         <v>220</v>
       </c>
-      <c r="T56" s="4">
+      <c r="T56" s="6">
         <v>121.715</v>
       </c>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
+      <c r="U56" s="6"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="6"/>
+      <c r="X56" s="6"/>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="6"/>
+      <c r="AB56" s="6"/>
+      <c r="AC56" s="6"/>
+      <c r="AD56" s="6"/>
+      <c r="AE56" s="6"/>
+      <c r="AF56" s="6"/>
       <c r="AG56" t="s">
         <v>114</v>
       </c>
@@ -2288,20 +3484,29 @@
         <v>13.17</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4">
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6"/>
+      <c r="T57" s="6">
         <v>13.17</v>
       </c>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
+      <c r="U57" s="6"/>
+      <c r="V57" s="6"/>
+      <c r="W57" s="6"/>
+      <c r="X57" s="6"/>
+      <c r="Y57" s="6"/>
+      <c r="Z57" s="6"/>
+      <c r="AA57" s="6"/>
+      <c r="AB57" s="6"/>
+      <c r="AC57" s="6"/>
+      <c r="AD57" s="6"/>
+      <c r="AE57" s="6"/>
+      <c r="AF57" s="6"/>
       <c r="AG57" t="s">
         <v>114</v>
       </c>
@@ -2326,20 +3531,29 @@
         <v>191</v>
       </c>
       <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4">
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6">
         <v>43.015000000000001</v>
       </c>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="4"/>
+      <c r="U58" s="6"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
+      <c r="X58" s="6"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="6"/>
+      <c r="AB58" s="6"/>
+      <c r="AC58" s="6"/>
+      <c r="AD58" s="6"/>
+      <c r="AE58" s="6"/>
+      <c r="AF58" s="6"/>
       <c r="AG58" t="s">
         <v>114</v>
       </c>
@@ -2361,20 +3575,29 @@
         <v>51.05</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4">
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6">
         <v>51.05</v>
       </c>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="4"/>
+      <c r="T59" s="6"/>
+      <c r="U59" s="6"/>
+      <c r="V59" s="6"/>
+      <c r="W59" s="6"/>
+      <c r="X59" s="6"/>
+      <c r="Y59" s="6"/>
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="6"/>
+      <c r="AB59" s="6"/>
+      <c r="AC59" s="6"/>
+      <c r="AD59" s="6"/>
+      <c r="AE59" s="6"/>
+      <c r="AF59" s="6"/>
       <c r="AG59" t="s">
         <v>114</v>
       </c>
@@ -2408,20 +3631,29 @@
         <v>109</v>
       </c>
       <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4">
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6">
         <v>288.26</v>
       </c>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="4"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6"/>
+      <c r="V60" s="6"/>
+      <c r="W60" s="6"/>
+      <c r="X60" s="6"/>
+      <c r="Y60" s="6"/>
+      <c r="Z60" s="6"/>
+      <c r="AA60" s="6"/>
+      <c r="AB60" s="6"/>
+      <c r="AC60" s="6"/>
+      <c r="AD60" s="6"/>
+      <c r="AE60" s="6"/>
+      <c r="AF60" s="6"/>
       <c r="AG60" t="s">
         <v>114</v>
       </c>
@@ -2443,20 +3675,29 @@
         <v>32.85</v>
       </c>
       <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4">
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6">
         <v>32.85</v>
       </c>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6"/>
+      <c r="U61" s="6"/>
+      <c r="V61" s="6"/>
+      <c r="W61" s="6"/>
+      <c r="X61" s="6"/>
+      <c r="Y61" s="6"/>
+      <c r="Z61" s="6"/>
+      <c r="AA61" s="6"/>
+      <c r="AB61" s="6"/>
+      <c r="AC61" s="6"/>
+      <c r="AD61" s="6"/>
+      <c r="AE61" s="6"/>
+      <c r="AF61" s="6"/>
       <c r="AG61" t="s">
         <v>114</v>
       </c>
@@ -2484,20 +3725,29 @@
         <v>188</v>
       </c>
       <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4">
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6">
         <v>223.29</v>
       </c>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
+      <c r="V62" s="6"/>
+      <c r="W62" s="6"/>
+      <c r="X62" s="6"/>
+      <c r="Y62" s="6"/>
+      <c r="Z62" s="6"/>
+      <c r="AA62" s="6"/>
+      <c r="AB62" s="6"/>
+      <c r="AC62" s="6"/>
+      <c r="AD62" s="6"/>
+      <c r="AE62" s="6"/>
+      <c r="AF62" s="6"/>
       <c r="AG62" t="s">
         <v>114</v>
       </c>
@@ -2519,20 +3769,29 @@
         <v>26.66</v>
       </c>
       <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4">
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6">
         <v>26.66</v>
       </c>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6"/>
+      <c r="T63" s="6"/>
+      <c r="U63" s="6"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6"/>
+      <c r="X63" s="6"/>
+      <c r="Y63" s="6"/>
+      <c r="Z63" s="6"/>
+      <c r="AA63" s="6"/>
+      <c r="AB63" s="6"/>
+      <c r="AC63" s="6"/>
+      <c r="AD63" s="6"/>
+      <c r="AE63" s="6"/>
+      <c r="AF63" s="6"/>
       <c r="AG63" t="s">
         <v>114</v>
       </c>
@@ -2560,20 +3819,31 @@
         <v>860</v>
       </c>
       <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4">
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6">
+        <v>59.73</v>
+      </c>
+      <c r="T64" s="6">
         <v>99.9</v>
       </c>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
+      <c r="U64" s="6"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="6"/>
+      <c r="X64" s="6"/>
+      <c r="Y64" s="6"/>
+      <c r="Z64" s="6"/>
+      <c r="AA64" s="6"/>
+      <c r="AB64" s="6"/>
+      <c r="AC64" s="6"/>
+      <c r="AD64" s="6"/>
+      <c r="AE64" s="6"/>
+      <c r="AF64" s="6"/>
       <c r="AG64" t="s">
         <v>114</v>
       </c>
@@ -2595,20 +3865,29 @@
         <v>31.4</v>
       </c>
       <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4">
-        <v>24</v>
-      </c>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6">
+        <v>31.4</v>
+      </c>
+      <c r="R65" s="6"/>
+      <c r="S65" s="6"/>
+      <c r="T65" s="6"/>
+      <c r="U65" s="6"/>
+      <c r="V65" s="6"/>
+      <c r="W65" s="6"/>
+      <c r="X65" s="6"/>
+      <c r="Y65" s="6"/>
+      <c r="Z65" s="6"/>
+      <c r="AA65" s="6"/>
+      <c r="AB65" s="6"/>
+      <c r="AC65" s="6"/>
+      <c r="AD65" s="6"/>
+      <c r="AE65" s="6"/>
+      <c r="AF65" s="6"/>
       <c r="AG65" t="s">
         <v>114</v>
       </c>
@@ -2642,28 +3921,37 @@
         <v>72</v>
       </c>
       <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4">
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6">
         <v>68</v>
       </c>
-      <c r="O66" s="4">
+      <c r="O66" s="6">
         <v>621.84500000000003</v>
       </c>
-      <c r="P66" s="4">
+      <c r="P66" s="6">
         <v>354.52499999999998</v>
       </c>
-      <c r="Q66" s="4">
+      <c r="Q66" s="6">
         <v>67.900000000000006</v>
       </c>
-      <c r="R66" s="4">
+      <c r="R66" s="6">
         <v>117.68</v>
       </c>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="6"/>
+      <c r="W66" s="6"/>
+      <c r="X66" s="6"/>
+      <c r="Y66" s="6"/>
+      <c r="Z66" s="6"/>
+      <c r="AA66" s="6"/>
+      <c r="AB66" s="6"/>
+      <c r="AC66" s="6"/>
+      <c r="AD66" s="6"/>
+      <c r="AE66" s="6"/>
+      <c r="AF66" s="6"/>
       <c r="AG66" t="s">
         <v>114</v>
       </c>
@@ -2685,18 +3973,27 @@
         <v>0</v>
       </c>
       <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
+      <c r="Y67" s="6"/>
+      <c r="Z67" s="6"/>
+      <c r="AA67" s="6"/>
+      <c r="AB67" s="6"/>
+      <c r="AC67" s="6"/>
+      <c r="AD67" s="6"/>
+      <c r="AE67" s="6"/>
+      <c r="AF67" s="6"/>
       <c r="AG67" t="s">
         <v>114</v>
       </c>
@@ -2730,20 +4027,29 @@
         <v>338</v>
       </c>
       <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4">
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6">
         <v>328.75</v>
       </c>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
+      <c r="V68" s="6"/>
+      <c r="W68" s="6"/>
+      <c r="X68" s="6"/>
+      <c r="Y68" s="6"/>
+      <c r="Z68" s="6"/>
+      <c r="AA68" s="6"/>
+      <c r="AB68" s="6"/>
+      <c r="AC68" s="6"/>
+      <c r="AD68" s="6"/>
+      <c r="AE68" s="6"/>
+      <c r="AF68" s="6"/>
       <c r="AG68" t="s">
         <v>114</v>
       </c>
@@ -2765,18 +4071,27 @@
         <v>0</v>
       </c>
       <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="6"/>
+      <c r="T69" s="6"/>
+      <c r="U69" s="6"/>
+      <c r="V69" s="6"/>
+      <c r="W69" s="6"/>
+      <c r="X69" s="6"/>
+      <c r="Y69" s="6"/>
+      <c r="Z69" s="6"/>
+      <c r="AA69" s="6"/>
+      <c r="AB69" s="6"/>
+      <c r="AC69" s="6"/>
+      <c r="AD69" s="6"/>
+      <c r="AE69" s="6"/>
+      <c r="AF69" s="6"/>
       <c r="AG69" t="s">
         <v>114</v>
       </c>
@@ -2810,22 +4125,31 @@
         <v>901</v>
       </c>
       <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4">
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6">
         <v>247.93</v>
       </c>
-      <c r="Q70" s="4">
+      <c r="Q70" s="6">
         <v>136.74</v>
       </c>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+      <c r="T70" s="6"/>
+      <c r="U70" s="6"/>
+      <c r="V70" s="6"/>
+      <c r="W70" s="6"/>
+      <c r="X70" s="6"/>
+      <c r="Y70" s="6"/>
+      <c r="Z70" s="6"/>
+      <c r="AA70" s="6"/>
+      <c r="AB70" s="6"/>
+      <c r="AC70" s="6"/>
+      <c r="AD70" s="6"/>
+      <c r="AE70" s="6"/>
+      <c r="AF70" s="6"/>
       <c r="AG70" t="s">
         <v>114</v>
       </c>
@@ -2847,20 +4171,29 @@
         <v>20.32</v>
       </c>
       <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4">
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6">
         <v>20.32</v>
       </c>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="6"/>
+      <c r="T71" s="6"/>
+      <c r="U71" s="6"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6"/>
+      <c r="X71" s="6"/>
+      <c r="Y71" s="6"/>
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6"/>
+      <c r="AB71" s="6"/>
+      <c r="AC71" s="6"/>
+      <c r="AD71" s="6"/>
+      <c r="AE71" s="6"/>
+      <c r="AF71" s="6"/>
       <c r="AG71" t="s">
         <v>114</v>
       </c>
@@ -2879,27 +4212,35 @@
         <v>207.5</v>
       </c>
       <c r="F72" s="5">
-        <v>276.38</v>
+        <v>197.8</v>
       </c>
       <c r="I72">
         <v>1801</v>
       </c>
       <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72">
-        <v>276.38</v>
-      </c>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
+      <c r="V72" s="6"/>
+      <c r="W72" s="6"/>
+      <c r="X72" s="6">
+        <v>197.8</v>
+      </c>
+      <c r="Y72" s="6"/>
+      <c r="Z72" s="6"/>
+      <c r="AA72" s="6"/>
+      <c r="AB72" s="6"/>
+      <c r="AC72" s="6"/>
+      <c r="AD72" s="6"/>
+      <c r="AE72" s="6"/>
+      <c r="AF72" s="6"/>
       <c r="AG72" t="s">
         <v>114</v>
       </c>
@@ -2921,22 +4262,30 @@
         <v>10.73</v>
       </c>
       <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73">
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+      <c r="R73" s="6"/>
+      <c r="S73" s="6"/>
+      <c r="T73" s="6"/>
+      <c r="U73" s="6"/>
+      <c r="V73" s="6"/>
+      <c r="W73" s="6"/>
+      <c r="X73" s="6">
         <f>6.22+4.51</f>
         <v>10.73</v>
       </c>
+      <c r="Y73" s="6"/>
+      <c r="Z73" s="6"/>
+      <c r="AA73" s="6"/>
+      <c r="AB73" s="6"/>
+      <c r="AC73" s="6"/>
+      <c r="AD73" s="6"/>
+      <c r="AE73" s="6"/>
+      <c r="AF73" s="6"/>
       <c r="AG73" t="s">
         <v>114</v>
       </c>
@@ -2961,20 +4310,29 @@
         <v>168</v>
       </c>
       <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4">
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
+      <c r="V74" s="6"/>
+      <c r="W74" s="6">
         <v>545.34</v>
       </c>
+      <c r="X74" s="6"/>
+      <c r="Y74" s="6"/>
+      <c r="Z74" s="6"/>
+      <c r="AA74" s="6"/>
+      <c r="AB74" s="6"/>
+      <c r="AC74" s="6"/>
+      <c r="AD74" s="6"/>
+      <c r="AE74" s="6"/>
+      <c r="AF74" s="6"/>
       <c r="AG74" t="s">
         <v>114</v>
       </c>
@@ -2996,20 +4354,29 @@
         <v>12.02</v>
       </c>
       <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4">
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="6"/>
+      <c r="R75" s="6"/>
+      <c r="S75" s="6"/>
+      <c r="T75" s="6"/>
+      <c r="U75" s="6"/>
+      <c r="V75" s="6"/>
+      <c r="W75" s="6">
         <v>12.02</v>
       </c>
+      <c r="X75" s="6"/>
+      <c r="Y75" s="6"/>
+      <c r="Z75" s="6"/>
+      <c r="AA75" s="6"/>
+      <c r="AB75" s="6"/>
+      <c r="AC75" s="6"/>
+      <c r="AD75" s="6"/>
+      <c r="AE75" s="6"/>
+      <c r="AF75" s="6"/>
       <c r="AG75" t="s">
         <v>114</v>
       </c>
@@ -3036,12 +4403,29 @@
       <c r="J76">
         <v>1152</v>
       </c>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4">
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6">
         <v>384.37</v>
       </c>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
+      <c r="V76" s="6"/>
+      <c r="W76" s="6"/>
+      <c r="X76" s="6"/>
+      <c r="Y76" s="6"/>
+      <c r="Z76" s="6"/>
+      <c r="AA76" s="6"/>
+      <c r="AB76" s="6"/>
+      <c r="AC76" s="6"/>
+      <c r="AD76" s="6"/>
+      <c r="AE76" s="6"/>
+      <c r="AF76" s="6"/>
       <c r="AG76" t="s">
         <v>114</v>
       </c>
@@ -3062,12 +4446,29 @@
       <c r="F77" s="5">
         <v>23.8</v>
       </c>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4">
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
+      <c r="P77" s="6"/>
+      <c r="Q77" s="6"/>
+      <c r="R77" s="6"/>
+      <c r="S77" s="6"/>
+      <c r="T77" s="6"/>
+      <c r="U77" s="6">
         <v>23.8</v>
       </c>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
+      <c r="V77" s="6"/>
+      <c r="W77" s="6"/>
+      <c r="X77" s="6"/>
+      <c r="Y77" s="6"/>
+      <c r="Z77" s="6"/>
+      <c r="AA77" s="6"/>
+      <c r="AB77" s="6"/>
+      <c r="AC77" s="6"/>
+      <c r="AD77" s="6"/>
+      <c r="AE77" s="6"/>
+      <c r="AF77" s="6"/>
       <c r="AG77" t="s">
         <v>114</v>
       </c>
@@ -3088,15 +4489,31 @@
       <c r="I78">
         <v>2885</v>
       </c>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4">
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
+      <c r="V78" s="6">
         <v>20.95</v>
       </c>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4">
+      <c r="W78" s="6"/>
+      <c r="X78" s="6">
         <v>70.260000000000005</v>
       </c>
+      <c r="Y78" s="6"/>
+      <c r="Z78" s="6"/>
+      <c r="AA78" s="6"/>
+      <c r="AB78" s="6"/>
+      <c r="AC78" s="6"/>
+      <c r="AD78" s="6"/>
+      <c r="AE78" s="6"/>
+      <c r="AF78" s="6"/>
       <c r="AG78" t="s">
         <v>114</v>
       </c>
@@ -3117,15 +4534,31 @@
       <c r="F79" s="5">
         <v>10.06</v>
       </c>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4">
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="6"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="6"/>
+      <c r="T79" s="6"/>
+      <c r="U79" s="6"/>
+      <c r="V79" s="6">
         <v>8.06</v>
       </c>
-      <c r="W79" s="4"/>
-      <c r="X79">
+      <c r="W79" s="6"/>
+      <c r="X79" s="6">
         <v>2</v>
       </c>
+      <c r="Y79" s="6"/>
+      <c r="Z79" s="6"/>
+      <c r="AA79" s="6"/>
+      <c r="AB79" s="6"/>
+      <c r="AC79" s="6"/>
+      <c r="AD79" s="6"/>
+      <c r="AE79" s="6"/>
+      <c r="AF79" s="6"/>
       <c r="AG79" t="s">
         <v>114</v>
       </c>
@@ -3143,15 +4576,32 @@
       <c r="F80" s="5">
         <v>230.72</v>
       </c>
-      <c r="T80" s="4"/>
-      <c r="U80" s="4"/>
-      <c r="V80" s="4">
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="6"/>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
+      <c r="V80" s="6">
         <f>230.02-55.56</f>
         <v>174.46</v>
       </c>
-      <c r="W80" s="4">
+      <c r="W80" s="6">
         <v>56.26</v>
       </c>
+      <c r="X80" s="6"/>
+      <c r="Y80" s="6"/>
+      <c r="Z80" s="6"/>
+      <c r="AA80" s="6"/>
+      <c r="AB80" s="6"/>
+      <c r="AC80" s="6"/>
+      <c r="AD80" s="6"/>
+      <c r="AE80" s="6"/>
+      <c r="AF80" s="6"/>
       <c r="AG80" t="s">
         <v>114</v>
       </c>
@@ -3169,10 +4619,27 @@
       <c r="E81">
         <v>210.02</v>
       </c>
-      <c r="T81" s="4"/>
-      <c r="U81" s="4"/>
-      <c r="V81" s="4"/>
-      <c r="W81" s="4"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
+      <c r="P81" s="6"/>
+      <c r="Q81" s="6"/>
+      <c r="R81" s="6"/>
+      <c r="S81" s="6"/>
+      <c r="T81" s="6"/>
+      <c r="U81" s="6"/>
+      <c r="V81" s="6"/>
+      <c r="W81" s="6"/>
+      <c r="X81" s="6"/>
+      <c r="Y81" s="6"/>
+      <c r="Z81" s="6"/>
+      <c r="AA81" s="6"/>
+      <c r="AB81" s="6"/>
+      <c r="AC81" s="6"/>
+      <c r="AD81" s="6"/>
+      <c r="AE81" s="6"/>
+      <c r="AF81" s="6"/>
       <c r="AG81" t="s">
         <v>114</v>
       </c>
@@ -3190,12 +4657,29 @@
       <c r="F82" s="5">
         <v>35.5</v>
       </c>
-      <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
-      <c r="V82" s="4">
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="6"/>
+      <c r="P82" s="6"/>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
+      <c r="V82" s="6">
         <v>35.5</v>
       </c>
-      <c r="W82" s="4"/>
+      <c r="W82" s="6"/>
+      <c r="X82" s="6"/>
+      <c r="Y82" s="6"/>
+      <c r="Z82" s="6"/>
+      <c r="AA82" s="6"/>
+      <c r="AB82" s="6"/>
+      <c r="AC82" s="6"/>
+      <c r="AD82" s="6"/>
+      <c r="AE82" s="6"/>
+      <c r="AF82" s="6"/>
       <c r="AG82" t="s">
         <v>114</v>
       </c>
@@ -3213,10 +4697,27 @@
       <c r="E83">
         <v>57.5</v>
       </c>
-      <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
-      <c r="V83" s="4"/>
-      <c r="W83" s="4"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="6"/>
+      <c r="R83" s="6"/>
+      <c r="S83" s="6"/>
+      <c r="T83" s="6"/>
+      <c r="U83" s="6"/>
+      <c r="V83" s="6"/>
+      <c r="W83" s="6"/>
+      <c r="X83" s="6"/>
+      <c r="Y83" s="6"/>
+      <c r="Z83" s="6"/>
+      <c r="AA83" s="6"/>
+      <c r="AB83" s="6"/>
+      <c r="AC83" s="6"/>
+      <c r="AD83" s="6"/>
+      <c r="AE83" s="6"/>
+      <c r="AF83" s="6"/>
       <c r="AG83" t="s">
         <v>114</v>
       </c>
@@ -3234,12 +4735,29 @@
       <c r="F84" s="5">
         <v>36.979999999999997</v>
       </c>
-      <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
-      <c r="V84" s="4">
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
+      <c r="V84" s="6">
         <v>36.979999999999997</v>
       </c>
-      <c r="W84" s="4"/>
+      <c r="W84" s="6"/>
+      <c r="X84" s="6"/>
+      <c r="Y84" s="6"/>
+      <c r="Z84" s="6"/>
+      <c r="AA84" s="6"/>
+      <c r="AB84" s="6"/>
+      <c r="AC84" s="6"/>
+      <c r="AD84" s="6"/>
+      <c r="AE84" s="6"/>
+      <c r="AF84" s="6"/>
       <c r="AG84" t="s">
         <v>114</v>
       </c>
@@ -3257,10 +4775,27 @@
       <c r="E85">
         <v>56</v>
       </c>
-      <c r="T85" s="4"/>
-      <c r="U85" s="4"/>
-      <c r="V85" s="4"/>
-      <c r="W85" s="4"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
+      <c r="P85" s="6"/>
+      <c r="Q85" s="6"/>
+      <c r="R85" s="6"/>
+      <c r="S85" s="6"/>
+      <c r="T85" s="6"/>
+      <c r="U85" s="6"/>
+      <c r="V85" s="6"/>
+      <c r="W85" s="6"/>
+      <c r="X85" s="6"/>
+      <c r="Y85" s="6"/>
+      <c r="Z85" s="6"/>
+      <c r="AA85" s="6"/>
+      <c r="AB85" s="6"/>
+      <c r="AC85" s="6"/>
+      <c r="AD85" s="6"/>
+      <c r="AE85" s="6"/>
+      <c r="AF85" s="6"/>
       <c r="AG85" t="s">
         <v>114</v>
       </c>
@@ -3281,12 +4816,29 @@
       <c r="J86">
         <v>628</v>
       </c>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-      <c r="V86" s="4">
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
+      <c r="V86" s="6">
         <v>39.04</v>
       </c>
-      <c r="W86" s="4"/>
+      <c r="W86" s="6"/>
+      <c r="X86" s="6"/>
+      <c r="Y86" s="6"/>
+      <c r="Z86" s="6"/>
+      <c r="AA86" s="6"/>
+      <c r="AB86" s="6"/>
+      <c r="AC86" s="6"/>
+      <c r="AD86" s="6"/>
+      <c r="AE86" s="6"/>
+      <c r="AF86" s="6"/>
       <c r="AG86" t="s">
         <v>114</v>
       </c>
@@ -3304,10 +4856,27 @@
       <c r="E87">
         <v>39.5</v>
       </c>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
+      <c r="P87" s="6"/>
+      <c r="Q87" s="6"/>
+      <c r="R87" s="6"/>
+      <c r="S87" s="6"/>
+      <c r="T87" s="6"/>
+      <c r="U87" s="6"/>
+      <c r="V87" s="6"/>
+      <c r="W87" s="6"/>
+      <c r="X87" s="6"/>
+      <c r="Y87" s="6"/>
+      <c r="Z87" s="6"/>
+      <c r="AA87" s="6"/>
+      <c r="AB87" s="6"/>
+      <c r="AC87" s="6"/>
+      <c r="AD87" s="6"/>
+      <c r="AE87" s="6"/>
+      <c r="AF87" s="6"/>
       <c r="AG87" t="s">
         <v>114</v>
       </c>
@@ -3325,12 +4894,29 @@
       <c r="F88" s="5">
         <v>34.42</v>
       </c>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4">
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
+      <c r="V88" s="6">
         <v>34.42</v>
       </c>
-      <c r="W88" s="4"/>
+      <c r="W88" s="6"/>
+      <c r="X88" s="6"/>
+      <c r="Y88" s="6"/>
+      <c r="Z88" s="6"/>
+      <c r="AA88" s="6"/>
+      <c r="AB88" s="6"/>
+      <c r="AC88" s="6"/>
+      <c r="AD88" s="6"/>
+      <c r="AE88" s="6"/>
+      <c r="AF88" s="6"/>
       <c r="AG88" t="s">
         <v>114</v>
       </c>
@@ -3348,10 +4934,27 @@
       <c r="E89">
         <v>63.5</v>
       </c>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="6"/>
+      <c r="R89" s="6"/>
+      <c r="S89" s="6"/>
+      <c r="T89" s="6"/>
+      <c r="U89" s="6"/>
+      <c r="V89" s="6"/>
+      <c r="W89" s="6"/>
+      <c r="X89" s="6"/>
+      <c r="Y89" s="6"/>
+      <c r="Z89" s="6"/>
+      <c r="AA89" s="6"/>
+      <c r="AB89" s="6"/>
+      <c r="AC89" s="6"/>
+      <c r="AD89" s="6"/>
+      <c r="AE89" s="6"/>
+      <c r="AF89" s="6"/>
       <c r="AG89" t="s">
         <v>114</v>
       </c>
@@ -3369,12 +4972,29 @@
       <c r="F90" s="5">
         <v>34.119999999999997</v>
       </c>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4">
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
+      <c r="P90" s="6"/>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
+      <c r="V90" s="6">
         <v>34.119999999999997</v>
       </c>
-      <c r="W90" s="4"/>
+      <c r="W90" s="6"/>
+      <c r="X90" s="6"/>
+      <c r="Y90" s="6"/>
+      <c r="Z90" s="6"/>
+      <c r="AA90" s="6"/>
+      <c r="AB90" s="6"/>
+      <c r="AC90" s="6"/>
+      <c r="AD90" s="6"/>
+      <c r="AE90" s="6"/>
+      <c r="AF90" s="6"/>
       <c r="AG90" t="s">
         <v>114</v>
       </c>
@@ -3392,10 +5012,27 @@
       <c r="E91">
         <v>67.5</v>
       </c>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="6"/>
+      <c r="R91" s="6"/>
+      <c r="S91" s="6"/>
+      <c r="T91" s="6"/>
+      <c r="U91" s="6"/>
+      <c r="V91" s="6"/>
+      <c r="W91" s="6"/>
+      <c r="X91" s="6"/>
+      <c r="Y91" s="6"/>
+      <c r="Z91" s="6"/>
+      <c r="AA91" s="6"/>
+      <c r="AB91" s="6"/>
+      <c r="AC91" s="6"/>
+      <c r="AD91" s="6"/>
+      <c r="AE91" s="6"/>
+      <c r="AF91" s="6"/>
       <c r="AG91" t="s">
         <v>114</v>
       </c>
@@ -3413,12 +5050,29 @@
       <c r="F92" s="5">
         <v>32.11</v>
       </c>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4">
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
+      <c r="V92" s="6">
         <v>32.11</v>
       </c>
-      <c r="W92" s="4"/>
+      <c r="W92" s="6"/>
+      <c r="X92" s="6"/>
+      <c r="Y92" s="6"/>
+      <c r="Z92" s="6"/>
+      <c r="AA92" s="6"/>
+      <c r="AB92" s="6"/>
+      <c r="AC92" s="6"/>
+      <c r="AD92" s="6"/>
+      <c r="AE92" s="6"/>
+      <c r="AF92" s="6"/>
       <c r="AG92" t="s">
         <v>114</v>
       </c>
@@ -3436,10 +5090,27 @@
       <c r="E93">
         <v>67.5</v>
       </c>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="6"/>
+      <c r="R93" s="6"/>
+      <c r="S93" s="6"/>
+      <c r="T93" s="6"/>
+      <c r="U93" s="6"/>
+      <c r="V93" s="6"/>
+      <c r="W93" s="6"/>
+      <c r="X93" s="6"/>
+      <c r="Y93" s="6"/>
+      <c r="Z93" s="6"/>
+      <c r="AA93" s="6"/>
+      <c r="AB93" s="6"/>
+      <c r="AC93" s="6"/>
+      <c r="AD93" s="6"/>
+      <c r="AE93" s="6"/>
+      <c r="AF93" s="6"/>
       <c r="AG93" t="s">
         <v>114</v>
       </c>
@@ -3457,12 +5128,29 @@
       <c r="F94" s="5">
         <v>35.9</v>
       </c>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4">
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
+      <c r="V94" s="6">
         <v>35.9</v>
       </c>
-      <c r="W94" s="4"/>
+      <c r="W94" s="6"/>
+      <c r="X94" s="6"/>
+      <c r="Y94" s="6"/>
+      <c r="Z94" s="6"/>
+      <c r="AA94" s="6"/>
+      <c r="AB94" s="6"/>
+      <c r="AC94" s="6"/>
+      <c r="AD94" s="6"/>
+      <c r="AE94" s="6"/>
+      <c r="AF94" s="6"/>
       <c r="AG94" t="s">
         <v>114</v>
       </c>
@@ -3480,10 +5168,27 @@
       <c r="E95">
         <v>84.5</v>
       </c>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="6"/>
+      <c r="Q95" s="6"/>
+      <c r="R95" s="6"/>
+      <c r="S95" s="6"/>
+      <c r="T95" s="6"/>
+      <c r="U95" s="6"/>
+      <c r="V95" s="6"/>
+      <c r="W95" s="6"/>
+      <c r="X95" s="6"/>
+      <c r="Y95" s="6"/>
+      <c r="Z95" s="6"/>
+      <c r="AA95" s="6"/>
+      <c r="AB95" s="6"/>
+      <c r="AC95" s="6"/>
+      <c r="AD95" s="6"/>
+      <c r="AE95" s="6"/>
+      <c r="AF95" s="6"/>
       <c r="AG95" t="s">
         <v>114</v>
       </c>
@@ -3504,12 +5209,29 @@
       <c r="F96" s="5">
         <v>32.19</v>
       </c>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4">
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="6"/>
+      <c r="P96" s="6"/>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
+      <c r="V96" s="6">
         <v>32.19</v>
       </c>
-      <c r="W96" s="4"/>
+      <c r="W96" s="6"/>
+      <c r="X96" s="6"/>
+      <c r="Y96" s="6"/>
+      <c r="Z96" s="6"/>
+      <c r="AA96" s="6"/>
+      <c r="AB96" s="6"/>
+      <c r="AC96" s="6"/>
+      <c r="AD96" s="6"/>
+      <c r="AE96" s="6"/>
+      <c r="AF96" s="6"/>
       <c r="AG96" t="s">
         <v>114</v>
       </c>
@@ -3527,10 +5249,27 @@
       <c r="E97">
         <v>114.5</v>
       </c>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="6"/>
+      <c r="T97" s="6"/>
+      <c r="U97" s="6"/>
+      <c r="V97" s="6"/>
+      <c r="W97" s="6"/>
+      <c r="X97" s="6"/>
+      <c r="Y97" s="6"/>
+      <c r="Z97" s="6"/>
+      <c r="AA97" s="6"/>
+      <c r="AB97" s="6"/>
+      <c r="AC97" s="6"/>
+      <c r="AD97" s="6"/>
+      <c r="AE97" s="6"/>
+      <c r="AF97" s="6"/>
       <c r="AG97" t="s">
         <v>114</v>
       </c>
@@ -3551,14 +5290,31 @@
       <c r="F98" s="5">
         <v>76.599999999999994</v>
       </c>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-      <c r="V98" s="4">
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
+      <c r="V98" s="6">
         <v>37.72</v>
       </c>
-      <c r="W98" s="4">
+      <c r="W98" s="6">
         <v>38.880000000000003</v>
       </c>
+      <c r="X98" s="6"/>
+      <c r="Y98" s="6"/>
+      <c r="Z98" s="6"/>
+      <c r="AA98" s="6"/>
+      <c r="AB98" s="6"/>
+      <c r="AC98" s="6"/>
+      <c r="AD98" s="6"/>
+      <c r="AE98" s="6"/>
+      <c r="AF98" s="6"/>
       <c r="AG98" t="s">
         <v>114</v>
       </c>
@@ -3576,10 +5332,27 @@
       <c r="E99">
         <v>58.5</v>
       </c>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="6"/>
+      <c r="P99" s="6"/>
+      <c r="Q99" s="6"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="6"/>
+      <c r="T99" s="6"/>
+      <c r="U99" s="6"/>
+      <c r="V99" s="6"/>
+      <c r="W99" s="6"/>
+      <c r="X99" s="6"/>
+      <c r="Y99" s="6"/>
+      <c r="Z99" s="6"/>
+      <c r="AA99" s="6"/>
+      <c r="AB99" s="6"/>
+      <c r="AC99" s="6"/>
+      <c r="AD99" s="6"/>
+      <c r="AE99" s="6"/>
+      <c r="AF99" s="6"/>
       <c r="AG99" t="s">
         <v>114</v>
       </c>
@@ -3600,14 +5373,31 @@
       <c r="F100" s="5">
         <v>84.62</v>
       </c>
-      <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
-      <c r="V100" s="4">
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="6"/>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
+      <c r="V100" s="6">
         <v>36.840000000000003</v>
       </c>
-      <c r="W100" s="4">
+      <c r="W100" s="6">
         <v>47.78</v>
       </c>
+      <c r="X100" s="6"/>
+      <c r="Y100" s="6"/>
+      <c r="Z100" s="6"/>
+      <c r="AA100" s="6"/>
+      <c r="AB100" s="6"/>
+      <c r="AC100" s="6"/>
+      <c r="AD100" s="6"/>
+      <c r="AE100" s="6"/>
+      <c r="AF100" s="6"/>
       <c r="AG100" t="s">
         <v>114</v>
       </c>
@@ -3625,10 +5415,27 @@
       <c r="E101">
         <v>37.5</v>
       </c>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="6"/>
+      <c r="O101" s="6"/>
+      <c r="P101" s="6"/>
+      <c r="Q101" s="6"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="6"/>
+      <c r="T101" s="6"/>
+      <c r="U101" s="6"/>
+      <c r="V101" s="6"/>
+      <c r="W101" s="6"/>
+      <c r="X101" s="6"/>
+      <c r="Y101" s="6"/>
+      <c r="Z101" s="6"/>
+      <c r="AA101" s="6"/>
+      <c r="AB101" s="6"/>
+      <c r="AC101" s="6"/>
+      <c r="AD101" s="6"/>
+      <c r="AE101" s="6"/>
+      <c r="AF101" s="6"/>
       <c r="AG101" t="s">
         <v>114</v>
       </c>
@@ -3649,12 +5456,29 @@
       <c r="F102" s="5">
         <v>35.5</v>
       </c>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4">
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="6"/>
+      <c r="O102" s="6"/>
+      <c r="P102" s="6"/>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
+      <c r="U102" s="6"/>
+      <c r="V102" s="6">
         <v>35.5</v>
       </c>
-      <c r="W102" s="4"/>
+      <c r="W102" s="6"/>
+      <c r="X102" s="6"/>
+      <c r="Y102" s="6"/>
+      <c r="Z102" s="6"/>
+      <c r="AA102" s="6"/>
+      <c r="AB102" s="6"/>
+      <c r="AC102" s="6"/>
+      <c r="AD102" s="6"/>
+      <c r="AE102" s="6"/>
+      <c r="AF102" s="6"/>
       <c r="AG102" t="s">
         <v>114</v>
       </c>
@@ -3672,10 +5496,27 @@
       <c r="E103">
         <v>32.5</v>
       </c>
-      <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
-      <c r="V103" s="4"/>
-      <c r="W103" s="4"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
+      <c r="O103" s="6"/>
+      <c r="P103" s="6"/>
+      <c r="Q103" s="6"/>
+      <c r="R103" s="6"/>
+      <c r="S103" s="6"/>
+      <c r="T103" s="6"/>
+      <c r="U103" s="6"/>
+      <c r="V103" s="6"/>
+      <c r="W103" s="6"/>
+      <c r="X103" s="6"/>
+      <c r="Y103" s="6"/>
+      <c r="Z103" s="6"/>
+      <c r="AA103" s="6"/>
+      <c r="AB103" s="6"/>
+      <c r="AC103" s="6"/>
+      <c r="AD103" s="6"/>
+      <c r="AE103" s="6"/>
+      <c r="AF103" s="6"/>
       <c r="AG103" t="s">
         <v>114</v>
       </c>
@@ -3696,12 +5537,29 @@
       <c r="F104" s="5">
         <v>34.380000000000003</v>
       </c>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-      <c r="V104" s="4">
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+      <c r="O104" s="6"/>
+      <c r="P104" s="6"/>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
+      <c r="V104" s="6">
         <v>34.380000000000003</v>
       </c>
-      <c r="W104" s="4"/>
+      <c r="W104" s="6"/>
+      <c r="X104" s="6"/>
+      <c r="Y104" s="6"/>
+      <c r="Z104" s="6"/>
+      <c r="AA104" s="6"/>
+      <c r="AB104" s="6"/>
+      <c r="AC104" s="6"/>
+      <c r="AD104" s="6"/>
+      <c r="AE104" s="6"/>
+      <c r="AF104" s="6"/>
       <c r="AG104" t="s">
         <v>114</v>
       </c>
@@ -3719,10 +5577,27 @@
       <c r="E105">
         <v>5.5</v>
       </c>
-      <c r="T105" s="4"/>
-      <c r="U105" s="4"/>
-      <c r="V105" s="4"/>
-      <c r="W105" s="4"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
+      <c r="O105" s="6"/>
+      <c r="P105" s="6"/>
+      <c r="Q105" s="6"/>
+      <c r="R105" s="6"/>
+      <c r="S105" s="6"/>
+      <c r="T105" s="6"/>
+      <c r="U105" s="6"/>
+      <c r="V105" s="6"/>
+      <c r="W105" s="6"/>
+      <c r="X105" s="6"/>
+      <c r="Y105" s="6"/>
+      <c r="Z105" s="6"/>
+      <c r="AA105" s="6"/>
+      <c r="AB105" s="6"/>
+      <c r="AC105" s="6"/>
+      <c r="AD105" s="6"/>
+      <c r="AE105" s="6"/>
+      <c r="AF105" s="6"/>
       <c r="AG105" t="s">
         <v>114</v>
       </c>
@@ -3743,14 +5618,31 @@
       <c r="F106" s="5">
         <v>167.19</v>
       </c>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
-      <c r="V106" s="4">
+      <c r="L106" s="6"/>
+      <c r="M106" s="6"/>
+      <c r="N106" s="6"/>
+      <c r="O106" s="6"/>
+      <c r="P106" s="6"/>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
+      <c r="V106" s="6">
         <v>43.97</v>
       </c>
-      <c r="W106" s="4">
+      <c r="W106" s="6">
         <v>123.22</v>
       </c>
+      <c r="X106" s="6"/>
+      <c r="Y106" s="6"/>
+      <c r="Z106" s="6"/>
+      <c r="AA106" s="6"/>
+      <c r="AB106" s="6"/>
+      <c r="AC106" s="6"/>
+      <c r="AD106" s="6"/>
+      <c r="AE106" s="6"/>
+      <c r="AF106" s="6"/>
       <c r="AG106" t="s">
         <v>114</v>
       </c>
@@ -3768,10 +5660,27 @@
       <c r="E107">
         <v>2</v>
       </c>
-      <c r="T107" s="4"/>
-      <c r="U107" s="4"/>
-      <c r="V107" s="4"/>
-      <c r="W107" s="4"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
+      <c r="N107" s="6"/>
+      <c r="O107" s="6"/>
+      <c r="P107" s="6"/>
+      <c r="Q107" s="6"/>
+      <c r="R107" s="6"/>
+      <c r="S107" s="6"/>
+      <c r="T107" s="6"/>
+      <c r="U107" s="6"/>
+      <c r="V107" s="6"/>
+      <c r="W107" s="6"/>
+      <c r="X107" s="6"/>
+      <c r="Y107" s="6"/>
+      <c r="Z107" s="6"/>
+      <c r="AA107" s="6"/>
+      <c r="AB107" s="6"/>
+      <c r="AC107" s="6"/>
+      <c r="AD107" s="6"/>
+      <c r="AE107" s="6"/>
+      <c r="AF107" s="6"/>
       <c r="AG107" t="s">
         <v>114</v>
       </c>
@@ -3795,12 +5704,29 @@
       <c r="J108">
         <v>531</v>
       </c>
-      <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
-      <c r="V108" s="4"/>
-      <c r="W108" s="4">
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="6"/>
+      <c r="O108" s="6"/>
+      <c r="P108" s="6"/>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+      <c r="U108" s="6"/>
+      <c r="V108" s="6"/>
+      <c r="W108" s="6">
         <v>189</v>
       </c>
+      <c r="X108" s="6"/>
+      <c r="Y108" s="6"/>
+      <c r="Z108" s="6"/>
+      <c r="AA108" s="6"/>
+      <c r="AB108" s="6"/>
+      <c r="AC108" s="6"/>
+      <c r="AD108" s="6"/>
+      <c r="AE108" s="6"/>
+      <c r="AF108" s="6"/>
       <c r="AG108" t="s">
         <v>114</v>
       </c>
@@ -3821,9 +5747,29 @@
       <c r="F109" s="5">
         <v>70.930000000000007</v>
       </c>
-      <c r="W109">
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="6"/>
+      <c r="O109" s="6"/>
+      <c r="P109" s="6"/>
+      <c r="Q109" s="6"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="6"/>
+      <c r="T109" s="6"/>
+      <c r="U109" s="6"/>
+      <c r="V109" s="6"/>
+      <c r="W109" s="6">
         <v>70.930000000000007</v>
       </c>
+      <c r="X109" s="6"/>
+      <c r="Y109" s="6"/>
+      <c r="Z109" s="6"/>
+      <c r="AA109" s="6"/>
+      <c r="AB109" s="6"/>
+      <c r="AC109" s="6"/>
+      <c r="AD109" s="6"/>
+      <c r="AE109" s="6"/>
+      <c r="AF109" s="6"/>
       <c r="AG109" t="s">
         <v>114</v>
       </c>
@@ -3847,12 +5793,31 @@
       <c r="I110">
         <v>223</v>
       </c>
-      <c r="V110">
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="6"/>
+      <c r="O110" s="6"/>
+      <c r="P110" s="6"/>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
+      <c r="V110" s="6">
         <v>329.56</v>
       </c>
-      <c r="W110" s="4">
+      <c r="W110" s="6">
         <v>34.29</v>
       </c>
+      <c r="X110" s="6"/>
+      <c r="Y110" s="6"/>
+      <c r="Z110" s="6"/>
+      <c r="AA110" s="6"/>
+      <c r="AB110" s="6"/>
+      <c r="AC110" s="6"/>
+      <c r="AD110" s="6"/>
+      <c r="AE110" s="6"/>
+      <c r="AF110" s="6"/>
       <c r="AG110" t="s">
         <v>114</v>
       </c>
@@ -3873,9 +5838,29 @@
       <c r="F111" s="5">
         <v>19.84</v>
       </c>
-      <c r="X111">
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="6"/>
+      <c r="O111" s="6"/>
+      <c r="P111" s="6"/>
+      <c r="Q111" s="6"/>
+      <c r="R111" s="6"/>
+      <c r="S111" s="6"/>
+      <c r="T111" s="6"/>
+      <c r="U111" s="6"/>
+      <c r="V111" s="6"/>
+      <c r="W111" s="6"/>
+      <c r="X111" s="6">
         <v>19.84</v>
       </c>
+      <c r="Y111" s="6"/>
+      <c r="Z111" s="6"/>
+      <c r="AA111" s="6"/>
+      <c r="AB111" s="6"/>
+      <c r="AC111" s="6"/>
+      <c r="AD111" s="6"/>
+      <c r="AE111" s="6"/>
+      <c r="AF111" s="6"/>
       <c r="AG111" t="s">
         <v>114</v>
       </c>
@@ -3896,12 +5881,31 @@
       <c r="F112" s="5">
         <v>89.05</v>
       </c>
-      <c r="V112">
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="6"/>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6"/>
+      <c r="T112" s="6"/>
+      <c r="U112" s="6"/>
+      <c r="V112" s="6">
         <v>32.99</v>
       </c>
-      <c r="W112">
+      <c r="W112" s="6">
         <v>56.06</v>
       </c>
+      <c r="X112" s="6"/>
+      <c r="Y112" s="6"/>
+      <c r="Z112" s="6"/>
+      <c r="AA112" s="6"/>
+      <c r="AB112" s="6"/>
+      <c r="AC112" s="6"/>
+      <c r="AD112" s="6"/>
+      <c r="AE112" s="6"/>
+      <c r="AF112" s="6"/>
       <c r="AG112" t="s">
         <v>114</v>
       </c>
@@ -3919,6 +5923,27 @@
       <c r="E113">
         <v>2</v>
       </c>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="6"/>
+      <c r="O113" s="6"/>
+      <c r="P113" s="6"/>
+      <c r="Q113" s="6"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="6"/>
+      <c r="T113" s="6"/>
+      <c r="U113" s="6"/>
+      <c r="V113" s="6"/>
+      <c r="W113" s="6"/>
+      <c r="X113" s="6"/>
+      <c r="Y113" s="6"/>
+      <c r="Z113" s="6"/>
+      <c r="AA113" s="6"/>
+      <c r="AB113" s="6"/>
+      <c r="AC113" s="6"/>
+      <c r="AD113" s="6"/>
+      <c r="AE113" s="6"/>
+      <c r="AF113" s="6"/>
       <c r="AG113" t="s">
         <v>114</v>
       </c>
@@ -3939,9 +5964,29 @@
       <c r="F114" s="5">
         <v>35.479999999999997</v>
       </c>
-      <c r="V114">
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="6"/>
+      <c r="O114" s="6"/>
+      <c r="P114" s="6"/>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
+      <c r="V114" s="6">
         <v>35.479999999999997</v>
       </c>
+      <c r="W114" s="6"/>
+      <c r="X114" s="6"/>
+      <c r="Y114" s="6"/>
+      <c r="Z114" s="6"/>
+      <c r="AA114" s="6"/>
+      <c r="AB114" s="6"/>
+      <c r="AC114" s="6"/>
+      <c r="AD114" s="6"/>
+      <c r="AE114" s="6"/>
+      <c r="AF114" s="6"/>
       <c r="AG114" t="s">
         <v>114</v>
       </c>
@@ -3959,6 +6004,27 @@
       <c r="E115">
         <v>26</v>
       </c>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="6"/>
+      <c r="T115" s="6"/>
+      <c r="U115" s="6"/>
+      <c r="V115" s="6"/>
+      <c r="W115" s="6"/>
+      <c r="X115" s="6"/>
+      <c r="Y115" s="6"/>
+      <c r="Z115" s="6"/>
+      <c r="AA115" s="6"/>
+      <c r="AB115" s="6"/>
+      <c r="AC115" s="6"/>
+      <c r="AD115" s="6"/>
+      <c r="AE115" s="6"/>
+      <c r="AF115" s="6"/>
       <c r="AG115" t="s">
         <v>114</v>
       </c>
@@ -3979,12 +6045,31 @@
       <c r="F116" s="5">
         <v>206.17</v>
       </c>
-      <c r="V116">
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="6"/>
+      <c r="O116" s="6"/>
+      <c r="P116" s="6"/>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
+      <c r="V116" s="6">
         <v>129.66999999999999</v>
       </c>
-      <c r="W116">
+      <c r="W116" s="6">
         <v>76.5</v>
       </c>
+      <c r="X116" s="6"/>
+      <c r="Y116" s="6"/>
+      <c r="Z116" s="6"/>
+      <c r="AA116" s="6"/>
+      <c r="AB116" s="6"/>
+      <c r="AC116" s="6"/>
+      <c r="AD116" s="6"/>
+      <c r="AE116" s="6"/>
+      <c r="AF116" s="6"/>
       <c r="AG116" t="s">
         <v>114</v>
       </c>
@@ -4002,6 +6087,27 @@
       <c r="E117">
         <v>86</v>
       </c>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6"/>
+      <c r="O117" s="6"/>
+      <c r="P117" s="6"/>
+      <c r="Q117" s="6"/>
+      <c r="R117" s="6"/>
+      <c r="S117" s="6"/>
+      <c r="T117" s="6"/>
+      <c r="U117" s="6"/>
+      <c r="V117" s="6"/>
+      <c r="W117" s="6"/>
+      <c r="X117" s="6"/>
+      <c r="Y117" s="6"/>
+      <c r="Z117" s="6"/>
+      <c r="AA117" s="6"/>
+      <c r="AB117" s="6"/>
+      <c r="AC117" s="6"/>
+      <c r="AD117" s="6"/>
+      <c r="AE117" s="6"/>
+      <c r="AF117" s="6"/>
       <c r="AG117" t="s">
         <v>114</v>
       </c>
@@ -4022,12 +6128,31 @@
       <c r="F118" s="5">
         <v>97.16</v>
       </c>
-      <c r="V118">
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="6"/>
+      <c r="O118" s="6"/>
+      <c r="P118" s="6"/>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
+      <c r="V118" s="6">
         <v>68.16</v>
       </c>
-      <c r="W118">
+      <c r="W118" s="6">
         <v>29</v>
       </c>
+      <c r="X118" s="6"/>
+      <c r="Y118" s="6"/>
+      <c r="Z118" s="6"/>
+      <c r="AA118" s="6"/>
+      <c r="AB118" s="6"/>
+      <c r="AC118" s="6"/>
+      <c r="AD118" s="6"/>
+      <c r="AE118" s="6"/>
+      <c r="AF118" s="6"/>
       <c r="AG118" t="s">
         <v>114</v>
       </c>
@@ -4045,6 +6170,27 @@
       <c r="E119">
         <v>40.5</v>
       </c>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6"/>
+      <c r="O119" s="6"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="6"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="6"/>
+      <c r="T119" s="6"/>
+      <c r="U119" s="6"/>
+      <c r="V119" s="6"/>
+      <c r="W119" s="6"/>
+      <c r="X119" s="6"/>
+      <c r="Y119" s="6"/>
+      <c r="Z119" s="6"/>
+      <c r="AA119" s="6"/>
+      <c r="AB119" s="6"/>
+      <c r="AC119" s="6"/>
+      <c r="AD119" s="6"/>
+      <c r="AE119" s="6"/>
+      <c r="AF119" s="6"/>
       <c r="AG119" t="s">
         <v>114</v>
       </c>
@@ -4065,9 +6211,29 @@
       <c r="F120" s="5">
         <v>35.42</v>
       </c>
-      <c r="V120">
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="6"/>
+      <c r="O120" s="6"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+      <c r="U120" s="6"/>
+      <c r="V120" s="6">
         <v>35.42</v>
       </c>
+      <c r="W120" s="6"/>
+      <c r="X120" s="6"/>
+      <c r="Y120" s="6"/>
+      <c r="Z120" s="6"/>
+      <c r="AA120" s="6"/>
+      <c r="AB120" s="6"/>
+      <c r="AC120" s="6"/>
+      <c r="AD120" s="6"/>
+      <c r="AE120" s="6"/>
+      <c r="AF120" s="6"/>
       <c r="AG120" t="s">
         <v>114</v>
       </c>
@@ -4085,6 +6251,27 @@
       <c r="E121">
         <v>2</v>
       </c>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="6"/>
+      <c r="O121" s="6"/>
+      <c r="P121" s="6"/>
+      <c r="Q121" s="6"/>
+      <c r="R121" s="6"/>
+      <c r="S121" s="6"/>
+      <c r="T121" s="6"/>
+      <c r="U121" s="6"/>
+      <c r="V121" s="6"/>
+      <c r="W121" s="6"/>
+      <c r="X121" s="6"/>
+      <c r="Y121" s="6"/>
+      <c r="Z121" s="6"/>
+      <c r="AA121" s="6"/>
+      <c r="AB121" s="6"/>
+      <c r="AC121" s="6"/>
+      <c r="AD121" s="6"/>
+      <c r="AE121" s="6"/>
+      <c r="AF121" s="6"/>
       <c r="AG121" t="s">
         <v>114</v>
       </c>
@@ -4105,9 +6292,29 @@
       <c r="F122" s="5">
         <v>34.409999999999997</v>
       </c>
-      <c r="V122">
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="6"/>
+      <c r="O122" s="6"/>
+      <c r="P122" s="6"/>
+      <c r="Q122" s="6"/>
+      <c r="R122" s="6"/>
+      <c r="S122" s="6"/>
+      <c r="T122" s="6"/>
+      <c r="U122" s="6"/>
+      <c r="V122" s="6">
         <v>34.409999999999997</v>
       </c>
+      <c r="W122" s="6"/>
+      <c r="X122" s="6"/>
+      <c r="Y122" s="6"/>
+      <c r="Z122" s="6"/>
+      <c r="AA122" s="6"/>
+      <c r="AB122" s="6"/>
+      <c r="AC122" s="6"/>
+      <c r="AD122" s="6"/>
+      <c r="AE122" s="6"/>
+      <c r="AF122" s="6"/>
       <c r="AG122" t="s">
         <v>114</v>
       </c>
@@ -4125,6 +6332,27 @@
       <c r="E123">
         <v>2</v>
       </c>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
+      <c r="N123" s="6"/>
+      <c r="O123" s="6"/>
+      <c r="P123" s="6"/>
+      <c r="Q123" s="6"/>
+      <c r="R123" s="6"/>
+      <c r="S123" s="6"/>
+      <c r="T123" s="6"/>
+      <c r="U123" s="6"/>
+      <c r="V123" s="6"/>
+      <c r="W123" s="6"/>
+      <c r="X123" s="6"/>
+      <c r="Y123" s="6"/>
+      <c r="Z123" s="6"/>
+      <c r="AA123" s="6"/>
+      <c r="AB123" s="6"/>
+      <c r="AC123" s="6"/>
+      <c r="AD123" s="6"/>
+      <c r="AE123" s="6"/>
+      <c r="AF123" s="6"/>
       <c r="AG123" t="s">
         <v>114</v>
       </c>
@@ -4145,9 +6373,29 @@
       <c r="F124" s="5">
         <v>47.44</v>
       </c>
-      <c r="V124">
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="6"/>
+      <c r="O124" s="6"/>
+      <c r="P124" s="6"/>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
+      <c r="V124" s="6">
         <v>47.44</v>
       </c>
+      <c r="W124" s="6"/>
+      <c r="X124" s="6"/>
+      <c r="Y124" s="6"/>
+      <c r="Z124" s="6"/>
+      <c r="AA124" s="6"/>
+      <c r="AB124" s="6"/>
+      <c r="AC124" s="6"/>
+      <c r="AD124" s="6"/>
+      <c r="AE124" s="6"/>
+      <c r="AF124" s="6"/>
       <c r="AG124" t="s">
         <v>114</v>
       </c>
@@ -4165,6 +6413,27 @@
       <c r="E125">
         <v>9.5</v>
       </c>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="N125" s="6"/>
+      <c r="O125" s="6"/>
+      <c r="P125" s="6"/>
+      <c r="Q125" s="6"/>
+      <c r="R125" s="6"/>
+      <c r="S125" s="6"/>
+      <c r="T125" s="6"/>
+      <c r="U125" s="6"/>
+      <c r="V125" s="6"/>
+      <c r="W125" s="6"/>
+      <c r="X125" s="6"/>
+      <c r="Y125" s="6"/>
+      <c r="Z125" s="6"/>
+      <c r="AA125" s="6"/>
+      <c r="AB125" s="6"/>
+      <c r="AC125" s="6"/>
+      <c r="AD125" s="6"/>
+      <c r="AE125" s="6"/>
+      <c r="AF125" s="6"/>
       <c r="AG125" t="s">
         <v>114</v>
       </c>
@@ -4185,12 +6454,31 @@
       <c r="F126" s="5">
         <v>255.86</v>
       </c>
-      <c r="V126">
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
+      <c r="N126" s="6"/>
+      <c r="O126" s="6"/>
+      <c r="P126" s="6"/>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="6"/>
+      <c r="T126" s="6"/>
+      <c r="U126" s="6"/>
+      <c r="V126" s="6">
         <v>67.05</v>
       </c>
-      <c r="X126">
+      <c r="W126" s="6"/>
+      <c r="X126" s="6">
         <v>188.81</v>
       </c>
+      <c r="Y126" s="6"/>
+      <c r="Z126" s="6"/>
+      <c r="AA126" s="6"/>
+      <c r="AB126" s="6"/>
+      <c r="AC126" s="6"/>
+      <c r="AD126" s="6"/>
+      <c r="AE126" s="6"/>
+      <c r="AF126" s="6"/>
       <c r="AG126" t="s">
         <v>114</v>
       </c>
@@ -4211,6 +6499,27 @@
       <c r="F127" s="5">
         <v>0</v>
       </c>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="6"/>
+      <c r="O127" s="6"/>
+      <c r="P127" s="6"/>
+      <c r="Q127" s="6"/>
+      <c r="R127" s="6"/>
+      <c r="S127" s="6"/>
+      <c r="T127" s="6"/>
+      <c r="U127" s="6"/>
+      <c r="V127" s="6"/>
+      <c r="W127" s="6"/>
+      <c r="X127" s="6"/>
+      <c r="Y127" s="6"/>
+      <c r="Z127" s="6"/>
+      <c r="AA127" s="6"/>
+      <c r="AB127" s="6"/>
+      <c r="AC127" s="6"/>
+      <c r="AD127" s="6"/>
+      <c r="AE127" s="6"/>
+      <c r="AF127" s="6"/>
       <c r="AG127" t="s">
         <v>114</v>
       </c>
@@ -4243,12 +6552,31 @@
       <c r="J128">
         <v>2397</v>
       </c>
-      <c r="S128">
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+      <c r="N128" s="6"/>
+      <c r="O128" s="6"/>
+      <c r="P128" s="6"/>
+      <c r="Q128" s="6"/>
+      <c r="R128" s="6"/>
+      <c r="S128" s="6">
         <v>162.16499999999999</v>
       </c>
-      <c r="T128">
+      <c r="T128" s="6">
         <v>283.32499999999999</v>
       </c>
+      <c r="U128" s="6"/>
+      <c r="V128" s="6"/>
+      <c r="W128" s="6"/>
+      <c r="X128" s="6"/>
+      <c r="Y128" s="6"/>
+      <c r="Z128" s="6"/>
+      <c r="AA128" s="6"/>
+      <c r="AB128" s="6"/>
+      <c r="AC128" s="6"/>
+      <c r="AD128" s="6"/>
+      <c r="AE128" s="6"/>
+      <c r="AF128" s="6"/>
       <c r="AG128" t="s">
         <v>114</v>
       </c>
@@ -4269,9 +6597,29 @@
       <c r="F129" s="5">
         <v>75.599999999999994</v>
       </c>
-      <c r="T129">
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+      <c r="N129" s="6"/>
+      <c r="O129" s="6"/>
+      <c r="P129" s="6"/>
+      <c r="Q129" s="6"/>
+      <c r="R129" s="6"/>
+      <c r="S129" s="6"/>
+      <c r="T129" s="6">
         <v>75.599999999999994</v>
       </c>
+      <c r="U129" s="6"/>
+      <c r="V129" s="6"/>
+      <c r="W129" s="6"/>
+      <c r="X129" s="6"/>
+      <c r="Y129" s="6"/>
+      <c r="Z129" s="6"/>
+      <c r="AA129" s="6"/>
+      <c r="AB129" s="6"/>
+      <c r="AC129" s="6"/>
+      <c r="AD129" s="6"/>
+      <c r="AE129" s="6"/>
+      <c r="AF129" s="6"/>
       <c r="AG129" t="s">
         <v>114</v>
       </c>
@@ -4295,9 +6643,29 @@
       <c r="I130">
         <v>788</v>
       </c>
-      <c r="T130">
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="6"/>
+      <c r="O130" s="6"/>
+      <c r="P130" s="6"/>
+      <c r="Q130" s="6"/>
+      <c r="R130" s="6"/>
+      <c r="S130" s="6"/>
+      <c r="T130" s="6">
         <v>629.14</v>
       </c>
+      <c r="U130" s="6"/>
+      <c r="V130" s="6"/>
+      <c r="W130" s="6"/>
+      <c r="X130" s="6"/>
+      <c r="Y130" s="6"/>
+      <c r="Z130" s="6"/>
+      <c r="AA130" s="6"/>
+      <c r="AB130" s="6"/>
+      <c r="AC130" s="6"/>
+      <c r="AD130" s="6"/>
+      <c r="AE130" s="6"/>
+      <c r="AF130" s="6"/>
       <c r="AG130" t="s">
         <v>114</v>
       </c>
@@ -4318,9 +6686,29 @@
       <c r="F131" s="5">
         <v>37.89</v>
       </c>
-      <c r="T131">
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
+      <c r="N131" s="6"/>
+      <c r="O131" s="6"/>
+      <c r="P131" s="6"/>
+      <c r="Q131" s="6"/>
+      <c r="R131" s="6"/>
+      <c r="S131" s="6"/>
+      <c r="T131" s="6">
         <v>37.89</v>
       </c>
+      <c r="U131" s="6"/>
+      <c r="V131" s="6"/>
+      <c r="W131" s="6"/>
+      <c r="X131" s="6"/>
+      <c r="Y131" s="6"/>
+      <c r="Z131" s="6"/>
+      <c r="AA131" s="6"/>
+      <c r="AB131" s="6"/>
+      <c r="AC131" s="6"/>
+      <c r="AD131" s="6"/>
+      <c r="AE131" s="6"/>
+      <c r="AF131" s="6"/>
       <c r="AG131" t="s">
         <v>114</v>
       </c>
@@ -4344,9 +6732,29 @@
       <c r="I132">
         <v>654</v>
       </c>
-      <c r="T132">
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="6"/>
+      <c r="O132" s="6"/>
+      <c r="P132" s="6"/>
+      <c r="Q132" s="6"/>
+      <c r="R132" s="6"/>
+      <c r="S132" s="6"/>
+      <c r="T132" s="6">
         <v>108.02</v>
       </c>
+      <c r="U132" s="6"/>
+      <c r="V132" s="6"/>
+      <c r="W132" s="6"/>
+      <c r="X132" s="6"/>
+      <c r="Y132" s="6"/>
+      <c r="Z132" s="6"/>
+      <c r="AA132" s="6"/>
+      <c r="AB132" s="6"/>
+      <c r="AC132" s="6"/>
+      <c r="AD132" s="6"/>
+      <c r="AE132" s="6"/>
+      <c r="AF132" s="6"/>
       <c r="AG132" t="s">
         <v>114</v>
       </c>
@@ -4367,9 +6775,29 @@
       <c r="F133" s="5">
         <v>1.55</v>
       </c>
-      <c r="T133">
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="6"/>
+      <c r="O133" s="6"/>
+      <c r="P133" s="6"/>
+      <c r="Q133" s="6"/>
+      <c r="R133" s="6"/>
+      <c r="S133" s="6"/>
+      <c r="T133" s="6">
         <v>1.55</v>
       </c>
+      <c r="U133" s="6"/>
+      <c r="V133" s="6"/>
+      <c r="W133" s="6"/>
+      <c r="X133" s="6"/>
+      <c r="Y133" s="6"/>
+      <c r="Z133" s="6"/>
+      <c r="AA133" s="6"/>
+      <c r="AB133" s="6"/>
+      <c r="AC133" s="6"/>
+      <c r="AD133" s="6"/>
+      <c r="AE133" s="6"/>
+      <c r="AF133" s="6"/>
       <c r="AG133" t="s">
         <v>114</v>
       </c>
@@ -4396,9 +6824,29 @@
       <c r="J134">
         <v>393</v>
       </c>
-      <c r="R134">
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="6"/>
+      <c r="O134" s="6"/>
+      <c r="P134" s="6"/>
+      <c r="Q134" s="6"/>
+      <c r="R134" s="6">
         <v>296.60000000000002</v>
       </c>
+      <c r="S134" s="6"/>
+      <c r="T134" s="6"/>
+      <c r="U134" s="6"/>
+      <c r="V134" s="6"/>
+      <c r="W134" s="6"/>
+      <c r="X134" s="6"/>
+      <c r="Y134" s="6"/>
+      <c r="Z134" s="6"/>
+      <c r="AA134" s="6"/>
+      <c r="AB134" s="6"/>
+      <c r="AC134" s="6"/>
+      <c r="AD134" s="6"/>
+      <c r="AE134" s="6"/>
+      <c r="AF134" s="6"/>
       <c r="AG134" t="s">
         <v>114</v>
       </c>
@@ -4419,6 +6867,27 @@
       <c r="F135" s="5">
         <v>0</v>
       </c>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
+      <c r="N135" s="6"/>
+      <c r="O135" s="6"/>
+      <c r="P135" s="6"/>
+      <c r="Q135" s="6"/>
+      <c r="R135" s="6"/>
+      <c r="S135" s="6"/>
+      <c r="T135" s="6"/>
+      <c r="U135" s="6"/>
+      <c r="V135" s="6"/>
+      <c r="W135" s="6"/>
+      <c r="X135" s="6"/>
+      <c r="Y135" s="6"/>
+      <c r="Z135" s="6"/>
+      <c r="AA135" s="6"/>
+      <c r="AB135" s="6"/>
+      <c r="AC135" s="6"/>
+      <c r="AD135" s="6"/>
+      <c r="AE135" s="6"/>
+      <c r="AF135" s="6"/>
       <c r="AG135" t="s">
         <v>114</v>
       </c>
@@ -4442,15 +6911,33 @@
       <c r="I136">
         <v>118</v>
       </c>
-      <c r="R136">
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
+      <c r="N136" s="6"/>
+      <c r="O136" s="6"/>
+      <c r="P136" s="6"/>
+      <c r="Q136" s="6"/>
+      <c r="R136" s="6">
         <v>102.5</v>
       </c>
-      <c r="U136">
+      <c r="S136" s="6"/>
+      <c r="T136" s="6"/>
+      <c r="U136" s="6">
         <v>28.8</v>
       </c>
-      <c r="V136">
+      <c r="V136" s="6">
         <v>73</v>
       </c>
+      <c r="W136" s="6"/>
+      <c r="X136" s="6"/>
+      <c r="Y136" s="6"/>
+      <c r="Z136" s="6"/>
+      <c r="AA136" s="6"/>
+      <c r="AB136" s="6"/>
+      <c r="AC136" s="6"/>
+      <c r="AD136" s="6"/>
+      <c r="AE136" s="6"/>
+      <c r="AF136" s="6"/>
       <c r="AG136" t="s">
         <v>115</v>
       </c>
@@ -4471,12 +6958,31 @@
       <c r="F137" s="5">
         <v>48</v>
       </c>
-      <c r="R137">
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
+      <c r="N137" s="6"/>
+      <c r="O137" s="6"/>
+      <c r="P137" s="6"/>
+      <c r="Q137" s="6"/>
+      <c r="R137" s="6">
         <v>16</v>
       </c>
-      <c r="V137">
+      <c r="S137" s="6"/>
+      <c r="T137" s="6"/>
+      <c r="U137" s="6"/>
+      <c r="V137" s="6">
         <v>32</v>
       </c>
+      <c r="W137" s="6"/>
+      <c r="X137" s="6"/>
+      <c r="Y137" s="6"/>
+      <c r="Z137" s="6"/>
+      <c r="AA137" s="6"/>
+      <c r="AB137" s="6"/>
+      <c r="AC137" s="6"/>
+      <c r="AD137" s="6"/>
+      <c r="AE137" s="6"/>
+      <c r="AF137" s="6"/>
       <c r="AG137" t="s">
         <v>115</v>
       </c>
@@ -4500,9 +7006,29 @@
       <c r="I138">
         <v>2295</v>
       </c>
-      <c r="X138" s="6">
+      <c r="L138" s="6"/>
+      <c r="M138" s="6"/>
+      <c r="N138" s="6"/>
+      <c r="O138" s="6"/>
+      <c r="P138" s="6"/>
+      <c r="Q138" s="6"/>
+      <c r="R138" s="6"/>
+      <c r="S138" s="6"/>
+      <c r="T138" s="6"/>
+      <c r="U138" s="6"/>
+      <c r="V138" s="6"/>
+      <c r="W138" s="6"/>
+      <c r="X138" s="7">
         <v>220.59</v>
       </c>
+      <c r="Y138" s="6"/>
+      <c r="Z138" s="6"/>
+      <c r="AA138" s="6"/>
+      <c r="AB138" s="6"/>
+      <c r="AC138" s="6"/>
+      <c r="AD138" s="6"/>
+      <c r="AE138" s="6"/>
+      <c r="AF138" s="6"/>
       <c r="AG138" t="s">
         <v>114</v>
       </c>
@@ -4520,6 +7046,27 @@
       <c r="E139">
         <v>130</v>
       </c>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
+      <c r="N139" s="6"/>
+      <c r="O139" s="6"/>
+      <c r="P139" s="6"/>
+      <c r="Q139" s="6"/>
+      <c r="R139" s="6"/>
+      <c r="S139" s="6"/>
+      <c r="T139" s="6"/>
+      <c r="U139" s="6"/>
+      <c r="V139" s="6"/>
+      <c r="W139" s="6"/>
+      <c r="X139" s="6"/>
+      <c r="Y139" s="6"/>
+      <c r="Z139" s="6"/>
+      <c r="AA139" s="6"/>
+      <c r="AB139" s="6"/>
+      <c r="AC139" s="6"/>
+      <c r="AD139" s="6"/>
+      <c r="AE139" s="6"/>
+      <c r="AF139" s="6"/>
       <c r="AG139" t="s">
         <v>114</v>
       </c>
@@ -4540,6 +7087,27 @@
       <c r="I140">
         <v>220</v>
       </c>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+      <c r="N140" s="6"/>
+      <c r="O140" s="6"/>
+      <c r="P140" s="6"/>
+      <c r="Q140" s="6"/>
+      <c r="R140" s="6"/>
+      <c r="S140" s="6"/>
+      <c r="T140" s="6"/>
+      <c r="U140" s="6"/>
+      <c r="V140" s="6"/>
+      <c r="W140" s="6"/>
+      <c r="X140" s="6"/>
+      <c r="Y140" s="6"/>
+      <c r="Z140" s="6"/>
+      <c r="AA140" s="6"/>
+      <c r="AB140" s="6"/>
+      <c r="AC140" s="6"/>
+      <c r="AD140" s="6"/>
+      <c r="AE140" s="6"/>
+      <c r="AF140" s="6"/>
     </row>
     <row r="141" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
@@ -4554,6 +7122,27 @@
       <c r="E141">
         <v>415.5</v>
       </c>
+      <c r="L141" s="6"/>
+      <c r="M141" s="6"/>
+      <c r="N141" s="6"/>
+      <c r="O141" s="6"/>
+      <c r="P141" s="6"/>
+      <c r="Q141" s="6"/>
+      <c r="R141" s="6"/>
+      <c r="S141" s="6"/>
+      <c r="T141" s="6"/>
+      <c r="U141" s="6"/>
+      <c r="V141" s="6"/>
+      <c r="W141" s="6"/>
+      <c r="X141" s="6"/>
+      <c r="Y141" s="6"/>
+      <c r="Z141" s="6"/>
+      <c r="AA141" s="6"/>
+      <c r="AB141" s="6"/>
+      <c r="AC141" s="6"/>
+      <c r="AD141" s="6"/>
+      <c r="AE141" s="6"/>
+      <c r="AF141" s="6"/>
     </row>
     <row r="142" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
@@ -4568,6 +7157,27 @@
       <c r="E142">
         <v>28.85</v>
       </c>
+      <c r="L142" s="6"/>
+      <c r="M142" s="6"/>
+      <c r="N142" s="6"/>
+      <c r="O142" s="6"/>
+      <c r="P142" s="6"/>
+      <c r="Q142" s="6"/>
+      <c r="R142" s="6"/>
+      <c r="S142" s="6"/>
+      <c r="T142" s="6"/>
+      <c r="U142" s="6"/>
+      <c r="V142" s="6"/>
+      <c r="W142" s="6"/>
+      <c r="X142" s="6"/>
+      <c r="Y142" s="6"/>
+      <c r="Z142" s="6"/>
+      <c r="AA142" s="6"/>
+      <c r="AB142" s="6"/>
+      <c r="AC142" s="6"/>
+      <c r="AD142" s="6"/>
+      <c r="AE142" s="6"/>
+      <c r="AF142" s="6"/>
     </row>
     <row r="143" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
@@ -4582,6 +7192,27 @@
       <c r="E143">
         <v>138.24</v>
       </c>
+      <c r="L143" s="6"/>
+      <c r="M143" s="6"/>
+      <c r="N143" s="6"/>
+      <c r="O143" s="6"/>
+      <c r="P143" s="6"/>
+      <c r="Q143" s="6"/>
+      <c r="R143" s="6"/>
+      <c r="S143" s="6"/>
+      <c r="T143" s="6"/>
+      <c r="U143" s="6"/>
+      <c r="V143" s="6"/>
+      <c r="W143" s="6"/>
+      <c r="X143" s="6"/>
+      <c r="Y143" s="6"/>
+      <c r="Z143" s="6"/>
+      <c r="AA143" s="6"/>
+      <c r="AB143" s="6"/>
+      <c r="AC143" s="6"/>
+      <c r="AD143" s="6"/>
+      <c r="AE143" s="6"/>
+      <c r="AF143" s="6"/>
     </row>
     <row r="144" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
@@ -4602,6 +7233,27 @@
       <c r="I144">
         <v>94</v>
       </c>
+      <c r="L144" s="6"/>
+      <c r="M144" s="6"/>
+      <c r="N144" s="6"/>
+      <c r="O144" s="6"/>
+      <c r="P144" s="6"/>
+      <c r="Q144" s="6"/>
+      <c r="R144" s="6"/>
+      <c r="S144" s="6"/>
+      <c r="T144" s="6"/>
+      <c r="U144" s="6"/>
+      <c r="V144" s="6"/>
+      <c r="W144" s="6"/>
+      <c r="X144" s="6"/>
+      <c r="Y144" s="6"/>
+      <c r="Z144" s="6"/>
+      <c r="AA144" s="6"/>
+      <c r="AB144" s="6"/>
+      <c r="AC144" s="6"/>
+      <c r="AD144" s="6"/>
+      <c r="AE144" s="6"/>
+      <c r="AF144" s="6"/>
       <c r="AG144" t="s">
         <v>115</v>
       </c>
@@ -4622,9 +7274,29 @@
       <c r="F145" s="5">
         <v>9</v>
       </c>
-      <c r="U145">
+      <c r="L145" s="6"/>
+      <c r="M145" s="6"/>
+      <c r="N145" s="6"/>
+      <c r="O145" s="6"/>
+      <c r="P145" s="6"/>
+      <c r="Q145" s="6"/>
+      <c r="R145" s="6"/>
+      <c r="S145" s="6"/>
+      <c r="T145" s="6"/>
+      <c r="U145" s="6">
         <v>9</v>
       </c>
+      <c r="V145" s="6"/>
+      <c r="W145" s="6"/>
+      <c r="X145" s="6"/>
+      <c r="Y145" s="6"/>
+      <c r="Z145" s="6"/>
+      <c r="AA145" s="6"/>
+      <c r="AB145" s="6"/>
+      <c r="AC145" s="6"/>
+      <c r="AD145" s="6"/>
+      <c r="AE145" s="6"/>
+      <c r="AF145" s="6"/>
       <c r="AG145" t="s">
         <v>115</v>
       </c>
@@ -4639,6 +7311,27 @@
       <c r="D146" t="s">
         <v>6</v>
       </c>
+      <c r="L146" s="6"/>
+      <c r="M146" s="6"/>
+      <c r="N146" s="6"/>
+      <c r="O146" s="6"/>
+      <c r="P146" s="6"/>
+      <c r="Q146" s="6"/>
+      <c r="R146" s="6"/>
+      <c r="S146" s="6"/>
+      <c r="T146" s="6"/>
+      <c r="U146" s="6"/>
+      <c r="V146" s="6"/>
+      <c r="W146" s="6"/>
+      <c r="X146" s="6"/>
+      <c r="Y146" s="6"/>
+      <c r="Z146" s="6"/>
+      <c r="AA146" s="6"/>
+      <c r="AB146" s="6"/>
+      <c r="AC146" s="6"/>
+      <c r="AD146" s="6"/>
+      <c r="AE146" s="6"/>
+      <c r="AF146" s="6"/>
     </row>
     <row r="147" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
@@ -4653,6 +7346,27 @@
       <c r="E147">
         <v>109.8</v>
       </c>
+      <c r="L147" s="6"/>
+      <c r="M147" s="6"/>
+      <c r="N147" s="6"/>
+      <c r="O147" s="6"/>
+      <c r="P147" s="6"/>
+      <c r="Q147" s="6"/>
+      <c r="R147" s="6"/>
+      <c r="S147" s="6"/>
+      <c r="T147" s="6"/>
+      <c r="U147" s="6"/>
+      <c r="V147" s="6"/>
+      <c r="W147" s="6"/>
+      <c r="X147" s="6"/>
+      <c r="Y147" s="6"/>
+      <c r="Z147" s="6"/>
+      <c r="AA147" s="6"/>
+      <c r="AB147" s="6"/>
+      <c r="AC147" s="6"/>
+      <c r="AD147" s="6"/>
+      <c r="AE147" s="6"/>
+      <c r="AF147" s="6"/>
     </row>
     <row r="148" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
@@ -4664,6 +7378,27 @@
       <c r="D148" t="s">
         <v>6</v>
       </c>
+      <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
+      <c r="N148" s="6"/>
+      <c r="O148" s="6"/>
+      <c r="P148" s="6"/>
+      <c r="Q148" s="6"/>
+      <c r="R148" s="6"/>
+      <c r="S148" s="6"/>
+      <c r="T148" s="6"/>
+      <c r="U148" s="6"/>
+      <c r="V148" s="6"/>
+      <c r="W148" s="6"/>
+      <c r="X148" s="6"/>
+      <c r="Y148" s="6"/>
+      <c r="Z148" s="6"/>
+      <c r="AA148" s="6"/>
+      <c r="AB148" s="6"/>
+      <c r="AC148" s="6"/>
+      <c r="AD148" s="6"/>
+      <c r="AE148" s="6"/>
+      <c r="AF148" s="6"/>
     </row>
     <row r="149" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
@@ -4678,6 +7413,27 @@
       <c r="E149">
         <v>220.48</v>
       </c>
+      <c r="L149" s="6"/>
+      <c r="M149" s="6"/>
+      <c r="N149" s="6"/>
+      <c r="O149" s="6"/>
+      <c r="P149" s="6"/>
+      <c r="Q149" s="6"/>
+      <c r="R149" s="6"/>
+      <c r="S149" s="6"/>
+      <c r="T149" s="6"/>
+      <c r="U149" s="6"/>
+      <c r="V149" s="6"/>
+      <c r="W149" s="6"/>
+      <c r="X149" s="6"/>
+      <c r="Y149" s="6"/>
+      <c r="Z149" s="6"/>
+      <c r="AA149" s="6"/>
+      <c r="AB149" s="6"/>
+      <c r="AC149" s="6"/>
+      <c r="AD149" s="6"/>
+      <c r="AE149" s="6"/>
+      <c r="AF149" s="6"/>
     </row>
     <row r="150" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
@@ -4692,6 +7448,27 @@
       <c r="I150">
         <v>32</v>
       </c>
+      <c r="L150" s="6"/>
+      <c r="M150" s="6"/>
+      <c r="N150" s="6"/>
+      <c r="O150" s="6"/>
+      <c r="P150" s="6"/>
+      <c r="Q150" s="6"/>
+      <c r="R150" s="6"/>
+      <c r="S150" s="6"/>
+      <c r="T150" s="6"/>
+      <c r="U150" s="6"/>
+      <c r="V150" s="6"/>
+      <c r="W150" s="6"/>
+      <c r="X150" s="6"/>
+      <c r="Y150" s="6"/>
+      <c r="Z150" s="6"/>
+      <c r="AA150" s="6"/>
+      <c r="AB150" s="6"/>
+      <c r="AC150" s="6"/>
+      <c r="AD150" s="6"/>
+      <c r="AE150" s="6"/>
+      <c r="AF150" s="6"/>
     </row>
     <row r="151" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
@@ -4706,6 +7483,27 @@
       <c r="E151">
         <v>59.5</v>
       </c>
+      <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
+      <c r="N151" s="6"/>
+      <c r="O151" s="6"/>
+      <c r="P151" s="6"/>
+      <c r="Q151" s="6"/>
+      <c r="R151" s="6"/>
+      <c r="S151" s="6"/>
+      <c r="T151" s="6"/>
+      <c r="U151" s="6"/>
+      <c r="V151" s="6"/>
+      <c r="W151" s="6"/>
+      <c r="X151" s="6"/>
+      <c r="Y151" s="6"/>
+      <c r="Z151" s="6"/>
+      <c r="AA151" s="6"/>
+      <c r="AB151" s="6"/>
+      <c r="AC151" s="6"/>
+      <c r="AD151" s="6"/>
+      <c r="AE151" s="6"/>
+      <c r="AF151" s="6"/>
     </row>
     <row r="152" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
@@ -4720,6 +7518,27 @@
       <c r="I152">
         <v>1180</v>
       </c>
+      <c r="L152" s="6"/>
+      <c r="M152" s="6"/>
+      <c r="N152" s="6"/>
+      <c r="O152" s="6"/>
+      <c r="P152" s="6"/>
+      <c r="Q152" s="6"/>
+      <c r="R152" s="6"/>
+      <c r="S152" s="6"/>
+      <c r="T152" s="6"/>
+      <c r="U152" s="6"/>
+      <c r="V152" s="6"/>
+      <c r="W152" s="6"/>
+      <c r="X152" s="6"/>
+      <c r="Y152" s="6"/>
+      <c r="Z152" s="6"/>
+      <c r="AA152" s="6"/>
+      <c r="AB152" s="6"/>
+      <c r="AC152" s="6"/>
+      <c r="AD152" s="6"/>
+      <c r="AE152" s="6"/>
+      <c r="AF152" s="6"/>
     </row>
     <row r="153" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
@@ -4734,6 +7553,27 @@
       <c r="E153">
         <v>382.5</v>
       </c>
+      <c r="L153" s="6"/>
+      <c r="M153" s="6"/>
+      <c r="N153" s="6"/>
+      <c r="O153" s="6"/>
+      <c r="P153" s="6"/>
+      <c r="Q153" s="6"/>
+      <c r="R153" s="6"/>
+      <c r="S153" s="6"/>
+      <c r="T153" s="6"/>
+      <c r="U153" s="6"/>
+      <c r="V153" s="6"/>
+      <c r="W153" s="6"/>
+      <c r="X153" s="6"/>
+      <c r="Y153" s="6"/>
+      <c r="Z153" s="6"/>
+      <c r="AA153" s="6"/>
+      <c r="AB153" s="6"/>
+      <c r="AC153" s="6"/>
+      <c r="AD153" s="6"/>
+      <c r="AE153" s="6"/>
+      <c r="AF153" s="6"/>
     </row>
     <row r="154" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
@@ -4748,6 +7588,27 @@
       <c r="E154">
         <v>418.5</v>
       </c>
+      <c r="L154" s="6"/>
+      <c r="M154" s="6"/>
+      <c r="N154" s="6"/>
+      <c r="O154" s="6"/>
+      <c r="P154" s="6"/>
+      <c r="Q154" s="6"/>
+      <c r="R154" s="6"/>
+      <c r="S154" s="6"/>
+      <c r="T154" s="6"/>
+      <c r="U154" s="6"/>
+      <c r="V154" s="6"/>
+      <c r="W154" s="6"/>
+      <c r="X154" s="6"/>
+      <c r="Y154" s="6"/>
+      <c r="Z154" s="6"/>
+      <c r="AA154" s="6"/>
+      <c r="AB154" s="6"/>
+      <c r="AC154" s="6"/>
+      <c r="AD154" s="6"/>
+      <c r="AE154" s="6"/>
+      <c r="AF154" s="6"/>
     </row>
     <row r="155" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
@@ -4762,6 +7623,27 @@
       <c r="E155">
         <v>441.5</v>
       </c>
+      <c r="L155" s="6"/>
+      <c r="M155" s="6"/>
+      <c r="N155" s="6"/>
+      <c r="O155" s="6"/>
+      <c r="P155" s="6"/>
+      <c r="Q155" s="6"/>
+      <c r="R155" s="6"/>
+      <c r="S155" s="6"/>
+      <c r="T155" s="6"/>
+      <c r="U155" s="6"/>
+      <c r="V155" s="6"/>
+      <c r="W155" s="6"/>
+      <c r="X155" s="6"/>
+      <c r="Y155" s="6"/>
+      <c r="Z155" s="6"/>
+      <c r="AA155" s="6"/>
+      <c r="AB155" s="6"/>
+      <c r="AC155" s="6"/>
+      <c r="AD155" s="6"/>
+      <c r="AE155" s="6"/>
+      <c r="AF155" s="6"/>
     </row>
     <row r="156" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B156" s="5" t="s">
@@ -4791,17 +7673,35 @@
       <c r="J156">
         <v>1901</v>
       </c>
-      <c r="U156">
+      <c r="L156" s="6"/>
+      <c r="M156" s="6"/>
+      <c r="N156" s="6"/>
+      <c r="O156" s="6"/>
+      <c r="P156" s="6"/>
+      <c r="Q156" s="6"/>
+      <c r="R156" s="6"/>
+      <c r="S156" s="6"/>
+      <c r="T156" s="6"/>
+      <c r="U156" s="6">
         <f>528.5-68.36</f>
         <v>460.14</v>
       </c>
-      <c r="V156">
+      <c r="V156" s="6">
         <f>52.4-0.15</f>
         <v>52.25</v>
       </c>
-      <c r="X156">
+      <c r="W156" s="6"/>
+      <c r="X156" s="6">
         <v>70.239999999999995</v>
       </c>
+      <c r="Y156" s="6"/>
+      <c r="Z156" s="6"/>
+      <c r="AA156" s="6"/>
+      <c r="AB156" s="6"/>
+      <c r="AC156" s="6"/>
+      <c r="AD156" s="6"/>
+      <c r="AE156" s="6"/>
+      <c r="AF156" s="6"/>
       <c r="AG156" t="s">
         <v>115</v>
       </c>
@@ -4822,15 +7722,33 @@
       <c r="F157" s="5">
         <v>91.31</v>
       </c>
-      <c r="U157">
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="6"/>
+      <c r="O157" s="6"/>
+      <c r="P157" s="6"/>
+      <c r="Q157" s="6"/>
+      <c r="R157" s="6"/>
+      <c r="S157" s="6"/>
+      <c r="T157" s="6"/>
+      <c r="U157" s="6">
         <v>42.7</v>
       </c>
-      <c r="W157">
+      <c r="V157" s="6"/>
+      <c r="W157" s="6">
         <v>39.799999999999997</v>
       </c>
-      <c r="X157">
+      <c r="X157" s="6">
         <v>8.81</v>
       </c>
+      <c r="Y157" s="6"/>
+      <c r="Z157" s="6"/>
+      <c r="AA157" s="6"/>
+      <c r="AB157" s="6"/>
+      <c r="AC157" s="6"/>
+      <c r="AD157" s="6"/>
+      <c r="AE157" s="6"/>
+      <c r="AF157" s="6"/>
       <c r="AG157" t="s">
         <v>115</v>
       </c>
@@ -4863,13 +7781,32 @@
       <c r="J158">
         <v>822</v>
       </c>
-      <c r="U158">
+      <c r="L158" s="6"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="6"/>
+      <c r="O158" s="6"/>
+      <c r="P158" s="6"/>
+      <c r="Q158" s="6"/>
+      <c r="R158" s="6"/>
+      <c r="S158" s="6"/>
+      <c r="T158" s="6"/>
+      <c r="U158" s="6">
         <f>67.2+51</f>
         <v>118.2</v>
       </c>
-      <c r="V158">
+      <c r="V158" s="6">
         <v>256.5</v>
       </c>
+      <c r="W158" s="6"/>
+      <c r="X158" s="6"/>
+      <c r="Y158" s="6"/>
+      <c r="Z158" s="6"/>
+      <c r="AA158" s="6"/>
+      <c r="AB158" s="6"/>
+      <c r="AC158" s="6"/>
+      <c r="AD158" s="6"/>
+      <c r="AE158" s="6"/>
+      <c r="AF158" s="6"/>
       <c r="AG158" t="s">
         <v>115</v>
       </c>
@@ -4890,9 +7827,29 @@
       <c r="F159" s="5">
         <v>65.599999999999994</v>
       </c>
-      <c r="W159">
+      <c r="L159" s="6"/>
+      <c r="M159" s="6"/>
+      <c r="N159" s="6"/>
+      <c r="O159" s="6"/>
+      <c r="P159" s="6"/>
+      <c r="Q159" s="6"/>
+      <c r="R159" s="6"/>
+      <c r="S159" s="6"/>
+      <c r="T159" s="6"/>
+      <c r="U159" s="6"/>
+      <c r="V159" s="6"/>
+      <c r="W159" s="6">
         <v>65.599999999999994</v>
       </c>
+      <c r="X159" s="6"/>
+      <c r="Y159" s="6"/>
+      <c r="Z159" s="6"/>
+      <c r="AA159" s="6"/>
+      <c r="AB159" s="6"/>
+      <c r="AC159" s="6"/>
+      <c r="AD159" s="6"/>
+      <c r="AE159" s="6"/>
+      <c r="AF159" s="6"/>
       <c r="AG159" t="s">
         <v>115</v>
       </c>
@@ -4919,9 +7876,29 @@
       <c r="I160">
         <v>597</v>
       </c>
-      <c r="V160">
+      <c r="L160" s="6"/>
+      <c r="M160" s="6"/>
+      <c r="N160" s="6"/>
+      <c r="O160" s="6"/>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="6"/>
+      <c r="R160" s="6"/>
+      <c r="S160" s="6"/>
+      <c r="T160" s="6"/>
+      <c r="U160" s="6"/>
+      <c r="V160" s="6">
         <v>207.4</v>
       </c>
+      <c r="W160" s="6"/>
+      <c r="X160" s="6"/>
+      <c r="Y160" s="6"/>
+      <c r="Z160" s="6"/>
+      <c r="AA160" s="6"/>
+      <c r="AB160" s="6"/>
+      <c r="AC160" s="6"/>
+      <c r="AD160" s="6"/>
+      <c r="AE160" s="6"/>
+      <c r="AF160" s="6"/>
       <c r="AG160" t="s">
         <v>115</v>
       </c>
@@ -4942,9 +7919,29 @@
       <c r="F161" s="5">
         <v>2</v>
       </c>
-      <c r="W161">
+      <c r="L161" s="6"/>
+      <c r="M161" s="6"/>
+      <c r="N161" s="6"/>
+      <c r="O161" s="6"/>
+      <c r="P161" s="6"/>
+      <c r="Q161" s="6"/>
+      <c r="R161" s="6"/>
+      <c r="S161" s="6"/>
+      <c r="T161" s="6"/>
+      <c r="U161" s="6"/>
+      <c r="V161" s="6"/>
+      <c r="W161" s="6">
         <v>2</v>
       </c>
+      <c r="X161" s="6"/>
+      <c r="Y161" s="6"/>
+      <c r="Z161" s="6"/>
+      <c r="AA161" s="6"/>
+      <c r="AB161" s="6"/>
+      <c r="AC161" s="6"/>
+      <c r="AD161" s="6"/>
+      <c r="AE161" s="6"/>
+      <c r="AF161" s="6"/>
       <c r="AG161" t="s">
         <v>115</v>
       </c>
@@ -4965,6 +7962,27 @@
       <c r="I162">
         <v>785</v>
       </c>
+      <c r="L162" s="6"/>
+      <c r="M162" s="6"/>
+      <c r="N162" s="6"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6"/>
+      <c r="R162" s="6"/>
+      <c r="S162" s="6"/>
+      <c r="T162" s="6"/>
+      <c r="U162" s="6"/>
+      <c r="V162" s="6"/>
+      <c r="W162" s="6"/>
+      <c r="X162" s="6"/>
+      <c r="Y162" s="6"/>
+      <c r="Z162" s="6"/>
+      <c r="AA162" s="6"/>
+      <c r="AB162" s="6"/>
+      <c r="AC162" s="6"/>
+      <c r="AD162" s="6"/>
+      <c r="AE162" s="6"/>
+      <c r="AF162" s="6"/>
     </row>
     <row r="163" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
@@ -4979,6 +7997,27 @@
       <c r="E163">
         <v>894.97</v>
       </c>
+      <c r="L163" s="6"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="6"/>
+      <c r="O163" s="6"/>
+      <c r="P163" s="6"/>
+      <c r="Q163" s="6"/>
+      <c r="R163" s="6"/>
+      <c r="S163" s="6"/>
+      <c r="T163" s="6"/>
+      <c r="U163" s="6"/>
+      <c r="V163" s="6"/>
+      <c r="W163" s="6"/>
+      <c r="X163" s="6"/>
+      <c r="Y163" s="6"/>
+      <c r="Z163" s="6"/>
+      <c r="AA163" s="6"/>
+      <c r="AB163" s="6"/>
+      <c r="AC163" s="6"/>
+      <c r="AD163" s="6"/>
+      <c r="AE163" s="6"/>
+      <c r="AF163" s="6"/>
     </row>
     <row r="164" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
@@ -4990,6 +8029,27 @@
       <c r="D164" t="s">
         <v>6</v>
       </c>
+      <c r="L164" s="6"/>
+      <c r="M164" s="6"/>
+      <c r="N164" s="6"/>
+      <c r="O164" s="6"/>
+      <c r="P164" s="6"/>
+      <c r="Q164" s="6"/>
+      <c r="R164" s="6"/>
+      <c r="S164" s="6"/>
+      <c r="T164" s="6"/>
+      <c r="U164" s="6"/>
+      <c r="V164" s="6"/>
+      <c r="W164" s="6"/>
+      <c r="X164" s="6"/>
+      <c r="Y164" s="6"/>
+      <c r="Z164" s="6"/>
+      <c r="AA164" s="6"/>
+      <c r="AB164" s="6"/>
+      <c r="AC164" s="6"/>
+      <c r="AD164" s="6"/>
+      <c r="AE164" s="6"/>
+      <c r="AF164" s="6"/>
     </row>
     <row r="165" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
@@ -5004,6 +8064,27 @@
       <c r="E165">
         <v>747</v>
       </c>
+      <c r="L165" s="6"/>
+      <c r="M165" s="6"/>
+      <c r="N165" s="6"/>
+      <c r="O165" s="6"/>
+      <c r="P165" s="6"/>
+      <c r="Q165" s="6"/>
+      <c r="R165" s="6"/>
+      <c r="S165" s="6"/>
+      <c r="T165" s="6"/>
+      <c r="U165" s="6"/>
+      <c r="V165" s="6"/>
+      <c r="W165" s="6"/>
+      <c r="X165" s="6"/>
+      <c r="Y165" s="6"/>
+      <c r="Z165" s="6"/>
+      <c r="AA165" s="6"/>
+      <c r="AB165" s="6"/>
+      <c r="AC165" s="6"/>
+      <c r="AD165" s="6"/>
+      <c r="AE165" s="6"/>
+      <c r="AF165" s="6"/>
     </row>
     <row r="166" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B166" s="5" t="s">
@@ -5024,9 +8105,29 @@
       <c r="I166">
         <v>288</v>
       </c>
-      <c r="X166">
+      <c r="L166" s="6"/>
+      <c r="M166" s="6"/>
+      <c r="N166" s="6"/>
+      <c r="O166" s="6"/>
+      <c r="P166" s="6"/>
+      <c r="Q166" s="6"/>
+      <c r="R166" s="6"/>
+      <c r="S166" s="6"/>
+      <c r="T166" s="6"/>
+      <c r="U166" s="6"/>
+      <c r="V166" s="6"/>
+      <c r="W166" s="6"/>
+      <c r="X166" s="6">
         <v>76.400000000000006</v>
       </c>
+      <c r="Y166" s="6"/>
+      <c r="Z166" s="6"/>
+      <c r="AA166" s="6"/>
+      <c r="AB166" s="6"/>
+      <c r="AC166" s="6"/>
+      <c r="AD166" s="6"/>
+      <c r="AE166" s="6"/>
+      <c r="AF166" s="6"/>
       <c r="AG166" t="s">
         <v>115</v>
       </c>
@@ -5044,6 +8145,27 @@
       <c r="E167">
         <v>59.6</v>
       </c>
+      <c r="L167" s="6"/>
+      <c r="M167" s="6"/>
+      <c r="N167" s="6"/>
+      <c r="O167" s="6"/>
+      <c r="P167" s="6"/>
+      <c r="Q167" s="6"/>
+      <c r="R167" s="6"/>
+      <c r="S167" s="6"/>
+      <c r="T167" s="6"/>
+      <c r="U167" s="6"/>
+      <c r="V167" s="6"/>
+      <c r="W167" s="6"/>
+      <c r="X167" s="6"/>
+      <c r="Y167" s="6"/>
+      <c r="Z167" s="6"/>
+      <c r="AA167" s="6"/>
+      <c r="AB167" s="6"/>
+      <c r="AC167" s="6"/>
+      <c r="AD167" s="6"/>
+      <c r="AE167" s="6"/>
+      <c r="AF167" s="6"/>
       <c r="AG167" t="s">
         <v>115</v>
       </c>
@@ -5067,13 +8189,32 @@
       <c r="I168">
         <v>415</v>
       </c>
-      <c r="W168">
+      <c r="L168" s="6"/>
+      <c r="M168" s="6"/>
+      <c r="N168" s="6"/>
+      <c r="O168" s="6"/>
+      <c r="P168" s="6"/>
+      <c r="Q168" s="6"/>
+      <c r="R168" s="6"/>
+      <c r="S168" s="6"/>
+      <c r="T168" s="6"/>
+      <c r="U168" s="6"/>
+      <c r="V168" s="6"/>
+      <c r="W168" s="6">
         <v>81.8</v>
       </c>
-      <c r="X168">
+      <c r="X168" s="6">
         <f>42+158.17+61.95+0.21</f>
         <v>262.33</v>
       </c>
+      <c r="Y168" s="6"/>
+      <c r="Z168" s="6"/>
+      <c r="AA168" s="6"/>
+      <c r="AB168" s="6"/>
+      <c r="AC168" s="6"/>
+      <c r="AD168" s="6"/>
+      <c r="AE168" s="6"/>
+      <c r="AF168" s="6"/>
       <c r="AG168" t="s">
         <v>115</v>
       </c>
@@ -5094,10 +8235,30 @@
       <c r="F169" s="5">
         <v>40.9</v>
       </c>
-      <c r="X169">
+      <c r="L169" s="6"/>
+      <c r="M169" s="6"/>
+      <c r="N169" s="6"/>
+      <c r="O169" s="6"/>
+      <c r="P169" s="6"/>
+      <c r="Q169" s="6"/>
+      <c r="R169" s="6"/>
+      <c r="S169" s="6"/>
+      <c r="T169" s="6"/>
+      <c r="U169" s="6"/>
+      <c r="V169" s="6"/>
+      <c r="W169" s="6"/>
+      <c r="X169" s="6">
         <f>11.35+17.44+12.11</f>
         <v>40.9</v>
       </c>
+      <c r="Y169" s="6"/>
+      <c r="Z169" s="6"/>
+      <c r="AA169" s="6"/>
+      <c r="AB169" s="6"/>
+      <c r="AC169" s="6"/>
+      <c r="AD169" s="6"/>
+      <c r="AE169" s="6"/>
+      <c r="AF169" s="6"/>
       <c r="AG169" t="s">
         <v>115</v>
       </c>
@@ -5118,6 +8279,27 @@
       <c r="I170">
         <v>141</v>
       </c>
+      <c r="L170" s="6"/>
+      <c r="M170" s="6"/>
+      <c r="N170" s="6"/>
+      <c r="O170" s="6"/>
+      <c r="P170" s="6"/>
+      <c r="Q170" s="6"/>
+      <c r="R170" s="6"/>
+      <c r="S170" s="6"/>
+      <c r="T170" s="6"/>
+      <c r="U170" s="6"/>
+      <c r="V170" s="6"/>
+      <c r="W170" s="6"/>
+      <c r="X170" s="6"/>
+      <c r="Y170" s="6"/>
+      <c r="Z170" s="6"/>
+      <c r="AA170" s="6"/>
+      <c r="AB170" s="6"/>
+      <c r="AC170" s="6"/>
+      <c r="AD170" s="6"/>
+      <c r="AE170" s="6"/>
+      <c r="AF170" s="6"/>
     </row>
     <row r="171" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
@@ -5132,6 +8314,27 @@
       <c r="E171">
         <v>28</v>
       </c>
+      <c r="L171" s="6"/>
+      <c r="M171" s="6"/>
+      <c r="N171" s="6"/>
+      <c r="O171" s="6"/>
+      <c r="P171" s="6"/>
+      <c r="Q171" s="6"/>
+      <c r="R171" s="6"/>
+      <c r="S171" s="6"/>
+      <c r="T171" s="6"/>
+      <c r="U171" s="6"/>
+      <c r="V171" s="6"/>
+      <c r="W171" s="6"/>
+      <c r="X171" s="6"/>
+      <c r="Y171" s="6"/>
+      <c r="Z171" s="6"/>
+      <c r="AA171" s="6"/>
+      <c r="AB171" s="6"/>
+      <c r="AC171" s="6"/>
+      <c r="AD171" s="6"/>
+      <c r="AE171" s="6"/>
+      <c r="AF171" s="6"/>
     </row>
     <row r="172" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
@@ -5143,6 +8346,27 @@
       <c r="D172" t="s">
         <v>6</v>
       </c>
+      <c r="L172" s="6"/>
+      <c r="M172" s="6"/>
+      <c r="N172" s="6"/>
+      <c r="O172" s="6"/>
+      <c r="P172" s="6"/>
+      <c r="Q172" s="6"/>
+      <c r="R172" s="6"/>
+      <c r="S172" s="6"/>
+      <c r="T172" s="6"/>
+      <c r="U172" s="6"/>
+      <c r="V172" s="6"/>
+      <c r="W172" s="6"/>
+      <c r="X172" s="6"/>
+      <c r="Y172" s="6"/>
+      <c r="Z172" s="6"/>
+      <c r="AA172" s="6"/>
+      <c r="AB172" s="6"/>
+      <c r="AC172" s="6"/>
+      <c r="AD172" s="6"/>
+      <c r="AE172" s="6"/>
+      <c r="AF172" s="6"/>
     </row>
     <row r="173" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
@@ -5157,6 +8381,27 @@
       <c r="E173">
         <v>125</v>
       </c>
+      <c r="L173" s="6"/>
+      <c r="M173" s="6"/>
+      <c r="N173" s="6"/>
+      <c r="O173" s="6"/>
+      <c r="P173" s="6"/>
+      <c r="Q173" s="6"/>
+      <c r="R173" s="6"/>
+      <c r="S173" s="6"/>
+      <c r="T173" s="6"/>
+      <c r="U173" s="6"/>
+      <c r="V173" s="6"/>
+      <c r="W173" s="6"/>
+      <c r="X173" s="6"/>
+      <c r="Y173" s="6"/>
+      <c r="Z173" s="6"/>
+      <c r="AA173" s="6"/>
+      <c r="AB173" s="6"/>
+      <c r="AC173" s="6"/>
+      <c r="AD173" s="6"/>
+      <c r="AE173" s="6"/>
+      <c r="AF173" s="6"/>
     </row>
     <row r="174" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
@@ -5174,6 +8419,27 @@
       <c r="I174">
         <v>134</v>
       </c>
+      <c r="L174" s="6"/>
+      <c r="M174" s="6"/>
+      <c r="N174" s="6"/>
+      <c r="O174" s="6"/>
+      <c r="P174" s="6"/>
+      <c r="Q174" s="6"/>
+      <c r="R174" s="6"/>
+      <c r="S174" s="6"/>
+      <c r="T174" s="6"/>
+      <c r="U174" s="6"/>
+      <c r="V174" s="6"/>
+      <c r="W174" s="6"/>
+      <c r="X174" s="6"/>
+      <c r="Y174" s="6"/>
+      <c r="Z174" s="6"/>
+      <c r="AA174" s="6"/>
+      <c r="AB174" s="6"/>
+      <c r="AC174" s="6"/>
+      <c r="AD174" s="6"/>
+      <c r="AE174" s="6"/>
+      <c r="AF174" s="6"/>
     </row>
     <row r="175" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
@@ -5188,6 +8454,27 @@
       <c r="E175">
         <v>15.2</v>
       </c>
+      <c r="L175" s="6"/>
+      <c r="M175" s="6"/>
+      <c r="N175" s="6"/>
+      <c r="O175" s="6"/>
+      <c r="P175" s="6"/>
+      <c r="Q175" s="6"/>
+      <c r="R175" s="6"/>
+      <c r="S175" s="6"/>
+      <c r="T175" s="6"/>
+      <c r="U175" s="6"/>
+      <c r="V175" s="6"/>
+      <c r="W175" s="6"/>
+      <c r="X175" s="6"/>
+      <c r="Y175" s="6"/>
+      <c r="Z175" s="6"/>
+      <c r="AA175" s="6"/>
+      <c r="AB175" s="6"/>
+      <c r="AC175" s="6"/>
+      <c r="AD175" s="6"/>
+      <c r="AE175" s="6"/>
+      <c r="AF175" s="6"/>
     </row>
     <row r="176" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
@@ -5199,6 +8486,27 @@
       <c r="D176" t="s">
         <v>6</v>
       </c>
+      <c r="L176" s="6"/>
+      <c r="M176" s="6"/>
+      <c r="N176" s="6"/>
+      <c r="O176" s="6"/>
+      <c r="P176" s="6"/>
+      <c r="Q176" s="6"/>
+      <c r="R176" s="6"/>
+      <c r="S176" s="6"/>
+      <c r="T176" s="6"/>
+      <c r="U176" s="6"/>
+      <c r="V176" s="6"/>
+      <c r="W176" s="6"/>
+      <c r="X176" s="6"/>
+      <c r="Y176" s="6"/>
+      <c r="Z176" s="6"/>
+      <c r="AA176" s="6"/>
+      <c r="AB176" s="6"/>
+      <c r="AC176" s="6"/>
+      <c r="AD176" s="6"/>
+      <c r="AE176" s="6"/>
+      <c r="AF176" s="6"/>
     </row>
     <row r="177" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
@@ -5213,6 +8521,27 @@
       <c r="E177">
         <v>1021.03</v>
       </c>
+      <c r="L177" s="6"/>
+      <c r="M177" s="6"/>
+      <c r="N177" s="6"/>
+      <c r="O177" s="6"/>
+      <c r="P177" s="6"/>
+      <c r="Q177" s="6"/>
+      <c r="R177" s="6"/>
+      <c r="S177" s="6"/>
+      <c r="T177" s="6"/>
+      <c r="U177" s="6"/>
+      <c r="V177" s="6"/>
+      <c r="W177" s="6"/>
+      <c r="X177" s="6"/>
+      <c r="Y177" s="6"/>
+      <c r="Z177" s="6"/>
+      <c r="AA177" s="6"/>
+      <c r="AB177" s="6"/>
+      <c r="AC177" s="6"/>
+      <c r="AD177" s="6"/>
+      <c r="AE177" s="6"/>
+      <c r="AF177" s="6"/>
     </row>
     <row r="178" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B178" s="5" t="s">
@@ -5233,13 +8562,32 @@
       <c r="I178">
         <v>37</v>
       </c>
-      <c r="W178">
+      <c r="L178" s="6"/>
+      <c r="M178" s="6"/>
+      <c r="N178" s="6"/>
+      <c r="O178" s="6"/>
+      <c r="P178" s="6"/>
+      <c r="Q178" s="6"/>
+      <c r="R178" s="6"/>
+      <c r="S178" s="6"/>
+      <c r="T178" s="6"/>
+      <c r="U178" s="6"/>
+      <c r="V178" s="6"/>
+      <c r="W178" s="6">
         <v>78.180000000000007</v>
       </c>
-      <c r="X178">
+      <c r="X178" s="6">
         <f>18.75+12+36.95</f>
         <v>67.7</v>
       </c>
+      <c r="Y178" s="6"/>
+      <c r="Z178" s="6"/>
+      <c r="AA178" s="6"/>
+      <c r="AB178" s="6"/>
+      <c r="AC178" s="6"/>
+      <c r="AD178" s="6"/>
+      <c r="AE178" s="6"/>
+      <c r="AF178" s="6"/>
       <c r="AG178" t="s">
         <v>114</v>
       </c>
@@ -5260,10 +8608,30 @@
       <c r="F179" s="5">
         <v>55.83</v>
       </c>
-      <c r="X179">
+      <c r="L179" s="6"/>
+      <c r="M179" s="6"/>
+      <c r="N179" s="6"/>
+      <c r="O179" s="6"/>
+      <c r="P179" s="6"/>
+      <c r="Q179" s="6"/>
+      <c r="R179" s="6"/>
+      <c r="S179" s="6"/>
+      <c r="T179" s="6"/>
+      <c r="U179" s="6"/>
+      <c r="V179" s="6"/>
+      <c r="W179" s="6"/>
+      <c r="X179" s="6">
         <f>34.75+6.11+14.97</f>
         <v>55.83</v>
       </c>
+      <c r="Y179" s="6"/>
+      <c r="Z179" s="6"/>
+      <c r="AA179" s="6"/>
+      <c r="AB179" s="6"/>
+      <c r="AC179" s="6"/>
+      <c r="AD179" s="6"/>
+      <c r="AE179" s="6"/>
+      <c r="AF179" s="6"/>
       <c r="AG179" t="s">
         <v>114</v>
       </c>
@@ -5278,6 +8646,27 @@
       <c r="D180" t="s">
         <v>6</v>
       </c>
+      <c r="L180" s="6"/>
+      <c r="M180" s="6"/>
+      <c r="N180" s="6"/>
+      <c r="O180" s="6"/>
+      <c r="P180" s="6"/>
+      <c r="Q180" s="6"/>
+      <c r="R180" s="6"/>
+      <c r="S180" s="6"/>
+      <c r="T180" s="6"/>
+      <c r="U180" s="6"/>
+      <c r="V180" s="6"/>
+      <c r="W180" s="6"/>
+      <c r="X180" s="6"/>
+      <c r="Y180" s="6"/>
+      <c r="Z180" s="6"/>
+      <c r="AA180" s="6"/>
+      <c r="AB180" s="6"/>
+      <c r="AC180" s="6"/>
+      <c r="AD180" s="6"/>
+      <c r="AE180" s="6"/>
+      <c r="AF180" s="6"/>
     </row>
     <row r="181" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
@@ -5292,6 +8681,27 @@
       <c r="E181">
         <v>226.5</v>
       </c>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
+      <c r="N181" s="6"/>
+      <c r="O181" s="6"/>
+      <c r="P181" s="6"/>
+      <c r="Q181" s="6"/>
+      <c r="R181" s="6"/>
+      <c r="S181" s="6"/>
+      <c r="T181" s="6"/>
+      <c r="U181" s="6"/>
+      <c r="V181" s="6"/>
+      <c r="W181" s="6"/>
+      <c r="X181" s="6"/>
+      <c r="Y181" s="6"/>
+      <c r="Z181" s="6"/>
+      <c r="AA181" s="6"/>
+      <c r="AB181" s="6"/>
+      <c r="AC181" s="6"/>
+      <c r="AD181" s="6"/>
+      <c r="AE181" s="6"/>
+      <c r="AF181" s="6"/>
     </row>
     <row r="182" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
@@ -5309,6 +8719,27 @@
       <c r="I182">
         <v>87</v>
       </c>
+      <c r="L182" s="6"/>
+      <c r="M182" s="6"/>
+      <c r="N182" s="6"/>
+      <c r="O182" s="6"/>
+      <c r="P182" s="6"/>
+      <c r="Q182" s="6"/>
+      <c r="R182" s="6"/>
+      <c r="S182" s="6"/>
+      <c r="T182" s="6"/>
+      <c r="U182" s="6"/>
+      <c r="V182" s="6"/>
+      <c r="W182" s="6"/>
+      <c r="X182" s="6"/>
+      <c r="Y182" s="6"/>
+      <c r="Z182" s="6"/>
+      <c r="AA182" s="6"/>
+      <c r="AB182" s="6"/>
+      <c r="AC182" s="6"/>
+      <c r="AD182" s="6"/>
+      <c r="AE182" s="6"/>
+      <c r="AF182" s="6"/>
     </row>
     <row r="183" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
@@ -5323,6 +8754,27 @@
       <c r="E183">
         <v>244.5</v>
       </c>
+      <c r="L183" s="6"/>
+      <c r="M183" s="6"/>
+      <c r="N183" s="6"/>
+      <c r="O183" s="6"/>
+      <c r="P183" s="6"/>
+      <c r="Q183" s="6"/>
+      <c r="R183" s="6"/>
+      <c r="S183" s="6"/>
+      <c r="T183" s="6"/>
+      <c r="U183" s="6"/>
+      <c r="V183" s="6"/>
+      <c r="W183" s="6"/>
+      <c r="X183" s="6"/>
+      <c r="Y183" s="6"/>
+      <c r="Z183" s="6"/>
+      <c r="AA183" s="6"/>
+      <c r="AB183" s="6"/>
+      <c r="AC183" s="6"/>
+      <c r="AD183" s="6"/>
+      <c r="AE183" s="6"/>
+      <c r="AF183" s="6"/>
     </row>
     <row r="184" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
@@ -5334,6 +8786,27 @@
       <c r="D184" t="s">
         <v>6</v>
       </c>
+      <c r="L184" s="6"/>
+      <c r="M184" s="6"/>
+      <c r="N184" s="6"/>
+      <c r="O184" s="6"/>
+      <c r="P184" s="6"/>
+      <c r="Q184" s="6"/>
+      <c r="R184" s="6"/>
+      <c r="S184" s="6"/>
+      <c r="T184" s="6"/>
+      <c r="U184" s="6"/>
+      <c r="V184" s="6"/>
+      <c r="W184" s="6"/>
+      <c r="X184" s="6"/>
+      <c r="Y184" s="6"/>
+      <c r="Z184" s="6"/>
+      <c r="AA184" s="6"/>
+      <c r="AB184" s="6"/>
+      <c r="AC184" s="6"/>
+      <c r="AD184" s="6"/>
+      <c r="AE184" s="6"/>
+      <c r="AF184" s="6"/>
     </row>
     <row r="185" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
@@ -5348,6 +8821,27 @@
       <c r="E185">
         <v>338.5</v>
       </c>
+      <c r="L185" s="6"/>
+      <c r="M185" s="6"/>
+      <c r="N185" s="6"/>
+      <c r="O185" s="6"/>
+      <c r="P185" s="6"/>
+      <c r="Q185" s="6"/>
+      <c r="R185" s="6"/>
+      <c r="S185" s="6"/>
+      <c r="T185" s="6"/>
+      <c r="U185" s="6"/>
+      <c r="V185" s="6"/>
+      <c r="W185" s="6"/>
+      <c r="X185" s="6"/>
+      <c r="Y185" s="6"/>
+      <c r="Z185" s="6"/>
+      <c r="AA185" s="6"/>
+      <c r="AB185" s="6"/>
+      <c r="AC185" s="6"/>
+      <c r="AD185" s="6"/>
+      <c r="AE185" s="6"/>
+      <c r="AF185" s="6"/>
     </row>
     <row r="186" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
@@ -5359,6 +8853,27 @@
       <c r="D186" t="s">
         <v>6</v>
       </c>
+      <c r="L186" s="6"/>
+      <c r="M186" s="6"/>
+      <c r="N186" s="6"/>
+      <c r="O186" s="6"/>
+      <c r="P186" s="6"/>
+      <c r="Q186" s="6"/>
+      <c r="R186" s="6"/>
+      <c r="S186" s="6"/>
+      <c r="T186" s="6"/>
+      <c r="U186" s="6"/>
+      <c r="V186" s="6"/>
+      <c r="W186" s="6"/>
+      <c r="X186" s="6"/>
+      <c r="Y186" s="6"/>
+      <c r="Z186" s="6"/>
+      <c r="AA186" s="6"/>
+      <c r="AB186" s="6"/>
+      <c r="AC186" s="6"/>
+      <c r="AD186" s="6"/>
+      <c r="AE186" s="6"/>
+      <c r="AF186" s="6"/>
     </row>
     <row r="187" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
@@ -5373,6 +8888,27 @@
       <c r="E187">
         <v>238</v>
       </c>
+      <c r="L187" s="6"/>
+      <c r="M187" s="6"/>
+      <c r="N187" s="6"/>
+      <c r="O187" s="6"/>
+      <c r="P187" s="6"/>
+      <c r="Q187" s="6"/>
+      <c r="R187" s="6"/>
+      <c r="S187" s="6"/>
+      <c r="T187" s="6"/>
+      <c r="U187" s="6"/>
+      <c r="V187" s="6"/>
+      <c r="W187" s="6"/>
+      <c r="X187" s="6"/>
+      <c r="Y187" s="6"/>
+      <c r="Z187" s="6"/>
+      <c r="AA187" s="6"/>
+      <c r="AB187" s="6"/>
+      <c r="AC187" s="6"/>
+      <c r="AD187" s="6"/>
+      <c r="AE187" s="6"/>
+      <c r="AF187" s="6"/>
     </row>
     <row r="188" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
@@ -5384,6 +8920,27 @@
       <c r="D188" t="s">
         <v>6</v>
       </c>
+      <c r="L188" s="6"/>
+      <c r="M188" s="6"/>
+      <c r="N188" s="6"/>
+      <c r="O188" s="6"/>
+      <c r="P188" s="6"/>
+      <c r="Q188" s="6"/>
+      <c r="R188" s="6"/>
+      <c r="S188" s="6"/>
+      <c r="T188" s="6"/>
+      <c r="U188" s="6"/>
+      <c r="V188" s="6"/>
+      <c r="W188" s="6"/>
+      <c r="X188" s="6"/>
+      <c r="Y188" s="6"/>
+      <c r="Z188" s="6"/>
+      <c r="AA188" s="6"/>
+      <c r="AB188" s="6"/>
+      <c r="AC188" s="6"/>
+      <c r="AD188" s="6"/>
+      <c r="AE188" s="6"/>
+      <c r="AF188" s="6"/>
     </row>
     <row r="189" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
@@ -5398,6 +8955,27 @@
       <c r="E189">
         <v>69</v>
       </c>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
+      <c r="O189" s="6"/>
+      <c r="P189" s="6"/>
+      <c r="Q189" s="6"/>
+      <c r="R189" s="6"/>
+      <c r="S189" s="6"/>
+      <c r="T189" s="6"/>
+      <c r="U189" s="6"/>
+      <c r="V189" s="6"/>
+      <c r="W189" s="6"/>
+      <c r="X189" s="6"/>
+      <c r="Y189" s="6"/>
+      <c r="Z189" s="6"/>
+      <c r="AA189" s="6"/>
+      <c r="AB189" s="6"/>
+      <c r="AC189" s="6"/>
+      <c r="AD189" s="6"/>
+      <c r="AE189" s="6"/>
+      <c r="AF189" s="6"/>
     </row>
     <row r="190" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
@@ -5409,6 +8987,27 @@
       <c r="D190" t="s">
         <v>6</v>
       </c>
+      <c r="L190" s="6"/>
+      <c r="M190" s="6"/>
+      <c r="N190" s="6"/>
+      <c r="O190" s="6"/>
+      <c r="P190" s="6"/>
+      <c r="Q190" s="6"/>
+      <c r="R190" s="6"/>
+      <c r="S190" s="6"/>
+      <c r="T190" s="6"/>
+      <c r="U190" s="6"/>
+      <c r="V190" s="6"/>
+      <c r="W190" s="6"/>
+      <c r="X190" s="6"/>
+      <c r="Y190" s="6"/>
+      <c r="Z190" s="6"/>
+      <c r="AA190" s="6"/>
+      <c r="AB190" s="6"/>
+      <c r="AC190" s="6"/>
+      <c r="AD190" s="6"/>
+      <c r="AE190" s="6"/>
+      <c r="AF190" s="6"/>
     </row>
     <row r="191" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
@@ -5423,6 +9022,27 @@
       <c r="E191">
         <v>140</v>
       </c>
+      <c r="L191" s="6"/>
+      <c r="M191" s="6"/>
+      <c r="N191" s="6"/>
+      <c r="O191" s="6"/>
+      <c r="P191" s="6"/>
+      <c r="Q191" s="6"/>
+      <c r="R191" s="6"/>
+      <c r="S191" s="6"/>
+      <c r="T191" s="6"/>
+      <c r="U191" s="6"/>
+      <c r="V191" s="6"/>
+      <c r="W191" s="6"/>
+      <c r="X191" s="6"/>
+      <c r="Y191" s="6"/>
+      <c r="Z191" s="6"/>
+      <c r="AA191" s="6"/>
+      <c r="AB191" s="6"/>
+      <c r="AC191" s="6"/>
+      <c r="AD191" s="6"/>
+      <c r="AE191" s="6"/>
+      <c r="AF191" s="6"/>
     </row>
     <row r="192" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
@@ -5434,6 +9054,27 @@
       <c r="D192" t="s">
         <v>6</v>
       </c>
+      <c r="L192" s="6"/>
+      <c r="M192" s="6"/>
+      <c r="N192" s="6"/>
+      <c r="O192" s="6"/>
+      <c r="P192" s="6"/>
+      <c r="Q192" s="6"/>
+      <c r="R192" s="6"/>
+      <c r="S192" s="6"/>
+      <c r="T192" s="6"/>
+      <c r="U192" s="6"/>
+      <c r="V192" s="6"/>
+      <c r="W192" s="6"/>
+      <c r="X192" s="6"/>
+      <c r="Y192" s="6"/>
+      <c r="Z192" s="6"/>
+      <c r="AA192" s="6"/>
+      <c r="AB192" s="6"/>
+      <c r="AC192" s="6"/>
+      <c r="AD192" s="6"/>
+      <c r="AE192" s="6"/>
+      <c r="AF192" s="6"/>
       <c r="AG192" t="s">
         <v>115</v>
       </c>
@@ -5451,6 +9092,27 @@
       <c r="E193">
         <v>858.5</v>
       </c>
+      <c r="L193" s="6"/>
+      <c r="M193" s="6"/>
+      <c r="N193" s="6"/>
+      <c r="O193" s="6"/>
+      <c r="P193" s="6"/>
+      <c r="Q193" s="6"/>
+      <c r="R193" s="6"/>
+      <c r="S193" s="6"/>
+      <c r="T193" s="6"/>
+      <c r="U193" s="6"/>
+      <c r="V193" s="6"/>
+      <c r="W193" s="6"/>
+      <c r="X193" s="6"/>
+      <c r="Y193" s="6"/>
+      <c r="Z193" s="6"/>
+      <c r="AA193" s="6"/>
+      <c r="AB193" s="6"/>
+      <c r="AC193" s="6"/>
+      <c r="AD193" s="6"/>
+      <c r="AE193" s="6"/>
+      <c r="AF193" s="6"/>
     </row>
     <row r="194" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
@@ -5462,6 +9124,27 @@
       <c r="D194" t="s">
         <v>6</v>
       </c>
+      <c r="L194" s="6"/>
+      <c r="M194" s="6"/>
+      <c r="N194" s="6"/>
+      <c r="O194" s="6"/>
+      <c r="P194" s="6"/>
+      <c r="Q194" s="6"/>
+      <c r="R194" s="6"/>
+      <c r="S194" s="6"/>
+      <c r="T194" s="6"/>
+      <c r="U194" s="6"/>
+      <c r="V194" s="6"/>
+      <c r="W194" s="6"/>
+      <c r="X194" s="6"/>
+      <c r="Y194" s="6"/>
+      <c r="Z194" s="6"/>
+      <c r="AA194" s="6"/>
+      <c r="AB194" s="6"/>
+      <c r="AC194" s="6"/>
+      <c r="AD194" s="6"/>
+      <c r="AE194" s="6"/>
+      <c r="AF194" s="6"/>
     </row>
     <row r="195" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
@@ -5476,6 +9159,27 @@
       <c r="E195">
         <v>168</v>
       </c>
+      <c r="L195" s="6"/>
+      <c r="M195" s="6"/>
+      <c r="N195" s="6"/>
+      <c r="O195" s="6"/>
+      <c r="P195" s="6"/>
+      <c r="Q195" s="6"/>
+      <c r="R195" s="6"/>
+      <c r="S195" s="6"/>
+      <c r="T195" s="6"/>
+      <c r="U195" s="6"/>
+      <c r="V195" s="6"/>
+      <c r="W195" s="6"/>
+      <c r="X195" s="6"/>
+      <c r="Y195" s="6"/>
+      <c r="Z195" s="6"/>
+      <c r="AA195" s="6"/>
+      <c r="AB195" s="6"/>
+      <c r="AC195" s="6"/>
+      <c r="AD195" s="6"/>
+      <c r="AE195" s="6"/>
+      <c r="AF195" s="6"/>
     </row>
     <row r="196" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
@@ -5487,6 +9191,27 @@
       <c r="D196" t="s">
         <v>6</v>
       </c>
+      <c r="L196" s="6"/>
+      <c r="M196" s="6"/>
+      <c r="N196" s="6"/>
+      <c r="O196" s="6"/>
+      <c r="P196" s="6"/>
+      <c r="Q196" s="6"/>
+      <c r="R196" s="6"/>
+      <c r="S196" s="6"/>
+      <c r="T196" s="6"/>
+      <c r="U196" s="6"/>
+      <c r="V196" s="6"/>
+      <c r="W196" s="6"/>
+      <c r="X196" s="6"/>
+      <c r="Y196" s="6"/>
+      <c r="Z196" s="6"/>
+      <c r="AA196" s="6"/>
+      <c r="AB196" s="6"/>
+      <c r="AC196" s="6"/>
+      <c r="AD196" s="6"/>
+      <c r="AE196" s="6"/>
+      <c r="AF196" s="6"/>
     </row>
     <row r="197" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
@@ -5501,6 +9226,27 @@
       <c r="E197">
         <v>180</v>
       </c>
+      <c r="L197" s="6"/>
+      <c r="M197" s="6"/>
+      <c r="N197" s="6"/>
+      <c r="O197" s="6"/>
+      <c r="P197" s="6"/>
+      <c r="Q197" s="6"/>
+      <c r="R197" s="6"/>
+      <c r="S197" s="6"/>
+      <c r="T197" s="6"/>
+      <c r="U197" s="6"/>
+      <c r="V197" s="6"/>
+      <c r="W197" s="6"/>
+      <c r="X197" s="6"/>
+      <c r="Y197" s="6"/>
+      <c r="Z197" s="6"/>
+      <c r="AA197" s="6"/>
+      <c r="AB197" s="6"/>
+      <c r="AC197" s="6"/>
+      <c r="AD197" s="6"/>
+      <c r="AE197" s="6"/>
+      <c r="AF197" s="6"/>
     </row>
     <row r="198" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
@@ -5515,6 +9261,27 @@
       <c r="I198">
         <v>182</v>
       </c>
+      <c r="L198" s="6"/>
+      <c r="M198" s="6"/>
+      <c r="N198" s="6"/>
+      <c r="O198" s="6"/>
+      <c r="P198" s="6"/>
+      <c r="Q198" s="6"/>
+      <c r="R198" s="6"/>
+      <c r="S198" s="6"/>
+      <c r="T198" s="6"/>
+      <c r="U198" s="6"/>
+      <c r="V198" s="6"/>
+      <c r="W198" s="6"/>
+      <c r="X198" s="6"/>
+      <c r="Y198" s="6"/>
+      <c r="Z198" s="6"/>
+      <c r="AA198" s="6"/>
+      <c r="AB198" s="6"/>
+      <c r="AC198" s="6"/>
+      <c r="AD198" s="6"/>
+      <c r="AE198" s="6"/>
+      <c r="AF198" s="6"/>
     </row>
     <row r="199" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
@@ -5529,6 +9296,27 @@
       <c r="E199">
         <v>238.52</v>
       </c>
+      <c r="L199" s="6"/>
+      <c r="M199" s="6"/>
+      <c r="N199" s="6"/>
+      <c r="O199" s="6"/>
+      <c r="P199" s="6"/>
+      <c r="Q199" s="6"/>
+      <c r="R199" s="6"/>
+      <c r="S199" s="6"/>
+      <c r="T199" s="6"/>
+      <c r="U199" s="6"/>
+      <c r="V199" s="6"/>
+      <c r="W199" s="6"/>
+      <c r="X199" s="6"/>
+      <c r="Y199" s="6"/>
+      <c r="Z199" s="6"/>
+      <c r="AA199" s="6"/>
+      <c r="AB199" s="6"/>
+      <c r="AC199" s="6"/>
+      <c r="AD199" s="6"/>
+      <c r="AE199" s="6"/>
+      <c r="AF199" s="6"/>
     </row>
     <row r="200" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
@@ -5540,6 +9328,27 @@
       <c r="D200" t="s">
         <v>6</v>
       </c>
+      <c r="L200" s="6"/>
+      <c r="M200" s="6"/>
+      <c r="N200" s="6"/>
+      <c r="O200" s="6"/>
+      <c r="P200" s="6"/>
+      <c r="Q200" s="6"/>
+      <c r="R200" s="6"/>
+      <c r="S200" s="6"/>
+      <c r="T200" s="6"/>
+      <c r="U200" s="6"/>
+      <c r="V200" s="6"/>
+      <c r="W200" s="6"/>
+      <c r="X200" s="6"/>
+      <c r="Y200" s="6"/>
+      <c r="Z200" s="6"/>
+      <c r="AA200" s="6"/>
+      <c r="AB200" s="6"/>
+      <c r="AC200" s="6"/>
+      <c r="AD200" s="6"/>
+      <c r="AE200" s="6"/>
+      <c r="AF200" s="6"/>
     </row>
     <row r="201" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
@@ -5554,6 +9363,27 @@
       <c r="E201">
         <v>229.5</v>
       </c>
+      <c r="L201" s="6"/>
+      <c r="M201" s="6"/>
+      <c r="N201" s="6"/>
+      <c r="O201" s="6"/>
+      <c r="P201" s="6"/>
+      <c r="Q201" s="6"/>
+      <c r="R201" s="6"/>
+      <c r="S201" s="6"/>
+      <c r="T201" s="6"/>
+      <c r="U201" s="6"/>
+      <c r="V201" s="6"/>
+      <c r="W201" s="6"/>
+      <c r="X201" s="6"/>
+      <c r="Y201" s="6"/>
+      <c r="Z201" s="6"/>
+      <c r="AA201" s="6"/>
+      <c r="AB201" s="6"/>
+      <c r="AC201" s="6"/>
+      <c r="AD201" s="6"/>
+      <c r="AE201" s="6"/>
+      <c r="AF201" s="6"/>
     </row>
     <row r="202" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
@@ -5565,6 +9395,27 @@
       <c r="D202" t="s">
         <v>6</v>
       </c>
+      <c r="L202" s="6"/>
+      <c r="M202" s="6"/>
+      <c r="N202" s="6"/>
+      <c r="O202" s="6"/>
+      <c r="P202" s="6"/>
+      <c r="Q202" s="6"/>
+      <c r="R202" s="6"/>
+      <c r="S202" s="6"/>
+      <c r="T202" s="6"/>
+      <c r="U202" s="6"/>
+      <c r="V202" s="6"/>
+      <c r="W202" s="6"/>
+      <c r="X202" s="6"/>
+      <c r="Y202" s="6"/>
+      <c r="Z202" s="6"/>
+      <c r="AA202" s="6"/>
+      <c r="AB202" s="6"/>
+      <c r="AC202" s="6"/>
+      <c r="AD202" s="6"/>
+      <c r="AE202" s="6"/>
+      <c r="AF202" s="6"/>
     </row>
     <row r="203" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
@@ -5579,6 +9430,27 @@
       <c r="E203">
         <v>1566.27</v>
       </c>
+      <c r="L203" s="6"/>
+      <c r="M203" s="6"/>
+      <c r="N203" s="6"/>
+      <c r="O203" s="6"/>
+      <c r="P203" s="6"/>
+      <c r="Q203" s="6"/>
+      <c r="R203" s="6"/>
+      <c r="S203" s="6"/>
+      <c r="T203" s="6"/>
+      <c r="U203" s="6"/>
+      <c r="V203" s="6"/>
+      <c r="W203" s="6"/>
+      <c r="X203" s="6"/>
+      <c r="Y203" s="6"/>
+      <c r="Z203" s="6"/>
+      <c r="AA203" s="6"/>
+      <c r="AB203" s="6"/>
+      <c r="AC203" s="6"/>
+      <c r="AD203" s="6"/>
+      <c r="AE203" s="6"/>
+      <c r="AF203" s="6"/>
     </row>
     <row r="204" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
@@ -5590,6 +9462,27 @@
       <c r="D204" t="s">
         <v>6</v>
       </c>
+      <c r="L204" s="6"/>
+      <c r="M204" s="6"/>
+      <c r="N204" s="6"/>
+      <c r="O204" s="6"/>
+      <c r="P204" s="6"/>
+      <c r="Q204" s="6"/>
+      <c r="R204" s="6"/>
+      <c r="S204" s="6"/>
+      <c r="T204" s="6"/>
+      <c r="U204" s="6"/>
+      <c r="V204" s="6"/>
+      <c r="W204" s="6"/>
+      <c r="X204" s="6"/>
+      <c r="Y204" s="6"/>
+      <c r="Z204" s="6"/>
+      <c r="AA204" s="6"/>
+      <c r="AB204" s="6"/>
+      <c r="AC204" s="6"/>
+      <c r="AD204" s="6"/>
+      <c r="AE204" s="6"/>
+      <c r="AF204" s="6"/>
     </row>
     <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
@@ -5604,6 +9497,27 @@
       <c r="E205">
         <v>95</v>
       </c>
+      <c r="L205" s="6"/>
+      <c r="M205" s="6"/>
+      <c r="N205" s="6"/>
+      <c r="O205" s="6"/>
+      <c r="P205" s="6"/>
+      <c r="Q205" s="6"/>
+      <c r="R205" s="6"/>
+      <c r="S205" s="6"/>
+      <c r="T205" s="6"/>
+      <c r="U205" s="6"/>
+      <c r="V205" s="6"/>
+      <c r="W205" s="6"/>
+      <c r="X205" s="6"/>
+      <c r="Y205" s="6"/>
+      <c r="Z205" s="6"/>
+      <c r="AA205" s="6"/>
+      <c r="AB205" s="6"/>
+      <c r="AC205" s="6"/>
+      <c r="AD205" s="6"/>
+      <c r="AE205" s="6"/>
+      <c r="AF205" s="6"/>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B206" s="5" t="s">
@@ -5621,9 +9535,29 @@
       <c r="F206" s="5">
         <v>34.57</v>
       </c>
-      <c r="V206">
+      <c r="L206" s="6"/>
+      <c r="M206" s="6"/>
+      <c r="N206" s="6"/>
+      <c r="O206" s="6"/>
+      <c r="P206" s="6"/>
+      <c r="Q206" s="6"/>
+      <c r="R206" s="6"/>
+      <c r="S206" s="6"/>
+      <c r="T206" s="6"/>
+      <c r="U206" s="6"/>
+      <c r="V206" s="6">
         <v>34.57</v>
       </c>
+      <c r="W206" s="6"/>
+      <c r="X206" s="6"/>
+      <c r="Y206" s="6"/>
+      <c r="Z206" s="6"/>
+      <c r="AA206" s="6"/>
+      <c r="AB206" s="6"/>
+      <c r="AC206" s="6"/>
+      <c r="AD206" s="6"/>
+      <c r="AE206" s="6"/>
+      <c r="AF206" s="6"/>
       <c r="AG206" t="s">
         <v>114</v>
       </c>
@@ -5641,6 +9575,27 @@
       <c r="E207">
         <v>158</v>
       </c>
+      <c r="L207" s="6"/>
+      <c r="M207" s="6"/>
+      <c r="N207" s="6"/>
+      <c r="O207" s="6"/>
+      <c r="P207" s="6"/>
+      <c r="Q207" s="6"/>
+      <c r="R207" s="6"/>
+      <c r="S207" s="6"/>
+      <c r="T207" s="6"/>
+      <c r="U207" s="6"/>
+      <c r="V207" s="6"/>
+      <c r="W207" s="6"/>
+      <c r="X207" s="6"/>
+      <c r="Y207" s="6"/>
+      <c r="Z207" s="6"/>
+      <c r="AA207" s="6"/>
+      <c r="AB207" s="6"/>
+      <c r="AC207" s="6"/>
+      <c r="AD207" s="6"/>
+      <c r="AE207" s="6"/>
+      <c r="AF207" s="6"/>
       <c r="AG207" t="s">
         <v>114</v>
       </c>
@@ -5667,9 +9622,29 @@
       <c r="J208">
         <v>27</v>
       </c>
-      <c r="S208">
+      <c r="L208" s="6"/>
+      <c r="M208" s="6"/>
+      <c r="N208" s="6"/>
+      <c r="O208" s="6"/>
+      <c r="P208" s="6"/>
+      <c r="Q208" s="6"/>
+      <c r="R208" s="6"/>
+      <c r="S208" s="6">
         <v>300.68</v>
       </c>
+      <c r="T208" s="6"/>
+      <c r="U208" s="6"/>
+      <c r="V208" s="6"/>
+      <c r="W208" s="6"/>
+      <c r="X208" s="6"/>
+      <c r="Y208" s="6"/>
+      <c r="Z208" s="6"/>
+      <c r="AA208" s="6"/>
+      <c r="AB208" s="6"/>
+      <c r="AC208" s="6"/>
+      <c r="AD208" s="6"/>
+      <c r="AE208" s="6"/>
+      <c r="AF208" s="6"/>
       <c r="AG208" t="s">
         <v>114</v>
       </c>
@@ -5690,15 +9665,33 @@
       <c r="F209" s="5">
         <v>337.46</v>
       </c>
-      <c r="Q209">
+      <c r="L209" s="6"/>
+      <c r="M209" s="6"/>
+      <c r="N209" s="6"/>
+      <c r="O209" s="6"/>
+      <c r="P209" s="6"/>
+      <c r="Q209" s="6">
         <v>127.69</v>
       </c>
-      <c r="W209">
+      <c r="R209" s="6"/>
+      <c r="S209" s="6"/>
+      <c r="T209" s="6"/>
+      <c r="U209" s="6"/>
+      <c r="V209" s="6"/>
+      <c r="W209" s="6">
         <v>42</v>
       </c>
-      <c r="X209">
+      <c r="X209" s="6">
         <v>167.77</v>
       </c>
+      <c r="Y209" s="6"/>
+      <c r="Z209" s="6"/>
+      <c r="AA209" s="6"/>
+      <c r="AB209" s="6"/>
+      <c r="AC209" s="6"/>
+      <c r="AD209" s="6"/>
+      <c r="AE209" s="6"/>
+      <c r="AF209" s="6"/>
       <c r="AG209" t="s">
         <v>114</v>
       </c>
@@ -5716,6 +9709,27 @@
       <c r="E210">
         <v>100.2</v>
       </c>
+      <c r="L210" s="6"/>
+      <c r="M210" s="6"/>
+      <c r="N210" s="6"/>
+      <c r="O210" s="6"/>
+      <c r="P210" s="6"/>
+      <c r="Q210" s="6"/>
+      <c r="R210" s="6"/>
+      <c r="S210" s="6"/>
+      <c r="T210" s="6"/>
+      <c r="U210" s="6"/>
+      <c r="V210" s="6"/>
+      <c r="W210" s="6"/>
+      <c r="X210" s="6"/>
+      <c r="Y210" s="6"/>
+      <c r="Z210" s="6"/>
+      <c r="AA210" s="6"/>
+      <c r="AB210" s="6"/>
+      <c r="AC210" s="6"/>
+      <c r="AD210" s="6"/>
+      <c r="AE210" s="6"/>
+      <c r="AF210" s="6"/>
     </row>
     <row r="211" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
@@ -5730,6 +9744,27 @@
       <c r="E211">
         <v>253.5</v>
       </c>
+      <c r="L211" s="6"/>
+      <c r="M211" s="6"/>
+      <c r="N211" s="6"/>
+      <c r="O211" s="6"/>
+      <c r="P211" s="6"/>
+      <c r="Q211" s="6"/>
+      <c r="R211" s="6"/>
+      <c r="S211" s="6"/>
+      <c r="T211" s="6"/>
+      <c r="U211" s="6"/>
+      <c r="V211" s="6"/>
+      <c r="W211" s="6"/>
+      <c r="X211" s="6"/>
+      <c r="Y211" s="6"/>
+      <c r="Z211" s="6"/>
+      <c r="AA211" s="6"/>
+      <c r="AB211" s="6"/>
+      <c r="AC211" s="6"/>
+      <c r="AD211" s="6"/>
+      <c r="AE211" s="6"/>
+      <c r="AF211" s="6"/>
     </row>
     <row r="212" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
@@ -5744,6 +9779,27 @@
       <c r="E212">
         <v>89.9</v>
       </c>
+      <c r="L212" s="6"/>
+      <c r="M212" s="6"/>
+      <c r="N212" s="6"/>
+      <c r="O212" s="6"/>
+      <c r="P212" s="6"/>
+      <c r="Q212" s="6"/>
+      <c r="R212" s="6"/>
+      <c r="S212" s="6"/>
+      <c r="T212" s="6"/>
+      <c r="U212" s="6"/>
+      <c r="V212" s="6"/>
+      <c r="W212" s="6"/>
+      <c r="X212" s="6"/>
+      <c r="Y212" s="6"/>
+      <c r="Z212" s="6"/>
+      <c r="AA212" s="6"/>
+      <c r="AB212" s="6"/>
+      <c r="AC212" s="6"/>
+      <c r="AD212" s="6"/>
+      <c r="AE212" s="6"/>
+      <c r="AF212" s="6"/>
     </row>
     <row r="213" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
@@ -5758,6 +9814,27 @@
       <c r="E213">
         <v>322.2</v>
       </c>
+      <c r="L213" s="6"/>
+      <c r="M213" s="6"/>
+      <c r="N213" s="6"/>
+      <c r="O213" s="6"/>
+      <c r="P213" s="6"/>
+      <c r="Q213" s="6"/>
+      <c r="R213" s="6"/>
+      <c r="S213" s="6"/>
+      <c r="T213" s="6"/>
+      <c r="U213" s="6"/>
+      <c r="V213" s="6"/>
+      <c r="W213" s="6"/>
+      <c r="X213" s="6"/>
+      <c r="Y213" s="6"/>
+      <c r="Z213" s="6"/>
+      <c r="AA213" s="6"/>
+      <c r="AB213" s="6"/>
+      <c r="AC213" s="6"/>
+      <c r="AD213" s="6"/>
+      <c r="AE213" s="6"/>
+      <c r="AF213" s="6"/>
     </row>
     <row r="214" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
@@ -5769,6 +9846,27 @@
       <c r="D214" t="s">
         <v>6</v>
       </c>
+      <c r="L214" s="6"/>
+      <c r="M214" s="6"/>
+      <c r="N214" s="6"/>
+      <c r="O214" s="6"/>
+      <c r="P214" s="6"/>
+      <c r="Q214" s="6"/>
+      <c r="R214" s="6"/>
+      <c r="S214" s="6"/>
+      <c r="T214" s="6"/>
+      <c r="U214" s="6"/>
+      <c r="V214" s="6"/>
+      <c r="W214" s="6"/>
+      <c r="X214" s="6"/>
+      <c r="Y214" s="6"/>
+      <c r="Z214" s="6"/>
+      <c r="AA214" s="6"/>
+      <c r="AB214" s="6"/>
+      <c r="AC214" s="6"/>
+      <c r="AD214" s="6"/>
+      <c r="AE214" s="6"/>
+      <c r="AF214" s="6"/>
     </row>
     <row r="215" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
@@ -5783,6 +9881,27 @@
       <c r="E215">
         <v>129.80000000000001</v>
       </c>
+      <c r="L215" s="6"/>
+      <c r="M215" s="6"/>
+      <c r="N215" s="6"/>
+      <c r="O215" s="6"/>
+      <c r="P215" s="6"/>
+      <c r="Q215" s="6"/>
+      <c r="R215" s="6"/>
+      <c r="S215" s="6"/>
+      <c r="T215" s="6"/>
+      <c r="U215" s="6"/>
+      <c r="V215" s="6"/>
+      <c r="W215" s="6"/>
+      <c r="X215" s="6"/>
+      <c r="Y215" s="6"/>
+      <c r="Z215" s="6"/>
+      <c r="AA215" s="6"/>
+      <c r="AB215" s="6"/>
+      <c r="AC215" s="6"/>
+      <c r="AD215" s="6"/>
+      <c r="AE215" s="6"/>
+      <c r="AF215" s="6"/>
     </row>
     <row r="216" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
@@ -5794,6 +9913,27 @@
       <c r="D216" t="s">
         <v>6</v>
       </c>
+      <c r="L216" s="6"/>
+      <c r="M216" s="6"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6"/>
+      <c r="P216" s="6"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="6"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="6"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="6"/>
+      <c r="AB216" s="6"/>
+      <c r="AC216" s="6"/>
+      <c r="AD216" s="6"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="6"/>
     </row>
     <row r="217" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
@@ -5808,6 +9948,27 @@
       <c r="E217">
         <v>205</v>
       </c>
+      <c r="L217" s="6"/>
+      <c r="M217" s="6"/>
+      <c r="N217" s="6"/>
+      <c r="O217" s="6"/>
+      <c r="P217" s="6"/>
+      <c r="Q217" s="6"/>
+      <c r="R217" s="6"/>
+      <c r="S217" s="6"/>
+      <c r="T217" s="6"/>
+      <c r="U217" s="6"/>
+      <c r="V217" s="6"/>
+      <c r="W217" s="6"/>
+      <c r="X217" s="6"/>
+      <c r="Y217" s="6"/>
+      <c r="Z217" s="6"/>
+      <c r="AA217" s="6"/>
+      <c r="AB217" s="6"/>
+      <c r="AC217" s="6"/>
+      <c r="AD217" s="6"/>
+      <c r="AE217" s="6"/>
+      <c r="AF217" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE97603-A5C3-4271-951A-6B91FEF1BAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBF2523-B246-4AA1-AD38-80CDB183820F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,18 +446,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -472,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -488,7 +482,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,7 +1605,7 @@
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C10">
@@ -1669,7 +1662,7 @@
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11">
@@ -1707,7 +1700,7 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12">
@@ -1758,7 +1751,7 @@
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13">
@@ -1799,7 +1792,7 @@
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14">
@@ -1812,7 +1805,8 @@
         <v>240.7</v>
       </c>
       <c r="F14" s="5">
-        <v>231.85</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]</f>
+        <v>159.47499999999999</v>
       </c>
       <c r="I14">
         <v>589</v>
@@ -1825,7 +1819,8 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="8">
-        <v>231.85</v>
+        <f>231.85-72.375</f>
+        <v>159.47499999999999</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -1848,7 +1843,7 @@
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15">
@@ -1891,7 +1886,7 @@
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16">
@@ -1904,7 +1899,8 @@
         <v>0</v>
       </c>
       <c r="F16" s="5">
-        <v>367.71</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]</f>
+        <v>295.33500000000004</v>
       </c>
       <c r="I16">
         <v>614</v>
@@ -1917,7 +1913,8 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="8">
-        <v>132.27000000000001</v>
+        <f>132.27-72.375</f>
+        <v>59.89500000000001</v>
       </c>
       <c r="Q16" s="8">
         <v>235.44</v>
@@ -1942,7 +1939,7 @@
       </c>
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17">
@@ -1959,9 +1956,7 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
-      <c r="Q17" s="9">
-        <v>154.93</v>
-      </c>
+      <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
@@ -1982,7 +1977,7 @@
       </c>
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18">
@@ -2031,7 +2026,7 @@
       </c>
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19">
@@ -2044,14 +2039,16 @@
         <v>754</v>
       </c>
       <c r="F19" s="5">
-        <v>445.46</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]+tb_base_dash_extensao[[#This Row],[produção Dezembro 2025]]</f>
+        <v>373.08500000000004</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6">
-        <v>242.97</v>
+        <f>242.97-72.375</f>
+        <v>170.595</v>
       </c>
       <c r="Q19" s="6">
         <v>148.49</v>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBF2523-B246-4AA1-AD38-80CDB183820F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0181AE7C-595D-4014-9D5E-707E2A20A0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9051,6 +9051,9 @@
       <c r="D192" t="s">
         <v>6</v>
       </c>
+      <c r="F192" s="5">
+        <v>78.19</v>
+      </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
       <c r="N192" s="6"/>
@@ -9064,7 +9067,9 @@
       <c r="V192" s="6"/>
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
-      <c r="Y192" s="6"/>
+      <c r="Y192" s="6">
+        <v>78.19</v>
+      </c>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>
       <c r="AB192" s="6"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0181AE7C-595D-4014-9D5E-707E2A20A0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC3DEE-9F23-4662-862F-278B02A0DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="121">
   <si>
     <t>Obra</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>CT LAGEADO MONTANTE</t>
+  </si>
+  <si>
+    <t>concuido</t>
   </si>
 </sst>
 </file>
@@ -7286,7 +7289,9 @@
       <c r="V145" s="6"/>
       <c r="W145" s="6"/>
       <c r="X145" s="6"/>
-      <c r="Y145" s="6"/>
+      <c r="Y145" s="6">
+        <v>42</v>
+      </c>
       <c r="Z145" s="6"/>
       <c r="AA145" s="6"/>
       <c r="AB145" s="6"/>
@@ -7700,7 +7705,7 @@
       <c r="AE156" s="6"/>
       <c r="AF156" s="6"/>
       <c r="AG156" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="2:33" x14ac:dyDescent="0.3">

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC3DEE-9F23-4662-862F-278B02A0DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21062300-F63A-41E9-91D4-9236807A7D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -9057,7 +9057,7 @@
         <v>6</v>
       </c>
       <c r="F192" s="5">
-        <v>78.19</v>
+        <v>158.69999999999999</v>
       </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
@@ -9073,7 +9073,8 @@
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
       <c r="Y192" s="6">
-        <v>78.19</v>
+        <f>78.19+80.53</f>
+        <v>158.72</v>
       </c>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21062300-F63A-41E9-91D4-9236807A7D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5E3A9A-5019-4D99-8281-814FC022FA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="121">
   <si>
     <t>Obra</t>
   </si>
@@ -9491,6 +9491,9 @@
       <c r="AD204" s="6"/>
       <c r="AE204" s="6"/>
       <c r="AF204" s="6"/>
+      <c r="AG204" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
@@ -9526,6 +9529,9 @@
       <c r="AD205" s="6"/>
       <c r="AE205" s="6"/>
       <c r="AF205" s="6"/>
+      <c r="AG205" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B206" s="5" t="s">

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5E3A9A-5019-4D99-8281-814FC022FA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA6F4DA-0E96-4337-9D01-E8E0A6C3B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7272,7 +7272,7 @@
         <v>1799.2</v>
       </c>
       <c r="F145" s="5">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
@@ -7290,7 +7290,7 @@
       <c r="W145" s="6"/>
       <c r="X145" s="6"/>
       <c r="Y145" s="6">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="Z145" s="6"/>
       <c r="AA145" s="6"/>
@@ -7743,7 +7743,9 @@
       <c r="X157" s="6">
         <v>8.81</v>
       </c>
-      <c r="Y157" s="6"/>
+      <c r="Y157" s="6">
+        <v>70.84</v>
+      </c>
       <c r="Z157" s="6"/>
       <c r="AA157" s="6"/>
       <c r="AB157" s="6"/>
@@ -7752,7 +7754,7 @@
       <c r="AE157" s="6"/>
       <c r="AF157" s="6"/>
       <c r="AG157" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158" spans="2:33" x14ac:dyDescent="0.3">
@@ -7810,7 +7812,7 @@
       <c r="AE158" s="6"/>
       <c r="AF158" s="6"/>
       <c r="AG158" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" spans="2:33" x14ac:dyDescent="0.3">
@@ -7844,7 +7846,10 @@
         <v>65.599999999999994</v>
       </c>
       <c r="X159" s="6"/>
-      <c r="Y159" s="6"/>
+      <c r="Y159" s="6">
+        <f>14.84+38.87+23.3</f>
+        <v>77.009999999999991</v>
+      </c>
       <c r="Z159" s="6"/>
       <c r="AA159" s="6"/>
       <c r="AB159" s="6"/>
@@ -7853,7 +7858,7 @@
       <c r="AE159" s="6"/>
       <c r="AF159" s="6"/>
       <c r="AG159" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="160" spans="2:33" x14ac:dyDescent="0.3">
@@ -7902,7 +7907,7 @@
       <c r="AE160" s="6"/>
       <c r="AF160" s="6"/>
       <c r="AG160" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="2:33" x14ac:dyDescent="0.3">
@@ -7945,7 +7950,7 @@
       <c r="AE161" s="6"/>
       <c r="AF161" s="6"/>
       <c r="AG161" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="2:33" x14ac:dyDescent="0.3">
@@ -8131,7 +8136,7 @@
       <c r="AE166" s="6"/>
       <c r="AF166" s="6"/>
       <c r="AG166" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="167" spans="2:33" x14ac:dyDescent="0.3">
@@ -8169,7 +8174,7 @@
       <c r="AE167" s="6"/>
       <c r="AF167" s="6"/>
       <c r="AG167" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="168" spans="2:33" x14ac:dyDescent="0.3">
@@ -8218,7 +8223,7 @@
       <c r="AE168" s="6"/>
       <c r="AF168" s="6"/>
       <c r="AG168" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="169" spans="2:33" x14ac:dyDescent="0.3">
@@ -8250,8 +8255,7 @@
       <c r="V169" s="6"/>
       <c r="W169" s="6"/>
       <c r="X169" s="6">
-        <f>11.35+17.44+12.11</f>
-        <v>40.9</v>
+        <v>47.56</v>
       </c>
       <c r="Y169" s="6"/>
       <c r="Z169" s="6"/>
@@ -8262,7 +8266,7 @@
       <c r="AE169" s="6"/>
       <c r="AF169" s="6"/>
       <c r="AG169" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="170" spans="2:33" x14ac:dyDescent="0.3">

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3201084-D6CB-45F5-AA24-265FB3B68E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD3C055-8608-4998-951C-58DFEC9569E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3267,7 +3267,9 @@
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
       <c r="X52" s="6"/>
-      <c r="Y52" s="6"/>
+      <c r="Y52" s="6">
+        <v>84.32</v>
+      </c>
       <c r="Z52" s="6"/>
       <c r="AA52" s="6"/>
       <c r="AB52" s="6"/>
@@ -9061,7 +9063,7 @@
         <v>6</v>
       </c>
       <c r="F192" s="5">
-        <v>268.02</v>
+        <v>311.68</v>
       </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
@@ -9077,7 +9079,7 @@
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
       <c r="Y192" s="6">
-        <v>268.02</v>
+        <v>311.68</v>
       </c>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD3C055-8608-4998-951C-58DFEC9569E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A90316-FFBD-4D44-B0A1-166DCDFF080B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,8 +36,36 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={429CB96A-1805-453F-B69D-EC0F1A12A00B}</author>
+    <author>tc={201ADE89-8424-4DD4-992A-B9E2A82C0E0F}</author>
+  </authors>
+  <commentList>
+    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{429CB96A-1805-453F-B69D-EC0F1A12A00B}">
+      <text>
+        <t xml:space="preserve">[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
+    Rever estensão em hdd que parece ser 1882,03
+</t>
+      </text>
+    </comment>
+    <comment ref="F133" authorId="1" shapeId="0" xr:uid="{201ADE89-8424-4DD4-992A-B9E2A82C0E0F}">
+      <text>
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
+    Conferir com o shape</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="122">
   <si>
     <t>Obra</t>
   </si>
@@ -400,13 +428,16 @@
   </si>
   <si>
     <t>concuido</t>
+  </si>
+  <si>
+    <t>CTS JD. LOURDES COMPLEMENTAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +479,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -469,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -485,6 +530,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,11 +848,17 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Cleulton Marcio Goncalves Freire" id="{9E65CB53-CCE2-40D8-8BFA-050DD8402F0F}" userId="S::cleulton.freire@integra6a.com::e0f6aed5-31ce-4d5d-9517-339b08a096f1" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF217">
-  <autoFilter ref="B1:AF217" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF217">
-    <sortCondition ref="C1:C217"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
+  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF218">
+    <sortCondition ref="C1:C218"/>
   </sortState>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Obra"/>
@@ -1128,13 +1180,25 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F69" dT="2026-05-20T16:25:44.73" personId="{9E65CB53-CCE2-40D8-8BFA-050DD8402F0F}" id="{429CB96A-1805-453F-B69D-EC0F1A12A00B}">
+    <text xml:space="preserve">Rever estensão em hdd que parece ser 1882,03
+</text>
+  </threadedComment>
+  <threadedComment ref="F133" dT="2026-05-20T18:24:26.57" personId="{9E65CB53-CCE2-40D8-8BFA-050DD8402F0F}" id="{201ADE89-8424-4DD4-992A-B9E2A82C0E0F}">
+    <text>Conferir com o shape</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG217"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AG218"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
@@ -1266,14 +1330,14 @@
         <v>156.30000000000001</v>
       </c>
       <c r="F2" s="5">
-        <v>162.59</v>
+        <v>150.44999999999999</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="8">
-        <v>162.59</v>
+        <v>150.44999999999999</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
@@ -1312,11 +1376,11 @@
         <v>37.4</v>
       </c>
       <c r="F3" s="5">
-        <v>6.19</v>
+        <v>27</v>
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="8">
-        <v>6.19</v>
+        <v>27</v>
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
@@ -2088,7 +2152,7 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>971</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
         <v>192.04</v>
@@ -2143,7 +2207,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>262</v>
+        <v>44.2</v>
       </c>
       <c r="F21" s="5">
         <v>19.91</v>
@@ -2186,7 +2250,7 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>155.4</v>
+        <v>291.8</v>
       </c>
       <c r="F22" s="5">
         <v>259.3</v>
@@ -2235,7 +2299,7 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>132.69999999999999</v>
+        <v>208.6</v>
       </c>
       <c r="F23" s="5">
         <v>39.75</v>
@@ -2750,16 +2814,13 @@
     </row>
     <row r="38" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38">
-        <v>13</v>
+        <v>96</v>
+      </c>
+      <c r="C38" s="1">
+        <v>12</v>
       </c>
       <c r="D38" t="s">
         <v>6</v>
-      </c>
-      <c r="I38">
-        <v>11130</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
@@ -2785,13 +2846,16 @@
     </row>
     <row r="39" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39">
-        <v>13</v>
+        <v>96</v>
+      </c>
+      <c r="C39" s="1">
+        <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
+      </c>
+      <c r="E39">
+        <v>205</v>
       </c>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
@@ -2817,7 +2881,7 @@
     </row>
     <row r="40" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40">
         <v>13</v>
@@ -2825,8 +2889,8 @@
       <c r="D40" t="s">
         <v>6</v>
       </c>
-      <c r="E40">
-        <v>1787.905</v>
+      <c r="I40">
+        <v>11130</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -2852,7 +2916,7 @@
     </row>
     <row r="41" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41">
         <v>13</v>
@@ -2884,7 +2948,7 @@
     </row>
     <row r="42" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="C42">
         <v>13</v>
@@ -2893,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="E42">
-        <v>1583.28</v>
+        <v>1787.905</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -2919,7 +2983,7 @@
     </row>
     <row r="43" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="C43">
         <v>13</v>
@@ -2951,7 +3015,7 @@
     </row>
     <row r="44" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C44">
         <v>13</v>
@@ -2960,7 +3024,7 @@
         <v>6</v>
       </c>
       <c r="E44">
-        <v>699.23500000000001</v>
+        <v>1583.28</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
@@ -2986,16 +3050,13 @@
     </row>
     <row r="45" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C45">
         <v>13</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
-      </c>
-      <c r="E45">
-        <v>166.2</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -3021,7 +3082,7 @@
     </row>
     <row r="46" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46">
         <v>13</v>
@@ -3030,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="E46">
-        <v>820.2</v>
+        <v>699.23500000000001</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -3056,7 +3117,7 @@
     </row>
     <row r="47" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47">
         <v>13</v>
@@ -3065,7 +3126,7 @@
         <v>7</v>
       </c>
       <c r="E47">
-        <v>191.4</v>
+        <v>166.2</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
@@ -3091,7 +3152,7 @@
     </row>
     <row r="48" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C48">
         <v>13</v>
@@ -3100,7 +3161,7 @@
         <v>6</v>
       </c>
       <c r="E48">
-        <v>165</v>
+        <v>820.2</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
@@ -3126,7 +3187,7 @@
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C49">
         <v>13</v>
@@ -3135,7 +3196,7 @@
         <v>7</v>
       </c>
       <c r="E49">
-        <v>43.5</v>
+        <v>191.4</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
@@ -3161,13 +3222,16 @@
     </row>
     <row r="50" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50">
         <v>13</v>
       </c>
       <c r="D50" t="s">
         <v>6</v>
+      </c>
+      <c r="E50">
+        <v>165</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
@@ -3193,7 +3257,7 @@
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51">
         <v>13</v>
@@ -3202,9 +3266,8 @@
         <v>7</v>
       </c>
       <c r="E51">
-        <v>201.5</v>
-      </c>
-      <c r="K51" s="4"/>
+        <v>43.5</v>
+      </c>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
@@ -3228,48 +3291,29 @@
       <c r="AF51" s="6"/>
     </row>
     <row r="52" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B52" s="5" t="s">
-        <v>10</v>
+      <c r="B52" t="s">
+        <v>37</v>
       </c>
       <c r="C52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
       </c>
-      <c r="E52">
-        <v>267</v>
-      </c>
-      <c r="F52" s="5">
-        <v>400</v>
-      </c>
-      <c r="I52">
-        <v>41</v>
-      </c>
-      <c r="J52">
-        <v>39</v>
-      </c>
-      <c r="K52" s="4"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
       <c r="Q52" s="6"/>
-      <c r="R52" s="6">
-        <v>75</v>
-      </c>
-      <c r="S52" s="6">
-        <v>325</v>
-      </c>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
       <c r="X52" s="6"/>
-      <c r="Y52" s="6">
-        <v>84.32</v>
-      </c>
+      <c r="Y52" s="6"/>
       <c r="Z52" s="6"/>
       <c r="AA52" s="6"/>
       <c r="AB52" s="6"/>
@@ -3278,24 +3322,21 @@
       <c r="AE52" s="6"/>
       <c r="AF52" s="6"/>
       <c r="AG52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B53" s="5" t="s">
-        <v>10</v>
+      <c r="B53" t="s">
+        <v>37</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
       </c>
       <c r="E53">
-        <v>233.1</v>
-      </c>
-      <c r="F53" s="5">
-        <v>0</v>
+        <v>201.5</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="6"/>
@@ -3325,10 +3366,10 @@
     </row>
     <row r="54" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B54" s="5" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="C54">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
@@ -3336,14 +3377,8 @@
       <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54" s="5">
-        <v>157.69999999999999</v>
-      </c>
-      <c r="I54">
-        <v>464</v>
-      </c>
-      <c r="J54">
-        <v>523</v>
+      <c r="F54">
+        <v>84.32</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="6"/>
@@ -3354,16 +3389,14 @@
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
-      <c r="T54" s="6">
-        <v>35</v>
-      </c>
-      <c r="U54" s="6">
-        <v>122.7</v>
-      </c>
+      <c r="T54" s="6"/>
+      <c r="U54" s="6"/>
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
       <c r="X54" s="6"/>
-      <c r="Y54" s="6"/>
+      <c r="Y54" s="6">
+        <v>84.32</v>
+      </c>
       <c r="Z54" s="6"/>
       <c r="AA54" s="6"/>
       <c r="AB54" s="6"/>
@@ -3380,16 +3413,22 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55">
-        <v>243.8</v>
+        <v>267</v>
       </c>
       <c r="F55" s="5">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="I55">
+        <v>41</v>
+      </c>
+      <c r="J55">
+        <v>39</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="6"/>
@@ -3398,8 +3437,12 @@
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
       <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
+      <c r="R55" s="6">
+        <v>75</v>
+      </c>
+      <c r="S55" s="6">
+        <v>325</v>
+      </c>
       <c r="T55" s="6"/>
       <c r="U55" s="6"/>
       <c r="V55" s="6"/>
@@ -3422,22 +3465,16 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E56">
+        <v>233.1</v>
+      </c>
+      <c r="F56" s="5">
         <v>0</v>
-      </c>
-      <c r="F56" s="5">
-        <v>341.71499999999997</v>
-      </c>
-      <c r="I56">
-        <v>2139</v>
-      </c>
-      <c r="J56">
-        <v>2126</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="6"/>
@@ -3447,12 +3484,8 @@
       <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
-      <c r="S56" s="6">
-        <v>220</v>
-      </c>
-      <c r="T56" s="6">
-        <v>121.715</v>
-      </c>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
       <c r="U56" s="6"/>
       <c r="V56" s="6"/>
       <c r="W56" s="6"/>
@@ -3474,16 +3507,22 @@
         <v>10</v>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57">
-        <v>276.10000000000002</v>
+        <v>0</v>
       </c>
       <c r="F57" s="5">
-        <v>13.17</v>
+        <v>157.69999999999999</v>
+      </c>
+      <c r="I57">
+        <v>464</v>
+      </c>
+      <c r="J57">
+        <v>523</v>
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="6"/>
@@ -3495,9 +3534,11 @@
       <c r="R57" s="6"/>
       <c r="S57" s="6"/>
       <c r="T57" s="6">
-        <v>13.17</v>
-      </c>
-      <c r="U57" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="U57" s="6">
+        <v>122.7</v>
+      </c>
       <c r="V57" s="6"/>
       <c r="W57" s="6"/>
       <c r="X57" s="6"/>
@@ -3518,19 +3559,16 @@
         <v>10</v>
       </c>
       <c r="C58">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E58">
+        <v>243.8</v>
       </c>
       <c r="F58" s="5">
-        <v>43.015000000000001</v>
-      </c>
-      <c r="I58">
-        <v>208</v>
-      </c>
-      <c r="J58">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="6"/>
@@ -3541,9 +3579,7 @@
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
-      <c r="T58" s="6">
-        <v>43.015000000000001</v>
-      </c>
+      <c r="T58" s="6"/>
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
@@ -3565,16 +3601,22 @@
         <v>10</v>
       </c>
       <c r="C59">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E59">
-        <v>83.2</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5">
-        <v>51.05</v>
+        <v>341.71499999999997</v>
+      </c>
+      <c r="I59">
+        <v>2139</v>
+      </c>
+      <c r="J59">
+        <v>2126</v>
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="6"/>
@@ -3585,9 +3627,11 @@
       <c r="Q59" s="6"/>
       <c r="R59" s="6"/>
       <c r="S59" s="6">
-        <v>51.05</v>
-      </c>
-      <c r="T59" s="6"/>
+        <v>220</v>
+      </c>
+      <c r="T59" s="6">
+        <v>121.715</v>
+      </c>
       <c r="U59" s="6"/>
       <c r="V59" s="6"/>
       <c r="W59" s="6"/>
@@ -3606,31 +3650,19 @@
     </row>
     <row r="60" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B60" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C60">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60">
-        <v>65.5</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="F60" s="5">
-        <v>288.26</v>
-      </c>
-      <c r="G60">
-        <v>17</v>
-      </c>
-      <c r="H60">
-        <v>51.09</v>
-      </c>
-      <c r="I60">
-        <v>139</v>
-      </c>
-      <c r="J60">
-        <v>109</v>
+        <v>13.17</v>
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="6"/>
@@ -3638,12 +3670,12 @@
       <c r="N60" s="6"/>
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
-      <c r="Q60" s="6">
-        <v>288.26</v>
-      </c>
+      <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
+      <c r="T60" s="6">
+        <v>13.17</v>
+      </c>
       <c r="U60" s="6"/>
       <c r="V60" s="6"/>
       <c r="W60" s="6"/>
@@ -3662,19 +3694,22 @@
     </row>
     <row r="61" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B61" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C61">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61">
-        <v>245.5</v>
+        <v>6</v>
       </c>
       <c r="F61" s="5">
-        <v>32.85</v>
+        <v>43.02</v>
+      </c>
+      <c r="I61">
+        <v>208</v>
+      </c>
+      <c r="J61">
+        <v>191</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="6"/>
@@ -3682,12 +3717,12 @@
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
-      <c r="Q61" s="6">
-        <v>32.85</v>
-      </c>
+      <c r="Q61" s="6"/>
       <c r="R61" s="6"/>
       <c r="S61" s="6"/>
-      <c r="T61" s="6"/>
+      <c r="T61" s="6">
+        <v>43.015000000000001</v>
+      </c>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
       <c r="W61" s="6"/>
@@ -3706,25 +3741,19 @@
     </row>
     <row r="62" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E62">
-        <v>412</v>
+        <v>83.2</v>
       </c>
       <c r="F62" s="5">
-        <v>223.29</v>
-      </c>
-      <c r="I62">
-        <v>219</v>
-      </c>
-      <c r="J62">
-        <v>188</v>
+        <v>51.05</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="6"/>
@@ -3733,10 +3762,10 @@
       <c r="O62" s="6"/>
       <c r="P62" s="6"/>
       <c r="Q62" s="6"/>
-      <c r="R62" s="6">
-        <v>223.29</v>
-      </c>
-      <c r="S62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6">
+        <v>51.05</v>
+      </c>
       <c r="T62" s="6"/>
       <c r="U62" s="6"/>
       <c r="V62" s="6"/>
@@ -3759,16 +3788,28 @@
         <v>9</v>
       </c>
       <c r="C63">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63">
-        <v>95.7</v>
+        <v>65.5</v>
       </c>
       <c r="F63" s="5">
-        <v>26.66</v>
+        <v>288.26</v>
+      </c>
+      <c r="G63">
+        <v>17</v>
+      </c>
+      <c r="H63">
+        <v>51.09</v>
+      </c>
+      <c r="I63">
+        <v>139</v>
+      </c>
+      <c r="J63">
+        <v>109</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="6"/>
@@ -3777,7 +3818,7 @@
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
       <c r="Q63" s="6">
-        <v>26.66</v>
+        <v>288.26</v>
       </c>
       <c r="R63" s="6"/>
       <c r="S63" s="6"/>
@@ -3803,22 +3844,16 @@
         <v>9</v>
       </c>
       <c r="C64">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E64">
-        <v>163.4</v>
+        <v>226.5</v>
       </c>
       <c r="F64" s="5">
-        <v>159.63</v>
-      </c>
-      <c r="I64">
-        <v>848</v>
-      </c>
-      <c r="J64">
-        <v>860</v>
+        <v>32.85</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="6"/>
@@ -3826,14 +3861,12 @@
       <c r="N64" s="6"/>
       <c r="O64" s="6"/>
       <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
+      <c r="Q64" s="6">
+        <v>32.85</v>
+      </c>
       <c r="R64" s="6"/>
-      <c r="S64" s="6">
-        <v>59.73</v>
-      </c>
-      <c r="T64" s="6">
-        <v>99.9</v>
-      </c>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
       <c r="U64" s="6"/>
       <c r="V64" s="6"/>
       <c r="W64" s="6"/>
@@ -3855,16 +3888,22 @@
         <v>9</v>
       </c>
       <c r="C65">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E65">
-        <v>24</v>
+        <v>366.4</v>
       </c>
       <c r="F65" s="5">
-        <v>31.4</v>
+        <v>223.29</v>
+      </c>
+      <c r="I65">
+        <v>219</v>
+      </c>
+      <c r="J65">
+        <v>188</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="6"/>
@@ -3872,10 +3911,10 @@
       <c r="N65" s="6"/>
       <c r="O65" s="6"/>
       <c r="P65" s="6"/>
-      <c r="Q65" s="6">
-        <v>31.4</v>
-      </c>
-      <c r="R65" s="6"/>
+      <c r="Q65" s="6"/>
+      <c r="R65" s="6">
+        <v>223.29</v>
+      </c>
       <c r="S65" s="6"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
@@ -3896,50 +3935,30 @@
     </row>
     <row r="66" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B66" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C66">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>475.4</v>
+        <v>95.7</v>
       </c>
       <c r="F66" s="5">
-        <v>1229.95</v>
-      </c>
-      <c r="G66">
-        <v>19</v>
-      </c>
-      <c r="H66">
-        <v>92.92</v>
-      </c>
-      <c r="I66">
-        <v>78</v>
-      </c>
-      <c r="J66">
-        <v>72</v>
+        <v>26.66</v>
       </c>
       <c r="K66" s="4"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="6">
-        <v>68</v>
-      </c>
-      <c r="O66" s="6">
-        <v>621.84500000000003</v>
-      </c>
-      <c r="P66" s="6">
-        <v>354.52499999999998</v>
-      </c>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
       <c r="Q66" s="6">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="R66" s="6">
-        <v>117.68</v>
-      </c>
+        <v>26.66</v>
+      </c>
+      <c r="R66" s="6"/>
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
       <c r="U66" s="6"/>
@@ -3960,19 +3979,25 @@
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B67" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C67">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>771.1</v>
+        <v>163.4</v>
       </c>
       <c r="F67" s="5">
-        <v>0</v>
+        <v>159.63</v>
+      </c>
+      <c r="I67">
+        <v>848</v>
+      </c>
+      <c r="J67">
+        <v>860</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="6"/>
@@ -3982,8 +4007,12 @@
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
       <c r="R67" s="6"/>
-      <c r="S67" s="6"/>
-      <c r="T67" s="6"/>
+      <c r="S67" s="6">
+        <v>59.73</v>
+      </c>
+      <c r="T67" s="6">
+        <v>99.9</v>
+      </c>
       <c r="U67" s="6"/>
       <c r="V67" s="6"/>
       <c r="W67" s="6"/>
@@ -4002,41 +4031,29 @@
     </row>
     <row r="68" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B68" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C68">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68">
-        <v>59.5</v>
+        <v>24</v>
       </c>
       <c r="F68" s="5">
-        <v>328.75</v>
-      </c>
-      <c r="G68">
-        <v>6</v>
-      </c>
-      <c r="H68">
-        <v>16.16</v>
-      </c>
-      <c r="I68">
-        <v>471</v>
-      </c>
-      <c r="J68">
-        <v>338</v>
+        <v>31.4</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
-      <c r="P68" s="6">
-        <v>328.75</v>
-      </c>
-      <c r="Q68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6">
+        <v>31.4</v>
+      </c>
       <c r="R68" s="6"/>
       <c r="S68" s="6"/>
       <c r="T68" s="6"/>
@@ -4061,25 +4078,48 @@
         <v>5</v>
       </c>
       <c r="C69">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E69">
-        <v>216</v>
-      </c>
-      <c r="F69" s="5">
-        <v>0</v>
+        <f>475.4-8.8</f>
+        <v>466.59999999999997</v>
+      </c>
+      <c r="F69" s="9">
+        <v>1229.95</v>
+      </c>
+      <c r="G69">
+        <v>19</v>
+      </c>
+      <c r="H69">
+        <v>92.92</v>
+      </c>
+      <c r="I69">
+        <v>78</v>
+      </c>
+      <c r="J69">
+        <v>72</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="6"/>
+      <c r="N69" s="6">
+        <v>68</v>
+      </c>
+      <c r="O69" s="6">
+        <v>621.84500000000003</v>
+      </c>
+      <c r="P69" s="6">
+        <v>354.52499999999998</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="R69" s="6">
+        <v>117.68</v>
+      </c>
       <c r="S69" s="6"/>
       <c r="T69" s="6"/>
       <c r="U69" s="6"/>
@@ -4103,40 +4143,25 @@
         <v>5</v>
       </c>
       <c r="C70">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70">
-        <v>352.8</v>
+        <f>12.3+771.1</f>
+        <v>783.4</v>
       </c>
       <c r="F70" s="5">
-        <v>384.67</v>
-      </c>
-      <c r="G70">
-        <v>7</v>
-      </c>
-      <c r="H70">
-        <v>24.74</v>
-      </c>
-      <c r="I70">
-        <v>987</v>
-      </c>
-      <c r="J70">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
       <c r="O70" s="6"/>
-      <c r="P70" s="6">
-        <v>247.93</v>
-      </c>
-      <c r="Q70" s="6">
-        <v>136.74</v>
-      </c>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
       <c r="T70" s="6"/>
@@ -4161,26 +4186,38 @@
         <v>5</v>
       </c>
       <c r="C71">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71">
-        <v>254.9</v>
-      </c>
-      <c r="F71" s="5">
-        <v>20.32</v>
+        <v>59.5</v>
+      </c>
+      <c r="F71" s="9">
+        <v>328.75</v>
+      </c>
+      <c r="G71">
+        <v>6</v>
+      </c>
+      <c r="H71">
+        <v>16.16</v>
+      </c>
+      <c r="I71">
+        <v>471</v>
+      </c>
+      <c r="J71">
+        <v>338</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
       <c r="O71" s="6"/>
-      <c r="P71" s="6"/>
-      <c r="Q71" s="6">
-        <v>20.32</v>
-      </c>
+      <c r="P71" s="6">
+        <v>328.75</v>
+      </c>
+      <c r="Q71" s="6"/>
       <c r="R71" s="6"/>
       <c r="S71" s="6"/>
       <c r="T71" s="6"/>
@@ -4202,22 +4239,19 @@
     </row>
     <row r="72" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B72" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C72">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72">
-        <v>207.5</v>
+        <v>216</v>
       </c>
       <c r="F72" s="5">
-        <v>197.8</v>
-      </c>
-      <c r="I72">
-        <v>1801</v>
+        <v>0</v>
       </c>
       <c r="K72" s="4"/>
       <c r="L72" s="6"/>
@@ -4232,9 +4266,7 @@
       <c r="U72" s="6"/>
       <c r="V72" s="6"/>
       <c r="W72" s="6"/>
-      <c r="X72" s="6">
-        <v>197.8</v>
-      </c>
+      <c r="X72" s="6"/>
       <c r="Y72" s="6"/>
       <c r="Z72" s="6"/>
       <c r="AA72" s="6"/>
@@ -4249,37 +4281,50 @@
     </row>
     <row r="73" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B73" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C73">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73">
-        <v>95</v>
-      </c>
-      <c r="F73" s="5">
-        <v>10.73</v>
+        <v>352.8</v>
+      </c>
+      <c r="F73" s="9">
+        <v>384.67</v>
+      </c>
+      <c r="G73">
+        <v>7</v>
+      </c>
+      <c r="H73">
+        <v>24.74</v>
+      </c>
+      <c r="I73">
+        <v>987</v>
+      </c>
+      <c r="J73">
+        <v>901</v>
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
       <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
+      <c r="P73" s="6">
+        <v>247.93</v>
+      </c>
+      <c r="Q73" s="6">
+        <v>136.74</v>
+      </c>
       <c r="R73" s="6"/>
       <c r="S73" s="6"/>
       <c r="T73" s="6"/>
       <c r="U73" s="6"/>
       <c r="V73" s="6"/>
       <c r="W73" s="6"/>
-      <c r="X73" s="6">
-        <f>6.22+4.51</f>
-        <v>10.73</v>
-      </c>
+      <c r="X73" s="6"/>
       <c r="Y73" s="6"/>
       <c r="Z73" s="6"/>
       <c r="AA73" s="6"/>
@@ -4294,22 +4339,19 @@
     </row>
     <row r="74" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B74" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C74">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74">
-        <v>315.5</v>
+        <v>254.9</v>
       </c>
       <c r="F74" s="5">
-        <v>545.34</v>
-      </c>
-      <c r="I74">
-        <v>168</v>
+        <v>20.32</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="6"/>
@@ -4317,15 +4359,15 @@
       <c r="N74" s="6"/>
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
-      <c r="Q74" s="6"/>
+      <c r="Q74" s="6">
+        <v>20.32</v>
+      </c>
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
       <c r="T74" s="6"/>
       <c r="U74" s="6"/>
       <c r="V74" s="6"/>
-      <c r="W74" s="6">
-        <v>545.34</v>
-      </c>
+      <c r="W74" s="6"/>
       <c r="X74" s="6"/>
       <c r="Y74" s="6"/>
       <c r="Z74" s="6"/>
@@ -4344,16 +4386,19 @@
         <v>12</v>
       </c>
       <c r="C75">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75">
-        <v>194.5</v>
+        <v>207.5</v>
       </c>
       <c r="F75" s="5">
-        <v>12.02</v>
+        <v>197.8</v>
+      </c>
+      <c r="I75">
+        <v>1801</v>
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="6"/>
@@ -4367,10 +4412,10 @@
       <c r="T75" s="6"/>
       <c r="U75" s="6"/>
       <c r="V75" s="6"/>
-      <c r="W75" s="6">
-        <v>12.02</v>
-      </c>
-      <c r="X75" s="6"/>
+      <c r="W75" s="6"/>
+      <c r="X75" s="6">
+        <v>197.8</v>
+      </c>
       <c r="Y75" s="6"/>
       <c r="Z75" s="6"/>
       <c r="AA75" s="6"/>
@@ -4385,26 +4430,21 @@
     </row>
     <row r="76" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B76" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C76">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D76" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E76">
-        <v>31.9</v>
+        <v>95</v>
       </c>
       <c r="F76" s="5">
-        <v>384.37</v>
-      </c>
-      <c r="I76">
-        <v>1302</v>
-      </c>
-      <c r="J76">
-        <v>1152</v>
-      </c>
+        <v>10.73</v>
+      </c>
+      <c r="K76" s="4"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
@@ -4414,12 +4454,13 @@
       <c r="R76" s="6"/>
       <c r="S76" s="6"/>
       <c r="T76" s="6"/>
-      <c r="U76" s="6">
-        <v>384.37</v>
-      </c>
+      <c r="U76" s="6"/>
       <c r="V76" s="6"/>
       <c r="W76" s="6"/>
-      <c r="X76" s="6"/>
+      <c r="X76" s="6">
+        <f>6.22+4.51</f>
+        <v>10.73</v>
+      </c>
       <c r="Y76" s="6"/>
       <c r="Z76" s="6"/>
       <c r="AA76" s="6"/>
@@ -4434,20 +4475,24 @@
     </row>
     <row r="77" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B77" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C77">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E77">
-        <v>600.73</v>
+        <v>315.5</v>
       </c>
       <c r="F77" s="5">
-        <v>23.8</v>
-      </c>
+        <v>545.34</v>
+      </c>
+      <c r="I77">
+        <v>168</v>
+      </c>
+      <c r="K77" s="4"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
@@ -4457,11 +4502,11 @@
       <c r="R77" s="6"/>
       <c r="S77" s="6"/>
       <c r="T77" s="6"/>
-      <c r="U77" s="6">
-        <v>23.8</v>
-      </c>
+      <c r="U77" s="6"/>
       <c r="V77" s="6"/>
-      <c r="W77" s="6"/>
+      <c r="W77" s="6">
+        <v>545.34</v>
+      </c>
       <c r="X77" s="6"/>
       <c r="Y77" s="6"/>
       <c r="Z77" s="6"/>
@@ -4477,20 +4522,21 @@
     </row>
     <row r="78" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B78" s="5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C78">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E78">
+        <v>194.5</v>
       </c>
       <c r="F78" s="5">
-        <v>91.21</v>
-      </c>
-      <c r="I78">
-        <v>2885</v>
-      </c>
+        <v>12.02</v>
+      </c>
+      <c r="K78" s="4"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
@@ -4501,13 +4547,11 @@
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
       <c r="U78" s="6"/>
-      <c r="V78" s="6">
-        <v>20.95</v>
-      </c>
-      <c r="W78" s="6"/>
-      <c r="X78" s="6">
-        <v>70.260000000000005</v>
-      </c>
+      <c r="V78" s="6"/>
+      <c r="W78" s="6">
+        <v>12.02</v>
+      </c>
+      <c r="X78" s="6"/>
       <c r="Y78" s="6"/>
       <c r="Z78" s="6"/>
       <c r="AA78" s="6"/>
@@ -4522,19 +4566,25 @@
     </row>
     <row r="79" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B79" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C79">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E79">
-        <v>100.5</v>
+        <v>31.9</v>
       </c>
       <c r="F79" s="5">
-        <v>10.06</v>
+        <v>384.37</v>
+      </c>
+      <c r="I79">
+        <v>1302</v>
+      </c>
+      <c r="J79">
+        <v>1152</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -4545,14 +4595,12 @@
       <c r="R79" s="6"/>
       <c r="S79" s="6"/>
       <c r="T79" s="6"/>
-      <c r="U79" s="6"/>
-      <c r="V79" s="6">
-        <v>8.06</v>
-      </c>
+      <c r="U79" s="6">
+        <v>384.37</v>
+      </c>
+      <c r="V79" s="6"/>
       <c r="W79" s="6"/>
-      <c r="X79" s="6">
-        <v>2</v>
-      </c>
+      <c r="X79" s="6"/>
       <c r="Y79" s="6"/>
       <c r="Z79" s="6"/>
       <c r="AA79" s="6"/>
@@ -4567,16 +4615,19 @@
     </row>
     <row r="80" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B80" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C80">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D80" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E80">
+        <v>600.73</v>
       </c>
       <c r="F80" s="5">
-        <v>230.72</v>
+        <v>23.8</v>
       </c>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
@@ -4587,14 +4638,11 @@
       <c r="R80" s="6"/>
       <c r="S80" s="6"/>
       <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
-      <c r="V80" s="6">
-        <f>230.02-55.56</f>
-        <v>174.46</v>
-      </c>
-      <c r="W80" s="6">
-        <v>56.26</v>
-      </c>
+      <c r="U80" s="6">
+        <v>23.8</v>
+      </c>
+      <c r="V80" s="6"/>
+      <c r="W80" s="6"/>
       <c r="X80" s="6"/>
       <c r="Y80" s="6"/>
       <c r="Z80" s="6"/>
@@ -4609,17 +4657,14 @@
       </c>
     </row>
     <row r="81" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B81" s="5" t="s">
-        <v>23</v>
+      <c r="B81" t="s">
+        <v>42</v>
       </c>
       <c r="C81">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81">
-        <v>210.02</v>
+        <v>6</v>
       </c>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
@@ -4647,17 +4692,17 @@
       </c>
     </row>
     <row r="82" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B82" s="5" t="s">
-        <v>23</v>
+      <c r="B82" t="s">
+        <v>42</v>
       </c>
       <c r="C82">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" s="5">
-        <v>35.5</v>
+        <v>7</v>
+      </c>
+      <c r="E82">
+        <v>220.48</v>
       </c>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
@@ -4669,9 +4714,7 @@
       <c r="S82" s="6"/>
       <c r="T82" s="6"/>
       <c r="U82" s="6"/>
-      <c r="V82" s="6">
-        <v>35.5</v>
-      </c>
+      <c r="V82" s="6"/>
       <c r="W82" s="6"/>
       <c r="X82" s="6"/>
       <c r="Y82" s="6"/>
@@ -4691,13 +4734,16 @@
         <v>23</v>
       </c>
       <c r="C83">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83">
-        <v>57.5</v>
+        <v>6</v>
+      </c>
+      <c r="F83" s="5">
+        <v>91.21</v>
+      </c>
+      <c r="I83">
+        <v>2885</v>
       </c>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
@@ -4709,9 +4755,13 @@
       <c r="S83" s="6"/>
       <c r="T83" s="6"/>
       <c r="U83" s="6"/>
-      <c r="V83" s="6"/>
+      <c r="V83" s="6">
+        <v>20.95</v>
+      </c>
       <c r="W83" s="6"/>
-      <c r="X83" s="6"/>
+      <c r="X83" s="6">
+        <v>70.260000000000005</v>
+      </c>
       <c r="Y83" s="6"/>
       <c r="Z83" s="6"/>
       <c r="AA83" s="6"/>
@@ -4729,13 +4779,16 @@
         <v>23</v>
       </c>
       <c r="C84">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E84">
+        <v>100.5</v>
       </c>
       <c r="F84" s="5">
-        <v>36.979999999999997</v>
+        <v>10.06</v>
       </c>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
@@ -4748,10 +4801,12 @@
       <c r="T84" s="6"/>
       <c r="U84" s="6"/>
       <c r="V84" s="6">
-        <v>36.979999999999997</v>
+        <v>8.06</v>
       </c>
       <c r="W84" s="6"/>
-      <c r="X84" s="6"/>
+      <c r="X84" s="6">
+        <v>2</v>
+      </c>
       <c r="Y84" s="6"/>
       <c r="Z84" s="6"/>
       <c r="AA84" s="6"/>
@@ -4769,13 +4824,13 @@
         <v>23</v>
       </c>
       <c r="C85">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85">
-        <v>56</v>
+        <v>6</v>
+      </c>
+      <c r="F85" s="5">
+        <v>230.72</v>
       </c>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
@@ -4787,8 +4842,13 @@
       <c r="S85" s="6"/>
       <c r="T85" s="6"/>
       <c r="U85" s="6"/>
-      <c r="V85" s="6"/>
-      <c r="W85" s="6"/>
+      <c r="V85" s="6">
+        <f>230.02-55.56</f>
+        <v>174.46</v>
+      </c>
+      <c r="W85" s="6">
+        <v>56.26</v>
+      </c>
       <c r="X85" s="6"/>
       <c r="Y85" s="6"/>
       <c r="Z85" s="6"/>
@@ -4807,16 +4867,13 @@
         <v>23</v>
       </c>
       <c r="C86">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D86" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" s="5">
-        <v>39.04</v>
-      </c>
-      <c r="J86">
-        <v>628</v>
+        <v>7</v>
+      </c>
+      <c r="E86">
+        <v>210.02</v>
       </c>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
@@ -4828,9 +4885,7 @@
       <c r="S86" s="6"/>
       <c r="T86" s="6"/>
       <c r="U86" s="6"/>
-      <c r="V86" s="6">
-        <v>39.04</v>
-      </c>
+      <c r="V86" s="6"/>
       <c r="W86" s="6"/>
       <c r="X86" s="6"/>
       <c r="Y86" s="6"/>
@@ -4850,13 +4905,13 @@
         <v>23</v>
       </c>
       <c r="C87">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
-      </c>
-      <c r="E87">
-        <v>39.5</v>
+        <v>6</v>
+      </c>
+      <c r="F87" s="5">
+        <v>35.5</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
@@ -4868,7 +4923,9 @@
       <c r="S87" s="6"/>
       <c r="T87" s="6"/>
       <c r="U87" s="6"/>
-      <c r="V87" s="6"/>
+      <c r="V87" s="6">
+        <v>35.5</v>
+      </c>
       <c r="W87" s="6"/>
       <c r="X87" s="6"/>
       <c r="Y87" s="6"/>
@@ -4888,13 +4945,13 @@
         <v>23</v>
       </c>
       <c r="C88">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" s="5">
-        <v>34.42</v>
+        <v>7</v>
+      </c>
+      <c r="E88">
+        <v>57.5</v>
       </c>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
@@ -4906,9 +4963,7 @@
       <c r="S88" s="6"/>
       <c r="T88" s="6"/>
       <c r="U88" s="6"/>
-      <c r="V88" s="6">
-        <v>34.42</v>
-      </c>
+      <c r="V88" s="6"/>
       <c r="W88" s="6"/>
       <c r="X88" s="6"/>
       <c r="Y88" s="6"/>
@@ -4928,13 +4983,13 @@
         <v>23</v>
       </c>
       <c r="C89">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89">
-        <v>63.5</v>
+        <v>6</v>
+      </c>
+      <c r="F89" s="5">
+        <v>36.979999999999997</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
@@ -4946,7 +5001,9 @@
       <c r="S89" s="6"/>
       <c r="T89" s="6"/>
       <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
+      <c r="V89" s="6">
+        <v>36.979999999999997</v>
+      </c>
       <c r="W89" s="6"/>
       <c r="X89" s="6"/>
       <c r="Y89" s="6"/>
@@ -4966,13 +5023,13 @@
         <v>23</v>
       </c>
       <c r="C90">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D90" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="5">
-        <v>34.119999999999997</v>
+        <v>7</v>
+      </c>
+      <c r="E90">
+        <v>56</v>
       </c>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
@@ -4984,9 +5041,7 @@
       <c r="S90" s="6"/>
       <c r="T90" s="6"/>
       <c r="U90" s="6"/>
-      <c r="V90" s="6">
-        <v>34.119999999999997</v>
-      </c>
+      <c r="V90" s="6"/>
       <c r="W90" s="6"/>
       <c r="X90" s="6"/>
       <c r="Y90" s="6"/>
@@ -5006,13 +5061,16 @@
         <v>23</v>
       </c>
       <c r="C91">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91">
-        <v>67.5</v>
+        <v>6</v>
+      </c>
+      <c r="F91" s="5">
+        <v>39.04</v>
+      </c>
+      <c r="J91">
+        <v>628</v>
       </c>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
@@ -5024,7 +5082,9 @@
       <c r="S91" s="6"/>
       <c r="T91" s="6"/>
       <c r="U91" s="6"/>
-      <c r="V91" s="6"/>
+      <c r="V91" s="6">
+        <v>39.04</v>
+      </c>
       <c r="W91" s="6"/>
       <c r="X91" s="6"/>
       <c r="Y91" s="6"/>
@@ -5044,13 +5104,13 @@
         <v>23</v>
       </c>
       <c r="C92">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>6</v>
-      </c>
-      <c r="F92" s="5">
-        <v>32.11</v>
+        <v>7</v>
+      </c>
+      <c r="E92">
+        <v>39.5</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
@@ -5062,9 +5122,7 @@
       <c r="S92" s="6"/>
       <c r="T92" s="6"/>
       <c r="U92" s="6"/>
-      <c r="V92" s="6">
-        <v>32.11</v>
-      </c>
+      <c r="V92" s="6"/>
       <c r="W92" s="6"/>
       <c r="X92" s="6"/>
       <c r="Y92" s="6"/>
@@ -5084,13 +5142,13 @@
         <v>23</v>
       </c>
       <c r="C93">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93">
-        <v>67.5</v>
+        <v>6</v>
+      </c>
+      <c r="F93" s="5">
+        <v>34.42</v>
       </c>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
@@ -5102,7 +5160,9 @@
       <c r="S93" s="6"/>
       <c r="T93" s="6"/>
       <c r="U93" s="6"/>
-      <c r="V93" s="6"/>
+      <c r="V93" s="6">
+        <v>34.42</v>
+      </c>
       <c r="W93" s="6"/>
       <c r="X93" s="6"/>
       <c r="Y93" s="6"/>
@@ -5122,13 +5182,13 @@
         <v>23</v>
       </c>
       <c r="C94">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" s="5">
-        <v>35.9</v>
+        <v>7</v>
+      </c>
+      <c r="E94">
+        <v>63.5</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
@@ -5140,9 +5200,7 @@
       <c r="S94" s="6"/>
       <c r="T94" s="6"/>
       <c r="U94" s="6"/>
-      <c r="V94" s="6">
-        <v>35.9</v>
-      </c>
+      <c r="V94" s="6"/>
       <c r="W94" s="6"/>
       <c r="X94" s="6"/>
       <c r="Y94" s="6"/>
@@ -5162,13 +5220,13 @@
         <v>23</v>
       </c>
       <c r="C95">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95">
-        <v>84.5</v>
+        <v>6</v>
+      </c>
+      <c r="F95" s="5">
+        <v>34.119999999999997</v>
       </c>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
@@ -5180,7 +5238,9 @@
       <c r="S95" s="6"/>
       <c r="T95" s="6"/>
       <c r="U95" s="6"/>
-      <c r="V95" s="6"/>
+      <c r="V95" s="6">
+        <v>34.119999999999997</v>
+      </c>
       <c r="W95" s="6"/>
       <c r="X95" s="6"/>
       <c r="Y95" s="6"/>
@@ -5200,16 +5260,13 @@
         <v>23</v>
       </c>
       <c r="C96">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E96">
-        <v>39</v>
-      </c>
-      <c r="F96" s="5">
-        <v>32.19</v>
+        <v>67.5</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
@@ -5221,9 +5278,7 @@
       <c r="S96" s="6"/>
       <c r="T96" s="6"/>
       <c r="U96" s="6"/>
-      <c r="V96" s="6">
-        <v>32.19</v>
-      </c>
+      <c r="V96" s="6"/>
       <c r="W96" s="6"/>
       <c r="X96" s="6"/>
       <c r="Y96" s="6"/>
@@ -5243,13 +5298,13 @@
         <v>23</v>
       </c>
       <c r="C97">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97">
-        <v>114.5</v>
+        <v>6</v>
+      </c>
+      <c r="F97" s="5">
+        <v>32.11</v>
       </c>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
@@ -5261,7 +5316,9 @@
       <c r="S97" s="6"/>
       <c r="T97" s="6"/>
       <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
+      <c r="V97" s="6">
+        <v>32.11</v>
+      </c>
       <c r="W97" s="6"/>
       <c r="X97" s="6"/>
       <c r="Y97" s="6"/>
@@ -5281,16 +5338,13 @@
         <v>23</v>
       </c>
       <c r="C98">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E98">
-        <v>35</v>
-      </c>
-      <c r="F98" s="5">
-        <v>76.599999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
@@ -5302,12 +5356,8 @@
       <c r="S98" s="6"/>
       <c r="T98" s="6"/>
       <c r="U98" s="6"/>
-      <c r="V98" s="6">
-        <v>37.72</v>
-      </c>
-      <c r="W98" s="6">
-        <v>38.880000000000003</v>
-      </c>
+      <c r="V98" s="6"/>
+      <c r="W98" s="6"/>
       <c r="X98" s="6"/>
       <c r="Y98" s="6"/>
       <c r="Z98" s="6"/>
@@ -5326,13 +5376,13 @@
         <v>23</v>
       </c>
       <c r="C99">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99">
-        <v>58.5</v>
+        <v>6</v>
+      </c>
+      <c r="F99" s="5">
+        <v>35.9</v>
       </c>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
@@ -5344,7 +5394,9 @@
       <c r="S99" s="6"/>
       <c r="T99" s="6"/>
       <c r="U99" s="6"/>
-      <c r="V99" s="6"/>
+      <c r="V99" s="6">
+        <v>35.9</v>
+      </c>
       <c r="W99" s="6"/>
       <c r="X99" s="6"/>
       <c r="Y99" s="6"/>
@@ -5364,16 +5416,13 @@
         <v>23</v>
       </c>
       <c r="C100">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100">
-        <v>61.5</v>
-      </c>
-      <c r="F100" s="5">
-        <v>84.62</v>
+        <v>84.5</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
@@ -5385,12 +5434,8 @@
       <c r="S100" s="6"/>
       <c r="T100" s="6"/>
       <c r="U100" s="6"/>
-      <c r="V100" s="6">
-        <v>36.840000000000003</v>
-      </c>
-      <c r="W100" s="6">
-        <v>47.78</v>
-      </c>
+      <c r="V100" s="6"/>
+      <c r="W100" s="6"/>
       <c r="X100" s="6"/>
       <c r="Y100" s="6"/>
       <c r="Z100" s="6"/>
@@ -5409,13 +5454,16 @@
         <v>23</v>
       </c>
       <c r="C101">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E101">
-        <v>37.5</v>
+        <v>39</v>
+      </c>
+      <c r="F101" s="5">
+        <v>32.19</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
@@ -5427,7 +5475,9 @@
       <c r="S101" s="6"/>
       <c r="T101" s="6"/>
       <c r="U101" s="6"/>
-      <c r="V101" s="6"/>
+      <c r="V101" s="6">
+        <v>32.19</v>
+      </c>
       <c r="W101" s="6"/>
       <c r="X101" s="6"/>
       <c r="Y101" s="6"/>
@@ -5447,16 +5497,13 @@
         <v>23</v>
       </c>
       <c r="C102">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D102" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E102">
-        <v>65.5</v>
-      </c>
-      <c r="F102" s="5">
-        <v>35.5</v>
+        <v>114.5</v>
       </c>
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
@@ -5468,9 +5515,7 @@
       <c r="S102" s="6"/>
       <c r="T102" s="6"/>
       <c r="U102" s="6"/>
-      <c r="V102" s="6">
-        <v>35.5</v>
-      </c>
+      <c r="V102" s="6"/>
       <c r="W102" s="6"/>
       <c r="X102" s="6"/>
       <c r="Y102" s="6"/>
@@ -5490,13 +5535,16 @@
         <v>23</v>
       </c>
       <c r="C103">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E103">
-        <v>32.5</v>
+        <v>35</v>
+      </c>
+      <c r="F103" s="5">
+        <v>76.599999999999994</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
@@ -5508,8 +5556,12 @@
       <c r="S103" s="6"/>
       <c r="T103" s="6"/>
       <c r="U103" s="6"/>
-      <c r="V103" s="6"/>
-      <c r="W103" s="6"/>
+      <c r="V103" s="6">
+        <v>37.72</v>
+      </c>
+      <c r="W103" s="6">
+        <v>38.880000000000003</v>
+      </c>
       <c r="X103" s="6"/>
       <c r="Y103" s="6"/>
       <c r="Z103" s="6"/>
@@ -5528,16 +5580,13 @@
         <v>23</v>
       </c>
       <c r="C104">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E104">
-        <v>91.5</v>
-      </c>
-      <c r="F104" s="5">
-        <v>34.380000000000003</v>
+        <v>58.5</v>
       </c>
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
@@ -5549,9 +5598,7 @@
       <c r="S104" s="6"/>
       <c r="T104" s="6"/>
       <c r="U104" s="6"/>
-      <c r="V104" s="6">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="V104" s="6"/>
       <c r="W104" s="6"/>
       <c r="X104" s="6"/>
       <c r="Y104" s="6"/>
@@ -5566,18 +5613,21 @@
         <v>114</v>
       </c>
     </row>
-    <row r="105" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B105" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C105">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E105">
-        <v>5.5</v>
+        <v>61.5</v>
+      </c>
+      <c r="F105" s="5">
+        <v>84.62</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
@@ -5589,8 +5639,12 @@
       <c r="S105" s="6"/>
       <c r="T105" s="6"/>
       <c r="U105" s="6"/>
-      <c r="V105" s="6"/>
-      <c r="W105" s="6"/>
+      <c r="V105" s="6">
+        <v>36.840000000000003</v>
+      </c>
+      <c r="W105" s="6">
+        <v>47.78</v>
+      </c>
       <c r="X105" s="6"/>
       <c r="Y105" s="6"/>
       <c r="Z105" s="6"/>
@@ -5604,21 +5658,18 @@
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C106">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D106" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E106">
-        <v>198</v>
-      </c>
-      <c r="F106" s="5">
-        <v>167.19</v>
+        <v>37.5</v>
       </c>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
@@ -5630,12 +5681,8 @@
       <c r="S106" s="6"/>
       <c r="T106" s="6"/>
       <c r="U106" s="6"/>
-      <c r="V106" s="6">
-        <v>43.97</v>
-      </c>
-      <c r="W106" s="6">
-        <v>123.22</v>
-      </c>
+      <c r="V106" s="6"/>
+      <c r="W106" s="6"/>
       <c r="X106" s="6"/>
       <c r="Y106" s="6"/>
       <c r="Z106" s="6"/>
@@ -5654,13 +5701,16 @@
         <v>23</v>
       </c>
       <c r="C107">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>65.5</v>
+      </c>
+      <c r="F107" s="5">
+        <v>35.5</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
@@ -5672,7 +5722,9 @@
       <c r="S107" s="6"/>
       <c r="T107" s="6"/>
       <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
+      <c r="V107" s="6">
+        <v>35.5</v>
+      </c>
       <c r="W107" s="6"/>
       <c r="X107" s="6"/>
       <c r="Y107" s="6"/>
@@ -5692,19 +5744,13 @@
         <v>23</v>
       </c>
       <c r="C108">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D108" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E108">
-        <v>75</v>
-      </c>
-      <c r="F108" s="5">
-        <v>189</v>
-      </c>
-      <c r="J108">
-        <v>531</v>
+        <v>32.5</v>
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
@@ -5717,9 +5763,7 @@
       <c r="T108" s="6"/>
       <c r="U108" s="6"/>
       <c r="V108" s="6"/>
-      <c r="W108" s="6">
-        <v>189</v>
-      </c>
+      <c r="W108" s="6"/>
       <c r="X108" s="6"/>
       <c r="Y108" s="6"/>
       <c r="Z108" s="6"/>
@@ -5738,16 +5782,16 @@
         <v>23</v>
       </c>
       <c r="C109">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D109" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E109">
-        <v>48.5</v>
+        <v>91.5</v>
       </c>
       <c r="F109" s="5">
-        <v>70.930000000000007</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -5759,10 +5803,10 @@
       <c r="S109" s="6"/>
       <c r="T109" s="6"/>
       <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6">
-        <v>70.930000000000007</v>
-      </c>
+      <c r="V109" s="6">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="W109" s="6"/>
       <c r="X109" s="6"/>
       <c r="Y109" s="6"/>
       <c r="Z109" s="6"/>
@@ -5778,22 +5822,16 @@
     </row>
     <row r="110" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B110" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C110">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E110">
-        <v>298</v>
-      </c>
-      <c r="F110" s="5">
-        <v>363.85</v>
-      </c>
-      <c r="I110">
-        <v>223</v>
+        <v>5.5</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -5805,12 +5843,8 @@
       <c r="S110" s="6"/>
       <c r="T110" s="6"/>
       <c r="U110" s="6"/>
-      <c r="V110" s="6">
-        <v>329.56</v>
-      </c>
-      <c r="W110" s="6">
-        <v>34.29</v>
-      </c>
+      <c r="V110" s="6"/>
+      <c r="W110" s="6"/>
       <c r="X110" s="6"/>
       <c r="Y110" s="6"/>
       <c r="Z110" s="6"/>
@@ -5826,19 +5860,19 @@
     </row>
     <row r="111" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B111" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C111">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E111">
-        <v>113.5</v>
+        <v>198</v>
       </c>
       <c r="F111" s="5">
-        <v>19.84</v>
+        <v>167.19</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -5850,11 +5884,13 @@
       <c r="S111" s="6"/>
       <c r="T111" s="6"/>
       <c r="U111" s="6"/>
-      <c r="V111" s="6"/>
-      <c r="W111" s="6"/>
-      <c r="X111" s="6">
-        <v>19.84</v>
-      </c>
+      <c r="V111" s="6">
+        <v>43.97</v>
+      </c>
+      <c r="W111" s="6">
+        <v>123.22</v>
+      </c>
+      <c r="X111" s="6"/>
       <c r="Y111" s="6"/>
       <c r="Z111" s="6"/>
       <c r="AA111" s="6"/>
@@ -5869,19 +5905,16 @@
     </row>
     <row r="112" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B112" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C112">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E112">
-        <v>88</v>
-      </c>
-      <c r="F112" s="5">
-        <v>89.05</v>
+        <v>2</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
@@ -5893,12 +5926,8 @@
       <c r="S112" s="6"/>
       <c r="T112" s="6"/>
       <c r="U112" s="6"/>
-      <c r="V112" s="6">
-        <v>32.99</v>
-      </c>
-      <c r="W112" s="6">
-        <v>56.06</v>
-      </c>
+      <c r="V112" s="6"/>
+      <c r="W112" s="6"/>
       <c r="X112" s="6"/>
       <c r="Y112" s="6"/>
       <c r="Z112" s="6"/>
@@ -5914,16 +5943,22 @@
     </row>
     <row r="113" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B113" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C113">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="F113" s="5">
+        <v>189</v>
+      </c>
+      <c r="J113">
+        <v>531</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
@@ -5936,7 +5971,9 @@
       <c r="T113" s="6"/>
       <c r="U113" s="6"/>
       <c r="V113" s="6"/>
-      <c r="W113" s="6"/>
+      <c r="W113" s="6">
+        <v>189</v>
+      </c>
       <c r="X113" s="6"/>
       <c r="Y113" s="6"/>
       <c r="Z113" s="6"/>
@@ -5952,19 +5989,19 @@
     </row>
     <row r="114" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B114" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C114">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E114">
-        <v>68.5</v>
+        <v>48.5</v>
       </c>
       <c r="F114" s="5">
-        <v>35.479999999999997</v>
+        <v>70.930000000000007</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
@@ -5976,10 +6013,10 @@
       <c r="S114" s="6"/>
       <c r="T114" s="6"/>
       <c r="U114" s="6"/>
-      <c r="V114" s="6">
-        <v>35.479999999999997</v>
-      </c>
-      <c r="W114" s="6"/>
+      <c r="V114" s="6"/>
+      <c r="W114" s="6">
+        <v>70.930000000000007</v>
+      </c>
       <c r="X114" s="6"/>
       <c r="Y114" s="6"/>
       <c r="Z114" s="6"/>
@@ -5998,13 +6035,19 @@
         <v>22</v>
       </c>
       <c r="C115">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115">
-        <v>26</v>
+        <v>298</v>
+      </c>
+      <c r="F115" s="5">
+        <v>363.85</v>
+      </c>
+      <c r="I115">
+        <v>223</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
@@ -6016,8 +6059,12 @@
       <c r="S115" s="6"/>
       <c r="T115" s="6"/>
       <c r="U115" s="6"/>
-      <c r="V115" s="6"/>
-      <c r="W115" s="6"/>
+      <c r="V115" s="6">
+        <v>329.56</v>
+      </c>
+      <c r="W115" s="6">
+        <v>34.29</v>
+      </c>
       <c r="X115" s="6"/>
       <c r="Y115" s="6"/>
       <c r="Z115" s="6"/>
@@ -6036,16 +6083,16 @@
         <v>22</v>
       </c>
       <c r="C116">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D116" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E116">
-        <v>216.5</v>
+        <v>113.5</v>
       </c>
       <c r="F116" s="5">
-        <v>206.17</v>
+        <v>19.84</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
@@ -6057,13 +6104,11 @@
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
       <c r="U116" s="6"/>
-      <c r="V116" s="6">
-        <v>129.66999999999999</v>
-      </c>
-      <c r="W116" s="6">
-        <v>76.5</v>
-      </c>
-      <c r="X116" s="6"/>
+      <c r="V116" s="6"/>
+      <c r="W116" s="6"/>
+      <c r="X116" s="6">
+        <v>19.84</v>
+      </c>
       <c r="Y116" s="6"/>
       <c r="Z116" s="6"/>
       <c r="AA116" s="6"/>
@@ -6081,13 +6126,16 @@
         <v>22</v>
       </c>
       <c r="C117">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D117" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="F117" s="5">
+        <v>89.05</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
@@ -6099,8 +6147,12 @@
       <c r="S117" s="6"/>
       <c r="T117" s="6"/>
       <c r="U117" s="6"/>
-      <c r="V117" s="6"/>
-      <c r="W117" s="6"/>
+      <c r="V117" s="6">
+        <v>32.99</v>
+      </c>
+      <c r="W117" s="6">
+        <v>56.06</v>
+      </c>
       <c r="X117" s="6"/>
       <c r="Y117" s="6"/>
       <c r="Z117" s="6"/>
@@ -6119,16 +6171,13 @@
         <v>22</v>
       </c>
       <c r="C118">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D118" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E118">
-        <v>68</v>
-      </c>
-      <c r="F118" s="5">
-        <v>97.16</v>
+        <v>2</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
@@ -6140,12 +6189,8 @@
       <c r="S118" s="6"/>
       <c r="T118" s="6"/>
       <c r="U118" s="6"/>
-      <c r="V118" s="6">
-        <v>68.16</v>
-      </c>
-      <c r="W118" s="6">
-        <v>29</v>
-      </c>
+      <c r="V118" s="6"/>
+      <c r="W118" s="6"/>
       <c r="X118" s="6"/>
       <c r="Y118" s="6"/>
       <c r="Z118" s="6"/>
@@ -6164,13 +6209,16 @@
         <v>22</v>
       </c>
       <c r="C119">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E119">
-        <v>40.5</v>
+        <v>68.5</v>
+      </c>
+      <c r="F119" s="5">
+        <v>35.479999999999997</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
@@ -6182,7 +6230,9 @@
       <c r="S119" s="6"/>
       <c r="T119" s="6"/>
       <c r="U119" s="6"/>
-      <c r="V119" s="6"/>
+      <c r="V119" s="6">
+        <v>35.479999999999997</v>
+      </c>
       <c r="W119" s="6"/>
       <c r="X119" s="6"/>
       <c r="Y119" s="6"/>
@@ -6202,16 +6252,13 @@
         <v>22</v>
       </c>
       <c r="C120">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D120" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E120">
-        <v>87.5</v>
-      </c>
-      <c r="F120" s="5">
-        <v>35.42</v>
+        <v>26</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
@@ -6223,9 +6270,7 @@
       <c r="S120" s="6"/>
       <c r="T120" s="6"/>
       <c r="U120" s="6"/>
-      <c r="V120" s="6">
-        <v>35.42</v>
-      </c>
+      <c r="V120" s="6"/>
       <c r="W120" s="6"/>
       <c r="X120" s="6"/>
       <c r="Y120" s="6"/>
@@ -6245,13 +6290,16 @@
         <v>22</v>
       </c>
       <c r="C121">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>216.5</v>
+      </c>
+      <c r="F121" s="5">
+        <v>206.17</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
@@ -6263,8 +6311,12 @@
       <c r="S121" s="6"/>
       <c r="T121" s="6"/>
       <c r="U121" s="6"/>
-      <c r="V121" s="6"/>
-      <c r="W121" s="6"/>
+      <c r="V121" s="6">
+        <v>129.66999999999999</v>
+      </c>
+      <c r="W121" s="6">
+        <v>76.5</v>
+      </c>
       <c r="X121" s="6"/>
       <c r="Y121" s="6"/>
       <c r="Z121" s="6"/>
@@ -6283,16 +6335,13 @@
         <v>22</v>
       </c>
       <c r="C122">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D122" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E122">
-        <v>84.5</v>
-      </c>
-      <c r="F122" s="5">
-        <v>34.409999999999997</v>
+        <v>86</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
@@ -6304,9 +6353,7 @@
       <c r="S122" s="6"/>
       <c r="T122" s="6"/>
       <c r="U122" s="6"/>
-      <c r="V122" s="6">
-        <v>34.409999999999997</v>
-      </c>
+      <c r="V122" s="6"/>
       <c r="W122" s="6"/>
       <c r="X122" s="6"/>
       <c r="Y122" s="6"/>
@@ -6326,13 +6373,16 @@
         <v>22</v>
       </c>
       <c r="C123">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>68</v>
+      </c>
+      <c r="F123" s="5">
+        <v>97.16</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
@@ -6344,8 +6394,12 @@
       <c r="S123" s="6"/>
       <c r="T123" s="6"/>
       <c r="U123" s="6"/>
-      <c r="V123" s="6"/>
-      <c r="W123" s="6"/>
+      <c r="V123" s="6">
+        <v>68.16</v>
+      </c>
+      <c r="W123" s="6">
+        <v>29</v>
+      </c>
       <c r="X123" s="6"/>
       <c r="Y123" s="6"/>
       <c r="Z123" s="6"/>
@@ -6364,16 +6418,13 @@
         <v>22</v>
       </c>
       <c r="C124">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E124">
-        <v>109</v>
-      </c>
-      <c r="F124" s="5">
-        <v>47.44</v>
+        <v>40.5</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6"/>
@@ -6385,9 +6436,7 @@
       <c r="S124" s="6"/>
       <c r="T124" s="6"/>
       <c r="U124" s="6"/>
-      <c r="V124" s="6">
-        <v>47.44</v>
-      </c>
+      <c r="V124" s="6"/>
       <c r="W124" s="6"/>
       <c r="X124" s="6"/>
       <c r="Y124" s="6"/>
@@ -6407,13 +6456,16 @@
         <v>22</v>
       </c>
       <c r="C125">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125">
-        <v>9.5</v>
+        <v>87.5</v>
+      </c>
+      <c r="F125" s="5">
+        <v>35.42</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
@@ -6425,7 +6477,9 @@
       <c r="S125" s="6"/>
       <c r="T125" s="6"/>
       <c r="U125" s="6"/>
-      <c r="V125" s="6"/>
+      <c r="V125" s="6">
+        <v>35.42</v>
+      </c>
       <c r="W125" s="6"/>
       <c r="X125" s="6"/>
       <c r="Y125" s="6"/>
@@ -6445,16 +6499,13 @@
         <v>22</v>
       </c>
       <c r="C126">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D126" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E126">
-        <v>255</v>
-      </c>
-      <c r="F126" s="5">
-        <v>255.86</v>
+        <v>2</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -6466,13 +6517,9 @@
       <c r="S126" s="6"/>
       <c r="T126" s="6"/>
       <c r="U126" s="6"/>
-      <c r="V126" s="6">
-        <v>67.05</v>
-      </c>
+      <c r="V126" s="6"/>
       <c r="W126" s="6"/>
-      <c r="X126" s="6">
-        <v>188.81</v>
-      </c>
+      <c r="X126" s="6"/>
       <c r="Y126" s="6"/>
       <c r="Z126" s="6"/>
       <c r="AA126" s="6"/>
@@ -6490,16 +6537,16 @@
         <v>22</v>
       </c>
       <c r="C127">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E127">
-        <v>144</v>
+        <v>84.5</v>
       </c>
       <c r="F127" s="5">
-        <v>0</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="L127" s="6"/>
       <c r="M127" s="6"/>
@@ -6511,7 +6558,9 @@
       <c r="S127" s="6"/>
       <c r="T127" s="6"/>
       <c r="U127" s="6"/>
-      <c r="V127" s="6"/>
+      <c r="V127" s="6">
+        <v>34.409999999999997</v>
+      </c>
       <c r="W127" s="6"/>
       <c r="X127" s="6"/>
       <c r="Y127" s="6"/>
@@ -6528,31 +6577,16 @@
     </row>
     <row r="128" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B128" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="C128">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D128" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E128">
-        <v>451.5</v>
-      </c>
-      <c r="F128" s="5">
-        <v>445.49</v>
-      </c>
-      <c r="G128">
-        <v>32</v>
-      </c>
-      <c r="H128">
-        <v>186.84</v>
-      </c>
-      <c r="I128">
-        <v>443</v>
-      </c>
-      <c r="J128">
-        <v>2397</v>
+        <v>2</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6"/>
@@ -6561,12 +6595,8 @@
       <c r="P128" s="6"/>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
-      <c r="S128" s="6">
-        <v>162.16499999999999</v>
-      </c>
-      <c r="T128" s="6">
-        <v>283.32499999999999</v>
-      </c>
+      <c r="S128" s="6"/>
+      <c r="T128" s="6"/>
       <c r="U128" s="6"/>
       <c r="V128" s="6"/>
       <c r="W128" s="6"/>
@@ -6585,19 +6615,19 @@
     </row>
     <row r="129" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B129" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="C129">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E129">
-        <v>144.5</v>
+        <v>109</v>
       </c>
       <c r="F129" s="5">
-        <v>75.599999999999994</v>
+        <v>47.44</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6"/>
@@ -6607,11 +6637,11 @@
       <c r="Q129" s="6"/>
       <c r="R129" s="6"/>
       <c r="S129" s="6"/>
-      <c r="T129" s="6">
-        <v>75.599999999999994</v>
-      </c>
+      <c r="T129" s="6"/>
       <c r="U129" s="6"/>
-      <c r="V129" s="6"/>
+      <c r="V129" s="6">
+        <v>47.44</v>
+      </c>
       <c r="W129" s="6"/>
       <c r="X129" s="6"/>
       <c r="Y129" s="6"/>
@@ -6628,22 +6658,16 @@
     </row>
     <row r="130" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B130" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="C130">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D130" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E130">
-        <v>451.5</v>
-      </c>
-      <c r="F130" s="5">
-        <v>629.14</v>
-      </c>
-      <c r="I130">
-        <v>788</v>
+        <v>9.5</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6"/>
@@ -6653,9 +6677,7 @@
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
       <c r="S130" s="6"/>
-      <c r="T130" s="6">
-        <v>629.14</v>
-      </c>
+      <c r="T130" s="6"/>
       <c r="U130" s="6"/>
       <c r="V130" s="6"/>
       <c r="W130" s="6"/>
@@ -6674,19 +6696,19 @@
     </row>
     <row r="131" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B131" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="C131">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E131">
-        <v>144.5</v>
+        <v>255</v>
       </c>
       <c r="F131" s="5">
-        <v>37.89</v>
+        <v>255.86</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6"/>
@@ -6696,13 +6718,15 @@
       <c r="Q131" s="6"/>
       <c r="R131" s="6"/>
       <c r="S131" s="6"/>
-      <c r="T131" s="6">
-        <v>37.89</v>
-      </c>
+      <c r="T131" s="6"/>
       <c r="U131" s="6"/>
-      <c r="V131" s="6"/>
+      <c r="V131" s="6">
+        <v>67.05</v>
+      </c>
       <c r="W131" s="6"/>
-      <c r="X131" s="6"/>
+      <c r="X131" s="6">
+        <v>188.81</v>
+      </c>
       <c r="Y131" s="6"/>
       <c r="Z131" s="6"/>
       <c r="AA131" s="6"/>
@@ -6717,22 +6741,19 @@
     </row>
     <row r="132" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B132" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="C132">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D132" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E132">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="F132" s="5">
-        <v>108.02</v>
-      </c>
-      <c r="I132">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
@@ -6742,9 +6763,7 @@
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
       <c r="S132" s="6"/>
-      <c r="T132" s="6">
-        <v>108.02</v>
-      </c>
+      <c r="T132" s="6"/>
       <c r="U132" s="6"/>
       <c r="V132" s="6"/>
       <c r="W132" s="6"/>
@@ -6766,16 +6785,28 @@
         <v>119</v>
       </c>
       <c r="C133">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E133">
-        <v>100</v>
-      </c>
-      <c r="F133" s="5">
-        <v>1.55</v>
+        <v>561.5</v>
+      </c>
+      <c r="F133" s="9">
+        <v>445.49</v>
+      </c>
+      <c r="G133">
+        <v>32</v>
+      </c>
+      <c r="H133">
+        <v>186.84</v>
+      </c>
+      <c r="I133">
+        <v>443</v>
+      </c>
+      <c r="J133">
+        <v>2397</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
@@ -6784,9 +6815,11 @@
       <c r="P133" s="6"/>
       <c r="Q133" s="6"/>
       <c r="R133" s="6"/>
-      <c r="S133" s="6"/>
+      <c r="S133" s="6">
+        <v>162.16499999999999</v>
+      </c>
       <c r="T133" s="6">
-        <v>1.55</v>
+        <v>283.32499999999999</v>
       </c>
       <c r="U133" s="6"/>
       <c r="V133" s="6"/>
@@ -6805,26 +6838,20 @@
       </c>
     </row>
     <row r="134" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B134" t="s">
-        <v>17</v>
+      <c r="B134" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C134">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D134" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E134">
-        <v>0</v>
-      </c>
-      <c r="F134" s="5">
-        <v>296.60000000000002</v>
-      </c>
-      <c r="I134">
-        <v>511</v>
-      </c>
-      <c r="J134">
-        <v>393</v>
+        <v>144.5</v>
+      </c>
+      <c r="F134" s="9">
+        <v>75.599999999999994</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
@@ -6832,11 +6859,11 @@
       <c r="O134" s="6"/>
       <c r="P134" s="6"/>
       <c r="Q134" s="6"/>
-      <c r="R134" s="6">
-        <v>296.60000000000002</v>
-      </c>
+      <c r="R134" s="6"/>
       <c r="S134" s="6"/>
-      <c r="T134" s="6"/>
+      <c r="T134" s="6">
+        <v>75.599999999999994</v>
+      </c>
       <c r="U134" s="6"/>
       <c r="V134" s="6"/>
       <c r="W134" s="6"/>
@@ -6854,20 +6881,23 @@
       </c>
     </row>
     <row r="135" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B135" t="s">
-        <v>17</v>
+      <c r="B135" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C135">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E135">
-        <v>437</v>
-      </c>
-      <c r="F135" s="5">
-        <v>0</v>
+        <v>451.5</v>
+      </c>
+      <c r="F135" s="9">
+        <v>629.14</v>
+      </c>
+      <c r="I135">
+        <v>788</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -6877,7 +6907,9 @@
       <c r="Q135" s="6"/>
       <c r="R135" s="6"/>
       <c r="S135" s="6"/>
-      <c r="T135" s="6"/>
+      <c r="T135" s="6">
+        <v>629.14</v>
+      </c>
       <c r="U135" s="6"/>
       <c r="V135" s="6"/>
       <c r="W135" s="6"/>
@@ -6895,23 +6927,20 @@
       </c>
     </row>
     <row r="136" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B136" t="s">
-        <v>17</v>
+      <c r="B136" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C136">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D136" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E136">
-        <v>141.5</v>
-      </c>
-      <c r="F136" s="5">
-        <v>204.3</v>
-      </c>
-      <c r="I136">
-        <v>118</v>
+        <v>144.5</v>
+      </c>
+      <c r="F136" s="9">
+        <v>37.89</v>
       </c>
       <c r="L136" s="6"/>
       <c r="M136" s="6"/>
@@ -6919,17 +6948,13 @@
       <c r="O136" s="6"/>
       <c r="P136" s="6"/>
       <c r="Q136" s="6"/>
-      <c r="R136" s="6">
-        <v>102.5</v>
-      </c>
+      <c r="R136" s="6"/>
       <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6">
-        <v>28.8</v>
-      </c>
-      <c r="V136" s="6">
-        <v>73</v>
-      </c>
+      <c r="T136" s="6">
+        <v>37.89</v>
+      </c>
+      <c r="U136" s="6"/>
+      <c r="V136" s="6"/>
       <c r="W136" s="6"/>
       <c r="X136" s="6"/>
       <c r="Y136" s="6"/>
@@ -6941,24 +6966,27 @@
       <c r="AE136" s="6"/>
       <c r="AF136" s="6"/>
       <c r="AG136" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="137" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B137" t="s">
-        <v>17</v>
+      <c r="B137" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C137">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E137">
-        <v>70.5</v>
-      </c>
-      <c r="F137" s="5">
-        <v>48</v>
+        <v>322</v>
+      </c>
+      <c r="F137" s="9">
+        <v>108.02</v>
+      </c>
+      <c r="I137">
+        <v>654</v>
       </c>
       <c r="L137" s="6"/>
       <c r="M137" s="6"/>
@@ -6966,15 +6994,13 @@
       <c r="O137" s="6"/>
       <c r="P137" s="6"/>
       <c r="Q137" s="6"/>
-      <c r="R137" s="6">
-        <v>16</v>
-      </c>
+      <c r="R137" s="6"/>
       <c r="S137" s="6"/>
-      <c r="T137" s="6"/>
+      <c r="T137" s="6">
+        <v>108.02</v>
+      </c>
       <c r="U137" s="6"/>
-      <c r="V137" s="6">
-        <v>32</v>
-      </c>
+      <c r="V137" s="6"/>
       <c r="W137" s="6"/>
       <c r="X137" s="6"/>
       <c r="Y137" s="6"/>
@@ -6991,22 +7017,19 @@
     </row>
     <row r="138" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B138" s="5" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="C138">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D138" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E138">
-        <v>75.5</v>
-      </c>
-      <c r="F138" s="5">
-        <v>220.59</v>
-      </c>
-      <c r="I138">
-        <v>2295</v>
+        <v>100</v>
+      </c>
+      <c r="F138" s="9">
+        <v>1.55</v>
       </c>
       <c r="L138" s="6"/>
       <c r="M138" s="6"/>
@@ -7016,13 +7039,13 @@
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
       <c r="S138" s="6"/>
-      <c r="T138" s="6"/>
+      <c r="T138" s="6">
+        <v>1.55</v>
+      </c>
       <c r="U138" s="6"/>
       <c r="V138" s="6"/>
       <c r="W138" s="6"/>
-      <c r="X138" s="7">
-        <v>220.59</v>
-      </c>
+      <c r="X138" s="6"/>
       <c r="Y138" s="6"/>
       <c r="Z138" s="6"/>
       <c r="AA138" s="6"/>
@@ -7032,21 +7055,30 @@
       <c r="AE138" s="6"/>
       <c r="AF138" s="6"/>
       <c r="AG138" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="139" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B139" s="5" t="s">
-        <v>38</v>
+      <c r="B139" t="s">
+        <v>17</v>
       </c>
       <c r="C139">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E139">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="F139" s="5">
+        <v>296.60000000000002</v>
+      </c>
+      <c r="I139">
+        <v>511</v>
+      </c>
+      <c r="J139">
+        <v>393</v>
       </c>
       <c r="L139" s="6"/>
       <c r="M139" s="6"/>
@@ -7054,7 +7086,9 @@
       <c r="O139" s="6"/>
       <c r="P139" s="6"/>
       <c r="Q139" s="6"/>
-      <c r="R139" s="6"/>
+      <c r="R139" s="6">
+        <v>296.60000000000002</v>
+      </c>
       <c r="S139" s="6"/>
       <c r="T139" s="6"/>
       <c r="U139" s="6"/>
@@ -7075,19 +7109,19 @@
     </row>
     <row r="140" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C140">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D140" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E140">
-        <v>174</v>
-      </c>
-      <c r="I140">
-        <v>220</v>
+        <v>437</v>
+      </c>
+      <c r="F140" s="5">
+        <v>0</v>
       </c>
       <c r="L140" s="6"/>
       <c r="M140" s="6"/>
@@ -7110,19 +7144,28 @@
       <c r="AD140" s="6"/>
       <c r="AE140" s="6"/>
       <c r="AF140" s="6"/>
+      <c r="AG140" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="141" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C141">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D141" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E141">
-        <v>415.5</v>
+        <v>141.5</v>
+      </c>
+      <c r="F141" s="5">
+        <v>204.3</v>
+      </c>
+      <c r="I141">
+        <v>118</v>
       </c>
       <c r="L141" s="6"/>
       <c r="M141" s="6"/>
@@ -7130,11 +7173,17 @@
       <c r="O141" s="6"/>
       <c r="P141" s="6"/>
       <c r="Q141" s="6"/>
-      <c r="R141" s="6"/>
+      <c r="R141" s="6">
+        <v>102.5</v>
+      </c>
       <c r="S141" s="6"/>
       <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
+      <c r="U141" s="6">
+        <v>28.8</v>
+      </c>
+      <c r="V141" s="6">
+        <v>73</v>
+      </c>
       <c r="W141" s="6"/>
       <c r="X141" s="6"/>
       <c r="Y141" s="6"/>
@@ -7148,16 +7197,19 @@
     </row>
     <row r="142" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C142">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D142" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E142">
-        <v>28.85</v>
+        <v>70.5</v>
+      </c>
+      <c r="F142" s="5">
+        <v>48</v>
       </c>
       <c r="L142" s="6"/>
       <c r="M142" s="6"/>
@@ -7165,11 +7217,15 @@
       <c r="O142" s="6"/>
       <c r="P142" s="6"/>
       <c r="Q142" s="6"/>
-      <c r="R142" s="6"/>
+      <c r="R142" s="6">
+        <v>16</v>
+      </c>
       <c r="S142" s="6"/>
       <c r="T142" s="6"/>
       <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
+      <c r="V142" s="6">
+        <v>32</v>
+      </c>
       <c r="W142" s="6"/>
       <c r="X142" s="6"/>
       <c r="Y142" s="6"/>
@@ -7182,17 +7238,23 @@
       <c r="AF142" s="6"/>
     </row>
     <row r="143" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B143" t="s">
-        <v>40</v>
+      <c r="B143" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C143">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E143">
-        <v>138.24</v>
+        <v>75.5</v>
+      </c>
+      <c r="F143" s="5">
+        <v>220.59</v>
+      </c>
+      <c r="I143">
+        <v>2295</v>
       </c>
       <c r="L143" s="6"/>
       <c r="M143" s="6"/>
@@ -7206,7 +7268,9 @@
       <c r="U143" s="6"/>
       <c r="V143" s="6"/>
       <c r="W143" s="6"/>
-      <c r="X143" s="6"/>
+      <c r="X143" s="7">
+        <v>220.59</v>
+      </c>
       <c r="Y143" s="6"/>
       <c r="Z143" s="6"/>
       <c r="AA143" s="6"/>
@@ -7217,23 +7281,17 @@
       <c r="AF143" s="6"/>
     </row>
     <row r="144" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B144" t="s">
-        <v>16</v>
+      <c r="B144" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C144">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D144" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E144">
-        <v>0</v>
-      </c>
-      <c r="F144" s="5">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="L144" s="6"/>
       <c r="M144" s="6"/>
@@ -7256,25 +7314,22 @@
       <c r="AD144" s="6"/>
       <c r="AE144" s="6"/>
       <c r="AF144" s="6"/>
-      <c r="AG144" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="145" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C145">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D145" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E145">
-        <v>1799.2</v>
-      </c>
-      <c r="F145" s="5">
-        <v>81</v>
+        <v>174</v>
+      </c>
+      <c r="I145">
+        <v>220</v>
       </c>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
@@ -7285,15 +7340,11 @@
       <c r="R145" s="6"/>
       <c r="S145" s="6"/>
       <c r="T145" s="6"/>
-      <c r="U145" s="6">
-        <v>9</v>
-      </c>
+      <c r="U145" s="6"/>
       <c r="V145" s="6"/>
       <c r="W145" s="6"/>
       <c r="X145" s="6"/>
-      <c r="Y145" s="6">
-        <v>72</v>
-      </c>
+      <c r="Y145" s="6"/>
       <c r="Z145" s="6"/>
       <c r="AA145" s="6"/>
       <c r="AB145" s="6"/>
@@ -7307,13 +7358,16 @@
     </row>
     <row r="146" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C146">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D146" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E146">
+        <v>415.5</v>
       </c>
       <c r="L146" s="6"/>
       <c r="M146" s="6"/>
@@ -7336,19 +7390,22 @@
       <c r="AD146" s="6"/>
       <c r="AE146" s="6"/>
       <c r="AF146" s="6"/>
+      <c r="AG146" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="147" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C147">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D147" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E147">
-        <v>109.8</v>
+        <v>28.85</v>
       </c>
       <c r="L147" s="6"/>
       <c r="M147" s="6"/>
@@ -7374,13 +7431,16 @@
     </row>
     <row r="148" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C148">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D148" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E148">
+        <v>138.24</v>
       </c>
       <c r="L148" s="6"/>
       <c r="M148" s="6"/>
@@ -7406,16 +7466,22 @@
     </row>
     <row r="149" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C149">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D149" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E149">
-        <v>220.48</v>
+        <v>0</v>
+      </c>
+      <c r="F149" s="5">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>94</v>
       </c>
       <c r="L149" s="6"/>
       <c r="M149" s="6"/>
@@ -7441,16 +7507,19 @@
     </row>
     <row r="150" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C150">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D150" t="s">
-        <v>6</v>
-      </c>
-      <c r="I150">
-        <v>32</v>
+        <v>7</v>
+      </c>
+      <c r="E150">
+        <v>1799.2</v>
+      </c>
+      <c r="F150" s="5">
+        <v>81</v>
       </c>
       <c r="L150" s="6"/>
       <c r="M150" s="6"/>
@@ -7461,11 +7530,15 @@
       <c r="R150" s="6"/>
       <c r="S150" s="6"/>
       <c r="T150" s="6"/>
-      <c r="U150" s="6"/>
+      <c r="U150" s="6">
+        <v>9</v>
+      </c>
       <c r="V150" s="6"/>
       <c r="W150" s="6"/>
       <c r="X150" s="6"/>
-      <c r="Y150" s="6"/>
+      <c r="Y150" s="6">
+        <v>72</v>
+      </c>
       <c r="Z150" s="6"/>
       <c r="AA150" s="6"/>
       <c r="AB150" s="6"/>
@@ -7476,16 +7549,13 @@
     </row>
     <row r="151" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C151">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D151" t="s">
-        <v>7</v>
-      </c>
-      <c r="E151">
-        <v>59.5</v>
+        <v>6</v>
       </c>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
@@ -7511,16 +7581,16 @@
     </row>
     <row r="152" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C152">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D152" t="s">
-        <v>6</v>
-      </c>
-      <c r="I152">
-        <v>1180</v>
+        <v>7</v>
+      </c>
+      <c r="E152">
+        <v>109.8</v>
       </c>
       <c r="L152" s="6"/>
       <c r="M152" s="6"/>
@@ -7546,16 +7616,16 @@
     </row>
     <row r="153" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C153">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
-      </c>
-      <c r="E153">
-        <v>382.5</v>
+        <v>6</v>
+      </c>
+      <c r="I153">
+        <v>32</v>
       </c>
       <c r="L153" s="6"/>
       <c r="M153" s="6"/>
@@ -7581,16 +7651,16 @@
     </row>
     <row r="154" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C154">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D154" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E154">
-        <v>418.5</v>
+        <v>59.5</v>
       </c>
       <c r="L154" s="6"/>
       <c r="M154" s="6"/>
@@ -7616,16 +7686,16 @@
     </row>
     <row r="155" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C155">
         <v>63</v>
       </c>
       <c r="D155" t="s">
-        <v>7</v>
-      </c>
-      <c r="E155">
-        <v>441.5</v>
+        <v>6</v>
+      </c>
+      <c r="I155">
+        <v>1180</v>
       </c>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
@@ -7650,32 +7720,17 @@
       <c r="AF155" s="6"/>
     </row>
     <row r="156" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B156" s="5" t="s">
-        <v>14</v>
+      <c r="B156" t="s">
+        <v>44</v>
       </c>
       <c r="C156">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D156" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E156">
-        <v>240.4</v>
-      </c>
-      <c r="F156" s="5">
-        <v>582.63</v>
-      </c>
-      <c r="G156">
-        <v>18</v>
-      </c>
-      <c r="H156">
-        <v>61.47</v>
-      </c>
-      <c r="I156">
-        <v>1989</v>
-      </c>
-      <c r="J156">
-        <v>1901</v>
+        <v>382.5</v>
       </c>
       <c r="L156" s="6"/>
       <c r="M156" s="6"/>
@@ -7686,18 +7741,10 @@
       <c r="R156" s="6"/>
       <c r="S156" s="6"/>
       <c r="T156" s="6"/>
-      <c r="U156" s="6">
-        <f>528.5-68.36</f>
-        <v>460.14</v>
-      </c>
-      <c r="V156" s="6">
-        <f>52.4-0.15</f>
-        <v>52.25</v>
-      </c>
+      <c r="U156" s="6"/>
+      <c r="V156" s="6"/>
       <c r="W156" s="6"/>
-      <c r="X156" s="6">
-        <v>70.239999999999995</v>
-      </c>
+      <c r="X156" s="6"/>
       <c r="Y156" s="6"/>
       <c r="Z156" s="6"/>
       <c r="AA156" s="6"/>
@@ -7706,25 +7753,19 @@
       <c r="AD156" s="6"/>
       <c r="AE156" s="6"/>
       <c r="AF156" s="6"/>
-      <c r="AG156" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="157" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B157" s="5" t="s">
-        <v>14</v>
+      <c r="B157" t="s">
+        <v>45</v>
       </c>
       <c r="C157">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E157">
-        <v>976.24</v>
-      </c>
-      <c r="F157" s="5">
-        <v>91.31</v>
+        <v>418.5</v>
       </c>
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
@@ -7735,19 +7776,11 @@
       <c r="R157" s="6"/>
       <c r="S157" s="6"/>
       <c r="T157" s="6"/>
-      <c r="U157" s="6">
-        <v>42.7</v>
-      </c>
+      <c r="U157" s="6"/>
       <c r="V157" s="6"/>
-      <c r="W157" s="6">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="X157" s="6">
-        <v>8.81</v>
-      </c>
-      <c r="Y157" s="6">
-        <v>70.84</v>
-      </c>
+      <c r="W157" s="6"/>
+      <c r="X157" s="6"/>
+      <c r="Y157" s="6"/>
       <c r="Z157" s="6"/>
       <c r="AA157" s="6"/>
       <c r="AB157" s="6"/>
@@ -7760,32 +7793,17 @@
       </c>
     </row>
     <row r="158" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B158" s="5" t="s">
-        <v>14</v>
+      <c r="B158" t="s">
+        <v>45</v>
       </c>
       <c r="C158">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D158" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E158">
-        <v>286</v>
-      </c>
-      <c r="F158" s="5">
-        <v>374.7</v>
-      </c>
-      <c r="G158">
-        <v>8</v>
-      </c>
-      <c r="H158">
-        <v>28.55</v>
-      </c>
-      <c r="I158">
-        <v>574</v>
-      </c>
-      <c r="J158">
-        <v>822</v>
+        <v>441.5</v>
       </c>
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
@@ -7796,13 +7814,8 @@
       <c r="R158" s="6"/>
       <c r="S158" s="6"/>
       <c r="T158" s="6"/>
-      <c r="U158" s="6">
-        <f>67.2+51</f>
-        <v>118.2</v>
-      </c>
-      <c r="V158" s="6">
-        <v>256.5</v>
-      </c>
+      <c r="U158" s="6"/>
+      <c r="V158" s="6"/>
       <c r="W158" s="6"/>
       <c r="X158" s="6"/>
       <c r="Y158" s="6"/>
@@ -7822,16 +7835,28 @@
         <v>14</v>
       </c>
       <c r="C159">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E159">
-        <v>566.29999999999995</v>
+        <v>240.4</v>
       </c>
       <c r="F159" s="5">
-        <v>65.599999999999994</v>
+        <v>582.63</v>
+      </c>
+      <c r="G159">
+        <v>18</v>
+      </c>
+      <c r="H159">
+        <v>61.47</v>
+      </c>
+      <c r="I159">
+        <v>1989</v>
+      </c>
+      <c r="J159">
+        <v>1901</v>
       </c>
       <c r="L159" s="6"/>
       <c r="M159" s="6"/>
@@ -7842,16 +7867,19 @@
       <c r="R159" s="6"/>
       <c r="S159" s="6"/>
       <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="X159" s="6"/>
-      <c r="Y159" s="6">
-        <f>14.84+38.87+23.3</f>
-        <v>77.009999999999991</v>
-      </c>
+      <c r="U159" s="6">
+        <f>528.5-68.36</f>
+        <v>460.14</v>
+      </c>
+      <c r="V159" s="6">
+        <f>52.4-0.15</f>
+        <v>52.25</v>
+      </c>
+      <c r="W159" s="6"/>
+      <c r="X159" s="6">
+        <v>70.239999999999995</v>
+      </c>
+      <c r="Y159" s="6"/>
       <c r="Z159" s="6"/>
       <c r="AA159" s="6"/>
       <c r="AB159" s="6"/>
@@ -7868,22 +7896,16 @@
         <v>14</v>
       </c>
       <c r="C160">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D160" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E160">
+        <v>976.24</v>
       </c>
       <c r="F160" s="5">
-        <v>207.4</v>
-      </c>
-      <c r="G160">
-        <v>7</v>
-      </c>
-      <c r="H160">
-        <v>21.76</v>
-      </c>
-      <c r="I160">
-        <v>597</v>
+        <v>162.15</v>
       </c>
       <c r="L160" s="6"/>
       <c r="M160" s="6"/>
@@ -7894,13 +7916,19 @@
       <c r="R160" s="6"/>
       <c r="S160" s="6"/>
       <c r="T160" s="6"/>
-      <c r="U160" s="6"/>
-      <c r="V160" s="6">
-        <v>207.4</v>
-      </c>
-      <c r="W160" s="6"/>
-      <c r="X160" s="6"/>
-      <c r="Y160" s="6"/>
+      <c r="U160" s="6">
+        <v>42.7</v>
+      </c>
+      <c r="V160" s="6"/>
+      <c r="W160" s="6">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="X160" s="6">
+        <v>8.81</v>
+      </c>
+      <c r="Y160" s="6">
+        <v>70.84</v>
+      </c>
       <c r="Z160" s="6"/>
       <c r="AA160" s="6"/>
       <c r="AB160" s="6"/>
@@ -7917,16 +7945,28 @@
         <v>14</v>
       </c>
       <c r="C161">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E161">
-        <v>116.6</v>
+        <v>286</v>
       </c>
       <c r="F161" s="5">
-        <v>2</v>
+        <v>374.7</v>
+      </c>
+      <c r="G161">
+        <v>8</v>
+      </c>
+      <c r="H161">
+        <v>28.55</v>
+      </c>
+      <c r="I161">
+        <v>574</v>
+      </c>
+      <c r="J161">
+        <v>822</v>
       </c>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
@@ -7937,11 +7977,14 @@
       <c r="R161" s="6"/>
       <c r="S161" s="6"/>
       <c r="T161" s="6"/>
-      <c r="U161" s="6"/>
-      <c r="V161" s="6"/>
-      <c r="W161" s="6">
-        <v>2</v>
-      </c>
+      <c r="U161" s="6">
+        <f>67.2+51</f>
+        <v>118.2</v>
+      </c>
+      <c r="V161" s="6">
+        <v>256.5</v>
+      </c>
+      <c r="W161" s="6"/>
       <c r="X161" s="6"/>
       <c r="Y161" s="6"/>
       <c r="Z161" s="6"/>
@@ -7956,20 +7999,20 @@
       </c>
     </row>
     <row r="162" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B162" t="s">
-        <v>46</v>
+      <c r="B162" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C162">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D162" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E162">
-        <v>772.07</v>
-      </c>
-      <c r="I162">
-        <v>785</v>
+        <v>566.29999999999995</v>
+      </c>
+      <c r="F162" s="5">
+        <v>142.61000000000001</v>
       </c>
       <c r="L162" s="6"/>
       <c r="M162" s="6"/>
@@ -7982,9 +8025,14 @@
       <c r="T162" s="6"/>
       <c r="U162" s="6"/>
       <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
+      <c r="W162" s="6">
+        <v>65.599999999999994</v>
+      </c>
       <c r="X162" s="6"/>
-      <c r="Y162" s="6"/>
+      <c r="Y162" s="6">
+        <f>14.84+38.87+23.3</f>
+        <v>77.009999999999991</v>
+      </c>
       <c r="Z162" s="6"/>
       <c r="AA162" s="6"/>
       <c r="AB162" s="6"/>
@@ -7992,19 +8040,31 @@
       <c r="AD162" s="6"/>
       <c r="AE162" s="6"/>
       <c r="AF162" s="6"/>
+      <c r="AG162" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="163" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B163" t="s">
-        <v>46</v>
+      <c r="B163" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C163">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
-      </c>
-      <c r="E163">
-        <v>894.97</v>
+        <v>6</v>
+      </c>
+      <c r="F163" s="5">
+        <v>207.4</v>
+      </c>
+      <c r="G163">
+        <v>7</v>
+      </c>
+      <c r="H163">
+        <v>21.76</v>
+      </c>
+      <c r="I163">
+        <v>597</v>
       </c>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
@@ -8016,7 +8076,9 @@
       <c r="S163" s="6"/>
       <c r="T163" s="6"/>
       <c r="U163" s="6"/>
-      <c r="V163" s="6"/>
+      <c r="V163" s="6">
+        <v>207.4</v>
+      </c>
       <c r="W163" s="6"/>
       <c r="X163" s="6"/>
       <c r="Y163" s="6"/>
@@ -8029,14 +8091,20 @@
       <c r="AF163" s="6"/>
     </row>
     <row r="164" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B164" t="s">
-        <v>47</v>
+      <c r="B164" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C164">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D164" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E164">
+        <v>116.6</v>
+      </c>
+      <c r="F164" s="5">
+        <v>2</v>
       </c>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
@@ -8049,7 +8117,9 @@
       <c r="T164" s="6"/>
       <c r="U164" s="6"/>
       <c r="V164" s="6"/>
-      <c r="W164" s="6"/>
+      <c r="W164" s="6">
+        <v>2</v>
+      </c>
       <c r="X164" s="6"/>
       <c r="Y164" s="6"/>
       <c r="Z164" s="6"/>
@@ -8062,16 +8132,19 @@
     </row>
     <row r="165" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C165">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E165">
-        <v>747</v>
+        <v>772.07</v>
+      </c>
+      <c r="I165">
+        <v>785</v>
       </c>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
@@ -8096,23 +8169,17 @@
       <c r="AF165" s="6"/>
     </row>
     <row r="166" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B166" s="5" t="s">
-        <v>48</v>
+      <c r="B166" t="s">
+        <v>46</v>
       </c>
       <c r="C166">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D166" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E166">
-        <v>205.65</v>
-      </c>
-      <c r="F166" s="5">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="I166">
-        <v>288</v>
+        <v>894.97</v>
       </c>
       <c r="L166" s="6"/>
       <c r="M166" s="6"/>
@@ -8126,9 +8193,7 @@
       <c r="U166" s="6"/>
       <c r="V166" s="6"/>
       <c r="W166" s="6"/>
-      <c r="X166" s="6">
-        <v>76.400000000000006</v>
-      </c>
+      <c r="X166" s="6"/>
       <c r="Y166" s="6"/>
       <c r="Z166" s="6"/>
       <c r="AA166" s="6"/>
@@ -8137,22 +8202,16 @@
       <c r="AD166" s="6"/>
       <c r="AE166" s="6"/>
       <c r="AF166" s="6"/>
-      <c r="AG166" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="167" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B167" s="5" t="s">
-        <v>48</v>
+      <c r="B167" t="s">
+        <v>47</v>
       </c>
       <c r="C167">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
-      </c>
-      <c r="E167">
-        <v>59.6</v>
+        <v>6</v>
       </c>
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
@@ -8180,23 +8239,17 @@
       </c>
     </row>
     <row r="168" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B168" s="5" t="s">
-        <v>48</v>
+      <c r="B168" t="s">
+        <v>47</v>
       </c>
       <c r="C168">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D168" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E168">
-        <v>62.5</v>
-      </c>
-      <c r="F168" s="5">
-        <v>344.13</v>
-      </c>
-      <c r="I168">
-        <v>415</v>
+        <v>747</v>
       </c>
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
@@ -8209,13 +8262,8 @@
       <c r="T168" s="6"/>
       <c r="U168" s="6"/>
       <c r="V168" s="6"/>
-      <c r="W168" s="6">
-        <v>81.8</v>
-      </c>
-      <c r="X168" s="6">
-        <f>42+158.17+61.95+0.21</f>
-        <v>262.33</v>
-      </c>
+      <c r="W168" s="6"/>
+      <c r="X168" s="6"/>
       <c r="Y168" s="6"/>
       <c r="Z168" s="6"/>
       <c r="AA168" s="6"/>
@@ -8233,16 +8281,19 @@
         <v>48</v>
       </c>
       <c r="C169">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E169">
-        <v>63</v>
+        <v>205.65</v>
       </c>
       <c r="F169" s="5">
-        <v>40.9</v>
+        <v>76.400000000000006</v>
+      </c>
+      <c r="I169">
+        <v>288</v>
       </c>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
@@ -8257,7 +8308,7 @@
       <c r="V169" s="6"/>
       <c r="W169" s="6"/>
       <c r="X169" s="6">
-        <v>47.56</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="Y169" s="6"/>
       <c r="Z169" s="6"/>
@@ -8272,20 +8323,17 @@
       </c>
     </row>
     <row r="170" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B170" t="s">
-        <v>49</v>
+      <c r="B170" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C170">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D170" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E170">
-        <v>217</v>
-      </c>
-      <c r="I170">
-        <v>141</v>
+        <v>59.6</v>
       </c>
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
@@ -8308,19 +8356,28 @@
       <c r="AD170" s="6"/>
       <c r="AE170" s="6"/>
       <c r="AF170" s="6"/>
+      <c r="AG170" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="171" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B171" t="s">
-        <v>49</v>
+      <c r="B171" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C171">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D171" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E171">
-        <v>28</v>
+        <v>62.5</v>
+      </c>
+      <c r="F171" s="5">
+        <v>344.13</v>
+      </c>
+      <c r="I171">
+        <v>415</v>
       </c>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
@@ -8333,8 +8390,13 @@
       <c r="T171" s="6"/>
       <c r="U171" s="6"/>
       <c r="V171" s="6"/>
-      <c r="W171" s="6"/>
-      <c r="X171" s="6"/>
+      <c r="W171" s="6">
+        <v>81.8</v>
+      </c>
+      <c r="X171" s="6">
+        <f>42+158.17+61.95+0.21</f>
+        <v>262.33</v>
+      </c>
       <c r="Y171" s="6"/>
       <c r="Z171" s="6"/>
       <c r="AA171" s="6"/>
@@ -8345,14 +8407,20 @@
       <c r="AF171" s="6"/>
     </row>
     <row r="172" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B172" t="s">
-        <v>50</v>
+      <c r="B172" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C172">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D172" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E172">
+        <v>63</v>
+      </c>
+      <c r="F172" s="5">
+        <v>47.56</v>
       </c>
       <c r="L172" s="6"/>
       <c r="M172" s="6"/>
@@ -8366,7 +8434,9 @@
       <c r="U172" s="6"/>
       <c r="V172" s="6"/>
       <c r="W172" s="6"/>
-      <c r="X172" s="6"/>
+      <c r="X172" s="6">
+        <v>47.56</v>
+      </c>
       <c r="Y172" s="6"/>
       <c r="Z172" s="6"/>
       <c r="AA172" s="6"/>
@@ -8378,16 +8448,19 @@
     </row>
     <row r="173" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C173">
         <v>71</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E173">
-        <v>125</v>
+        <v>217</v>
+      </c>
+      <c r="I173">
+        <v>141</v>
       </c>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
@@ -8413,19 +8486,16 @@
     </row>
     <row r="174" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C174">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D174" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E174">
-        <v>131.30000000000001</v>
-      </c>
-      <c r="I174">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="L174" s="6"/>
       <c r="M174" s="6"/>
@@ -8451,16 +8521,13 @@
     </row>
     <row r="175" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C175">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D175" t="s">
-        <v>7</v>
-      </c>
-      <c r="E175">
-        <v>15.2</v>
+        <v>6</v>
       </c>
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
@@ -8486,13 +8553,16 @@
     </row>
     <row r="176" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="C176">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D176" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E176">
+        <v>125</v>
       </c>
       <c r="L176" s="6"/>
       <c r="M176" s="6"/>
@@ -8518,16 +8588,19 @@
     </row>
     <row r="177" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C177">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D177" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E177">
-        <v>1021.03</v>
+        <v>131.30000000000001</v>
+      </c>
+      <c r="I177">
+        <v>134</v>
       </c>
       <c r="L177" s="6"/>
       <c r="M177" s="6"/>
@@ -8552,23 +8625,17 @@
       <c r="AF177" s="6"/>
     </row>
     <row r="178" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B178" s="5" t="s">
-        <v>52</v>
+      <c r="B178" t="s">
+        <v>51</v>
       </c>
       <c r="C178">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D178" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E178">
-        <v>341.2</v>
-      </c>
-      <c r="F178" s="5">
-        <v>145.88</v>
-      </c>
-      <c r="I178">
-        <v>37</v>
+        <v>15.2</v>
       </c>
       <c r="L178" s="6"/>
       <c r="M178" s="6"/>
@@ -8581,13 +8648,8 @@
       <c r="T178" s="6"/>
       <c r="U178" s="6"/>
       <c r="V178" s="6"/>
-      <c r="W178" s="6">
-        <v>78.180000000000007</v>
-      </c>
-      <c r="X178" s="6">
-        <f>18.75+12+36.95</f>
-        <v>67.7</v>
-      </c>
+      <c r="W178" s="6"/>
+      <c r="X178" s="6"/>
       <c r="Y178" s="6"/>
       <c r="Z178" s="6"/>
       <c r="AA178" s="6"/>
@@ -8596,25 +8658,16 @@
       <c r="AD178" s="6"/>
       <c r="AE178" s="6"/>
       <c r="AF178" s="6"/>
-      <c r="AG178" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="179" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B179" s="5" t="s">
-        <v>52</v>
+      <c r="B179" t="s">
+        <v>95</v>
       </c>
       <c r="C179">
         <v>74</v>
       </c>
       <c r="D179" t="s">
-        <v>7</v>
-      </c>
-      <c r="E179">
-        <v>83.8</v>
-      </c>
-      <c r="F179" s="5">
-        <v>55.83</v>
+        <v>6</v>
       </c>
       <c r="L179" s="6"/>
       <c r="M179" s="6"/>
@@ -8628,10 +8681,7 @@
       <c r="U179" s="6"/>
       <c r="V179" s="6"/>
       <c r="W179" s="6"/>
-      <c r="X179" s="6">
-        <f>34.75+6.11+14.97</f>
-        <v>55.83</v>
-      </c>
+      <c r="X179" s="6"/>
       <c r="Y179" s="6"/>
       <c r="Z179" s="6"/>
       <c r="AA179" s="6"/>
@@ -8646,13 +8696,16 @@
     </row>
     <row r="180" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C180">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D180" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E180">
+        <v>1021.03</v>
       </c>
       <c r="L180" s="6"/>
       <c r="M180" s="6"/>
@@ -8675,19 +8728,28 @@
       <c r="AD180" s="6"/>
       <c r="AE180" s="6"/>
       <c r="AF180" s="6"/>
+      <c r="AG180" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="181" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B181" t="s">
-        <v>53</v>
+      <c r="B181" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C181">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E181">
-        <v>226.5</v>
+        <v>341.2</v>
+      </c>
+      <c r="F181" s="5">
+        <v>145.88</v>
+      </c>
+      <c r="I181">
+        <v>37</v>
       </c>
       <c r="L181" s="6"/>
       <c r="M181" s="6"/>
@@ -8700,8 +8762,13 @@
       <c r="T181" s="6"/>
       <c r="U181" s="6"/>
       <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="6"/>
+      <c r="W181" s="6">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="X181" s="6">
+        <f>18.75+12+36.95</f>
+        <v>67.7</v>
+      </c>
       <c r="Y181" s="6"/>
       <c r="Z181" s="6"/>
       <c r="AA181" s="6"/>
@@ -8712,20 +8779,20 @@
       <c r="AF181" s="6"/>
     </row>
     <row r="182" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B182" t="s">
-        <v>54</v>
+      <c r="B182" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C182">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D182" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E182">
-        <v>375</v>
-      </c>
-      <c r="I182">
-        <v>87</v>
+        <v>83.8</v>
+      </c>
+      <c r="F182" s="5">
+        <v>55.83</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -8739,7 +8806,10 @@
       <c r="U182" s="6"/>
       <c r="V182" s="6"/>
       <c r="W182" s="6"/>
-      <c r="X182" s="6"/>
+      <c r="X182" s="6">
+        <f>34.75+6.11+14.97</f>
+        <v>55.83</v>
+      </c>
       <c r="Y182" s="6"/>
       <c r="Z182" s="6"/>
       <c r="AA182" s="6"/>
@@ -8751,16 +8821,13 @@
     </row>
     <row r="183" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C183">
         <v>75</v>
       </c>
       <c r="D183" t="s">
-        <v>7</v>
-      </c>
-      <c r="E183">
-        <v>244.5</v>
+        <v>6</v>
       </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
@@ -8786,13 +8853,16 @@
     </row>
     <row r="184" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C184">
         <v>75</v>
       </c>
       <c r="D184" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E184">
+        <v>226.5</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -8818,16 +8888,19 @@
     </row>
     <row r="185" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C185">
         <v>75</v>
       </c>
       <c r="D185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E185">
-        <v>338.5</v>
+        <v>375</v>
+      </c>
+      <c r="I185">
+        <v>87</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -8853,13 +8926,16 @@
     </row>
     <row r="186" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C186">
         <v>75</v>
       </c>
       <c r="D186" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E186">
+        <v>244.5</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -8885,16 +8961,13 @@
     </row>
     <row r="187" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C187">
         <v>75</v>
       </c>
       <c r="D187" t="s">
-        <v>7</v>
-      </c>
-      <c r="E187">
-        <v>238</v>
+        <v>6</v>
       </c>
       <c r="L187" s="6"/>
       <c r="M187" s="6"/>
@@ -8920,13 +8993,16 @@
     </row>
     <row r="188" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C188">
         <v>75</v>
       </c>
       <c r="D188" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E188">
+        <v>338.5</v>
       </c>
       <c r="L188" s="6"/>
       <c r="M188" s="6"/>
@@ -8952,16 +9028,13 @@
     </row>
     <row r="189" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C189">
         <v>75</v>
       </c>
       <c r="D189" t="s">
-        <v>7</v>
-      </c>
-      <c r="E189">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="L189" s="6"/>
       <c r="M189" s="6"/>
@@ -8987,13 +9060,16 @@
     </row>
     <row r="190" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C190">
         <v>75</v>
       </c>
       <c r="D190" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E190">
+        <v>238</v>
       </c>
       <c r="L190" s="6"/>
       <c r="M190" s="6"/>
@@ -9019,16 +9095,13 @@
     </row>
     <row r="191" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C191">
         <v>75</v>
       </c>
       <c r="D191" t="s">
-        <v>7</v>
-      </c>
-      <c r="E191">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="L191" s="6"/>
       <c r="M191" s="6"/>
@@ -9054,16 +9127,16 @@
     </row>
     <row r="192" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="C192">
         <v>75</v>
       </c>
       <c r="D192" t="s">
-        <v>6</v>
-      </c>
-      <c r="F192" s="5">
-        <v>311.68</v>
+        <v>7</v>
+      </c>
+      <c r="E192">
+        <v>69</v>
       </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
@@ -9078,9 +9151,7 @@
       <c r="V192" s="6"/>
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
-      <c r="Y192" s="6">
-        <v>311.68</v>
-      </c>
+      <c r="Y192" s="6"/>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>
       <c r="AB192" s="6"/>
@@ -9088,22 +9159,16 @@
       <c r="AD192" s="6"/>
       <c r="AE192" s="6"/>
       <c r="AF192" s="6"/>
-      <c r="AG192" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="193" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="C193">
         <v>75</v>
       </c>
       <c r="D193" t="s">
-        <v>7</v>
-      </c>
-      <c r="E193">
-        <v>858.5</v>
+        <v>6</v>
       </c>
       <c r="L193" s="6"/>
       <c r="M193" s="6"/>
@@ -9126,16 +9191,22 @@
       <c r="AD193" s="6"/>
       <c r="AE193" s="6"/>
       <c r="AF193" s="6"/>
+      <c r="AG193" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="194" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C194">
         <v>75</v>
       </c>
       <c r="D194" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E194">
+        <v>140</v>
       </c>
       <c r="L194" s="6"/>
       <c r="M194" s="6"/>
@@ -9161,16 +9232,16 @@
     </row>
     <row r="195" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C195">
         <v>75</v>
       </c>
       <c r="D195" t="s">
-        <v>7</v>
-      </c>
-      <c r="E195">
-        <v>168</v>
+        <v>6</v>
+      </c>
+      <c r="F195" s="5">
+        <v>311.68</v>
       </c>
       <c r="L195" s="6"/>
       <c r="M195" s="6"/>
@@ -9185,7 +9256,9 @@
       <c r="V195" s="6"/>
       <c r="W195" s="6"/>
       <c r="X195" s="6"/>
-      <c r="Y195" s="6"/>
+      <c r="Y195" s="6">
+        <v>311.68</v>
+      </c>
       <c r="Z195" s="6"/>
       <c r="AA195" s="6"/>
       <c r="AB195" s="6"/>
@@ -9196,13 +9269,16 @@
     </row>
     <row r="196" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="C196">
         <v>75</v>
       </c>
       <c r="D196" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E196">
+        <v>858.5</v>
       </c>
       <c r="L196" s="6"/>
       <c r="M196" s="6"/>
@@ -9228,16 +9304,13 @@
     </row>
     <row r="197" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C197">
         <v>75</v>
       </c>
       <c r="D197" t="s">
-        <v>7</v>
-      </c>
-      <c r="E197">
-        <v>180</v>
+        <v>6</v>
       </c>
       <c r="L197" s="6"/>
       <c r="M197" s="6"/>
@@ -9263,16 +9336,16 @@
     </row>
     <row r="198" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="C198">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D198" t="s">
-        <v>6</v>
-      </c>
-      <c r="I198">
-        <v>182</v>
+        <v>7</v>
+      </c>
+      <c r="E198">
+        <v>168</v>
       </c>
       <c r="L198" s="6"/>
       <c r="M198" s="6"/>
@@ -9298,16 +9371,13 @@
     </row>
     <row r="199" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C199">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D199" t="s">
-        <v>7</v>
-      </c>
-      <c r="E199">
-        <v>238.52</v>
+        <v>6</v>
       </c>
       <c r="L199" s="6"/>
       <c r="M199" s="6"/>
@@ -9333,13 +9403,16 @@
     </row>
     <row r="200" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C200">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D200" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E200">
+        <v>180</v>
       </c>
       <c r="L200" s="6"/>
       <c r="M200" s="6"/>
@@ -9365,16 +9438,16 @@
     </row>
     <row r="201" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C201">
         <v>76</v>
       </c>
       <c r="D201" t="s">
-        <v>7</v>
-      </c>
-      <c r="E201">
-        <v>229.5</v>
+        <v>6</v>
+      </c>
+      <c r="I201">
+        <v>182</v>
       </c>
       <c r="L201" s="6"/>
       <c r="M201" s="6"/>
@@ -9400,13 +9473,16 @@
     </row>
     <row r="202" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C202">
         <v>76</v>
       </c>
       <c r="D202" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E202">
+        <v>238.52</v>
       </c>
       <c r="L202" s="6"/>
       <c r="M202" s="6"/>
@@ -9432,16 +9508,13 @@
     </row>
     <row r="203" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C203">
         <v>76</v>
       </c>
       <c r="D203" t="s">
-        <v>7</v>
-      </c>
-      <c r="E203">
-        <v>1566.27</v>
+        <v>6</v>
       </c>
       <c r="L203" s="6"/>
       <c r="M203" s="6"/>
@@ -9467,13 +9540,16 @@
     </row>
     <row r="204" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C204">
         <v>76</v>
       </c>
       <c r="D204" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E204">
+        <v>229.5</v>
       </c>
       <c r="L204" s="6"/>
       <c r="M204" s="6"/>
@@ -9496,22 +9572,16 @@
       <c r="AD204" s="6"/>
       <c r="AE204" s="6"/>
       <c r="AF204" s="6"/>
-      <c r="AG204" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C205">
         <v>76</v>
       </c>
       <c r="D205" t="s">
-        <v>7</v>
-      </c>
-      <c r="E205">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="L205" s="6"/>
       <c r="M205" s="6"/>
@@ -9539,20 +9609,17 @@
       </c>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B206" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>88</v>
+      <c r="B206" t="s">
+        <v>62</v>
+      </c>
+      <c r="C206">
+        <v>76</v>
       </c>
       <c r="D206" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E206">
-        <v>0</v>
-      </c>
-      <c r="F206" s="5">
-        <v>34.57</v>
+        <v>1566.27</v>
       </c>
       <c r="L206" s="6"/>
       <c r="M206" s="6"/>
@@ -9564,9 +9631,7 @@
       <c r="S206" s="6"/>
       <c r="T206" s="6"/>
       <c r="U206" s="6"/>
-      <c r="V206" s="6">
-        <v>34.57</v>
-      </c>
+      <c r="V206" s="6"/>
       <c r="W206" s="6"/>
       <c r="X206" s="6"/>
       <c r="Y206" s="6"/>
@@ -9578,21 +9643,18 @@
       <c r="AE206" s="6"/>
       <c r="AF206" s="6"/>
       <c r="AG206" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="207" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B207" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>88</v>
+      <c r="B207" t="s">
+        <v>93</v>
+      </c>
+      <c r="C207">
+        <v>76</v>
       </c>
       <c r="D207" t="s">
-        <v>7</v>
-      </c>
-      <c r="E207">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="L207" s="6"/>
       <c r="M207" s="6"/>
@@ -9621,25 +9683,16 @@
     </row>
     <row r="208" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
-        <v>11</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="C208">
+        <v>76</v>
       </c>
       <c r="D208" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E208">
-        <v>351</v>
-      </c>
-      <c r="F208" s="5">
-        <v>300.68</v>
-      </c>
-      <c r="I208">
-        <v>8</v>
-      </c>
-      <c r="J208">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="L208" s="6"/>
       <c r="M208" s="6"/>
@@ -9648,9 +9701,7 @@
       <c r="P208" s="6"/>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
-      <c r="S208" s="6">
-        <v>300.68</v>
-      </c>
+      <c r="S208" s="6"/>
       <c r="T208" s="6"/>
       <c r="U208" s="6"/>
       <c r="V208" s="6"/>
@@ -9669,40 +9720,36 @@
       </c>
     </row>
     <row r="209" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B209" t="s">
-        <v>11</v>
+      <c r="B209" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D209" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E209">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F209" s="5">
-        <v>337.46</v>
+        <v>34.57</v>
       </c>
       <c r="L209" s="6"/>
       <c r="M209" s="6"/>
       <c r="N209" s="6"/>
       <c r="O209" s="6"/>
       <c r="P209" s="6"/>
-      <c r="Q209" s="6">
-        <v>127.69</v>
-      </c>
+      <c r="Q209" s="6"/>
       <c r="R209" s="6"/>
       <c r="S209" s="6"/>
       <c r="T209" s="6"/>
       <c r="U209" s="6"/>
-      <c r="V209" s="6"/>
-      <c r="W209" s="6">
-        <v>42</v>
-      </c>
-      <c r="X209" s="6">
-        <v>167.77</v>
-      </c>
+      <c r="V209" s="6">
+        <v>34.57</v>
+      </c>
+      <c r="W209" s="6"/>
+      <c r="X209" s="6"/>
       <c r="Y209" s="6"/>
       <c r="Z209" s="6"/>
       <c r="AA209" s="6"/>
@@ -9716,17 +9763,17 @@
       </c>
     </row>
     <row r="210" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B210" t="s">
-        <v>63</v>
+      <c r="B210" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D210" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E210">
-        <v>100.2</v>
+        <v>158</v>
       </c>
       <c r="L210" s="6"/>
       <c r="M210" s="6"/>
@@ -9749,19 +9796,31 @@
       <c r="AD210" s="6"/>
       <c r="AE210" s="6"/>
       <c r="AF210" s="6"/>
+      <c r="AG210" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="211" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D211" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E211">
-        <v>253.5</v>
+        <v>351</v>
+      </c>
+      <c r="F211" s="5">
+        <v>300.68</v>
+      </c>
+      <c r="I211">
+        <v>8</v>
+      </c>
+      <c r="J211">
+        <v>27</v>
       </c>
       <c r="L211" s="6"/>
       <c r="M211" s="6"/>
@@ -9770,7 +9829,9 @@
       <c r="P211" s="6"/>
       <c r="Q211" s="6"/>
       <c r="R211" s="6"/>
-      <c r="S211" s="6"/>
+      <c r="S211" s="6">
+        <v>300.68</v>
+      </c>
       <c r="T211" s="6"/>
       <c r="U211" s="6"/>
       <c r="V211" s="6"/>
@@ -9787,30 +9848,39 @@
     </row>
     <row r="212" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D212" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E212">
-        <v>89.9</v>
+        <v>152</v>
+      </c>
+      <c r="F212" s="5">
+        <v>337.46</v>
       </c>
       <c r="L212" s="6"/>
       <c r="M212" s="6"/>
       <c r="N212" s="6"/>
       <c r="O212" s="6"/>
       <c r="P212" s="6"/>
-      <c r="Q212" s="6"/>
+      <c r="Q212" s="6">
+        <v>127.69</v>
+      </c>
       <c r="R212" s="6"/>
       <c r="S212" s="6"/>
       <c r="T212" s="6"/>
       <c r="U212" s="6"/>
       <c r="V212" s="6"/>
-      <c r="W212" s="6"/>
-      <c r="X212" s="6"/>
+      <c r="W212" s="6">
+        <v>42</v>
+      </c>
+      <c r="X212" s="6">
+        <v>167.77</v>
+      </c>
       <c r="Y212" s="6"/>
       <c r="Z212" s="6"/>
       <c r="AA212" s="6"/>
@@ -9822,16 +9892,16 @@
     </row>
     <row r="213" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E213">
-        <v>322.2</v>
+        <v>100.2</v>
       </c>
       <c r="L213" s="6"/>
       <c r="M213" s="6"/>
@@ -9857,13 +9927,16 @@
     </row>
     <row r="214" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D214" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E214">
+        <v>253.5</v>
       </c>
       <c r="L214" s="6"/>
       <c r="M214" s="6"/>
@@ -9889,16 +9962,16 @@
     </row>
     <row r="215" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D215" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E215">
-        <v>129.80000000000001</v>
+        <v>89.9</v>
       </c>
       <c r="L215" s="6"/>
       <c r="M215" s="6"/>
@@ -9924,13 +9997,16 @@
     </row>
     <row r="216" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
-        <v>96</v>
-      </c>
-      <c r="C216" s="1">
-        <v>12</v>
+        <v>65</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D216" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E216">
+        <v>322.2</v>
       </c>
       <c r="L216" s="6"/>
       <c r="M216" s="6"/>
@@ -9956,16 +10032,13 @@
     </row>
     <row r="217" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
-        <v>96</v>
-      </c>
-      <c r="C217" s="1">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D217" t="s">
-        <v>7</v>
-      </c>
-      <c r="E217">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="L217" s="6"/>
       <c r="M217" s="6"/>
@@ -9989,13 +10062,49 @@
       <c r="AE217" s="6"/>
       <c r="AF217" s="6"/>
     </row>
+    <row r="218" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B218" t="s">
+        <v>64</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D218" t="s">
+        <v>7</v>
+      </c>
+      <c r="E218">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="L218" s="6"/>
+      <c r="M218" s="6"/>
+      <c r="N218" s="6"/>
+      <c r="O218" s="6"/>
+      <c r="P218" s="6"/>
+      <c r="Q218" s="6"/>
+      <c r="R218" s="6"/>
+      <c r="S218" s="6"/>
+      <c r="T218" s="6"/>
+      <c r="U218" s="6"/>
+      <c r="V218" s="6"/>
+      <c r="W218" s="6"/>
+      <c r="X218" s="6"/>
+      <c r="Y218" s="6"/>
+      <c r="Z218" s="6"/>
+      <c r="AA218" s="6"/>
+      <c r="AB218" s="6"/>
+      <c r="AC218" s="6"/>
+      <c r="AD218" s="6"/>
+      <c r="AE218" s="6"/>
+      <c r="AF218" s="6"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8680C7E9-C780-447B-908C-14B9740642F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8266D4C-FEFC-4618-BE67-91F82CF17AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9171,7 +9171,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>374.4</v>
+        <v>454.5</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8266D4C-FEFC-4618-BE67-91F82CF17AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF016727-AA40-4CC2-9C6F-750C3C0D77BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,17 +817,17 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="produção Novembro 2025" dataDxfId="13"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="produção Dezembro 2025" dataDxfId="12"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="produção Janeiro 2026" dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="produção Fevereiro 2026" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="produção Março 2026" dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="produção Abril 2026" dataDxfId="8"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="produção Maio 2026" dataDxfId="7"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="produção Junho 2026" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="produção Julho 2026" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="produção Agosto 2026" dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="produção Setembro 2026" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="produção Outubro 2026" dataDxfId="2"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="produção Novembro 2026" dataDxfId="1"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="produção Dezembro 2026" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="produção Fevereiro 2026" dataDxfId="0"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="produção Março 2026" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="produção Abril 2026" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="produção Maio 2026" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="produção Junho 2026" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="produção Julho 2026" dataDxfId="6"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="produção Agosto 2026" dataDxfId="5"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="produção Setembro 2026" dataDxfId="4"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="produção Outubro 2026" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="produção Novembro 2026" dataDxfId="2"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="produção Dezembro 2026" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1118,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG218"/>
+  <dimension ref="A1:AL218"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -1135,7 +1135,9 @@
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="15" width="7.6640625" customWidth="1"/>
     <col min="16" max="16" width="14.5546875" customWidth="1"/>
-    <col min="17" max="32" width="7.6640625" customWidth="1"/>
+    <col min="17" max="23" width="7.6640625" customWidth="1"/>
+    <col min="24" max="24" width="9.88671875" customWidth="1"/>
+    <col min="25" max="32" width="7.6640625" customWidth="1"/>
     <col min="33" max="33" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7251,7 +7253,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>67</v>
       </c>
@@ -7289,7 +7291,7 @@
       <c r="AE145" s="4"/>
       <c r="AF145" s="4"/>
     </row>
-    <row r="146" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>67</v>
       </c>
@@ -7324,7 +7326,7 @@
       <c r="AE146" s="4"/>
       <c r="AF146" s="4"/>
     </row>
-    <row r="147" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>68</v>
       </c>
@@ -7359,7 +7361,7 @@
       <c r="AE147" s="4"/>
       <c r="AF147" s="4"/>
     </row>
-    <row r="148" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>68</v>
       </c>
@@ -7394,7 +7396,7 @@
       <c r="AE148" s="4"/>
       <c r="AF148" s="4"/>
     </row>
-    <row r="149" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>69</v>
       </c>
@@ -7435,7 +7437,7 @@
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
     </row>
-    <row r="150" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>69</v>
       </c>
@@ -7480,7 +7482,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>70</v>
       </c>
@@ -7512,7 +7514,7 @@
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
     </row>
-    <row r="152" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>70</v>
       </c>
@@ -7547,7 +7549,7 @@
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
     </row>
-    <row r="153" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>71</v>
       </c>
@@ -7582,7 +7584,7 @@
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
     </row>
-    <row r="154" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>71</v>
       </c>
@@ -7617,7 +7619,7 @@
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
     </row>
-    <row r="155" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>72</v>
       </c>
@@ -7651,8 +7653,11 @@
       <c r="AD155" s="4"/>
       <c r="AE155" s="4"/>
       <c r="AF155" s="4"/>
-    </row>
-    <row r="156" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AL155">
+        <v>1746.61</v>
+      </c>
+    </row>
+    <row r="156" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>72</v>
       </c>
@@ -7686,8 +7691,11 @@
       <c r="AD156" s="4"/>
       <c r="AE156" s="4"/>
       <c r="AF156" s="4"/>
-    </row>
-    <row r="157" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AL156">
+        <v>1471.49</v>
+      </c>
+    </row>
+    <row r="157" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>73</v>
       </c>
@@ -7724,8 +7732,12 @@
       <c r="AG157" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="158" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AL157">
+        <f>AL155-AL156</f>
+        <v>275.11999999999989</v>
+      </c>
+    </row>
+    <row r="158" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>73</v>
       </c>
@@ -7763,7 +7775,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B159" s="3" t="s">
         <v>75</v>
       </c>
@@ -7777,7 +7789,7 @@
         <v>240.4</v>
       </c>
       <c r="F159" s="3">
-        <v>582.63</v>
+        <v>766.04399999999998</v>
       </c>
       <c r="G159">
         <v>18</v>
@@ -7801,12 +7813,12 @@
       <c r="S159" s="4"/>
       <c r="T159" s="4"/>
       <c r="U159" s="4">
-        <f>528.5-68.36</f>
-        <v>460.14</v>
+        <f>528.5-68.36+91.707</f>
+        <v>551.84699999999998</v>
       </c>
       <c r="V159" s="4">
-        <f>52.4-0.15</f>
-        <v>52.25</v>
+        <f>52.4-0.15+91.707</f>
+        <v>143.95699999999999</v>
       </c>
       <c r="W159" s="4"/>
       <c r="X159" s="4">
@@ -7824,7 +7836,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="160" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B160" s="3" t="s">
         <v>75</v>
       </c>
@@ -7872,6 +7884,10 @@
       <c r="AG160" t="s">
         <v>74</v>
       </c>
+      <c r="AL160">
+        <f>AL157/3</f>
+        <v>91.706666666666635</v>
+      </c>
     </row>
     <row r="161" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B161" s="3" t="s">
@@ -7887,7 +7903,7 @@
         <v>286</v>
       </c>
       <c r="F161" s="3">
-        <v>374.7</v>
+        <v>466.40699999999998</v>
       </c>
       <c r="G161">
         <v>8</v>
@@ -7915,7 +7931,8 @@
         <v>118.2</v>
       </c>
       <c r="V161" s="4">
-        <v>256.5</v>
+        <f>256.5+91.707</f>
+        <v>348.20699999999999</v>
       </c>
       <c r="W161" s="4"/>
       <c r="X161" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF016727-AA40-4CC2-9C6F-750C3C0D77BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CE51A2-4BD7-44B5-B94A-3CAAE165E5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -817,17 +817,17 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="produção Novembro 2025" dataDxfId="13"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="produção Dezembro 2025" dataDxfId="12"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="produção Janeiro 2026" dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="produção Fevereiro 2026" dataDxfId="0"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="produção Março 2026" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="produção Abril 2026" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="produção Maio 2026" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="produção Junho 2026" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="produção Julho 2026" dataDxfId="6"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="produção Agosto 2026" dataDxfId="5"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="produção Setembro 2026" dataDxfId="4"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="produção Outubro 2026" dataDxfId="3"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="produção Novembro 2026" dataDxfId="2"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="produção Dezembro 2026" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="produção Fevereiro 2026" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="produção Março 2026" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="produção Abril 2026" dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="produção Maio 2026" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="produção Junho 2026" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="produção Julho 2026" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="produção Agosto 2026" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="produção Setembro 2026" dataDxfId="3"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="produção Outubro 2026" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="produção Novembro 2026" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="produção Dezembro 2026" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>84.32</v>
+        <v>162.9</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="4"/>
@@ -3321,7 +3321,8 @@
       <c r="W54" s="4"/>
       <c r="X54" s="4"/>
       <c r="Y54" s="4">
-        <v>84.32</v>
+        <f>78.58+84.32</f>
+        <v>162.89999999999998</v>
       </c>
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>
@@ -8039,6 +8040,9 @@
       <c r="AD163" s="4"/>
       <c r="AE163" s="4"/>
       <c r="AF163" s="4"/>
+      <c r="AG163" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="164" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B164" s="3" t="s">
@@ -8079,6 +8083,9 @@
       <c r="AD164" s="4"/>
       <c r="AE164" s="4"/>
       <c r="AF164" s="4"/>
+      <c r="AG164" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="165" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B165" t="s">

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CE51A2-4BD7-44B5-B94A-3CAAE165E5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025F1614-BF82-4C33-923E-358A18CE3888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7452,7 +7452,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>81</v>
+        <v>282</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7470,7 +7470,7 @@
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4">
-        <v>72</v>
+        <v>273</v>
       </c>
       <c r="Z150" s="4"/>
       <c r="AA150" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025F1614-BF82-4C33-923E-358A18CE3888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D15A9C-A368-465C-860A-542118E352C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7452,7 +7452,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D15A9C-A368-465C-860A-542118E352C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B5CE6C-56E4-4BCA-BBE2-B48DA483B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7452,7 +7452,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7463,14 +7463,12 @@
       <c r="R150" s="4"/>
       <c r="S150" s="4"/>
       <c r="T150" s="4"/>
-      <c r="U150" s="4">
-        <v>9</v>
-      </c>
+      <c r="U150" s="4"/>
       <c r="V150" s="4"/>
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="Z150" s="4"/>
       <c r="AA150" s="4"/>
@@ -9195,7 +9193,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>454.5</v>
+        <v>592.20000000000005</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9211,8 +9209,8 @@
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
       <c r="Y195" s="4">
-        <f>62.701+311.68+80.157</f>
-        <v>454.53800000000001</v>
+        <f>62.701+311.68+80.157+52.62+85.03</f>
+        <v>592.18799999999999</v>
       </c>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B5CE6C-56E4-4BCA-BBE2-B48DA483B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86F1CA1-20F9-4B5A-89D3-47DC3706369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -7452,7 +7452,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7468,7 +7468,7 @@
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="Z150" s="4"/>
       <c r="AA150" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86F1CA1-20F9-4B5A-89D3-47DC3706369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0B521B-21D3-4A64-8CFA-71029D5E5BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>162.9</v>
+        <v>308.3</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="4"/>
@@ -3321,8 +3321,8 @@
       <c r="W54" s="4"/>
       <c r="X54" s="4"/>
       <c r="Y54" s="4">
-        <f>78.58+84.32</f>
-        <v>162.89999999999998</v>
+        <f>78.58+84.32+66.57+78.843</f>
+        <v>308.31299999999999</v>
       </c>
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0B521B-21D3-4A64-8CFA-71029D5E5BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196EAB5F-F9DC-44BF-86A5-A2D3BA47891F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -8805,6 +8805,9 @@
       <c r="AD183" s="4"/>
       <c r="AE183" s="4"/>
       <c r="AF183" s="4"/>
+      <c r="AG183" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="184" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
@@ -9193,7 +9196,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>592.20000000000005</v>
+        <v>454.56</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9209,8 +9212,7 @@
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
       <c r="Y195" s="4">
-        <f>62.701+311.68+80.157+52.62+85.03</f>
-        <v>592.18799999999999</v>
+        <v>454.56</v>
       </c>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196EAB5F-F9DC-44BF-86A5-A2D3BA47891F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F631A82-82E5-4D48-97A4-6D3A1211F86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -3247,9 +3247,6 @@
       <c r="AD52" s="4"/>
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
-      <c r="AG52" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="53" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
@@ -3286,9 +3283,6 @@
       <c r="AD53" s="4"/>
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
-      <c r="AG53" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="54" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
@@ -3303,7 +3297,7 @@
       <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <v>308.3</v>
       </c>
       <c r="K54" s="2"/>
@@ -3332,7 +3326,7 @@
       <c r="AE54" s="4"/>
       <c r="AF54" s="4"/>
       <c r="AG54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="2:33" x14ac:dyDescent="0.3">
@@ -7452,7 +7446,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>345</v>
+        <v>888</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7468,7 +7462,7 @@
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4">
-        <v>345</v>
+        <v>888</v>
       </c>
       <c r="Z150" s="4"/>
       <c r="AA150" s="4"/>
@@ -7728,9 +7722,6 @@
       <c r="AD157" s="4"/>
       <c r="AE157" s="4"/>
       <c r="AF157" s="4"/>
-      <c r="AG157" t="s">
-        <v>74</v>
-      </c>
       <c r="AL157">
         <f>AL155-AL156</f>
         <v>275.11999999999989</v>
@@ -7770,9 +7761,6 @@
       <c r="AD158" s="4"/>
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
-      <c r="AG158" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="159" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B159" s="3" t="s">
@@ -8680,9 +8668,6 @@
       <c r="AD180" s="4"/>
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
-      <c r="AG180" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="181" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B181" s="3" t="s">
@@ -8773,6 +8758,9 @@
       <c r="AD182" s="4"/>
       <c r="AE182" s="4"/>
       <c r="AF182" s="4"/>
+      <c r="AG182" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="183" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
@@ -9196,7 +9184,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>454.56</v>
+        <v>539.59</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9212,7 +9200,8 @@
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
       <c r="Y195" s="4">
-        <v>454.56</v>
+        <f>454.56+85.03</f>
+        <v>539.59</v>
       </c>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>
@@ -9668,7 +9657,9 @@
       <c r="V208" s="4"/>
       <c r="W208" s="4"/>
       <c r="X208" s="4"/>
-      <c r="Y208" s="4"/>
+      <c r="Y208" s="4">
+        <v>56.1</v>
+      </c>
       <c r="Z208" s="4"/>
       <c r="AA208" s="4"/>
       <c r="AB208" s="4"/>
@@ -10061,9 +10052,9 @@
   </sheetData>
   <autoFilter ref="A1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F631A82-82E5-4D48-97A4-6D3A1211F86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A871C8-6823-4757-B691-A06C4DCFF530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -9644,6 +9644,9 @@
       <c r="E208">
         <v>95</v>
       </c>
+      <c r="F208" s="3">
+        <v>56.1</v>
+      </c>
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
       <c r="N208" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A871C8-6823-4757-B691-A06C4DCFF530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69902AD-2067-401B-909F-C333BE192426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25245" yWindow="4230" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -9184,7 +9184,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>539.59</v>
+        <v>592.21</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9200,8 +9200,7 @@
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
       <c r="Y195" s="4">
-        <f>454.56+85.03</f>
-        <v>539.59</v>
+        <v>592.21</v>
       </c>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69902AD-2067-401B-909F-C333BE192426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA2308F-CEEB-4798-A0F0-6CF4B79DAA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25245" yWindow="4230" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -2568,8 +2568,11 @@
       <c r="AD32" s="4"/>
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="AG32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>44</v>
       </c>
@@ -2603,8 +2606,11 @@
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="AG33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>45</v>
       </c>
@@ -2636,7 +2642,7 @@
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>45</v>
       </c>
@@ -2671,7 +2677,7 @@
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
     </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>46</v>
       </c>
@@ -2703,7 +2709,7 @@
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>46</v>
       </c>
@@ -2738,7 +2744,7 @@
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>47</v>
       </c>
@@ -2769,8 +2775,11 @@
       <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="AG38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>47</v>
       </c>
@@ -2805,7 +2814,7 @@
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
     </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>48</v>
       </c>
@@ -2840,7 +2849,7 @@
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
     </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>48</v>
       </c>
@@ -2872,7 +2881,7 @@
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>49</v>
       </c>
@@ -2907,7 +2916,7 @@
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>49</v>
       </c>
@@ -2939,7 +2948,7 @@
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>50</v>
       </c>
@@ -2974,7 +2983,7 @@
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>50</v>
       </c>
@@ -3006,7 +3015,7 @@
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>51</v>
       </c>
@@ -3041,7 +3050,7 @@
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>51</v>
       </c>
@@ -3076,7 +3085,7 @@
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>52</v>
       </c>
@@ -7446,7 +7455,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>888</v>
+        <v>943.4</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7464,7 +7473,9 @@
       <c r="Y150" s="4">
         <v>888</v>
       </c>
-      <c r="Z150" s="4"/>
+      <c r="Z150" s="4">
+        <v>55.4</v>
+      </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
       <c r="AC150" s="4"/>
@@ -8936,6 +8947,9 @@
       <c r="AD187" s="4"/>
       <c r="AE187" s="4"/>
       <c r="AF187" s="4"/>
+      <c r="AG187" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="188" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
@@ -8971,6 +8985,9 @@
       <c r="AD188" s="4"/>
       <c r="AE188" s="4"/>
       <c r="AF188" s="4"/>
+      <c r="AG188" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="189" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
@@ -9184,7 +9201,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>592.21</v>
+        <v>736.35</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9202,7 +9219,10 @@
       <c r="Y195" s="4">
         <v>592.21</v>
       </c>
-      <c r="Z195" s="4"/>
+      <c r="Z195" s="4">
+        <f>64.57+79.57</f>
+        <v>144.13999999999999</v>
+      </c>
       <c r="AA195" s="4"/>
       <c r="AB195" s="4"/>
       <c r="AC195" s="4"/>
@@ -9355,6 +9375,9 @@
       <c r="AD199" s="4"/>
       <c r="AE199" s="4"/>
       <c r="AF199" s="4"/>
+      <c r="AG199" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="200" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
@@ -9390,6 +9413,9 @@
       <c r="AD200" s="4"/>
       <c r="AE200" s="4"/>
       <c r="AF200" s="4"/>
+      <c r="AG200" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="201" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
@@ -9644,7 +9670,7 @@
         <v>95</v>
       </c>
       <c r="F208" s="3">
-        <v>56.1</v>
+        <v>93.1</v>
       </c>
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
@@ -9662,7 +9688,9 @@
       <c r="Y208" s="4">
         <v>56.1</v>
       </c>
-      <c r="Z208" s="4"/>
+      <c r="Z208" s="4">
+        <v>37</v>
+      </c>
       <c r="AA208" s="4"/>
       <c r="AB208" s="4"/>
       <c r="AC208" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA2308F-CEEB-4798-A0F0-6CF4B79DAA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169ADDE0-D6CC-47F5-BD01-014BA377EE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8978,7 +8978,9 @@
       <c r="W188" s="4"/>
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
-      <c r="Z188" s="4"/>
+      <c r="Z188" s="4">
+        <v>103.03</v>
+      </c>
       <c r="AA188" s="4"/>
       <c r="AB188" s="4"/>
       <c r="AC188" s="4"/>
@@ -9220,8 +9222,8 @@
         <v>592.21</v>
       </c>
       <c r="Z195" s="4">
-        <f>64.57+79.57</f>
-        <v>144.13999999999999</v>
+        <f>64.57+79.57+66.725</f>
+        <v>210.86499999999998</v>
       </c>
       <c r="AA195" s="4"/>
       <c r="AB195" s="4"/>
@@ -9406,7 +9408,9 @@
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
       <c r="Y200" s="4"/>
-      <c r="Z200" s="4"/>
+      <c r="Z200" s="4">
+        <v>20.2</v>
+      </c>
       <c r="AA200" s="4"/>
       <c r="AB200" s="4"/>
       <c r="AC200" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169ADDE0-D6CC-47F5-BD01-014BA377EE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206CF054-EACD-405E-B087-782B00BED439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8964,6 +8964,9 @@
       <c r="E188">
         <v>338.5</v>
       </c>
+      <c r="F188" s="3">
+        <v>103.03</v>
+      </c>
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
       <c r="N188" s="4"/>
@@ -9203,7 +9206,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>736.35</v>
+        <v>759.41499999999996</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9219,7 +9222,8 @@
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
       <c r="Y195" s="4">
-        <v>592.21</v>
+        <f>592.21-43.66</f>
+        <v>548.55000000000007</v>
       </c>
       <c r="Z195" s="4">
         <f>64.57+79.57+66.725</f>
@@ -9394,6 +9398,9 @@
       <c r="E200">
         <v>180</v>
       </c>
+      <c r="F200" s="3">
+        <v>63.86</v>
+      </c>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
       <c r="N200" s="4"/>
@@ -9407,7 +9414,9 @@
       <c r="V200" s="4"/>
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
-      <c r="Y200" s="4"/>
+      <c r="Y200" s="4">
+        <v>43.66</v>
+      </c>
       <c r="Z200" s="4">
         <v>20.2</v>
       </c>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206CF054-EACD-405E-B087-782B00BED439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D40517A-E907-471C-868E-856086DEADAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7455,7 +7455,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>943.4</v>
+        <v>1028.4000000000001</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7474,7 +7474,7 @@
         <v>888</v>
       </c>
       <c r="Z150" s="4">
-        <v>55.4</v>
+        <v>140.4</v>
       </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
@@ -8965,7 +8965,7 @@
         <v>338.5</v>
       </c>
       <c r="F188" s="3">
-        <v>103.03</v>
+        <v>123.6</v>
       </c>
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
@@ -8982,7 +8982,7 @@
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
       <c r="Z188" s="4">
-        <v>103.03</v>
+        <v>123.6</v>
       </c>
       <c r="AA188" s="4"/>
       <c r="AB188" s="4"/>
@@ -9206,7 +9206,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>759.41499999999996</v>
+        <v>823.09500000000003</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9226,8 +9226,8 @@
         <v>548.55000000000007</v>
       </c>
       <c r="Z195" s="4">
-        <f>64.57+79.57+66.725</f>
-        <v>210.86499999999998</v>
+        <f>64.57+79.57+66.725+63.68</f>
+        <v>274.54499999999996</v>
       </c>
       <c r="AA195" s="4"/>
       <c r="AB195" s="4"/>
@@ -9399,7 +9399,7 @@
         <v>180</v>
       </c>
       <c r="F200" s="3">
-        <v>63.86</v>
+        <v>68.86</v>
       </c>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
@@ -9418,7 +9418,7 @@
         <v>43.66</v>
       </c>
       <c r="Z200" s="4">
-        <v>20.2</v>
+        <v>25.2</v>
       </c>
       <c r="AA200" s="4"/>
       <c r="AB200" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D40517A-E907-471C-868E-856086DEADAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEEE24B-B25E-4B48-BD34-2A13491500AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE_DASH_EXTENSAO!$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE_DASH_EXTENSAO!$AG$1:$AG$218</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -793,9 +793,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
   <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF218">
-    <sortCondition ref="C1:C218"/>
-  </sortState>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Obra"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bloco"/>
@@ -1135,7 +1132,9 @@
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="15" width="7.6640625" customWidth="1"/>
     <col min="16" max="16" width="14.5546875" customWidth="1"/>
-    <col min="17" max="23" width="7.6640625" customWidth="1"/>
+    <col min="17" max="21" width="7.6640625" customWidth="1"/>
+    <col min="22" max="22" width="36" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.6640625" customWidth="1"/>
     <col min="24" max="24" width="9.88671875" customWidth="1"/>
     <col min="25" max="32" width="7.6640625" customWidth="1"/>
     <col min="33" max="33" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -7474,7 +7473,7 @@
         <v>888</v>
       </c>
       <c r="Z150" s="4">
-        <v>140.4</v>
+        <v>209.9</v>
       </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
@@ -10093,7 +10092,7 @@
       <c r="AF218" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="AG1:AG218" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEEE24B-B25E-4B48-BD34-2A13491500AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEB0680-7D73-42CE-B2B5-65BD18FBBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2560,7 +2560,9 @@
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
+      <c r="Z32" s="4">
+        <v>38.299999999999997</v>
+      </c>
       <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
       <c r="AC32" s="4"/>
@@ -2568,7 +2570,7 @@
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
       <c r="AG32" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.3">
@@ -7473,7 +7475,7 @@
         <v>888</v>
       </c>
       <c r="Z150" s="4">
-        <v>209.9</v>
+        <v>339.2</v>
       </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
@@ -8964,7 +8966,7 @@
         <v>338.5</v>
       </c>
       <c r="F188" s="3">
-        <v>123.6</v>
+        <v>300.3</v>
       </c>
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
@@ -8981,7 +8983,7 @@
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
       <c r="Z188" s="4">
-        <v>123.6</v>
+        <v>300.3</v>
       </c>
       <c r="AA188" s="4"/>
       <c r="AB188" s="4"/>
@@ -9225,8 +9227,8 @@
         <v>548.55000000000007</v>
       </c>
       <c r="Z195" s="4">
-        <f>64.57+79.57+66.725+63.68</f>
-        <v>274.54499999999996</v>
+        <f>64.57+79.57+66.725+63.68+57.846</f>
+        <v>332.39099999999996</v>
       </c>
       <c r="AA195" s="4"/>
       <c r="AB195" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEB0680-7D73-42CE-B2B5-65BD18FBBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE93373-2C15-4A62-A2D8-97CA376E985F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -2807,7 +2807,9 @@
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
+      <c r="Z39" s="4">
+        <v>11.5</v>
+      </c>
       <c r="AA39" s="4"/>
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
@@ -7475,7 +7477,7 @@
         <v>888</v>
       </c>
       <c r="Z150" s="4">
-        <v>339.2</v>
+        <v>428.7</v>
       </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
@@ -8836,7 +8838,9 @@
       <c r="W184" s="4"/>
       <c r="X184" s="4"/>
       <c r="Y184" s="4"/>
-      <c r="Z184" s="4"/>
+      <c r="Z184" s="4">
+        <v>42</v>
+      </c>
       <c r="AA184" s="4"/>
       <c r="AB184" s="4"/>
       <c r="AC184" s="4"/>
@@ -9419,7 +9423,7 @@
         <v>43.66</v>
       </c>
       <c r="Z200" s="4">
-        <v>25.2</v>
+        <v>117.2</v>
       </c>
       <c r="AA200" s="4"/>
       <c r="AB200" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE93373-2C15-4A62-A2D8-97CA376E985F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77884FDC-C6A3-407C-BDD4-AF07C4518E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -2546,6 +2546,9 @@
       <c r="D32" t="s">
         <v>34</v>
       </c>
+      <c r="F32" s="3">
+        <v>38.299999999999997</v>
+      </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
@@ -2793,6 +2796,9 @@
       <c r="E39">
         <v>205</v>
       </c>
+      <c r="F39" s="3">
+        <v>11.5</v>
+      </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
@@ -7458,7 +7464,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>1028.4000000000001</v>
+        <v>1316.7</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -8824,6 +8830,9 @@
       <c r="E184">
         <v>226.5</v>
       </c>
+      <c r="F184" s="3">
+        <v>42</v>
+      </c>
       <c r="L184" s="4"/>
       <c r="M184" s="4"/>
       <c r="N184" s="4"/>
@@ -8970,7 +8979,7 @@
         <v>338.5</v>
       </c>
       <c r="F188" s="3">
-        <v>300.3</v>
+        <v>377.8</v>
       </c>
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
@@ -8987,7 +8996,7 @@
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
       <c r="Z188" s="4">
-        <v>300.3</v>
+        <v>377.8</v>
       </c>
       <c r="AA188" s="4"/>
       <c r="AB188" s="4"/>
@@ -9211,7 +9220,7 @@
         <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>823.09500000000003</v>
+        <v>880.94100000000003</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9404,7 +9413,7 @@
         <v>180</v>
       </c>
       <c r="F200" s="3">
-        <v>68.86</v>
+        <v>160.86000000000001</v>
       </c>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77884FDC-C6A3-407C-BDD4-AF07C4518E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2EF3D5-C9E1-4C09-AF92-C9E53AEC36D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -7464,7 +7464,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>1316.7</v>
+        <v>1403.2</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7483,7 +7483,7 @@
         <v>888</v>
       </c>
       <c r="Z150" s="4">
-        <v>428.7</v>
+        <v>515.20000000000005</v>
       </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
@@ -9591,6 +9591,9 @@
       <c r="D205" t="s">
         <v>34</v>
       </c>
+      <c r="F205" s="3">
+        <v>24</v>
+      </c>
       <c r="L205" s="4"/>
       <c r="M205" s="4"/>
       <c r="N205" s="4"/>
@@ -9605,13 +9608,18 @@
       <c r="W205" s="4"/>
       <c r="X205" s="4"/>
       <c r="Y205" s="4"/>
-      <c r="Z205" s="4"/>
+      <c r="Z205" s="4">
+        <v>24</v>
+      </c>
       <c r="AA205" s="4"/>
       <c r="AB205" s="4"/>
       <c r="AC205" s="4"/>
       <c r="AD205" s="4"/>
       <c r="AE205" s="4"/>
       <c r="AF205" s="4"/>
+      <c r="AG205" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B206" t="s">

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2EF3D5-C9E1-4C09-AF92-C9E53AEC36D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA516CB1-52F3-42DF-A693-8663F4E35CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="126">
   <si>
     <t>Data</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rede existente </t>
   </si>
 </sst>
 </file>
@@ -792,7 +795,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
-  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="RCE RUA JOSÉ MILITÃO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Obra"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bloco"/>
@@ -1133,7 +1142,7 @@
     <col min="14" max="15" width="7.6640625" customWidth="1"/>
     <col min="16" max="16" width="14.5546875" customWidth="1"/>
     <col min="17" max="21" width="7.6640625" customWidth="1"/>
-    <col min="22" max="22" width="36" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.33203125" customWidth="1"/>
     <col min="23" max="23" width="7.6640625" customWidth="1"/>
     <col min="24" max="24" width="9.88671875" customWidth="1"/>
     <col min="25" max="32" width="7.6640625" customWidth="1"/>
@@ -1241,7 +1250,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>33</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>33</v>
       </c>
@@ -1330,7 +1339,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1375,7 +1384,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
@@ -1418,7 +1427,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
@@ -1461,7 +1470,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
@@ -1504,7 +1513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
@@ -1552,7 +1561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1596,7 +1605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
@@ -1653,7 +1662,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>37</v>
       </c>
@@ -1691,7 +1700,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>37</v>
       </c>
@@ -1742,7 +1751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
@@ -1783,7 +1792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>37</v>
       </c>
@@ -1834,7 +1843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1877,7 +1886,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
@@ -1930,7 +1939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>37</v>
       </c>
@@ -1968,7 +1977,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>37</v>
       </c>
@@ -2017,7 +2026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
@@ -2066,7 +2075,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
@@ -2121,7 +2130,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
@@ -2164,7 +2173,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
@@ -2213,7 +2222,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>38</v>
       </c>
@@ -2256,7 +2265,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>39</v>
       </c>
@@ -2297,7 +2306,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>39</v>
       </c>
@@ -2332,7 +2341,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>41</v>
       </c>
@@ -2367,7 +2376,7 @@
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
     </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>41</v>
       </c>
@@ -2402,7 +2411,7 @@
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
     </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>42</v>
       </c>
@@ -2437,7 +2446,7 @@
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
     </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>42</v>
       </c>
@@ -2469,7 +2478,7 @@
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
     </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>43</v>
       </c>
@@ -2501,7 +2510,7 @@
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
     </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>43</v>
       </c>
@@ -2536,7 +2545,7 @@
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
     </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>44</v>
       </c>
@@ -2576,7 +2585,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>44</v>
       </c>
@@ -2614,7 +2623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>45</v>
       </c>
@@ -2646,7 +2655,7 @@
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
     </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>45</v>
       </c>
@@ -2681,7 +2690,7 @@
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
     </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>46</v>
       </c>
@@ -2713,7 +2722,7 @@
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>46</v>
       </c>
@@ -2748,7 +2757,7 @@
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>47</v>
       </c>
@@ -2783,7 +2792,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>47</v>
       </c>
@@ -2823,7 +2832,7 @@
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
     </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>48</v>
       </c>
@@ -2858,7 +2867,7 @@
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
     </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>48</v>
       </c>
@@ -2890,7 +2899,7 @@
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>49</v>
       </c>
@@ -2925,7 +2934,7 @@
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>49</v>
       </c>
@@ -2957,7 +2966,7 @@
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>50</v>
       </c>
@@ -2992,7 +3001,7 @@
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>50</v>
       </c>
@@ -3024,7 +3033,7 @@
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>51</v>
       </c>
@@ -3059,7 +3068,7 @@
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>51</v>
       </c>
@@ -3094,7 +3103,7 @@
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>52</v>
       </c>
@@ -3129,7 +3138,7 @@
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
     </row>
-    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>52</v>
       </c>
@@ -3164,7 +3173,7 @@
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
     </row>
-    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>53</v>
       </c>
@@ -3199,7 +3208,7 @@
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
     </row>
-    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>53</v>
       </c>
@@ -3234,7 +3243,7 @@
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
     </row>
-    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>54</v>
       </c>
@@ -3266,7 +3275,7 @@
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
     </row>
-    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>54</v>
       </c>
@@ -3302,7 +3311,7 @@
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
     </row>
-    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>55</v>
       </c>
@@ -3347,7 +3356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>56</v>
       </c>
@@ -3399,7 +3408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>56</v>
       </c>
@@ -3441,7 +3450,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>56</v>
       </c>
@@ -3493,7 +3502,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>56</v>
       </c>
@@ -3535,7 +3544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>56</v>
       </c>
@@ -3587,7 +3596,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>56</v>
       </c>
@@ -3631,7 +3640,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>56</v>
       </c>
@@ -3678,7 +3687,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>56</v>
       </c>
@@ -3722,7 +3731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>57</v>
       </c>
@@ -3778,7 +3787,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>57</v>
       </c>
@@ -3822,7 +3831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>57</v>
       </c>
@@ -3872,7 +3881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>57</v>
       </c>
@@ -3916,7 +3925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>57</v>
       </c>
@@ -3968,7 +3977,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>57</v>
       </c>
@@ -4012,7 +4021,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>58</v>
       </c>
@@ -4077,7 +4086,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>58</v>
       </c>
@@ -4120,7 +4129,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>58</v>
       </c>
@@ -4176,7 +4185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>58</v>
       </c>
@@ -4218,7 +4227,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>58</v>
       </c>
@@ -4276,7 +4285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>58</v>
       </c>
@@ -4320,7 +4329,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>59</v>
       </c>
@@ -4367,7 +4376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
         <v>59</v>
       </c>
@@ -4412,7 +4421,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
         <v>59</v>
       </c>
@@ -4459,7 +4468,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>59</v>
       </c>
@@ -4503,7 +4512,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
         <v>60</v>
       </c>
@@ -4552,7 +4561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
         <v>60</v>
       </c>
@@ -4595,7 +4604,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>61</v>
       </c>
@@ -4630,7 +4639,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>61</v>
       </c>
@@ -4668,7 +4677,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B83" s="3" t="s">
         <v>62</v>
       </c>
@@ -4713,7 +4722,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B84" s="3" t="s">
         <v>62</v>
       </c>
@@ -4758,7 +4767,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
         <v>62</v>
       </c>
@@ -4801,7 +4810,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B86" s="3" t="s">
         <v>62</v>
       </c>
@@ -4839,7 +4848,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
         <v>62</v>
       </c>
@@ -4879,7 +4888,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
         <v>62</v>
       </c>
@@ -4917,7 +4926,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>62</v>
       </c>
@@ -4957,7 +4966,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B90" s="3" t="s">
         <v>62</v>
       </c>
@@ -4995,7 +5004,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B91" s="3" t="s">
         <v>62</v>
       </c>
@@ -5038,7 +5047,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
         <v>62</v>
       </c>
@@ -5076,7 +5085,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
         <v>62</v>
       </c>
@@ -5116,7 +5125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B94" s="3" t="s">
         <v>62</v>
       </c>
@@ -5154,7 +5163,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
         <v>62</v>
       </c>
@@ -5194,7 +5203,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>62</v>
       </c>
@@ -5232,7 +5241,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="3" t="s">
         <v>62</v>
       </c>
@@ -5272,7 +5281,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
         <v>62</v>
       </c>
@@ -5310,7 +5319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" s="3" t="s">
         <v>62</v>
       </c>
@@ -5350,7 +5359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" s="3" t="s">
         <v>62</v>
       </c>
@@ -5388,7 +5397,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" s="3" t="s">
         <v>62</v>
       </c>
@@ -5431,7 +5440,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" s="3" t="s">
         <v>62</v>
       </c>
@@ -5469,7 +5478,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
         <v>62</v>
       </c>
@@ -5514,7 +5523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" s="3" t="s">
         <v>62</v>
       </c>
@@ -5552,7 +5561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" s="3" t="s">
         <v>62</v>
       </c>
@@ -5597,7 +5606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="3" t="s">
         <v>62</v>
       </c>
@@ -5635,7 +5644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
         <v>62</v>
       </c>
@@ -5678,7 +5687,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" s="3" t="s">
         <v>62</v>
       </c>
@@ -5716,7 +5725,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
         <v>62</v>
       </c>
@@ -5759,7 +5768,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
         <v>62</v>
       </c>
@@ -5797,7 +5806,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B111" s="3" t="s">
         <v>62</v>
       </c>
@@ -5842,7 +5851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B112" s="3" t="s">
         <v>62</v>
       </c>
@@ -5880,7 +5889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B113" s="3" t="s">
         <v>62</v>
       </c>
@@ -5926,7 +5935,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B114" s="3" t="s">
         <v>62</v>
       </c>
@@ -5969,7 +5978,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
         <v>63</v>
       </c>
@@ -6017,7 +6026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" s="3" t="s">
         <v>63</v>
       </c>
@@ -6060,7 +6069,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
         <v>63</v>
       </c>
@@ -6105,7 +6114,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
         <v>63</v>
       </c>
@@ -6143,7 +6152,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
         <v>63</v>
       </c>
@@ -6186,7 +6195,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
         <v>63</v>
       </c>
@@ -6224,7 +6233,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
         <v>63</v>
       </c>
@@ -6269,7 +6278,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
         <v>63</v>
       </c>
@@ -6307,7 +6316,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" s="3" t="s">
         <v>63</v>
       </c>
@@ -6352,7 +6361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" s="3" t="s">
         <v>63</v>
       </c>
@@ -6390,7 +6399,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" s="3" t="s">
         <v>63</v>
       </c>
@@ -6433,7 +6442,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" s="3" t="s">
         <v>63</v>
       </c>
@@ -6471,7 +6480,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" s="3" t="s">
         <v>63</v>
       </c>
@@ -6514,7 +6523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" s="3" t="s">
         <v>63</v>
       </c>
@@ -6552,7 +6561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" s="3" t="s">
         <v>63</v>
       </c>
@@ -6595,7 +6604,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" s="3" t="s">
         <v>63</v>
       </c>
@@ -6633,7 +6642,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" s="3" t="s">
         <v>63</v>
       </c>
@@ -6678,7 +6687,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
         <v>63</v>
       </c>
@@ -6719,7 +6728,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" s="3" t="s">
         <v>64</v>
       </c>
@@ -6776,7 +6785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B134" s="3" t="s">
         <v>64</v>
       </c>
@@ -6819,7 +6828,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B135" s="3" t="s">
         <v>64</v>
       </c>
@@ -6865,7 +6874,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B136" s="3" t="s">
         <v>64</v>
       </c>
@@ -6908,7 +6917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B137" s="3" t="s">
         <v>64</v>
       </c>
@@ -6954,7 +6963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" s="3" t="s">
         <v>64</v>
       </c>
@@ -6997,7 +7006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>65</v>
       </c>
@@ -7046,7 +7055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>65</v>
       </c>
@@ -7087,7 +7096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>65</v>
       </c>
@@ -7137,7 +7146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>65</v>
       </c>
@@ -7182,7 +7191,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" s="3" t="s">
         <v>66</v>
       </c>
@@ -7228,7 +7237,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" s="3" t="s">
         <v>66</v>
       </c>
@@ -7266,7 +7275,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>67</v>
       </c>
@@ -7304,7 +7313,7 @@
       <c r="AE145" s="4"/>
       <c r="AF145" s="4"/>
     </row>
-    <row r="146" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>67</v>
       </c>
@@ -7339,7 +7348,7 @@
       <c r="AE146" s="4"/>
       <c r="AF146" s="4"/>
     </row>
-    <row r="147" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>68</v>
       </c>
@@ -7374,7 +7383,7 @@
       <c r="AE147" s="4"/>
       <c r="AF147" s="4"/>
     </row>
-    <row r="148" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>68</v>
       </c>
@@ -7409,7 +7418,7 @@
       <c r="AE148" s="4"/>
       <c r="AF148" s="4"/>
     </row>
-    <row r="149" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>69</v>
       </c>
@@ -7450,7 +7459,7 @@
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
     </row>
-    <row r="150" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>69</v>
       </c>
@@ -7464,7 +7473,7 @@
         <v>1799.2</v>
       </c>
       <c r="F150" s="3">
-        <v>1403.2</v>
+        <v>1432.2</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7483,7 +7492,7 @@
         <v>888</v>
       </c>
       <c r="Z150" s="4">
-        <v>515.20000000000005</v>
+        <v>544.20000000000005</v>
       </c>
       <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
@@ -7495,7 +7504,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>70</v>
       </c>
@@ -7527,7 +7536,7 @@
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
     </row>
-    <row r="152" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>70</v>
       </c>
@@ -7562,7 +7571,7 @@
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
     </row>
-    <row r="153" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>71</v>
       </c>
@@ -7597,7 +7606,7 @@
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
     </row>
-    <row r="154" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>71</v>
       </c>
@@ -7632,7 +7641,7 @@
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
     </row>
-    <row r="155" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>72</v>
       </c>
@@ -7670,7 +7679,7 @@
         <v>1746.61</v>
       </c>
     </row>
-    <row r="156" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>72</v>
       </c>
@@ -7708,7 +7717,7 @@
         <v>1471.49</v>
       </c>
     </row>
-    <row r="157" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>73</v>
       </c>
@@ -7747,7 +7756,7 @@
         <v>275.11999999999989</v>
       </c>
     </row>
-    <row r="158" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>73</v>
       </c>
@@ -7782,7 +7791,7 @@
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
     </row>
-    <row r="159" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" s="3" t="s">
         <v>75</v>
       </c>
@@ -7843,7 +7852,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="160" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" s="3" t="s">
         <v>75</v>
       </c>
@@ -7896,7 +7905,7 @@
         <v>91.706666666666635</v>
       </c>
     </row>
-    <row r="161" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" s="3" t="s">
         <v>75</v>
       </c>
@@ -7955,7 +7964,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="162" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" s="3" t="s">
         <v>75</v>
       </c>
@@ -8001,7 +8010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="163" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" s="3" t="s">
         <v>75</v>
       </c>
@@ -8050,7 +8059,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="164" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" s="3" t="s">
         <v>75</v>
       </c>
@@ -8093,7 +8102,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="165" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>76</v>
       </c>
@@ -8131,7 +8140,7 @@
       <c r="AE165" s="4"/>
       <c r="AF165" s="4"/>
     </row>
-    <row r="166" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>76</v>
       </c>
@@ -8166,7 +8175,7 @@
       <c r="AE166" s="4"/>
       <c r="AF166" s="4"/>
     </row>
-    <row r="167" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>77</v>
       </c>
@@ -8198,7 +8207,7 @@
       <c r="AE167" s="4"/>
       <c r="AF167" s="4"/>
     </row>
-    <row r="168" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>77</v>
       </c>
@@ -8233,7 +8242,7 @@
       <c r="AE168" s="4"/>
       <c r="AF168" s="4"/>
     </row>
-    <row r="169" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
         <v>78</v>
       </c>
@@ -8279,7 +8288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B170" s="3" t="s">
         <v>78</v>
       </c>
@@ -8317,7 +8326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B171" s="3" t="s">
         <v>78</v>
       </c>
@@ -8366,7 +8375,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B172" s="3" t="s">
         <v>78</v>
       </c>
@@ -8409,7 +8418,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>79</v>
       </c>
@@ -8447,7 +8456,7 @@
       <c r="AE173" s="4"/>
       <c r="AF173" s="4"/>
     </row>
-    <row r="174" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>79</v>
       </c>
@@ -8482,7 +8491,7 @@
       <c r="AE174" s="4"/>
       <c r="AF174" s="4"/>
     </row>
-    <row r="175" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>80</v>
       </c>
@@ -8514,7 +8523,7 @@
       <c r="AE175" s="4"/>
       <c r="AF175" s="4"/>
     </row>
-    <row r="176" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>80</v>
       </c>
@@ -8549,7 +8558,7 @@
       <c r="AE176" s="4"/>
       <c r="AF176" s="4"/>
     </row>
-    <row r="177" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>81</v>
       </c>
@@ -8587,7 +8596,7 @@
       <c r="AE177" s="4"/>
       <c r="AF177" s="4"/>
     </row>
-    <row r="178" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>81</v>
       </c>
@@ -8622,7 +8631,7 @@
       <c r="AE178" s="4"/>
       <c r="AF178" s="4"/>
     </row>
-    <row r="179" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>82</v>
       </c>
@@ -8654,7 +8663,7 @@
       <c r="AE179" s="4"/>
       <c r="AF179" s="4"/>
     </row>
-    <row r="180" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>82</v>
       </c>
@@ -8689,7 +8698,7 @@
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
     </row>
-    <row r="181" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" s="3" t="s">
         <v>83</v>
       </c>
@@ -8738,7 +8747,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" s="3" t="s">
         <v>83</v>
       </c>
@@ -8782,7 +8791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>84</v>
       </c>
@@ -8817,7 +8826,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>84</v>
       </c>
@@ -8857,7 +8866,7 @@
       <c r="AE184" s="4"/>
       <c r="AF184" s="4"/>
     </row>
-    <row r="185" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>85</v>
       </c>
@@ -8895,7 +8904,7 @@
       <c r="AE185" s="4"/>
       <c r="AF185" s="4"/>
     </row>
-    <row r="186" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>85</v>
       </c>
@@ -8930,7 +8939,7 @@
       <c r="AE186" s="4"/>
       <c r="AF186" s="4"/>
     </row>
-    <row r="187" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>86</v>
       </c>
@@ -8965,7 +8974,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>86</v>
       </c>
@@ -9008,7 +9017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>87</v>
       </c>
@@ -9040,7 +9049,7 @@
       <c r="AE189" s="4"/>
       <c r="AF189" s="4"/>
     </row>
-    <row r="190" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>87</v>
       </c>
@@ -9075,7 +9084,7 @@
       <c r="AE190" s="4"/>
       <c r="AF190" s="4"/>
     </row>
-    <row r="191" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>88</v>
       </c>
@@ -9107,7 +9116,7 @@
       <c r="AE191" s="4"/>
       <c r="AF191" s="4"/>
     </row>
-    <row r="192" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>88</v>
       </c>
@@ -9142,7 +9151,7 @@
       <c r="AE192" s="4"/>
       <c r="AF192" s="4"/>
     </row>
-    <row r="193" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>89</v>
       </c>
@@ -9174,7 +9183,7 @@
       <c r="AE193" s="4"/>
       <c r="AF193" s="4"/>
     </row>
-    <row r="194" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>89</v>
       </c>
@@ -9209,7 +9218,7 @@
       <c r="AE194" s="4"/>
       <c r="AF194" s="4"/>
     </row>
-    <row r="195" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>90</v>
       </c>
@@ -9253,7 +9262,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>90</v>
       </c>
@@ -9291,7 +9300,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>91</v>
       </c>
@@ -9326,7 +9335,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>91</v>
       </c>
@@ -9364,7 +9373,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>92</v>
       </c>
@@ -9399,7 +9408,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>92</v>
       </c>
@@ -9478,6 +9487,9 @@
       <c r="AD201" s="4"/>
       <c r="AE201" s="4"/>
       <c r="AF201" s="4"/>
+      <c r="AG201" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="202" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
@@ -9513,8 +9525,11 @@
       <c r="AD202" s="4"/>
       <c r="AE202" s="4"/>
       <c r="AF202" s="4"/>
-    </row>
-    <row r="203" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG202" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="203" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>94</v>
       </c>
@@ -9546,7 +9561,7 @@
       <c r="AE203" s="4"/>
       <c r="AF203" s="4"/>
     </row>
-    <row r="204" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>94</v>
       </c>
@@ -9581,7 +9596,7 @@
       <c r="AE204" s="4"/>
       <c r="AF204" s="4"/>
     </row>
-    <row r="205" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>95</v>
       </c>
@@ -9621,7 +9636,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>95</v>
       </c>
@@ -9656,7 +9671,7 @@
       <c r="AE206" s="4"/>
       <c r="AF206" s="4"/>
     </row>
-    <row r="207" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>96</v>
       </c>
@@ -9691,7 +9706,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>96</v>
       </c>
@@ -9736,7 +9751,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="209" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" s="3" t="s">
         <v>62</v>
       </c>
@@ -9779,7 +9794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" s="3" t="s">
         <v>62</v>
       </c>
@@ -9817,7 +9832,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>98</v>
       </c>
@@ -9863,7 +9878,7 @@
       <c r="AE211" s="4"/>
       <c r="AF211" s="4"/>
     </row>
-    <row r="212" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>98</v>
       </c>
@@ -9907,7 +9922,7 @@
       <c r="AE212" s="4"/>
       <c r="AF212" s="4"/>
     </row>
-    <row r="213" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>100</v>
       </c>
@@ -9942,7 +9957,7 @@
       <c r="AE213" s="4"/>
       <c r="AF213" s="4"/>
     </row>
-    <row r="214" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>100</v>
       </c>
@@ -9977,7 +9992,7 @@
       <c r="AE214" s="4"/>
       <c r="AF214" s="4"/>
     </row>
-    <row r="215" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>102</v>
       </c>
@@ -10012,7 +10027,7 @@
       <c r="AE215" s="4"/>
       <c r="AF215" s="4"/>
     </row>
-    <row r="216" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>102</v>
       </c>
@@ -10047,7 +10062,7 @@
       <c r="AE216" s="4"/>
       <c r="AF216" s="4"/>
     </row>
-    <row r="217" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>104</v>
       </c>
@@ -10079,7 +10094,7 @@
       <c r="AE217" s="4"/>
       <c r="AF217" s="4"/>
     </row>
-    <row r="218" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>104</v>
       </c>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFBE20F-9C81-4ABA-8E0B-45582CC3C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED96A70-3D12-4F17-AEF2-A3ACCDE3CC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -9436,7 +9436,7 @@
         <v>180</v>
       </c>
       <c r="F200" s="3">
-        <v>160.86000000000001</v>
+        <v>167.96</v>
       </c>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
@@ -9455,9 +9455,11 @@
         <v>43.66</v>
       </c>
       <c r="Z200" s="9">
-        <v>198.8</v>
-      </c>
-      <c r="AA200" s="4"/>
+        <v>89.8</v>
+      </c>
+      <c r="AA200" s="4">
+        <v>34.5</v>
+      </c>
       <c r="AB200" s="4"/>
       <c r="AC200" s="4"/>
       <c r="AD200" s="4"/>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED96A70-3D12-4F17-AEF2-A3ACCDE3CC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD004AC-E1EE-4D7E-B6E0-236C936CEFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -262,9 +262,6 @@
   </si>
   <si>
     <t>CTS MAR DE CORAL</t>
-  </si>
-  <si>
-    <t>concuido</t>
   </si>
   <si>
     <t xml:space="preserve">REC JD. SÃO MARTINHO </t>
@@ -802,7 +799,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
-  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="RCE COMUNIDADE JD. UNIÃO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF218">
+    <sortCondition ref="B1:B218"/>
+  </sortState>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Obra"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bloco"/>
@@ -1253,36 +1259,47 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
       </c>
       <c r="E2">
-        <v>156.30000000000001</v>
-      </c>
-      <c r="F2" s="3">
-        <v>150.44999999999999</v>
+        <v>561.5</v>
+      </c>
+      <c r="F2" s="7">
+        <v>445.49</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="H2">
+        <v>186.84</v>
+      </c>
+      <c r="I2">
+        <v>443</v>
+      </c>
+      <c r="J2">
+        <v>2397</v>
       </c>
       <c r="L2" s="4"/>
-      <c r="M2" s="6">
-        <v>150.44999999999999</v>
-      </c>
+      <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="S2" s="4">
+        <v>162.16499999999999</v>
+      </c>
+      <c r="T2" s="4">
+        <v>283.32499999999999</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1299,33 +1316,33 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
       </c>
       <c r="E3">
-        <v>37.4</v>
-      </c>
-      <c r="F3" s="3">
-        <v>27</v>
+        <v>144.5</v>
+      </c>
+      <c r="F3" s="7">
+        <v>75.599999999999994</v>
       </c>
       <c r="L3" s="4"/>
-      <c r="M3" s="6">
-        <v>27</v>
-      </c>
+      <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="T3" s="4">
+        <v>75.599999999999994</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -1342,35 +1359,36 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="3">
-        <v>59.64</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
+      <c r="E4">
+        <v>451.5</v>
+      </c>
+      <c r="F4" s="7">
+        <v>629.14</v>
+      </c>
+      <c r="I4">
+        <v>788</v>
       </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="6">
-        <v>47.94</v>
-      </c>
-      <c r="N4" s="6">
-        <v>11.7</v>
-      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="T4" s="4">
+        <v>629.14</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1387,25 +1405,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
       </c>
       <c r="E5">
-        <v>108.9</v>
-      </c>
-      <c r="F5" s="3">
-        <v>47.5</v>
-      </c>
-      <c r="L5" s="6">
-        <v>47.5</v>
-      </c>
+        <v>144.5</v>
+      </c>
+      <c r="F5" s="7">
+        <v>37.89</v>
+      </c>
+      <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -1413,7 +1429,9 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="T5" s="4">
+        <v>37.89</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -1430,33 +1448,36 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="3">
-        <v>105.6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="E6">
+        <v>322</v>
+      </c>
+      <c r="F6" s="7">
+        <v>108.02</v>
+      </c>
+      <c r="I6">
+        <v>654</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="6">
-        <v>105.6</v>
-      </c>
+      <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="T6" s="4">
+        <v>108.02</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1473,33 +1494,33 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
       </c>
       <c r="E7">
-        <v>112.7</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2.2999999999999998</v>
+        <v>100</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1.55</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="6">
-        <v>2.2999999999999998</v>
-      </c>
+      <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="T7" s="4">
+        <v>1.55</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1516,32 +1537,28 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8">
-        <v>109.9</v>
+        <v>298</v>
       </c>
       <c r="F8" s="3">
-        <v>131.43</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
+        <v>363.85</v>
+      </c>
+      <c r="I8">
+        <v>223</v>
       </c>
       <c r="L8" s="4"/>
-      <c r="M8" s="6">
-        <v>66.83</v>
-      </c>
-      <c r="N8" s="6">
-        <v>64.599999999999994</v>
-      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -1549,8 +1566,12 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
+      <c r="V8" s="4">
+        <v>329.56</v>
+      </c>
+      <c r="W8" s="4">
+        <v>34.29</v>
+      </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
       <c r="Z8" s="9"/>
@@ -1564,24 +1585,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>36</v>
       </c>
       <c r="E9">
-        <v>18.8</v>
-      </c>
-      <c r="I9">
-        <v>2305</v>
-      </c>
-      <c r="J9">
-        <v>2706</v>
+        <v>113.5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>19.84</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1595,7 +1613,9 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="X9" s="4">
+        <v>19.84</v>
+      </c>
       <c r="Y9" s="4"/>
       <c r="Z9" s="9"/>
       <c r="AA9" s="4"/>
@@ -1608,50 +1628,38 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F10" s="3">
-        <v>523.65499999999997</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>136.19</v>
-      </c>
-      <c r="I10">
-        <v>797</v>
-      </c>
-      <c r="J10">
-        <v>599</v>
+        <v>89.05</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="6">
-        <v>217.93</v>
-      </c>
-      <c r="O10" s="6">
-        <v>305.72500000000002</v>
-      </c>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
+      <c r="V10" s="4">
+        <v>32.99</v>
+      </c>
+      <c r="W10" s="4">
+        <v>56.06</v>
+      </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="9"/>
@@ -1665,18 +1673,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>36</v>
       </c>
       <c r="E11">
-        <v>469.7</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1703,43 +1711,35 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12">
-        <v>124.2</v>
+        <v>68.5</v>
       </c>
       <c r="F12" s="3">
-        <v>342.71</v>
-      </c>
-      <c r="I12">
-        <v>91</v>
-      </c>
-      <c r="J12">
-        <v>595</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="6">
-        <v>134.10499999999999</v>
-      </c>
-      <c r="P12" s="6">
-        <v>208.60499999999999</v>
-      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="V12" s="4">
+        <v>35.479999999999997</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1754,21 +1754,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>36</v>
       </c>
       <c r="E13">
-        <v>83</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -1795,44 +1792,38 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14">
-        <v>240.7</v>
+        <v>216.5</v>
       </c>
       <c r="F14" s="3">
-        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]</f>
-        <v>159.47499999999999</v>
-      </c>
-      <c r="I14">
-        <v>589</v>
-      </c>
-      <c r="J14">
-        <v>109</v>
+        <v>206.17</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="6">
-        <f>231.85-72.375</f>
-        <v>159.47499999999999</v>
-      </c>
+      <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
+      <c r="V14" s="4">
+        <v>129.66999999999999</v>
+      </c>
+      <c r="W14" s="4">
+        <v>76.5</v>
+      </c>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
       <c r="Z14" s="9"/>
@@ -1846,29 +1837,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
         <v>36</v>
       </c>
       <c r="E15">
-        <v>118.5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4.0599999999999996</v>
+        <v>86</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="6">
-        <v>4.0599999999999996</v>
-      </c>
+      <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -1889,46 +1875,38 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3">
-        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]</f>
-        <v>295.33500000000004</v>
-      </c>
-      <c r="I16">
-        <v>614</v>
-      </c>
-      <c r="J16">
-        <v>3229</v>
+        <v>97.16</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="6">
-        <f>132.27-72.375</f>
-        <v>59.89500000000001</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>235.44</v>
-      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
+      <c r="V16" s="4">
+        <v>68.16</v>
+      </c>
+      <c r="W16" s="4">
+        <v>29</v>
+      </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
       <c r="Z16" s="9"/>
@@ -1942,18 +1920,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
         <v>36</v>
       </c>
       <c r="E17">
-        <v>232.1</v>
+        <v>40.5</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1980,41 +1958,35 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
       </c>
       <c r="E18">
-        <v>70.5</v>
+        <v>87.5</v>
       </c>
       <c r="F18" s="3">
-        <v>253.94</v>
-      </c>
-      <c r="I18">
-        <v>2964</v>
-      </c>
-      <c r="J18">
-        <v>42</v>
+        <v>35.42</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="4">
-        <v>253.94</v>
-      </c>
+      <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
+      <c r="V18" s="4">
+        <v>35.42</v>
+      </c>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2029,39 +2001,28 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19">
-        <v>754</v>
-      </c>
-      <c r="F19" s="3">
-        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]+tb_base_dash_extensao[[#This Row],[produção Dezembro 2025]]</f>
-        <v>373.08500000000004</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="4">
-        <f>242.97-72.375</f>
-        <v>170.595</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>148.49</v>
-      </c>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
-      <c r="T19" s="4">
-        <v>54</v>
-      </c>
+      <c r="T19" s="4"/>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -2078,33 +2039,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="F20" s="3">
-        <v>192.04</v>
-      </c>
-      <c r="G20">
-        <v>8</v>
-      </c>
-      <c r="H20">
-        <v>26.74</v>
-      </c>
-      <c r="I20">
-        <v>322</v>
-      </c>
-      <c r="J20">
-        <v>661</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2112,13 +2061,13 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
-      <c r="R20" s="4">
-        <v>192.04</v>
-      </c>
+      <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
+      <c r="V20" s="4">
+        <v>34.409999999999997</v>
+      </c>
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
@@ -2133,21 +2082,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
         <v>36</v>
       </c>
       <c r="E21">
-        <v>44.2</v>
-      </c>
-      <c r="F21" s="3">
-        <v>19.91</v>
+        <v>2</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2155,9 +2101,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
-      <c r="R21" s="4">
-        <v>19.91</v>
-      </c>
+      <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -2176,27 +2120,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22">
-        <v>291.8</v>
+        <v>109</v>
       </c>
       <c r="F22" s="3">
-        <v>259.3</v>
-      </c>
-      <c r="I22">
-        <v>723</v>
-      </c>
-      <c r="J22">
-        <v>270</v>
+        <v>47.44</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2204,13 +2142,13 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
-      <c r="R22" s="4">
-        <v>259.3</v>
-      </c>
+      <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
+      <c r="V22" s="4">
+        <v>47.44</v>
+      </c>
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
@@ -2225,21 +2163,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
         <v>36</v>
       </c>
       <c r="E23">
-        <v>208.6</v>
-      </c>
-      <c r="F23" s="3">
-        <v>39.75</v>
+        <v>9.5</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2247,9 +2182,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
-      <c r="R23" s="4">
-        <v>39.75</v>
-      </c>
+      <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -2268,21 +2201,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>39</v>
+    <row r="24" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
         <v>34</v>
       </c>
       <c r="E24">
-        <v>457</v>
-      </c>
-      <c r="I24">
-        <v>43</v>
+        <v>255</v>
+      </c>
+      <c r="F24" s="3">
+        <v>255.86</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2294,9 +2227,13 @@
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
+      <c r="V24" s="4">
+        <v>67.05</v>
+      </c>
       <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
+      <c r="X24" s="4">
+        <v>188.81</v>
+      </c>
       <c r="Y24" s="4"/>
       <c r="Z24" s="9"/>
       <c r="AA24" s="4"/>
@@ -2309,15 +2246,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>39</v>
+    <row r="25" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
+      </c>
+      <c r="E25">
+        <v>144</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2344,18 +2287,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>41</v>
+    <row r="26" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
         <v>34</v>
       </c>
-      <c r="E26">
-        <v>137</v>
+      <c r="F26" s="3">
+        <v>91.21</v>
+      </c>
+      <c r="I26">
+        <v>2885</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2367,9 +2313,13 @@
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
+      <c r="V26" s="4">
+        <v>20.95</v>
+      </c>
       <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
+      <c r="X26" s="4">
+        <v>70.260000000000005</v>
+      </c>
       <c r="Y26" s="4"/>
       <c r="Z26" s="9"/>
       <c r="AA26" s="4"/>
@@ -2379,18 +2329,21 @@
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
     </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>41</v>
+    <row r="27" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
       </c>
       <c r="E27">
-        <v>636</v>
+        <v>100.5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>10.06</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2402,9 +2355,13 @@
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
+      <c r="V27" s="4">
+        <v>8.06</v>
+      </c>
       <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
+      <c r="X27" s="4">
+        <v>2</v>
+      </c>
       <c r="Y27" s="4"/>
       <c r="Z27" s="9"/>
       <c r="AA27" s="4"/>
@@ -2414,18 +2371,18 @@
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
     </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>42</v>
+    <row r="28" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
-      <c r="E28">
-        <v>20</v>
+      <c r="F28" s="3">
+        <v>230.72</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2437,8 +2394,13 @@
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
+      <c r="V28" s="4">
+        <f>230.02-55.56</f>
+        <v>174.46</v>
+      </c>
+      <c r="W28" s="4">
+        <v>56.26</v>
+      </c>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
       <c r="Z28" s="9"/>
@@ -2449,15 +2411,18 @@
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
     </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>42</v>
+    <row r="29" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
         <v>36</v>
+      </c>
+      <c r="E29">
+        <v>210.02</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2481,15 +2446,18 @@
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
     </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>43</v>
+    <row r="30" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
         <v>34</v>
+      </c>
+      <c r="F30" s="3">
+        <v>35.5</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2501,7 +2469,9 @@
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
+      <c r="V30" s="4">
+        <v>35.5</v>
+      </c>
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
@@ -2513,18 +2483,18 @@
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
     </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>43</v>
+    <row r="31" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
         <v>36</v>
       </c>
       <c r="E31">
-        <v>110</v>
+        <v>57.5</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2548,18 +2518,18 @@
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
     </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
-        <v>44</v>
+    <row r="32" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="3">
-        <v>38.299999999999997</v>
+        <v>36.979999999999997</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2571,13 +2541,13 @@
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
+      <c r="V32" s="4">
+        <v>36.979999999999997</v>
+      </c>
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
-      <c r="Z32" s="9">
-        <v>38.299999999999997</v>
-      </c>
+      <c r="Z32" s="9"/>
       <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
       <c r="AC32" s="4"/>
@@ -2588,18 +2558,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>44</v>
+    <row r="33" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
       </c>
       <c r="E33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2626,15 +2596,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>45</v>
+    <row r="34" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
         <v>34</v>
+      </c>
+      <c r="F34" s="3">
+        <v>39.04</v>
+      </c>
+      <c r="J34">
+        <v>628</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -2646,7 +2622,9 @@
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
+      <c r="V34" s="4">
+        <v>39.04</v>
+      </c>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
@@ -2658,18 +2636,18 @@
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
     </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>45</v>
+    <row r="35" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
         <v>36</v>
       </c>
       <c r="E35">
-        <v>34</v>
+        <v>39.5</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -2693,15 +2671,18 @@
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
     </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
-        <v>46</v>
+    <row r="36" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
+      </c>
+      <c r="F36" s="3">
+        <v>34.42</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
@@ -2713,7 +2694,9 @@
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
+      <c r="V36" s="4">
+        <v>34.42</v>
+      </c>
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
@@ -2725,18 +2708,18 @@
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
-        <v>46</v>
+    <row r="37" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
         <v>36</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>63.5</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -2760,15 +2743,18 @@
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="1">
-        <v>12</v>
+    <row r="38" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38">
+        <v>33</v>
       </c>
       <c r="D38" t="s">
         <v>34</v>
+      </c>
+      <c r="F38" s="3">
+        <v>34.119999999999997</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -2780,7 +2766,9 @@
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
+      <c r="V38" s="4">
+        <v>34.119999999999997</v>
+      </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
@@ -2795,21 +2783,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="1">
-        <v>12</v>
+    <row r="39" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39">
+        <v>33</v>
       </c>
       <c r="D39" t="s">
         <v>36</v>
       </c>
       <c r="E39">
-        <v>205</v>
-      </c>
-      <c r="F39" s="3">
-        <v>169.1</v>
+        <v>67.5</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -2825,9 +2810,7 @@
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
-      <c r="Z39" s="9">
-        <v>169.1</v>
-      </c>
+      <c r="Z39" s="9"/>
       <c r="AA39" s="4"/>
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
@@ -2835,18 +2818,18 @@
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
     </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
-        <v>48</v>
+    <row r="40" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s">
         <v>34</v>
       </c>
-      <c r="I40">
-        <v>11130</v>
+      <c r="F40" s="3">
+        <v>32.11</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -2858,7 +2841,9 @@
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
+      <c r="V40" s="4">
+        <v>32.11</v>
+      </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
@@ -2870,15 +2855,18 @@
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
     </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
-        <v>48</v>
+    <row r="41" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
         <v>36</v>
+      </c>
+      <c r="E41">
+        <v>67.5</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -2902,18 +2890,18 @@
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
-        <v>49</v>
+    <row r="42" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D42" t="s">
         <v>34</v>
       </c>
-      <c r="E42">
-        <v>1787.905</v>
+      <c r="F42" s="3">
+        <v>35.9</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -2925,7 +2913,9 @@
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
+      <c r="V42" s="4">
+        <v>35.9</v>
+      </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
@@ -2937,15 +2927,18 @@
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>49</v>
+    <row r="43" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s">
         <v>36</v>
+      </c>
+      <c r="E43">
+        <v>84.5</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -2969,18 +2962,21 @@
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>50</v>
+    <row r="44" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C44">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
         <v>34</v>
       </c>
       <c r="E44">
-        <v>1583.28</v>
+        <v>39</v>
+      </c>
+      <c r="F44" s="3">
+        <v>32.19</v>
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -2992,7 +2988,9 @@
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
+      <c r="V44" s="4">
+        <v>32.19</v>
+      </c>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
@@ -3004,15 +3002,18 @@
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>50</v>
+    <row r="45" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C45">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
         <v>36</v>
+      </c>
+      <c r="E45">
+        <v>114.5</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -3036,18 +3037,21 @@
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
-        <v>51</v>
+    <row r="46" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C46">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
         <v>34</v>
       </c>
       <c r="E46">
-        <v>699.23500000000001</v>
+        <v>35</v>
+      </c>
+      <c r="F46" s="3">
+        <v>76.599999999999994</v>
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -3059,8 +3063,12 @@
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="4"/>
+      <c r="V46" s="4">
+        <v>37.72</v>
+      </c>
+      <c r="W46" s="4">
+        <v>38.880000000000003</v>
+      </c>
       <c r="X46" s="4"/>
       <c r="Y46" s="4"/>
       <c r="Z46" s="9"/>
@@ -3071,18 +3079,18 @@
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
-        <v>51</v>
+    <row r="47" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C47">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
         <v>36</v>
       </c>
       <c r="E47">
-        <v>166.2</v>
+        <v>58.5</v>
       </c>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -3106,18 +3114,21 @@
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
-        <v>52</v>
+    <row r="48" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C48">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
         <v>34</v>
       </c>
       <c r="E48">
-        <v>820.2</v>
+        <v>61.5</v>
+      </c>
+      <c r="F48" s="3">
+        <v>84.62</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -3129,8 +3140,12 @@
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
+      <c r="V48" s="4">
+        <v>36.840000000000003</v>
+      </c>
+      <c r="W48" s="4">
+        <v>47.78</v>
+      </c>
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
       <c r="Z48" s="9"/>
@@ -3141,18 +3156,18 @@
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
     </row>
-    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
-        <v>52</v>
+    <row r="49" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C49">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D49" t="s">
         <v>36</v>
       </c>
       <c r="E49">
-        <v>191.4</v>
+        <v>37.5</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -3176,18 +3191,21 @@
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
     </row>
-    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
-        <v>53</v>
+    <row r="50" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D50" t="s">
         <v>34</v>
       </c>
       <c r="E50">
-        <v>165</v>
+        <v>65.5</v>
+      </c>
+      <c r="F50" s="3">
+        <v>35.5</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -3199,7 +3217,9 @@
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
+      <c r="V50" s="4">
+        <v>35.5</v>
+      </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4"/>
@@ -3211,18 +3231,18 @@
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
     </row>
-    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
-        <v>53</v>
+    <row r="51" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C51">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
         <v>36</v>
       </c>
       <c r="E51">
-        <v>43.5</v>
+        <v>32.5</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -3246,15 +3266,21 @@
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
     </row>
-    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
-        <v>54</v>
+    <row r="52" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
         <v>34</v>
+      </c>
+      <c r="E52">
+        <v>91.5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>34.380000000000003</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -3266,7 +3292,9 @@
       <c r="S52" s="4"/>
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
+      <c r="V52" s="4">
+        <v>34.380000000000003</v>
+      </c>
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
@@ -3278,20 +3306,19 @@
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
     </row>
-    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
-        <v>54</v>
+    <row r="53" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C53">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D53" t="s">
         <v>36</v>
       </c>
       <c r="E53">
-        <v>201.5</v>
-      </c>
-      <c r="K53" s="2"/>
+        <v>5.5</v>
+      </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
@@ -3314,23 +3341,22 @@
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
     </row>
-    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C54">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
         <v>34</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="F54" s="3">
-        <v>320.31299999999999</v>
-      </c>
-      <c r="K54" s="2"/>
+        <v>167.19</v>
+      </c>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
@@ -3341,16 +3367,15 @@
       <c r="S54" s="4"/>
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
+      <c r="V54" s="4">
+        <v>43.97</v>
+      </c>
+      <c r="W54" s="4">
+        <v>123.22</v>
+      </c>
       <c r="X54" s="4"/>
-      <c r="Y54" s="4">
-        <f>78.58+84.32+66.57+78.843</f>
-        <v>308.31299999999999</v>
-      </c>
-      <c r="Z54" s="9">
-        <v>12</v>
-      </c>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="9"/>
       <c r="AA54" s="4"/>
       <c r="AB54" s="4"/>
       <c r="AC54" s="4"/>
@@ -3361,41 +3386,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C55">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D55" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E55">
-        <v>267</v>
-      </c>
-      <c r="F55" s="3">
-        <v>400</v>
-      </c>
-      <c r="I55">
-        <v>41</v>
-      </c>
-      <c r="J55">
-        <v>39</v>
-      </c>
-      <c r="K55" s="2"/>
+        <v>2</v>
+      </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
-      <c r="R55" s="4">
-        <v>75</v>
-      </c>
-      <c r="S55" s="4">
-        <v>325</v>
-      </c>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
@@ -3413,23 +3424,25 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E56">
-        <v>233.1</v>
+        <v>75</v>
       </c>
       <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="J56">
+        <v>531</v>
+      </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
@@ -3441,7 +3454,9 @@
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
+      <c r="W56" s="4">
+        <v>189</v>
+      </c>
       <c r="X56" s="4"/>
       <c r="Y56" s="4"/>
       <c r="Z56" s="9"/>
@@ -3455,29 +3470,22 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C57">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="F57" s="3">
-        <v>157.69999999999999</v>
-      </c>
-      <c r="I57">
-        <v>464</v>
-      </c>
-      <c r="J57">
-        <v>523</v>
-      </c>
-      <c r="K57" s="2"/>
+        <v>70.930000000000007</v>
+      </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
@@ -3486,14 +3494,12 @@
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
       <c r="S57" s="4"/>
-      <c r="T57" s="4">
-        <v>35</v>
-      </c>
-      <c r="U57" s="4">
-        <v>122.7</v>
-      </c>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
       <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
+      <c r="W57" s="4">
+        <v>70.930000000000007</v>
+      </c>
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
       <c r="Z57" s="9"/>
@@ -3507,23 +3513,22 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58">
-        <v>15</v>
+        <v>62</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="D58" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E58">
-        <v>243.8</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="2"/>
+        <v>34.57</v>
+      </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
@@ -3534,7 +3539,9 @@
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
+      <c r="V58" s="4">
+        <v>34.57</v>
+      </c>
       <c r="W58" s="4"/>
       <c r="X58" s="4"/>
       <c r="Y58" s="4"/>
@@ -3549,29 +3556,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59">
-        <v>16</v>
+        <v>62</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="D59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>341.71499999999997</v>
-      </c>
-      <c r="I59">
-        <v>2139</v>
-      </c>
-      <c r="J59">
-        <v>2126</v>
-      </c>
-      <c r="K59" s="2"/>
+        <v>158</v>
+      </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
@@ -3579,12 +3576,8 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
-      <c r="S59" s="4">
-        <v>220</v>
-      </c>
-      <c r="T59" s="4">
-        <v>121.715</v>
-      </c>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
@@ -3601,34 +3594,55 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E60">
-        <v>276.10000000000002</v>
-      </c>
-      <c r="F60" s="3">
-        <v>13.17</v>
+        <f>475.4-8.8</f>
+        <v>466.59999999999997</v>
+      </c>
+      <c r="F60" s="7">
+        <v>1229.95</v>
+      </c>
+      <c r="G60">
+        <v>19</v>
+      </c>
+      <c r="H60">
+        <v>92.92</v>
+      </c>
+      <c r="I60">
+        <v>78</v>
+      </c>
+      <c r="J60">
+        <v>72</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
+      <c r="N60" s="4">
+        <v>68</v>
+      </c>
+      <c r="O60" s="4">
+        <v>621.84500000000003</v>
+      </c>
+      <c r="P60" s="4">
+        <v>354.52499999999998</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="R60" s="4">
+        <v>117.68</v>
+      </c>
       <c r="S60" s="4"/>
-      <c r="T60" s="4">
-        <v>13.17</v>
-      </c>
+      <c r="T60" s="4"/>
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
@@ -3645,24 +3659,22 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C61">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E61">
+        <f>12.3+771.1</f>
+        <v>783.4</v>
       </c>
       <c r="F61" s="3">
-        <v>43.02</v>
-      </c>
-      <c r="I61">
-        <v>208</v>
-      </c>
-      <c r="J61">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="4"/>
@@ -3673,9 +3685,7 @@
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
       <c r="S61" s="4"/>
-      <c r="T61" s="4">
-        <v>43.015000000000001</v>
-      </c>
+      <c r="T61" s="4"/>
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
@@ -3692,33 +3702,45 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C62">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E62">
-        <v>83.2</v>
-      </c>
-      <c r="F62" s="3">
-        <v>51.05</v>
+        <v>59.5</v>
+      </c>
+      <c r="F62" s="7">
+        <v>328.75</v>
+      </c>
+      <c r="G62">
+        <v>6</v>
+      </c>
+      <c r="H62">
+        <v>16.16</v>
+      </c>
+      <c r="I62">
+        <v>471</v>
+      </c>
+      <c r="J62">
+        <v>338</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
+      <c r="P62" s="4">
+        <v>328.75</v>
+      </c>
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
-      <c r="S62" s="4">
-        <v>51.05</v>
-      </c>
+      <c r="S62" s="4"/>
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
@@ -3736,33 +3758,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C63">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E63">
-        <v>65.5</v>
+        <v>216</v>
       </c>
       <c r="F63" s="3">
-        <v>288.26</v>
-      </c>
-      <c r="G63">
-        <v>17</v>
-      </c>
-      <c r="H63">
-        <v>51.09</v>
-      </c>
-      <c r="I63">
-        <v>139</v>
-      </c>
-      <c r="J63">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="4"/>
@@ -3770,9 +3780,7 @@
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
       <c r="P63" s="4"/>
-      <c r="Q63" s="4">
-        <v>288.26</v>
-      </c>
+      <c r="Q63" s="4"/>
       <c r="R63" s="4"/>
       <c r="S63" s="4"/>
       <c r="T63" s="4"/>
@@ -3792,30 +3800,44 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C64">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E64">
-        <v>226.5</v>
-      </c>
-      <c r="F64" s="3">
-        <v>32.85</v>
+        <v>352.8</v>
+      </c>
+      <c r="F64" s="7">
+        <v>384.67</v>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="H64">
+        <v>24.74</v>
+      </c>
+      <c r="I64">
+        <v>987</v>
+      </c>
+      <c r="J64">
+        <v>901</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
+      <c r="P64" s="4">
+        <v>247.93</v>
+      </c>
       <c r="Q64" s="4">
-        <v>32.85</v>
+        <v>136.74</v>
       </c>
       <c r="R64" s="4"/>
       <c r="S64" s="4"/>
@@ -3836,27 +3858,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C65">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E65">
-        <v>366.4</v>
+        <v>254.9</v>
       </c>
       <c r="F65" s="3">
-        <v>223.29</v>
-      </c>
-      <c r="I65">
-        <v>219</v>
-      </c>
-      <c r="J65">
-        <v>188</v>
+        <v>20.32</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="4"/>
@@ -3864,10 +3880,10 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4">
-        <v>223.29</v>
-      </c>
+      <c r="Q65" s="4">
+        <v>20.32</v>
+      </c>
+      <c r="R65" s="4"/>
       <c r="S65" s="4"/>
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
@@ -3886,21 +3902,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C66">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E66">
-        <v>95.7</v>
+        <v>207.5</v>
       </c>
       <c r="F66" s="3">
-        <v>26.66</v>
+        <v>197.8</v>
+      </c>
+      <c r="I66">
+        <v>1801</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="4"/>
@@ -3908,16 +3927,16 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
       <c r="P66" s="4"/>
-      <c r="Q66" s="4">
-        <v>26.66</v>
-      </c>
+      <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
+      <c r="X66" s="4">
+        <v>197.8</v>
+      </c>
       <c r="Y66" s="4"/>
       <c r="Z66" s="9"/>
       <c r="AA66" s="4"/>
@@ -3930,27 +3949,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C67">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D67" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E67">
-        <v>163.4</v>
+        <v>95</v>
       </c>
       <c r="F67" s="3">
-        <v>159.63</v>
-      </c>
-      <c r="I67">
-        <v>848</v>
-      </c>
-      <c r="J67">
-        <v>860</v>
+        <v>10.73</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="4"/>
@@ -3960,16 +3973,15 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
       <c r="R67" s="4"/>
-      <c r="S67" s="4">
-        <v>59.73</v>
-      </c>
-      <c r="T67" s="4">
-        <v>99.9</v>
-      </c>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
+      <c r="X67" s="4">
+        <f>6.22+4.51</f>
+        <v>10.73</v>
+      </c>
       <c r="Y67" s="4"/>
       <c r="Z67" s="9"/>
       <c r="AA67" s="4"/>
@@ -3982,21 +3994,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C68">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E68">
-        <v>24</v>
+        <v>315.5</v>
       </c>
       <c r="F68" s="3">
-        <v>31.4</v>
+        <v>545.34</v>
+      </c>
+      <c r="I68">
+        <v>168</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="4"/>
@@ -4004,15 +4019,15 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
       <c r="P68" s="4"/>
-      <c r="Q68" s="4">
-        <v>31.4</v>
-      </c>
+      <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
       <c r="S68" s="4"/>
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
+      <c r="W68" s="4">
+        <v>545.34</v>
+      </c>
       <c r="X68" s="4"/>
       <c r="Y68" s="4"/>
       <c r="Z68" s="9"/>
@@ -4026,58 +4041,37 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E69">
-        <f>475.4-8.8</f>
-        <v>466.59999999999997</v>
-      </c>
-      <c r="F69" s="7">
-        <v>1229.95</v>
-      </c>
-      <c r="G69">
-        <v>19</v>
-      </c>
-      <c r="H69">
-        <v>92.92</v>
-      </c>
-      <c r="I69">
-        <v>78</v>
-      </c>
-      <c r="J69">
-        <v>72</v>
+        <v>194.5</v>
+      </c>
+      <c r="F69" s="3">
+        <v>12.02</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="4">
-        <v>68</v>
-      </c>
-      <c r="O69" s="4">
-        <v>621.84500000000003</v>
-      </c>
-      <c r="P69" s="4">
-        <v>354.52499999999998</v>
-      </c>
-      <c r="Q69" s="4">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="R69" s="4">
-        <v>117.68</v>
-      </c>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
       <c r="S69" s="4"/>
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
+      <c r="W69" s="4">
+        <v>12.02</v>
+      </c>
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
       <c r="Z69" s="9"/>
@@ -4091,26 +4085,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C70">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E70">
-        <f>12.3+771.1</f>
-        <v>783.4</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="2"/>
+        <v>150.44999999999999</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
+      </c>
       <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
+      <c r="M70" s="6">
+        <v>150.44999999999999</v>
+      </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
       <c r="P70" s="4"/>
@@ -4134,42 +4131,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C71">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E71">
-        <v>59.5</v>
-      </c>
-      <c r="F71" s="7">
-        <v>328.75</v>
-      </c>
-      <c r="G71">
-        <v>6</v>
-      </c>
-      <c r="H71">
-        <v>16.16</v>
-      </c>
-      <c r="I71">
-        <v>471</v>
-      </c>
-      <c r="J71">
-        <v>338</v>
-      </c>
-      <c r="K71" s="2"/>
+        <v>37.4</v>
+      </c>
+      <c r="F71" s="3">
+        <v>27</v>
+      </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
+      <c r="M71" s="6">
+        <v>27</v>
+      </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
-      <c r="P71" s="4">
-        <v>328.75</v>
-      </c>
+      <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
@@ -4190,26 +4174,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C72">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72">
-        <v>216</v>
+        <v>34</v>
       </c>
       <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="K72" s="2"/>
+        <v>59.64</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
       <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
+      <c r="M72" s="6">
+        <v>47.94</v>
+      </c>
+      <c r="N72" s="6">
+        <v>11.7</v>
+      </c>
       <c r="O72" s="4"/>
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
@@ -4232,45 +4219,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E73">
-        <v>352.8</v>
-      </c>
-      <c r="F73" s="7">
-        <v>384.67</v>
-      </c>
-      <c r="G73">
-        <v>7</v>
-      </c>
-      <c r="H73">
-        <v>24.74</v>
-      </c>
-      <c r="I73">
-        <v>987</v>
-      </c>
-      <c r="J73">
-        <v>901</v>
-      </c>
-      <c r="K73" s="2"/>
-      <c r="L73" s="4"/>
+        <v>108.9</v>
+      </c>
+      <c r="F73" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="L73" s="6">
+        <v>47.5</v>
+      </c>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
-      <c r="P73" s="4">
-        <v>247.93</v>
-      </c>
-      <c r="Q73" s="4">
-        <v>136.74</v>
-      </c>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
       <c r="T73" s="4"/>
@@ -4290,31 +4262,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C74">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
-      </c>
-      <c r="E74">
-        <v>254.9</v>
+        <v>34</v>
       </c>
       <c r="F74" s="3">
-        <v>20.32</v>
-      </c>
-      <c r="K74" s="2"/>
+        <v>105.6</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
       <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="M74" s="6">
+        <v>105.6</v>
+      </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
       <c r="P74" s="4"/>
-      <c r="Q74" s="4">
-        <v>20.32</v>
-      </c>
+      <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
       <c r="T74" s="4"/>
@@ -4334,29 +4305,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C75">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E75">
-        <v>207.5</v>
+        <v>112.7</v>
       </c>
       <c r="F75" s="3">
-        <v>197.8</v>
-      </c>
-      <c r="I75">
-        <v>1801</v>
-      </c>
-      <c r="K75" s="2"/>
+        <v>2.2999999999999998</v>
+      </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
+      <c r="N75" s="6">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="O75" s="4"/>
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
@@ -4366,9 +4335,7 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
-      <c r="X75" s="4">
-        <v>197.8</v>
-      </c>
+      <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
       <c r="Z75" s="9"/>
       <c r="AA75" s="4"/>
@@ -4381,26 +4348,32 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C76">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E76">
-        <v>95</v>
+        <v>109.9</v>
       </c>
       <c r="F76" s="3">
-        <v>10.73</v>
-      </c>
-      <c r="K76" s="2"/>
+        <v>131.43</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
+      <c r="M76" s="6">
+        <v>66.83</v>
+      </c>
+      <c r="N76" s="6">
+        <v>64.599999999999994</v>
+      </c>
       <c r="O76" s="4"/>
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
@@ -4410,10 +4383,7 @@
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
-      <c r="X76" s="4">
-        <f>6.22+4.51</f>
-        <v>10.73</v>
-      </c>
+      <c r="X76" s="4"/>
       <c r="Y76" s="4"/>
       <c r="Z76" s="9"/>
       <c r="AA76" s="4"/>
@@ -4426,26 +4396,25 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C77">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E77">
-        <v>315.5</v>
-      </c>
-      <c r="F77" s="3">
-        <v>545.34</v>
+        <v>18.8</v>
       </c>
       <c r="I77">
-        <v>168</v>
-      </c>
-      <c r="K77" s="2"/>
+        <v>2305</v>
+      </c>
+      <c r="J77">
+        <v>2706</v>
+      </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
@@ -4457,9 +4426,7 @@
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
-      <c r="W77" s="4">
-        <v>545.34</v>
-      </c>
+      <c r="W77" s="4"/>
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
       <c r="Z77" s="9"/>
@@ -4473,37 +4440,48 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C78">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E78">
-        <v>194.5</v>
+        <v>0</v>
       </c>
       <c r="F78" s="3">
-        <v>12.02</v>
-      </c>
-      <c r="K78" s="2"/>
+        <v>192.04</v>
+      </c>
+      <c r="G78">
+        <v>8</v>
+      </c>
+      <c r="H78">
+        <v>26.74</v>
+      </c>
+      <c r="I78">
+        <v>322</v>
+      </c>
+      <c r="J78">
+        <v>661</v>
+      </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
+      <c r="R78" s="4">
+        <v>192.04</v>
+      </c>
       <c r="S78" s="4"/>
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
-      <c r="W78" s="4">
-        <v>12.02</v>
-      </c>
+      <c r="W78" s="4"/>
       <c r="X78" s="4"/>
       <c r="Y78" s="4"/>
       <c r="Z78" s="9"/>
@@ -4517,27 +4495,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C79">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E79">
-        <v>31.9</v>
+        <v>44.2</v>
       </c>
       <c r="F79" s="3">
-        <v>384.37</v>
-      </c>
-      <c r="I79">
-        <v>1302</v>
-      </c>
-      <c r="J79">
-        <v>1152</v>
+        <v>19.91</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -4545,12 +4517,12 @@
       <c r="O79" s="4"/>
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
+      <c r="R79" s="4">
+        <v>19.91</v>
+      </c>
       <c r="S79" s="4"/>
       <c r="T79" s="4"/>
-      <c r="U79" s="4">
-        <v>384.37</v>
-      </c>
+      <c r="U79" s="4"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
@@ -4566,21 +4538,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C80">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E80">
-        <v>600.73</v>
+        <v>291.8</v>
       </c>
       <c r="F80" s="3">
-        <v>23.8</v>
+        <v>259.3</v>
+      </c>
+      <c r="I80">
+        <v>723</v>
+      </c>
+      <c r="J80">
+        <v>270</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -4588,12 +4566,12 @@
       <c r="O80" s="4"/>
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
+      <c r="R80" s="4">
+        <v>259.3</v>
+      </c>
       <c r="S80" s="4"/>
       <c r="T80" s="4"/>
-      <c r="U80" s="4">
-        <v>23.8</v>
-      </c>
+      <c r="U80" s="4"/>
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
       <c r="X80" s="4"/>
@@ -4609,15 +4587,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
-        <v>61</v>
+    <row r="81" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C81">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E81">
+        <v>208.6</v>
+      </c>
+      <c r="F81" s="3">
+        <v>39.75</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -4625,7 +4609,9 @@
       <c r="O81" s="4"/>
       <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
+      <c r="R81" s="4">
+        <v>39.75</v>
+      </c>
       <c r="S81" s="4"/>
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
@@ -4644,18 +4630,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B82" t="s">
-        <v>61</v>
+    <row r="82" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C82">
         <v>26</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E82">
-        <v>220.48</v>
+        <v>31.9</v>
+      </c>
+      <c r="F82" s="3">
+        <v>384.37</v>
+      </c>
+      <c r="I82">
+        <v>1302</v>
+      </c>
+      <c r="J82">
+        <v>1152</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -4666,7 +4661,9 @@
       <c r="R82" s="4"/>
       <c r="S82" s="4"/>
       <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
+      <c r="U82" s="4">
+        <v>384.37</v>
+      </c>
       <c r="V82" s="4"/>
       <c r="W82" s="4"/>
       <c r="X82" s="4"/>
@@ -4682,21 +4679,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B83" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C83">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E83">
+        <v>600.73</v>
       </c>
       <c r="F83" s="3">
-        <v>91.21</v>
-      </c>
-      <c r="I83">
-        <v>2885</v>
+        <v>23.8</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -4707,14 +4704,12 @@
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
       <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
-      <c r="V83" s="4">
-        <v>20.95</v>
-      </c>
+      <c r="U83" s="4">
+        <v>23.8</v>
+      </c>
+      <c r="V83" s="4"/>
       <c r="W83" s="4"/>
-      <c r="X83" s="4">
-        <v>70.260000000000005</v>
-      </c>
+      <c r="X83" s="4"/>
       <c r="Y83" s="4"/>
       <c r="Z83" s="9"/>
       <c r="AA83" s="4"/>
@@ -4727,39 +4722,50 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B84" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C84">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E84">
-        <v>100.5</v>
+        <v>65.5</v>
       </c>
       <c r="F84" s="3">
-        <v>10.06</v>
-      </c>
+        <v>288.26</v>
+      </c>
+      <c r="G84">
+        <v>17</v>
+      </c>
+      <c r="H84">
+        <v>51.09</v>
+      </c>
+      <c r="I84">
+        <v>139</v>
+      </c>
+      <c r="J84">
+        <v>109</v>
+      </c>
+      <c r="K84" s="2"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
       <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
+      <c r="Q84" s="4">
+        <v>288.26</v>
+      </c>
       <c r="R84" s="4"/>
       <c r="S84" s="4"/>
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
-      <c r="V84" s="4">
-        <v>8.06</v>
-      </c>
+      <c r="V84" s="4"/>
       <c r="W84" s="4"/>
-      <c r="X84" s="4">
-        <v>2</v>
-      </c>
+      <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
       <c r="Z84" s="9"/>
       <c r="AA84" s="4"/>
@@ -4772,36 +4778,37 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C85">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E85">
+        <v>226.5</v>
       </c>
       <c r="F85" s="3">
-        <v>230.72</v>
-      </c>
+        <v>32.85</v>
+      </c>
+      <c r="K85" s="2"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
       <c r="P85" s="4"/>
-      <c r="Q85" s="4"/>
+      <c r="Q85" s="4">
+        <v>32.85</v>
+      </c>
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
-      <c r="V85" s="4">
-        <f>230.02-55.56</f>
-        <v>174.46</v>
-      </c>
-      <c r="W85" s="4">
-        <v>56.26</v>
-      </c>
+      <c r="V85" s="4"/>
+      <c r="W85" s="4"/>
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
       <c r="Z85" s="9"/>
@@ -4815,26 +4822,38 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B86" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C86">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E86">
-        <v>210.02</v>
-      </c>
+        <v>366.4</v>
+      </c>
+      <c r="F86" s="3">
+        <v>223.29</v>
+      </c>
+      <c r="I86">
+        <v>219</v>
+      </c>
+      <c r="J86">
+        <v>188</v>
+      </c>
+      <c r="K86" s="2"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
+      <c r="R86" s="4">
+        <v>223.29</v>
+      </c>
       <c r="S86" s="4"/>
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
@@ -4853,32 +4872,36 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C87">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E87">
+        <v>95.7</v>
       </c>
       <c r="F87" s="3">
-        <v>35.5</v>
-      </c>
+        <v>26.66</v>
+      </c>
+      <c r="K87" s="2"/>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
       <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
+      <c r="Q87" s="4">
+        <v>26.66</v>
+      </c>
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
-      <c r="V87" s="4">
-        <v>35.5</v>
-      </c>
+      <c r="V87" s="4"/>
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
@@ -4893,19 +4916,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C88">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E88">
-        <v>57.5</v>
-      </c>
+        <v>163.4</v>
+      </c>
+      <c r="F88" s="3">
+        <v>159.63</v>
+      </c>
+      <c r="I88">
+        <v>848</v>
+      </c>
+      <c r="J88">
+        <v>860</v>
+      </c>
+      <c r="K88" s="2"/>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
@@ -4913,8 +4946,12 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
       <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
+      <c r="S88" s="4">
+        <v>59.73</v>
+      </c>
+      <c r="T88" s="4">
+        <v>99.9</v>
+      </c>
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
       <c r="W88" s="4"/>
@@ -4931,32 +4968,36 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C89">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E89">
+        <v>24</v>
       </c>
       <c r="F89" s="3">
-        <v>36.979999999999997</v>
-      </c>
+        <v>31.4</v>
+      </c>
+      <c r="K89" s="2"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
       <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
+      <c r="Q89" s="4">
+        <v>31.4</v>
+      </c>
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
-      <c r="V89" s="4">
-        <v>36.979999999999997</v>
-      </c>
+      <c r="V89" s="4"/>
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
@@ -4971,18 +5012,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B90" s="3" t="s">
-        <v>62</v>
+    <row r="90" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>52</v>
       </c>
       <c r="C90">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E90">
-        <v>56</v>
+        <v>820.2</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -5009,21 +5050,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B91" s="3" t="s">
-        <v>62</v>
+    <row r="91" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>52</v>
       </c>
       <c r="C91">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>34</v>
-      </c>
-      <c r="F91" s="3">
-        <v>39.04</v>
-      </c>
-      <c r="J91">
-        <v>628</v>
+        <v>36</v>
+      </c>
+      <c r="E91">
+        <v>191.4</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -5035,9 +5073,7 @@
       <c r="S91" s="4"/>
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
-      <c r="V91" s="4">
-        <v>39.04</v>
-      </c>
+      <c r="V91" s="4"/>
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
@@ -5052,27 +5088,41 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C92">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E92">
-        <v>39.5</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="F92" s="3">
+        <v>400</v>
+      </c>
+      <c r="I92">
+        <v>41</v>
+      </c>
+      <c r="J92">
+        <v>39</v>
+      </c>
+      <c r="K92" s="2"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
+      <c r="R92" s="4">
+        <v>75</v>
+      </c>
+      <c r="S92" s="4">
+        <v>325</v>
+      </c>
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
@@ -5090,19 +5140,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C93">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E93">
+        <v>233.1</v>
       </c>
       <c r="F93" s="3">
-        <v>34.42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K93" s="2"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
@@ -5113,9 +5167,7 @@
       <c r="S93" s="4"/>
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
-      <c r="V93" s="4">
-        <v>34.42</v>
-      </c>
+      <c r="V93" s="4"/>
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
       <c r="Y93" s="4"/>
@@ -5130,19 +5182,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B94" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C94">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E94">
-        <v>63.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="I94">
+        <v>464</v>
+      </c>
+      <c r="J94">
+        <v>523</v>
+      </c>
+      <c r="K94" s="2"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
@@ -5151,8 +5213,12 @@
       <c r="Q94" s="4"/>
       <c r="R94" s="4"/>
       <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
+      <c r="T94" s="4">
+        <v>35</v>
+      </c>
+      <c r="U94" s="4">
+        <v>122.7</v>
+      </c>
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
@@ -5168,19 +5234,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C95">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E95">
+        <v>243.8</v>
       </c>
       <c r="F95" s="3">
-        <v>34.119999999999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K95" s="2"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
@@ -5191,9 +5261,7 @@
       <c r="S95" s="4"/>
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
-      <c r="V95" s="4">
-        <v>34.119999999999997</v>
-      </c>
+      <c r="V95" s="4"/>
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
@@ -5208,19 +5276,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C96">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E96">
-        <v>67.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
+        <v>341.71499999999997</v>
+      </c>
+      <c r="I96">
+        <v>2139</v>
+      </c>
+      <c r="J96">
+        <v>2126</v>
+      </c>
+      <c r="K96" s="2"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
@@ -5228,8 +5306,12 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
       <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
+      <c r="S96" s="4">
+        <v>220</v>
+      </c>
+      <c r="T96" s="4">
+        <v>121.715</v>
+      </c>
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
       <c r="W96" s="4"/>
@@ -5246,19 +5328,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C97">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E97">
+        <v>276.10000000000002</v>
       </c>
       <c r="F97" s="3">
-        <v>32.11</v>
-      </c>
+        <v>13.17</v>
+      </c>
+      <c r="K97" s="2"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
@@ -5267,11 +5353,11 @@
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
       <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
+      <c r="T97" s="4">
+        <v>13.17</v>
+      </c>
       <c r="U97" s="4"/>
-      <c r="V97" s="4">
-        <v>32.11</v>
-      </c>
+      <c r="V97" s="4"/>
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
       <c r="Y97" s="4"/>
@@ -5286,19 +5372,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C98">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
-      </c>
-      <c r="E98">
-        <v>67.5</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F98" s="3">
+        <v>43.02</v>
+      </c>
+      <c r="I98">
+        <v>208</v>
+      </c>
+      <c r="J98">
+        <v>191</v>
+      </c>
+      <c r="K98" s="2"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
@@ -5307,7 +5400,9 @@
       <c r="Q98" s="4"/>
       <c r="R98" s="4"/>
       <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
+      <c r="T98" s="4">
+        <v>43.015000000000001</v>
+      </c>
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
       <c r="W98" s="4"/>
@@ -5324,19 +5419,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C99">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E99">
+        <v>83.2</v>
       </c>
       <c r="F99" s="3">
-        <v>35.9</v>
-      </c>
+        <v>51.05</v>
+      </c>
+      <c r="K99" s="2"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
@@ -5344,12 +5443,12 @@
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
       <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
+      <c r="S99" s="4">
+        <v>51.05</v>
+      </c>
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
-      <c r="V99" s="4">
-        <v>35.9</v>
-      </c>
+      <c r="V99" s="4"/>
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
       <c r="Y99" s="4"/>
@@ -5364,19 +5463,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C100">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E100">
-        <v>84.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>320.31299999999999</v>
+      </c>
+      <c r="K100" s="2"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
@@ -5390,8 +5493,13 @@
       <c r="V100" s="4"/>
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
-      <c r="Y100" s="4"/>
-      <c r="Z100" s="9"/>
+      <c r="Y100" s="4">
+        <f>78.58+84.32+66.57+78.843</f>
+        <v>308.31299999999999</v>
+      </c>
+      <c r="Z100" s="9">
+        <v>12</v>
+      </c>
       <c r="AA100" s="4"/>
       <c r="AB100" s="4"/>
       <c r="AC100" s="4"/>
@@ -5402,35 +5510,49 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C101">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D101" t="s">
         <v>34</v>
       </c>
       <c r="E101">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>32.19</v>
+        <v>523.65499999999997</v>
+      </c>
+      <c r="G101">
+        <v>47</v>
+      </c>
+      <c r="H101">
+        <v>136.19</v>
+      </c>
+      <c r="I101">
+        <v>797</v>
+      </c>
+      <c r="J101">
+        <v>599</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
+      <c r="N101" s="6">
+        <v>217.93</v>
+      </c>
+      <c r="O101" s="6">
+        <v>305.72500000000002</v>
+      </c>
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
       <c r="R101" s="4"/>
       <c r="S101" s="4"/>
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
-      <c r="V101" s="4">
-        <v>32.19</v>
-      </c>
+      <c r="V101" s="4"/>
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
       <c r="Y101" s="4"/>
@@ -5445,18 +5567,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C102">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D102" t="s">
         <v>36</v>
       </c>
       <c r="E102">
-        <v>114.5</v>
+        <v>469.7</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -5483,38 +5605,44 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C103">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D103" t="s">
         <v>34</v>
       </c>
       <c r="E103">
-        <v>35</v>
+        <v>124.2</v>
       </c>
       <c r="F103" s="3">
-        <v>76.599999999999994</v>
+        <v>342.71</v>
+      </c>
+      <c r="I103">
+        <v>91</v>
+      </c>
+      <c r="J103">
+        <v>595</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
+      <c r="O103" s="6">
+        <v>134.10499999999999</v>
+      </c>
+      <c r="P103" s="6">
+        <v>208.60499999999999</v>
+      </c>
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
       <c r="S103" s="4"/>
       <c r="T103" s="4"/>
       <c r="U103" s="4"/>
-      <c r="V103" s="4">
-        <v>37.72</v>
-      </c>
-      <c r="W103" s="4">
-        <v>38.880000000000003</v>
-      </c>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
       <c r="X103" s="4"/>
       <c r="Y103" s="4"/>
       <c r="Z103" s="9"/>
@@ -5528,18 +5656,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C104">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D104" t="s">
         <v>36</v>
       </c>
       <c r="E104">
-        <v>58.5</v>
+        <v>83</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -5566,38 +5697,44 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C105">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D105" t="s">
         <v>34</v>
       </c>
       <c r="E105">
-        <v>61.5</v>
+        <v>240.7</v>
       </c>
       <c r="F105" s="3">
-        <v>84.62</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]</f>
+        <v>159.47499999999999</v>
+      </c>
+      <c r="I105">
+        <v>589</v>
+      </c>
+      <c r="J105">
+        <v>109</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
-      <c r="P105" s="4"/>
+      <c r="P105" s="6">
+        <f>231.85-72.375</f>
+        <v>159.47499999999999</v>
+      </c>
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
       <c r="S105" s="4"/>
       <c r="T105" s="4"/>
       <c r="U105" s="4"/>
-      <c r="V105" s="4">
-        <v>36.840000000000003</v>
-      </c>
-      <c r="W105" s="4">
-        <v>47.78</v>
-      </c>
+      <c r="V105" s="4"/>
+      <c r="W105" s="4"/>
       <c r="X105" s="4"/>
       <c r="Y105" s="4"/>
       <c r="Z105" s="9"/>
@@ -5611,24 +5748,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C106">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D106" t="s">
         <v>36</v>
       </c>
       <c r="E106">
-        <v>37.5</v>
+        <v>118.5</v>
+      </c>
+      <c r="F106" s="3">
+        <v>4.0599999999999996</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
+      <c r="P106" s="6">
+        <v>4.0599999999999996</v>
+      </c>
       <c r="Q106" s="4"/>
       <c r="R106" s="4"/>
       <c r="S106" s="4"/>
@@ -5649,35 +5791,45 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C107">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
         <v>34</v>
       </c>
       <c r="E107">
-        <v>65.5</v>
+        <v>0</v>
       </c>
       <c r="F107" s="3">
-        <v>35.5</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]</f>
+        <v>295.33500000000004</v>
+      </c>
+      <c r="I107">
+        <v>614</v>
+      </c>
+      <c r="J107">
+        <v>3229</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
+      <c r="P107" s="6">
+        <f>132.27-72.375</f>
+        <v>59.89500000000001</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>235.44</v>
+      </c>
       <c r="R107" s="4"/>
       <c r="S107" s="4"/>
       <c r="T107" s="4"/>
       <c r="U107" s="4"/>
-      <c r="V107" s="4">
-        <v>35.5</v>
-      </c>
+      <c r="V107" s="4"/>
       <c r="W107" s="4"/>
       <c r="X107" s="4"/>
       <c r="Y107" s="4"/>
@@ -5692,18 +5844,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C108">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D108" t="s">
         <v>36</v>
       </c>
       <c r="E108">
-        <v>32.5</v>
+        <v>232.1</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
@@ -5730,35 +5882,41 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C109">
+        <v>9</v>
+      </c>
+      <c r="D109" t="s">
+        <v>34</v>
+      </c>
+      <c r="E109">
+        <v>70.5</v>
+      </c>
+      <c r="F109" s="3">
+        <v>253.94</v>
+      </c>
+      <c r="I109">
+        <v>2964</v>
+      </c>
+      <c r="J109">
         <v>42</v>
-      </c>
-      <c r="D109" t="s">
-        <v>34</v>
-      </c>
-      <c r="E109">
-        <v>91.5</v>
-      </c>
-      <c r="F109" s="3">
-        <v>34.380000000000003</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
       <c r="P109" s="4"/>
-      <c r="Q109" s="4"/>
+      <c r="Q109" s="4">
+        <v>253.94</v>
+      </c>
       <c r="R109" s="4"/>
       <c r="S109" s="4"/>
       <c r="T109" s="4"/>
       <c r="U109" s="4"/>
-      <c r="V109" s="4">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="V109" s="4"/>
       <c r="W109" s="4"/>
       <c r="X109" s="4"/>
       <c r="Y109" s="4"/>
@@ -5773,28 +5931,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C110">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D110" t="s">
         <v>36</v>
       </c>
       <c r="E110">
-        <v>5.5</v>
+        <v>754</v>
+      </c>
+      <c r="F110" s="3">
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]+tb_base_dash_extensao[[#This Row],[produção Dezembro 2025]]</f>
+        <v>373.08500000000004</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
-      <c r="Q110" s="4"/>
+      <c r="P110" s="4">
+        <f>242.97-72.375</f>
+        <v>170.595</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>148.49</v>
+      </c>
       <c r="R110" s="4"/>
       <c r="S110" s="4"/>
-      <c r="T110" s="4"/>
+      <c r="T110" s="4">
+        <v>54</v>
+      </c>
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
       <c r="W110" s="4"/>
@@ -5811,21 +5980,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B111" s="3" t="s">
-        <v>62</v>
+    <row r="111" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
+        <v>89</v>
       </c>
       <c r="C111">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D111" t="s">
         <v>34</v>
       </c>
-      <c r="E111">
-        <v>198</v>
-      </c>
       <c r="F111" s="3">
-        <v>167.19</v>
+        <v>880.94100000000003</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -5837,15 +6003,17 @@
       <c r="S111" s="4"/>
       <c r="T111" s="4"/>
       <c r="U111" s="4"/>
-      <c r="V111" s="4">
-        <v>43.97</v>
-      </c>
-      <c r="W111" s="4">
-        <v>123.22</v>
-      </c>
+      <c r="V111" s="4"/>
+      <c r="W111" s="4"/>
       <c r="X111" s="4"/>
-      <c r="Y111" s="4"/>
-      <c r="Z111" s="9"/>
+      <c r="Y111" s="4">
+        <f>592.21-43.66</f>
+        <v>548.55000000000007</v>
+      </c>
+      <c r="Z111" s="9">
+        <f>64.57+79.57+66.725+63.68+57.846</f>
+        <v>332.39099999999996</v>
+      </c>
       <c r="AA111" s="4"/>
       <c r="AB111" s="4"/>
       <c r="AC111" s="4"/>
@@ -5856,18 +6024,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B112" s="3" t="s">
-        <v>62</v>
+    <row r="112" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>89</v>
       </c>
       <c r="C112">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D112" t="s">
         <v>36</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>858.5</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -5894,24 +6062,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B113" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C113">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D113" t="s">
         <v>34</v>
       </c>
       <c r="E113">
-        <v>75</v>
+        <v>205.65</v>
       </c>
       <c r="F113" s="3">
-        <v>189</v>
-      </c>
-      <c r="J113">
-        <v>531</v>
+        <v>76.400000000000006</v>
+      </c>
+      <c r="I113">
+        <v>288</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -5924,10 +6092,10 @@
       <c r="T113" s="4"/>
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
-      <c r="W113" s="4">
-        <v>189</v>
-      </c>
-      <c r="X113" s="4"/>
+      <c r="W113" s="4"/>
+      <c r="X113" s="4">
+        <v>76.400000000000006</v>
+      </c>
       <c r="Y113" s="4"/>
       <c r="Z113" s="9"/>
       <c r="AA113" s="4"/>
@@ -5940,21 +6108,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B114" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C114">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D114" t="s">
         <v>36</v>
       </c>
       <c r="E114">
-        <v>48.5</v>
-      </c>
-      <c r="F114" s="3">
-        <v>70.930000000000007</v>
+        <v>59.6</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
@@ -5967,9 +6132,7 @@
       <c r="T114" s="4"/>
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
-      <c r="W114" s="4">
-        <v>70.930000000000007</v>
-      </c>
+      <c r="W114" s="4"/>
       <c r="X114" s="4"/>
       <c r="Y114" s="4"/>
       <c r="Z114" s="9"/>
@@ -5983,24 +6146,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C115">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D115" t="s">
         <v>34</v>
       </c>
       <c r="E115">
-        <v>298</v>
+        <v>62.5</v>
       </c>
       <c r="F115" s="3">
-        <v>363.85</v>
+        <v>344.13</v>
       </c>
       <c r="I115">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
@@ -6012,13 +6175,14 @@
       <c r="S115" s="4"/>
       <c r="T115" s="4"/>
       <c r="U115" s="4"/>
-      <c r="V115" s="4">
-        <v>329.56</v>
-      </c>
+      <c r="V115" s="4"/>
       <c r="W115" s="4">
-        <v>34.29</v>
-      </c>
-      <c r="X115" s="4"/>
+        <v>81.8</v>
+      </c>
+      <c r="X115" s="4">
+        <f>42+158.17+61.95+0.21</f>
+        <v>262.33</v>
+      </c>
       <c r="Y115" s="4"/>
       <c r="Z115" s="9"/>
       <c r="AA115" s="4"/>
@@ -6031,21 +6195,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" s="3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C116">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D116" t="s">
         <v>36</v>
       </c>
       <c r="E116">
-        <v>113.5</v>
+        <v>63</v>
       </c>
       <c r="F116" s="3">
-        <v>19.84</v>
+        <v>47.56</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -6060,7 +6224,7 @@
       <c r="V116" s="4"/>
       <c r="W116" s="4"/>
       <c r="X116" s="4">
-        <v>19.84</v>
+        <v>47.56</v>
       </c>
       <c r="Y116" s="4"/>
       <c r="Z116" s="9"/>
@@ -6074,21 +6238,33 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C117">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D117" t="s">
         <v>34</v>
       </c>
       <c r="E117">
-        <v>88</v>
+        <v>240.4</v>
       </c>
       <c r="F117" s="3">
-        <v>89.05</v>
+        <v>766.04399999999998</v>
+      </c>
+      <c r="G117">
+        <v>18</v>
+      </c>
+      <c r="H117">
+        <v>61.47</v>
+      </c>
+      <c r="I117">
+        <v>1989</v>
+      </c>
+      <c r="J117">
+        <v>1901</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
@@ -6099,14 +6275,18 @@
       <c r="R117" s="4"/>
       <c r="S117" s="4"/>
       <c r="T117" s="4"/>
-      <c r="U117" s="4"/>
+      <c r="U117" s="4">
+        <f>528.5-68.36+91.707</f>
+        <v>551.84699999999998</v>
+      </c>
       <c r="V117" s="4">
-        <v>32.99</v>
-      </c>
-      <c r="W117" s="4">
-        <v>56.06</v>
-      </c>
-      <c r="X117" s="4"/>
+        <f>52.4-0.15+91.707</f>
+        <v>143.95699999999999</v>
+      </c>
+      <c r="W117" s="4"/>
+      <c r="X117" s="4">
+        <v>70.239999999999995</v>
+      </c>
       <c r="Y117" s="4"/>
       <c r="Z117" s="9"/>
       <c r="AA117" s="4"/>
@@ -6119,18 +6299,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C118">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D118" t="s">
         <v>36</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>976.24</v>
+      </c>
+      <c r="F118" s="3">
+        <v>162.15</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
@@ -6141,11 +6324,19 @@
       <c r="R118" s="4"/>
       <c r="S118" s="4"/>
       <c r="T118" s="4"/>
-      <c r="U118" s="4"/>
+      <c r="U118" s="4">
+        <v>42.7</v>
+      </c>
       <c r="V118" s="4"/>
-      <c r="W118" s="4"/>
-      <c r="X118" s="4"/>
-      <c r="Y118" s="4"/>
+      <c r="W118" s="4">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="X118" s="4">
+        <v>8.81</v>
+      </c>
+      <c r="Y118" s="4">
+        <v>70.84</v>
+      </c>
       <c r="Z118" s="9"/>
       <c r="AA118" s="4"/>
       <c r="AB118" s="4"/>
@@ -6157,21 +6348,33 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C119">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D119" t="s">
         <v>34</v>
       </c>
       <c r="E119">
-        <v>68.5</v>
+        <v>286</v>
       </c>
       <c r="F119" s="3">
-        <v>35.479999999999997</v>
+        <v>466.40699999999998</v>
+      </c>
+      <c r="G119">
+        <v>8</v>
+      </c>
+      <c r="H119">
+        <v>28.55</v>
+      </c>
+      <c r="I119">
+        <v>574</v>
+      </c>
+      <c r="J119">
+        <v>822</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
@@ -6182,9 +6385,13 @@
       <c r="R119" s="4"/>
       <c r="S119" s="4"/>
       <c r="T119" s="4"/>
-      <c r="U119" s="4"/>
+      <c r="U119" s="4">
+        <f>67.2+51</f>
+        <v>118.2</v>
+      </c>
       <c r="V119" s="4">
-        <v>35.479999999999997</v>
+        <f>256.5+91.707</f>
+        <v>348.20699999999999</v>
       </c>
       <c r="W119" s="4"/>
       <c r="X119" s="4"/>
@@ -6200,18 +6407,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C120">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D120" t="s">
         <v>36</v>
       </c>
       <c r="E120">
-        <v>26</v>
+        <v>566.29999999999995</v>
+      </c>
+      <c r="F120" s="3">
+        <v>142.61000000000001</v>
       </c>
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
@@ -6224,9 +6434,14 @@
       <c r="T120" s="4"/>
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
-      <c r="W120" s="4"/>
+      <c r="W120" s="4">
+        <v>65.599999999999994</v>
+      </c>
       <c r="X120" s="4"/>
-      <c r="Y120" s="4"/>
+      <c r="Y120" s="4">
+        <f>14.84+38.87+23.3</f>
+        <v>77.009999999999991</v>
+      </c>
       <c r="Z120" s="9"/>
       <c r="AA120" s="4"/>
       <c r="AB120" s="4"/>
@@ -6238,21 +6453,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C121">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D121" t="s">
         <v>34</v>
       </c>
-      <c r="E121">
-        <v>216.5</v>
-      </c>
       <c r="F121" s="3">
-        <v>206.17</v>
+        <v>207.4</v>
+      </c>
+      <c r="G121">
+        <v>7</v>
+      </c>
+      <c r="H121">
+        <v>21.76</v>
+      </c>
+      <c r="I121">
+        <v>597</v>
       </c>
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
@@ -6265,11 +6486,9 @@
       <c r="T121" s="4"/>
       <c r="U121" s="4"/>
       <c r="V121" s="4">
-        <v>129.66999999999999</v>
-      </c>
-      <c r="W121" s="4">
-        <v>76.5</v>
-      </c>
+        <v>207.4</v>
+      </c>
+      <c r="W121" s="4"/>
       <c r="X121" s="4"/>
       <c r="Y121" s="4"/>
       <c r="Z121" s="9"/>
@@ -6283,18 +6502,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C122">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D122" t="s">
         <v>36</v>
       </c>
       <c r="E122">
-        <v>86</v>
+        <v>116.6</v>
+      </c>
+      <c r="F122" s="3">
+        <v>2</v>
       </c>
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
@@ -6307,7 +6529,9 @@
       <c r="T122" s="4"/>
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
-      <c r="W122" s="4"/>
+      <c r="W122" s="4">
+        <v>2</v>
+      </c>
       <c r="X122" s="4"/>
       <c r="Y122" s="4"/>
       <c r="Z122" s="9"/>
@@ -6321,21 +6545,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B123" s="3" t="s">
-        <v>63</v>
+    <row r="123" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B123" t="s">
+        <v>50</v>
       </c>
       <c r="C123">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D123" t="s">
         <v>34</v>
       </c>
       <c r="E123">
-        <v>68</v>
-      </c>
-      <c r="F123" s="3">
-        <v>97.16</v>
+        <v>1583.28</v>
       </c>
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
@@ -6347,12 +6568,8 @@
       <c r="S123" s="4"/>
       <c r="T123" s="4"/>
       <c r="U123" s="4"/>
-      <c r="V123" s="4">
-        <v>68.16</v>
-      </c>
-      <c r="W123" s="4">
-        <v>29</v>
-      </c>
+      <c r="V123" s="4"/>
+      <c r="W123" s="4"/>
       <c r="X123" s="4"/>
       <c r="Y123" s="4"/>
       <c r="Z123" s="9"/>
@@ -6366,18 +6583,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B124" s="3" t="s">
-        <v>63</v>
+    <row r="124" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B124" t="s">
+        <v>50</v>
       </c>
       <c r="C124">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D124" t="s">
         <v>36</v>
-      </c>
-      <c r="E124">
-        <v>40.5</v>
       </c>
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
@@ -6404,21 +6618,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B125" s="3" t="s">
-        <v>63</v>
+    <row r="125" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B125" t="s">
+        <v>53</v>
       </c>
       <c r="C125">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D125" t="s">
         <v>34</v>
       </c>
       <c r="E125">
-        <v>87.5</v>
-      </c>
-      <c r="F125" s="3">
-        <v>35.42</v>
+        <v>165</v>
       </c>
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
@@ -6430,9 +6641,7 @@
       <c r="S125" s="4"/>
       <c r="T125" s="4"/>
       <c r="U125" s="4"/>
-      <c r="V125" s="4">
-        <v>35.42</v>
-      </c>
+      <c r="V125" s="4"/>
       <c r="W125" s="4"/>
       <c r="X125" s="4"/>
       <c r="Y125" s="4"/>
@@ -6447,18 +6656,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B126" s="3" t="s">
-        <v>63</v>
+    <row r="126" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B126" t="s">
+        <v>53</v>
       </c>
       <c r="C126">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D126" t="s">
         <v>36</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>43.5</v>
       </c>
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
@@ -6485,21 +6694,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B127" s="3" t="s">
-        <v>63</v>
+    <row r="127" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B127" t="s">
+        <v>48</v>
       </c>
       <c r="C127">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D127" t="s">
         <v>34</v>
       </c>
-      <c r="E127">
-        <v>84.5</v>
-      </c>
-      <c r="F127" s="3">
-        <v>34.409999999999997</v>
+      <c r="I127">
+        <v>11130</v>
       </c>
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
@@ -6511,9 +6717,7 @@
       <c r="S127" s="4"/>
       <c r="T127" s="4"/>
       <c r="U127" s="4"/>
-      <c r="V127" s="4">
-        <v>34.409999999999997</v>
-      </c>
+      <c r="V127" s="4"/>
       <c r="W127" s="4"/>
       <c r="X127" s="4"/>
       <c r="Y127" s="4"/>
@@ -6528,18 +6732,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B128" s="3" t="s">
-        <v>63</v>
+    <row r="128" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
+        <v>48</v>
       </c>
       <c r="C128">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D128" t="s">
         <v>36</v>
-      </c>
-      <c r="E128">
-        <v>2</v>
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -6566,21 +6767,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B129" s="3" t="s">
-        <v>63</v>
+    <row r="129" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B129" t="s">
+        <v>70</v>
       </c>
       <c r="C129">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D129" t="s">
         <v>34</v>
-      </c>
-      <c r="E129">
-        <v>109</v>
-      </c>
-      <c r="F129" s="3">
-        <v>47.44</v>
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -6592,9 +6787,7 @@
       <c r="S129" s="4"/>
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
-      <c r="V129" s="4">
-        <v>47.44</v>
-      </c>
+      <c r="V129" s="4"/>
       <c r="W129" s="4"/>
       <c r="X129" s="4"/>
       <c r="Y129" s="4"/>
@@ -6609,18 +6802,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B130" s="3" t="s">
-        <v>63</v>
+    <row r="130" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>70</v>
       </c>
       <c r="C130">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D130" t="s">
         <v>36</v>
       </c>
       <c r="E130">
-        <v>9.5</v>
+        <v>109.8</v>
       </c>
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
@@ -6647,21 +6840,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C131">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D131" t="s">
         <v>34</v>
       </c>
       <c r="E131">
-        <v>255</v>
+        <v>341.2</v>
       </c>
       <c r="F131" s="3">
-        <v>255.86</v>
+        <v>145.88</v>
+      </c>
+      <c r="I131">
+        <v>37</v>
       </c>
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
@@ -6673,12 +6869,13 @@
       <c r="S131" s="4"/>
       <c r="T131" s="4"/>
       <c r="U131" s="4"/>
-      <c r="V131" s="4">
-        <v>67.05</v>
-      </c>
-      <c r="W131" s="4"/>
+      <c r="V131" s="4"/>
+      <c r="W131" s="4">
+        <v>78.180000000000007</v>
+      </c>
       <c r="X131" s="4">
-        <v>188.81</v>
+        <f>18.75+12+36.95</f>
+        <v>67.7</v>
       </c>
       <c r="Y131" s="4"/>
       <c r="Z131" s="9"/>
@@ -6692,21 +6889,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C132">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D132" t="s">
         <v>36</v>
       </c>
       <c r="E132">
-        <v>144</v>
+        <v>83.8</v>
       </c>
       <c r="F132" s="3">
-        <v>0</v>
+        <v>55.83</v>
       </c>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
@@ -6720,7 +6917,10 @@
       <c r="U132" s="4"/>
       <c r="V132" s="4"/>
       <c r="W132" s="4"/>
-      <c r="X132" s="4"/>
+      <c r="X132" s="4">
+        <f>34.75+6.11+14.97</f>
+        <v>55.83</v>
+      </c>
       <c r="Y132" s="4"/>
       <c r="Z132" s="9"/>
       <c r="AA132" s="4"/>
@@ -6733,33 +6933,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B133" s="3" t="s">
-        <v>64</v>
+    <row r="133" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B133" t="s">
+        <v>71</v>
       </c>
       <c r="C133">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D133" t="s">
         <v>34</v>
       </c>
-      <c r="E133">
-        <v>561.5</v>
-      </c>
-      <c r="F133" s="7">
-        <v>445.49</v>
-      </c>
-      <c r="G133">
+      <c r="I133">
         <v>32</v>
-      </c>
-      <c r="H133">
-        <v>186.84</v>
-      </c>
-      <c r="I133">
-        <v>443</v>
-      </c>
-      <c r="J133">
-        <v>2397</v>
       </c>
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
@@ -6768,12 +6953,8 @@
       <c r="P133" s="4"/>
       <c r="Q133" s="4"/>
       <c r="R133" s="4"/>
-      <c r="S133" s="4">
-        <v>162.16499999999999</v>
-      </c>
-      <c r="T133" s="4">
-        <v>283.32499999999999</v>
-      </c>
+      <c r="S133" s="4"/>
+      <c r="T133" s="4"/>
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
       <c r="W133" s="4"/>
@@ -6790,21 +6971,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B134" s="3" t="s">
-        <v>64</v>
+    <row r="134" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B134" t="s">
+        <v>71</v>
       </c>
       <c r="C134">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D134" t="s">
         <v>36</v>
       </c>
       <c r="E134">
-        <v>144.5</v>
-      </c>
-      <c r="F134" s="7">
-        <v>75.599999999999994</v>
+        <v>59.5</v>
+      </c>
+      <c r="F134" s="3">
+        <v>68.2</v>
       </c>
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
@@ -6814,15 +6995,15 @@
       <c r="Q134" s="4"/>
       <c r="R134" s="4"/>
       <c r="S134" s="4"/>
-      <c r="T134" s="4">
-        <v>75.599999999999994</v>
-      </c>
+      <c r="T134" s="4"/>
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
       <c r="W134" s="4"/>
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
-      <c r="Z134" s="9"/>
+      <c r="Z134" s="9">
+        <v>68.2</v>
+      </c>
       <c r="AA134" s="4"/>
       <c r="AB134" s="4"/>
       <c r="AC134" s="4"/>
@@ -6833,24 +7014,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B135" s="3" t="s">
-        <v>64</v>
+    <row r="135" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B135" t="s">
+        <v>80</v>
       </c>
       <c r="C135">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D135" t="s">
         <v>34</v>
       </c>
       <c r="E135">
-        <v>451.5</v>
-      </c>
-      <c r="F135" s="7">
-        <v>629.14</v>
+        <v>131.30000000000001</v>
       </c>
       <c r="I135">
-        <v>788</v>
+        <v>134</v>
       </c>
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
@@ -6860,9 +7038,7 @@
       <c r="Q135" s="4"/>
       <c r="R135" s="4"/>
       <c r="S135" s="4"/>
-      <c r="T135" s="4">
-        <v>629.14</v>
-      </c>
+      <c r="T135" s="4"/>
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
       <c r="W135" s="4"/>
@@ -6879,21 +7055,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B136" s="3" t="s">
-        <v>64</v>
+    <row r="136" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B136" t="s">
+        <v>80</v>
       </c>
       <c r="C136">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D136" t="s">
         <v>36</v>
       </c>
       <c r="E136">
-        <v>144.5</v>
-      </c>
-      <c r="F136" s="7">
-        <v>37.89</v>
+        <v>15.2</v>
       </c>
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
@@ -6903,9 +7076,7 @@
       <c r="Q136" s="4"/>
       <c r="R136" s="4"/>
       <c r="S136" s="4"/>
-      <c r="T136" s="4">
-        <v>37.89</v>
-      </c>
+      <c r="T136" s="4"/>
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
       <c r="W136" s="4"/>
@@ -6922,24 +7093,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B137" s="3" t="s">
-        <v>64</v>
+    <row r="137" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B137" t="s">
+        <v>51</v>
       </c>
       <c r="C137">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D137" t="s">
         <v>34</v>
       </c>
       <c r="E137">
-        <v>322</v>
-      </c>
-      <c r="F137" s="7">
-        <v>108.02</v>
-      </c>
-      <c r="I137">
-        <v>654</v>
+        <v>699.23500000000001</v>
       </c>
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
@@ -6949,9 +7114,7 @@
       <c r="Q137" s="4"/>
       <c r="R137" s="4"/>
       <c r="S137" s="4"/>
-      <c r="T137" s="4">
-        <v>108.02</v>
-      </c>
+      <c r="T137" s="4"/>
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
       <c r="W137" s="4"/>
@@ -6968,21 +7131,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B138" s="3" t="s">
-        <v>64</v>
+    <row r="138" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B138" t="s">
+        <v>51</v>
       </c>
       <c r="C138">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D138" t="s">
         <v>36</v>
       </c>
       <c r="E138">
-        <v>100</v>
-      </c>
-      <c r="F138" s="7">
-        <v>1.55</v>
+        <v>166.2</v>
       </c>
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
@@ -6992,9 +7152,7 @@
       <c r="Q138" s="4"/>
       <c r="R138" s="4"/>
       <c r="S138" s="4"/>
-      <c r="T138" s="4">
-        <v>1.55</v>
-      </c>
+      <c r="T138" s="4"/>
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
       <c r="W138" s="4"/>
@@ -7011,27 +7169,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C139">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
         <v>34</v>
       </c>
       <c r="E139">
-        <v>0</v>
-      </c>
-      <c r="F139" s="3">
-        <v>296.60000000000002</v>
-      </c>
-      <c r="I139">
-        <v>511</v>
-      </c>
-      <c r="J139">
-        <v>393</v>
+        <v>1787.905</v>
       </c>
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
@@ -7039,9 +7188,7 @@
       <c r="O139" s="4"/>
       <c r="P139" s="4"/>
       <c r="Q139" s="4"/>
-      <c r="R139" s="4">
-        <v>296.60000000000002</v>
-      </c>
+      <c r="R139" s="4"/>
       <c r="S139" s="4"/>
       <c r="T139" s="4"/>
       <c r="U139" s="4"/>
@@ -7060,21 +7207,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C140">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D140" t="s">
         <v>36</v>
-      </c>
-      <c r="E140">
-        <v>437</v>
-      </c>
-      <c r="F140" s="3">
-        <v>0</v>
       </c>
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
@@ -7101,24 +7242,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C141">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D141" t="s">
         <v>34</v>
-      </c>
-      <c r="E141">
-        <v>141.5</v>
-      </c>
-      <c r="F141" s="3">
-        <v>204.3</v>
-      </c>
-      <c r="I141">
-        <v>118</v>
       </c>
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
@@ -7126,17 +7258,11 @@
       <c r="O141" s="4"/>
       <c r="P141" s="4"/>
       <c r="Q141" s="4"/>
-      <c r="R141" s="4">
-        <v>102.5</v>
-      </c>
+      <c r="R141" s="4"/>
       <c r="S141" s="4"/>
       <c r="T141" s="4"/>
-      <c r="U141" s="4">
-        <v>28.8</v>
-      </c>
-      <c r="V141" s="4">
-        <v>73</v>
-      </c>
+      <c r="U141" s="4"/>
+      <c r="V141" s="4"/>
       <c r="W141" s="4"/>
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
@@ -7151,21 +7277,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C142">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D142" t="s">
         <v>36</v>
       </c>
       <c r="E142">
-        <v>70.5</v>
-      </c>
-      <c r="F142" s="3">
-        <v>48</v>
+        <v>1021.03</v>
       </c>
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
@@ -7173,15 +7296,11 @@
       <c r="O142" s="4"/>
       <c r="P142" s="4"/>
       <c r="Q142" s="4"/>
-      <c r="R142" s="4">
-        <v>16</v>
-      </c>
+      <c r="R142" s="4"/>
       <c r="S142" s="4"/>
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
-      <c r="V142" s="4">
-        <v>32</v>
-      </c>
+      <c r="V142" s="4"/>
       <c r="W142" s="4"/>
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
@@ -7196,24 +7315,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B143" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C143">
-        <v>59</v>
+    <row r="143" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B143" t="s">
+        <v>47</v>
+      </c>
+      <c r="C143" s="1">
+        <v>12</v>
       </c>
       <c r="D143" t="s">
         <v>34</v>
-      </c>
-      <c r="E143">
-        <v>75.5</v>
-      </c>
-      <c r="F143" s="3">
-        <v>220.59</v>
-      </c>
-      <c r="I143">
-        <v>2295</v>
       </c>
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
@@ -7227,9 +7337,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
       <c r="W143" s="4"/>
-      <c r="X143" s="5">
-        <v>220.59</v>
-      </c>
+      <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
       <c r="Z143" s="9"/>
       <c r="AA143" s="4"/>
@@ -7242,18 +7350,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B144" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C144">
-        <v>59</v>
+    <row r="144" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B144" t="s">
+        <v>47</v>
+      </c>
+      <c r="C144" s="1">
+        <v>12</v>
       </c>
       <c r="D144" t="s">
         <v>36</v>
       </c>
       <c r="E144">
-        <v>130</v>
+        <v>205</v>
+      </c>
+      <c r="F144" s="3">
+        <v>216.1</v>
       </c>
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
@@ -7269,8 +7380,12 @@
       <c r="W144" s="4"/>
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
-      <c r="Z144" s="9"/>
-      <c r="AA144" s="4"/>
+      <c r="Z144" s="9">
+        <v>169.1</v>
+      </c>
+      <c r="AA144" s="4">
+        <v>47</v>
+      </c>
       <c r="AB144" s="4"/>
       <c r="AC144" s="4"/>
       <c r="AD144" s="4"/>
@@ -7280,21 +7395,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C145">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D145" t="s">
         <v>34</v>
       </c>
       <c r="E145">
-        <v>174</v>
+        <v>0</v>
+      </c>
+      <c r="F145" s="3">
+        <v>296.60000000000002</v>
       </c>
       <c r="I145">
-        <v>220</v>
+        <v>511</v>
+      </c>
+      <c r="J145">
+        <v>393</v>
       </c>
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
@@ -7302,7 +7423,9 @@
       <c r="O145" s="4"/>
       <c r="P145" s="4"/>
       <c r="Q145" s="4"/>
-      <c r="R145" s="4"/>
+      <c r="R145" s="4">
+        <v>296.60000000000002</v>
+      </c>
       <c r="S145" s="4"/>
       <c r="T145" s="4"/>
       <c r="U145" s="4"/>
@@ -7318,18 +7441,21 @@
       <c r="AE145" s="4"/>
       <c r="AF145" s="4"/>
     </row>
-    <row r="146" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C146">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D146" t="s">
         <v>36</v>
       </c>
       <c r="E146">
-        <v>415.5</v>
+        <v>437</v>
+      </c>
+      <c r="F146" s="3">
+        <v>0</v>
       </c>
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
@@ -7353,18 +7479,24 @@
       <c r="AE146" s="4"/>
       <c r="AF146" s="4"/>
     </row>
-    <row r="147" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C147">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D147" t="s">
         <v>34</v>
       </c>
       <c r="E147">
-        <v>28.85</v>
+        <v>141.5</v>
+      </c>
+      <c r="F147" s="3">
+        <v>204.3</v>
+      </c>
+      <c r="I147">
+        <v>118</v>
       </c>
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
@@ -7372,11 +7504,17 @@
       <c r="O147" s="4"/>
       <c r="P147" s="4"/>
       <c r="Q147" s="4"/>
-      <c r="R147" s="4"/>
+      <c r="R147" s="4">
+        <v>102.5</v>
+      </c>
       <c r="S147" s="4"/>
       <c r="T147" s="4"/>
-      <c r="U147" s="4"/>
-      <c r="V147" s="4"/>
+      <c r="U147" s="4">
+        <v>28.8</v>
+      </c>
+      <c r="V147" s="4">
+        <v>73</v>
+      </c>
       <c r="W147" s="4"/>
       <c r="X147" s="4"/>
       <c r="Y147" s="4"/>
@@ -7388,18 +7526,21 @@
       <c r="AE147" s="4"/>
       <c r="AF147" s="4"/>
     </row>
-    <row r="148" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C148">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D148" t="s">
         <v>36</v>
       </c>
       <c r="E148">
-        <v>138.24</v>
+        <v>70.5</v>
+      </c>
+      <c r="F148" s="3">
+        <v>48</v>
       </c>
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
@@ -7407,11 +7548,15 @@
       <c r="O148" s="4"/>
       <c r="P148" s="4"/>
       <c r="Q148" s="4"/>
-      <c r="R148" s="4"/>
+      <c r="R148" s="4">
+        <v>16</v>
+      </c>
       <c r="S148" s="4"/>
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
-      <c r="V148" s="4"/>
+      <c r="V148" s="4">
+        <v>32</v>
+      </c>
       <c r="W148" s="4"/>
       <c r="X148" s="4"/>
       <c r="Y148" s="4"/>
@@ -7423,24 +7568,15 @@
       <c r="AE148" s="4"/>
       <c r="AF148" s="4"/>
     </row>
-    <row r="149" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C149">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D149" t="s">
         <v>34</v>
-      </c>
-      <c r="E149">
-        <v>0</v>
-      </c>
-      <c r="F149" s="3">
-        <v>0</v>
-      </c>
-      <c r="I149">
-        <v>94</v>
       </c>
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
@@ -7464,21 +7600,18 @@
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
     </row>
-    <row r="150" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C150">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D150" t="s">
         <v>36</v>
       </c>
       <c r="E150">
-        <v>1799.2</v>
-      </c>
-      <c r="F150" s="3">
-        <v>1696.2</v>
+        <v>125</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -7493,15 +7626,9 @@
       <c r="V150" s="4"/>
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
-      <c r="Y150" s="4">
-        <v>930</v>
-      </c>
-      <c r="Z150" s="9">
-        <v>584.20000000000005</v>
-      </c>
-      <c r="AA150" s="4">
-        <v>182</v>
-      </c>
+      <c r="Y150" s="4"/>
+      <c r="Z150" s="9"/>
+      <c r="AA150" s="4"/>
       <c r="AB150" s="4"/>
       <c r="AC150" s="4"/>
       <c r="AD150" s="4"/>
@@ -7511,15 +7638,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B151" t="s">
-        <v>70</v>
+    <row r="151" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B151" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C151">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D151" t="s">
         <v>34</v>
+      </c>
+      <c r="E151">
+        <v>75.5</v>
+      </c>
+      <c r="F151" s="3">
+        <v>220.59</v>
+      </c>
+      <c r="I151">
+        <v>2295</v>
       </c>
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
@@ -7533,7 +7669,9 @@
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
       <c r="W151" s="4"/>
-      <c r="X151" s="4"/>
+      <c r="X151" s="5">
+        <v>220.59</v>
+      </c>
       <c r="Y151" s="4"/>
       <c r="Z151" s="9"/>
       <c r="AA151" s="4"/>
@@ -7543,18 +7681,18 @@
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
     </row>
-    <row r="152" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B152" t="s">
-        <v>70</v>
+    <row r="152" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B152" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C152">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D152" t="s">
         <v>36</v>
       </c>
       <c r="E152">
-        <v>109.8</v>
+        <v>130</v>
       </c>
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
@@ -7578,18 +7716,21 @@
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
     </row>
-    <row r="153" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C153">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D153" t="s">
         <v>34</v>
       </c>
+      <c r="E153">
+        <v>174</v>
+      </c>
       <c r="I153">
-        <v>32</v>
+        <v>220</v>
       </c>
       <c r="L153" s="4"/>
       <c r="M153" s="4"/>
@@ -7613,21 +7754,18 @@
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
     </row>
-    <row r="154" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C154">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D154" t="s">
         <v>36</v>
       </c>
       <c r="E154">
-        <v>59.5</v>
-      </c>
-      <c r="F154" s="3">
-        <v>68.2</v>
+        <v>415.5</v>
       </c>
       <c r="L154" s="4"/>
       <c r="M154" s="4"/>
@@ -7643,9 +7781,7 @@
       <c r="W154" s="4"/>
       <c r="X154" s="4"/>
       <c r="Y154" s="4"/>
-      <c r="Z154" s="9">
-        <v>68.2</v>
-      </c>
+      <c r="Z154" s="9"/>
       <c r="AA154" s="4"/>
       <c r="AB154" s="4"/>
       <c r="AC154" s="4"/>
@@ -7653,18 +7789,15 @@
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
     </row>
-    <row r="155" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C155">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D155" t="s">
         <v>34</v>
-      </c>
-      <c r="I155">
-        <v>1180</v>
       </c>
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
@@ -7691,18 +7824,18 @@
         <v>1746.61</v>
       </c>
     </row>
-    <row r="156" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C156">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D156" t="s">
         <v>36</v>
       </c>
       <c r="E156">
-        <v>382.5</v>
+        <v>238</v>
       </c>
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
@@ -7729,18 +7862,15 @@
         <v>1471.49</v>
       </c>
     </row>
-    <row r="157" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C157">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D157" t="s">
         <v>34</v>
-      </c>
-      <c r="E157">
-        <v>418.5</v>
       </c>
       <c r="L157" s="4"/>
       <c r="M157" s="4"/>
@@ -7768,18 +7898,18 @@
         <v>275.11999999999989</v>
       </c>
     </row>
-    <row r="158" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C158">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D158" t="s">
         <v>36</v>
       </c>
       <c r="E158">
-        <v>441.5</v>
+        <v>69</v>
       </c>
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
@@ -7803,33 +7933,15 @@
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
     </row>
-    <row r="159" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B159" s="3" t="s">
-        <v>74</v>
+    <row r="159" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B159" t="s">
+        <v>88</v>
       </c>
       <c r="C159">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D159" t="s">
         <v>34</v>
-      </c>
-      <c r="E159">
-        <v>240.4</v>
-      </c>
-      <c r="F159" s="3">
-        <v>766.04399999999998</v>
-      </c>
-      <c r="G159">
-        <v>18</v>
-      </c>
-      <c r="H159">
-        <v>61.47</v>
-      </c>
-      <c r="I159">
-        <v>1989</v>
-      </c>
-      <c r="J159">
-        <v>1901</v>
       </c>
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
@@ -7840,18 +7952,10 @@
       <c r="R159" s="4"/>
       <c r="S159" s="4"/>
       <c r="T159" s="4"/>
-      <c r="U159" s="4">
-        <f>528.5-68.36+91.707</f>
-        <v>551.84699999999998</v>
-      </c>
-      <c r="V159" s="4">
-        <f>52.4-0.15+91.707</f>
-        <v>143.95699999999999</v>
-      </c>
+      <c r="U159" s="4"/>
+      <c r="V159" s="4"/>
       <c r="W159" s="4"/>
-      <c r="X159" s="4">
-        <v>70.239999999999995</v>
-      </c>
+      <c r="X159" s="4"/>
       <c r="Y159" s="4"/>
       <c r="Z159" s="9"/>
       <c r="AA159" s="4"/>
@@ -7861,24 +7965,21 @@
       <c r="AE159" s="4"/>
       <c r="AF159" s="4"/>
       <c r="AG159" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="160" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B160" t="s">
+        <v>88</v>
+      </c>
+      <c r="C160">
         <v>75</v>
-      </c>
-    </row>
-    <row r="160" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B160" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C160">
-        <v>64</v>
       </c>
       <c r="D160" t="s">
         <v>36</v>
       </c>
       <c r="E160">
-        <v>976.24</v>
-      </c>
-      <c r="F160" s="3">
-        <v>162.15</v>
+        <v>140</v>
       </c>
       <c r="L160" s="4"/>
       <c r="M160" s="4"/>
@@ -7889,19 +7990,11 @@
       <c r="R160" s="4"/>
       <c r="S160" s="4"/>
       <c r="T160" s="4"/>
-      <c r="U160" s="4">
-        <v>42.7</v>
-      </c>
+      <c r="U160" s="4"/>
       <c r="V160" s="4"/>
-      <c r="W160" s="4">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="X160" s="4">
-        <v>8.81</v>
-      </c>
-      <c r="Y160" s="4">
-        <v>70.84</v>
-      </c>
+      <c r="W160" s="4"/>
+      <c r="X160" s="4"/>
+      <c r="Y160" s="4"/>
       <c r="Z160" s="9"/>
       <c r="AA160" s="4"/>
       <c r="AB160" s="4"/>
@@ -7910,40 +8003,22 @@
       <c r="AE160" s="4"/>
       <c r="AF160" s="4"/>
       <c r="AG160" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="AL160">
         <f>AL157/3</f>
         <v>91.706666666666635</v>
       </c>
     </row>
-    <row r="161" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B161" s="3" t="s">
-        <v>74</v>
+    <row r="161" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B161" t="s">
+        <v>76</v>
       </c>
       <c r="C161">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D161" t="s">
         <v>34</v>
-      </c>
-      <c r="E161">
-        <v>286</v>
-      </c>
-      <c r="F161" s="3">
-        <v>466.40699999999998</v>
-      </c>
-      <c r="G161">
-        <v>8</v>
-      </c>
-      <c r="H161">
-        <v>28.55</v>
-      </c>
-      <c r="I161">
-        <v>574</v>
-      </c>
-      <c r="J161">
-        <v>822</v>
       </c>
       <c r="L161" s="4"/>
       <c r="M161" s="4"/>
@@ -7954,14 +8029,8 @@
       <c r="R161" s="4"/>
       <c r="S161" s="4"/>
       <c r="T161" s="4"/>
-      <c r="U161" s="4">
-        <f>67.2+51</f>
-        <v>118.2</v>
-      </c>
-      <c r="V161" s="4">
-        <f>256.5+91.707</f>
-        <v>348.20699999999999</v>
-      </c>
+      <c r="U161" s="4"/>
+      <c r="V161" s="4"/>
       <c r="W161" s="4"/>
       <c r="X161" s="4"/>
       <c r="Y161" s="4"/>
@@ -7973,24 +8042,21 @@
       <c r="AE161" s="4"/>
       <c r="AF161" s="4"/>
       <c r="AG161" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="162" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B162" s="3" t="s">
-        <v>74</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="162" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B162" t="s">
+        <v>76</v>
       </c>
       <c r="C162">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D162" t="s">
         <v>36</v>
       </c>
       <c r="E162">
-        <v>566.29999999999995</v>
-      </c>
-      <c r="F162" s="3">
-        <v>142.61000000000001</v>
+        <v>747</v>
       </c>
       <c r="L162" s="4"/>
       <c r="M162" s="4"/>
@@ -8003,14 +8069,9 @@
       <c r="T162" s="4"/>
       <c r="U162" s="4"/>
       <c r="V162" s="4"/>
-      <c r="W162" s="4">
-        <v>65.599999999999994</v>
-      </c>
+      <c r="W162" s="4"/>
       <c r="X162" s="4"/>
-      <c r="Y162" s="4">
-        <f>14.84+38.87+23.3</f>
-        <v>77.009999999999991</v>
-      </c>
+      <c r="Y162" s="4"/>
       <c r="Z162" s="9"/>
       <c r="AA162" s="4"/>
       <c r="AB162" s="4"/>
@@ -8019,30 +8080,18 @@
       <c r="AE162" s="4"/>
       <c r="AF162" s="4"/>
       <c r="AG162" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="163" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B163" t="s">
+        <v>85</v>
+      </c>
+      <c r="C163">
         <v>75</v>
       </c>
-    </row>
-    <row r="163" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B163" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C163">
-        <v>66</v>
-      </c>
       <c r="D163" t="s">
         <v>34</v>
-      </c>
-      <c r="F163" s="3">
-        <v>207.4</v>
-      </c>
-      <c r="G163">
-        <v>7</v>
-      </c>
-      <c r="H163">
-        <v>21.76</v>
-      </c>
-      <c r="I163">
-        <v>597</v>
       </c>
       <c r="L163" s="4"/>
       <c r="M163" s="4"/>
@@ -8054,9 +8103,7 @@
       <c r="S163" s="4"/>
       <c r="T163" s="4"/>
       <c r="U163" s="4"/>
-      <c r="V163" s="4">
-        <v>207.4</v>
-      </c>
+      <c r="V163" s="4"/>
       <c r="W163" s="4"/>
       <c r="X163" s="4"/>
       <c r="Y163" s="4"/>
@@ -8068,24 +8115,24 @@
       <c r="AE163" s="4"/>
       <c r="AF163" s="4"/>
       <c r="AG163" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="164" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B164" t="s">
+        <v>85</v>
+      </c>
+      <c r="C164">
         <v>75</v>
-      </c>
-    </row>
-    <row r="164" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B164" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C164">
-        <v>66</v>
       </c>
       <c r="D164" t="s">
         <v>36</v>
       </c>
       <c r="E164">
-        <v>116.6</v>
+        <v>338.5</v>
       </c>
       <c r="F164" s="3">
-        <v>2</v>
+        <v>377.8</v>
       </c>
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
@@ -8098,12 +8145,12 @@
       <c r="T164" s="4"/>
       <c r="U164" s="4"/>
       <c r="V164" s="4"/>
-      <c r="W164" s="4">
-        <v>2</v>
-      </c>
+      <c r="W164" s="4"/>
       <c r="X164" s="4"/>
       <c r="Y164" s="4"/>
-      <c r="Z164" s="9"/>
+      <c r="Z164" s="9">
+        <v>377.8</v>
+      </c>
       <c r="AA164" s="4"/>
       <c r="AB164" s="4"/>
       <c r="AC164" s="4"/>
@@ -8111,24 +8158,18 @@
       <c r="AE164" s="4"/>
       <c r="AF164" s="4"/>
       <c r="AG164" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C165">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D165" t="s">
         <v>34</v>
-      </c>
-      <c r="E165">
-        <v>772.07</v>
-      </c>
-      <c r="I165">
-        <v>785</v>
       </c>
       <c r="L165" s="4"/>
       <c r="M165" s="4"/>
@@ -8154,16 +8195,19 @@
     </row>
     <row r="166" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C166">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D166" t="s">
         <v>36</v>
       </c>
       <c r="E166">
-        <v>894.97</v>
+        <v>226.5</v>
+      </c>
+      <c r="F166" s="3">
+        <v>258.7</v>
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
@@ -8179,20 +8223,24 @@
       <c r="W166" s="4"/>
       <c r="X166" s="4"/>
       <c r="Y166" s="4"/>
-      <c r="Z166" s="9"/>
-      <c r="AA166" s="4"/>
+      <c r="Z166" s="9">
+        <v>100.7</v>
+      </c>
+      <c r="AA166" s="4">
+        <v>158</v>
+      </c>
       <c r="AB166" s="4"/>
       <c r="AC166" s="4"/>
       <c r="AD166" s="4"/>
       <c r="AE166" s="4"/>
       <c r="AF166" s="4"/>
     </row>
-    <row r="167" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C167">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D167" t="s">
         <v>34</v>
@@ -8219,18 +8267,21 @@
       <c r="AE167" s="4"/>
       <c r="AF167" s="4"/>
     </row>
-    <row r="168" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C168">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D168" t="s">
         <v>36</v>
       </c>
       <c r="E168">
-        <v>747</v>
+        <v>1566.27</v>
+      </c>
+      <c r="F168" s="3">
+        <v>332</v>
       </c>
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
@@ -8246,32 +8297,27 @@
       <c r="W168" s="4"/>
       <c r="X168" s="4"/>
       <c r="Y168" s="4"/>
-      <c r="Z168" s="9"/>
-      <c r="AA168" s="4"/>
+      <c r="Z168" s="9">
+        <v>42</v>
+      </c>
+      <c r="AA168" s="4">
+        <v>290</v>
+      </c>
       <c r="AB168" s="4"/>
       <c r="AC168" s="4"/>
       <c r="AD168" s="4"/>
       <c r="AE168" s="4"/>
       <c r="AF168" s="4"/>
     </row>
-    <row r="169" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B169" s="3" t="s">
-        <v>78</v>
+    <row r="169" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B169" t="s">
+        <v>91</v>
       </c>
       <c r="C169">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D169" t="s">
         <v>34</v>
-      </c>
-      <c r="E169">
-        <v>205.65</v>
-      </c>
-      <c r="F169" s="3">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="I169">
-        <v>288</v>
       </c>
       <c r="L169" s="4"/>
       <c r="M169" s="4"/>
@@ -8285,9 +8331,7 @@
       <c r="U169" s="4"/>
       <c r="V169" s="4"/>
       <c r="W169" s="4"/>
-      <c r="X169" s="4">
-        <v>76.400000000000006</v>
-      </c>
+      <c r="X169" s="4"/>
       <c r="Y169" s="4"/>
       <c r="Z169" s="9"/>
       <c r="AA169" s="4"/>
@@ -8300,18 +8344,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B170" s="3" t="s">
-        <v>78</v>
+    <row r="170" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B170" t="s">
+        <v>91</v>
       </c>
       <c r="C170">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D170" t="s">
         <v>36</v>
       </c>
       <c r="E170">
-        <v>59.6</v>
+        <v>180</v>
+      </c>
+      <c r="F170" s="3">
+        <v>167.96</v>
       </c>
       <c r="L170" s="4"/>
       <c r="M170" s="4"/>
@@ -8326,9 +8373,15 @@
       <c r="V170" s="4"/>
       <c r="W170" s="4"/>
       <c r="X170" s="4"/>
-      <c r="Y170" s="4"/>
-      <c r="Z170" s="9"/>
-      <c r="AA170" s="4"/>
+      <c r="Y170" s="4">
+        <v>43.66</v>
+      </c>
+      <c r="Z170" s="9">
+        <v>89.8</v>
+      </c>
+      <c r="AA170" s="4">
+        <v>34.5</v>
+      </c>
       <c r="AB170" s="4"/>
       <c r="AC170" s="4"/>
       <c r="AD170" s="4"/>
@@ -8338,24 +8391,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B171" s="3" t="s">
-        <v>78</v>
+    <row r="171" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B171" t="s">
+        <v>42</v>
       </c>
       <c r="C171">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="D171" t="s">
         <v>34</v>
       </c>
       <c r="E171">
-        <v>62.5</v>
-      </c>
-      <c r="F171" s="3">
-        <v>344.13</v>
-      </c>
-      <c r="I171">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="L171" s="4"/>
       <c r="M171" s="4"/>
@@ -8368,13 +8415,8 @@
       <c r="T171" s="4"/>
       <c r="U171" s="4"/>
       <c r="V171" s="4"/>
-      <c r="W171" s="4">
-        <v>81.8</v>
-      </c>
-      <c r="X171" s="4">
-        <f>42+158.17+61.95+0.21</f>
-        <v>262.33</v>
-      </c>
+      <c r="W171" s="4"/>
+      <c r="X171" s="4"/>
       <c r="Y171" s="4"/>
       <c r="Z171" s="9"/>
       <c r="AA171" s="4"/>
@@ -8387,21 +8429,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B172" s="3" t="s">
-        <v>78</v>
+    <row r="172" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B172" t="s">
+        <v>42</v>
       </c>
       <c r="C172">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="D172" t="s">
         <v>36</v>
-      </c>
-      <c r="E172">
-        <v>63</v>
-      </c>
-      <c r="F172" s="3">
-        <v>47.56</v>
       </c>
       <c r="L172" s="4"/>
       <c r="M172" s="4"/>
@@ -8415,9 +8451,7 @@
       <c r="U172" s="4"/>
       <c r="V172" s="4"/>
       <c r="W172" s="4"/>
-      <c r="X172" s="4">
-        <v>47.56</v>
-      </c>
+      <c r="X172" s="4"/>
       <c r="Y172" s="4"/>
       <c r="Z172" s="9"/>
       <c r="AA172" s="4"/>
@@ -8430,21 +8464,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C173">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D173" t="s">
         <v>34</v>
       </c>
       <c r="E173">
-        <v>217</v>
-      </c>
-      <c r="I173">
-        <v>141</v>
+        <v>28.85</v>
       </c>
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
@@ -8468,18 +8499,18 @@
       <c r="AE173" s="4"/>
       <c r="AF173" s="4"/>
     </row>
-    <row r="174" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C174">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D174" t="s">
         <v>36</v>
       </c>
       <c r="E174">
-        <v>28</v>
+        <v>138.24</v>
       </c>
       <c r="L174" s="4"/>
       <c r="M174" s="4"/>
@@ -8503,15 +8534,27 @@
       <c r="AE174" s="4"/>
       <c r="AF174" s="4"/>
     </row>
-    <row r="175" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
-        <v>80</v>
-      </c>
-      <c r="C175">
-        <v>71</v>
+        <v>98</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="D175" t="s">
         <v>34</v>
+      </c>
+      <c r="E175">
+        <v>351</v>
+      </c>
+      <c r="F175" s="3">
+        <v>300.68</v>
+      </c>
+      <c r="I175">
+        <v>8</v>
+      </c>
+      <c r="J175">
+        <v>27</v>
       </c>
       <c r="L175" s="4"/>
       <c r="M175" s="4"/>
@@ -8520,7 +8563,9 @@
       <c r="P175" s="4"/>
       <c r="Q175" s="4"/>
       <c r="R175" s="4"/>
-      <c r="S175" s="4"/>
+      <c r="S175" s="4">
+        <v>300.68</v>
+      </c>
       <c r="T175" s="4"/>
       <c r="U175" s="4"/>
       <c r="V175" s="4"/>
@@ -8535,32 +8580,41 @@
       <c r="AE175" s="4"/>
       <c r="AF175" s="4"/>
     </row>
-    <row r="176" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
-        <v>80</v>
-      </c>
-      <c r="C176">
-        <v>71</v>
+        <v>98</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="D176" t="s">
         <v>36</v>
       </c>
       <c r="E176">
-        <v>125</v>
+        <v>152</v>
+      </c>
+      <c r="F176" s="3">
+        <v>337.46</v>
       </c>
       <c r="L176" s="4"/>
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
       <c r="O176" s="4"/>
       <c r="P176" s="4"/>
-      <c r="Q176" s="4"/>
+      <c r="Q176" s="4">
+        <v>127.69</v>
+      </c>
       <c r="R176" s="4"/>
       <c r="S176" s="4"/>
       <c r="T176" s="4"/>
       <c r="U176" s="4"/>
       <c r="V176" s="4"/>
-      <c r="W176" s="4"/>
-      <c r="X176" s="4"/>
+      <c r="W176" s="4">
+        <v>42</v>
+      </c>
+      <c r="X176" s="4">
+        <v>167.77</v>
+      </c>
       <c r="Y176" s="4"/>
       <c r="Z176" s="9"/>
       <c r="AA176" s="4"/>
@@ -8570,21 +8624,18 @@
       <c r="AE176" s="4"/>
       <c r="AF176" s="4"/>
     </row>
-    <row r="177" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
-        <v>81</v>
-      </c>
-      <c r="C177">
-        <v>73</v>
+        <v>100</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D177" t="s">
         <v>34</v>
       </c>
       <c r="E177">
-        <v>131.30000000000001</v>
-      </c>
-      <c r="I177">
-        <v>134</v>
+        <v>100.2</v>
       </c>
       <c r="L177" s="4"/>
       <c r="M177" s="4"/>
@@ -8608,18 +8659,18 @@
       <c r="AE177" s="4"/>
       <c r="AF177" s="4"/>
     </row>
-    <row r="178" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
-        <v>81</v>
-      </c>
-      <c r="C178">
-        <v>73</v>
+        <v>100</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D178" t="s">
         <v>36</v>
       </c>
       <c r="E178">
-        <v>15.2</v>
+        <v>253.5</v>
       </c>
       <c r="L178" s="4"/>
       <c r="M178" s="4"/>
@@ -8643,15 +8694,18 @@
       <c r="AE178" s="4"/>
       <c r="AF178" s="4"/>
     </row>
-    <row r="179" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
-        <v>82</v>
-      </c>
-      <c r="C179">
-        <v>74</v>
+        <v>102</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D179" t="s">
         <v>34</v>
+      </c>
+      <c r="E179">
+        <v>89.9</v>
       </c>
       <c r="L179" s="4"/>
       <c r="M179" s="4"/>
@@ -8675,18 +8729,18 @@
       <c r="AE179" s="4"/>
       <c r="AF179" s="4"/>
     </row>
-    <row r="180" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
-        <v>82</v>
-      </c>
-      <c r="C180">
-        <v>74</v>
+        <v>102</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D180" t="s">
         <v>36</v>
       </c>
       <c r="E180">
-        <v>1021.03</v>
+        <v>322.2</v>
       </c>
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
@@ -8710,24 +8764,15 @@
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
     </row>
-    <row r="181" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B181" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C181">
-        <v>74</v>
+    <row r="181" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B181" t="s">
+        <v>104</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D181" t="s">
         <v>34</v>
-      </c>
-      <c r="E181">
-        <v>341.2</v>
-      </c>
-      <c r="F181" s="3">
-        <v>145.88</v>
-      </c>
-      <c r="I181">
-        <v>37</v>
       </c>
       <c r="L181" s="4"/>
       <c r="M181" s="4"/>
@@ -8740,13 +8785,8 @@
       <c r="T181" s="4"/>
       <c r="U181" s="4"/>
       <c r="V181" s="4"/>
-      <c r="W181" s="4">
-        <v>78.180000000000007</v>
-      </c>
-      <c r="X181" s="4">
-        <f>18.75+12+36.95</f>
-        <v>67.7</v>
-      </c>
+      <c r="W181" s="4"/>
+      <c r="X181" s="4"/>
       <c r="Y181" s="4"/>
       <c r="Z181" s="9"/>
       <c r="AA181" s="4"/>
@@ -8759,21 +8799,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B182" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C182">
-        <v>74</v>
+    <row r="182" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B182" t="s">
+        <v>104</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D182" t="s">
         <v>36</v>
       </c>
       <c r="E182">
-        <v>83.8</v>
-      </c>
-      <c r="F182" s="3">
-        <v>55.83</v>
+        <v>129.80000000000001</v>
       </c>
       <c r="L182" s="4"/>
       <c r="M182" s="4"/>
@@ -8787,10 +8824,7 @@
       <c r="U182" s="4"/>
       <c r="V182" s="4"/>
       <c r="W182" s="4"/>
-      <c r="X182" s="4">
-        <f>34.75+6.11+14.97</f>
-        <v>55.83</v>
-      </c>
+      <c r="X182" s="4"/>
       <c r="Y182" s="4"/>
       <c r="Z182" s="9"/>
       <c r="AA182" s="4"/>
@@ -8803,9 +8837,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C183">
         <v>75</v>
@@ -8838,9 +8872,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C184">
         <v>75</v>
@@ -8849,10 +8883,7 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>226.5</v>
-      </c>
-      <c r="F184" s="3">
-        <v>189.9</v>
+        <v>168</v>
       </c>
       <c r="L184" s="4"/>
       <c r="M184" s="4"/>
@@ -8868,33 +8899,29 @@
       <c r="W184" s="4"/>
       <c r="X184" s="4"/>
       <c r="Y184" s="4"/>
-      <c r="Z184" s="9">
-        <v>100.7</v>
-      </c>
-      <c r="AA184" s="4">
-        <v>89.2</v>
-      </c>
+      <c r="Z184" s="9"/>
+      <c r="AA184" s="4"/>
       <c r="AB184" s="4"/>
       <c r="AC184" s="4"/>
       <c r="AD184" s="4"/>
       <c r="AE184" s="4"/>
       <c r="AF184" s="4"/>
     </row>
-    <row r="185" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C185">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D185" t="s">
         <v>34</v>
       </c>
       <c r="E185">
-        <v>375</v>
+        <v>217</v>
       </c>
       <c r="I185">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="L185" s="4"/>
       <c r="M185" s="4"/>
@@ -8918,18 +8945,18 @@
       <c r="AE185" s="4"/>
       <c r="AF185" s="4"/>
     </row>
-    <row r="186" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C186">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D186" t="s">
         <v>36</v>
       </c>
       <c r="E186">
-        <v>244.5</v>
+        <v>28</v>
       </c>
       <c r="L186" s="4"/>
       <c r="M186" s="4"/>
@@ -8953,15 +8980,18 @@
       <c r="AE186" s="4"/>
       <c r="AF186" s="4"/>
     </row>
-    <row r="187" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="C187">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D187" t="s">
         <v>34</v>
+      </c>
+      <c r="F187" s="3">
+        <v>38.299999999999997</v>
       </c>
       <c r="L187" s="4"/>
       <c r="M187" s="4"/>
@@ -8977,7 +9007,9 @@
       <c r="W187" s="4"/>
       <c r="X187" s="4"/>
       <c r="Y187" s="4"/>
-      <c r="Z187" s="9"/>
+      <c r="Z187" s="9">
+        <v>38.299999999999997</v>
+      </c>
       <c r="AA187" s="4"/>
       <c r="AB187" s="4"/>
       <c r="AC187" s="4"/>
@@ -8988,21 +9020,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="C188">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D188" t="s">
         <v>36</v>
       </c>
       <c r="E188">
-        <v>338.5</v>
-      </c>
-      <c r="F188" s="3">
-        <v>377.8</v>
+        <v>55</v>
       </c>
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
@@ -9018,9 +9047,7 @@
       <c r="W188" s="4"/>
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
-      <c r="Z188" s="9">
-        <v>377.8</v>
-      </c>
+      <c r="Z188" s="9"/>
       <c r="AA188" s="4"/>
       <c r="AB188" s="4"/>
       <c r="AC188" s="4"/>
@@ -9031,12 +9058,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C189">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D189" t="s">
         <v>34</v>
@@ -9063,18 +9090,18 @@
       <c r="AE189" s="4"/>
       <c r="AF189" s="4"/>
     </row>
-    <row r="190" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C190">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D190" t="s">
         <v>36</v>
       </c>
       <c r="E190">
-        <v>238</v>
+        <v>34</v>
       </c>
       <c r="L190" s="4"/>
       <c r="M190" s="4"/>
@@ -9098,12 +9125,12 @@
       <c r="AE190" s="4"/>
       <c r="AF190" s="4"/>
     </row>
-    <row r="191" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C191">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D191" t="s">
         <v>34</v>
@@ -9130,19 +9157,20 @@
       <c r="AE191" s="4"/>
       <c r="AF191" s="4"/>
     </row>
-    <row r="192" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C192">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D192" t="s">
         <v>36</v>
       </c>
       <c r="E192">
-        <v>69</v>
-      </c>
+        <v>201.5</v>
+      </c>
+      <c r="K192" s="2"/>
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
       <c r="N192" s="4"/>
@@ -9165,12 +9193,12 @@
       <c r="AE192" s="4"/>
       <c r="AF192" s="4"/>
     </row>
-    <row r="193" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C193">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D193" t="s">
         <v>34</v>
@@ -9197,18 +9225,18 @@
       <c r="AE193" s="4"/>
       <c r="AF193" s="4"/>
     </row>
-    <row r="194" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C194">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D194" t="s">
         <v>36</v>
       </c>
       <c r="E194">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="L194" s="4"/>
       <c r="M194" s="4"/>
@@ -9232,18 +9260,18 @@
       <c r="AE194" s="4"/>
       <c r="AF194" s="4"/>
     </row>
-    <row r="195" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C195">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D195" t="s">
         <v>34</v>
       </c>
-      <c r="F195" s="3">
-        <v>880.94100000000003</v>
+      <c r="I195">
+        <v>182</v>
       </c>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -9258,14 +9286,8 @@
       <c r="V195" s="4"/>
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
-      <c r="Y195" s="4">
-        <f>592.21-43.66</f>
-        <v>548.55000000000007</v>
-      </c>
-      <c r="Z195" s="9">
-        <f>64.57+79.57+66.725+63.68+57.846</f>
-        <v>332.39099999999996</v>
-      </c>
+      <c r="Y195" s="4"/>
+      <c r="Z195" s="9"/>
       <c r="AA195" s="4"/>
       <c r="AB195" s="4"/>
       <c r="AC195" s="4"/>
@@ -9276,18 +9298,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C196">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D196" t="s">
         <v>36</v>
       </c>
       <c r="E196">
-        <v>858.5</v>
+        <v>238.52</v>
       </c>
       <c r="L196" s="4"/>
       <c r="M196" s="4"/>
@@ -9314,12 +9336,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C197">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D197" t="s">
         <v>34</v>
@@ -9349,18 +9371,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C198">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D198" t="s">
         <v>36</v>
       </c>
       <c r="E198">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="L198" s="4"/>
       <c r="M198" s="4"/>
@@ -9387,15 +9409,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="C199">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D199" t="s">
         <v>34</v>
+      </c>
+      <c r="E199">
+        <v>137</v>
       </c>
       <c r="L199" s="4"/>
       <c r="M199" s="4"/>
@@ -9422,21 +9447,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="C200">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D200" t="s">
         <v>36</v>
       </c>
       <c r="E200">
-        <v>180</v>
-      </c>
-      <c r="F200" s="3">
-        <v>167.96</v>
+        <v>636</v>
       </c>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
@@ -9451,15 +9473,9 @@
       <c r="V200" s="4"/>
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
-      <c r="Y200" s="4">
-        <v>43.66</v>
-      </c>
-      <c r="Z200" s="9">
-        <v>89.8</v>
-      </c>
-      <c r="AA200" s="4">
-        <v>34.5</v>
-      </c>
+      <c r="Y200" s="4"/>
+      <c r="Z200" s="9"/>
+      <c r="AA200" s="4"/>
       <c r="AB200" s="4"/>
       <c r="AC200" s="4"/>
       <c r="AD200" s="4"/>
@@ -9469,18 +9485,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C201">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="D201" t="s">
         <v>34</v>
-      </c>
-      <c r="I201">
-        <v>182</v>
       </c>
       <c r="L201" s="4"/>
       <c r="M201" s="4"/>
@@ -9504,21 +9517,21 @@
       <c r="AE201" s="4"/>
       <c r="AF201" s="4"/>
       <c r="AG201" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="202" spans="2:33" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="202" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C202">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="D202" t="s">
         <v>36</v>
       </c>
       <c r="E202">
-        <v>238.52</v>
+        <v>220.48</v>
       </c>
       <c r="L202" s="4"/>
       <c r="M202" s="4"/>
@@ -9542,12 +9555,12 @@
       <c r="AE202" s="4"/>
       <c r="AF202" s="4"/>
       <c r="AG202" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="203" spans="2:33" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="203" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C203">
         <v>76</v>
@@ -9576,10 +9589,13 @@
       <c r="AD203" s="4"/>
       <c r="AE203" s="4"/>
       <c r="AF203" s="4"/>
-    </row>
-    <row r="204" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG203" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="204" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C204">
         <v>76</v>
@@ -9588,7 +9604,10 @@
         <v>36</v>
       </c>
       <c r="E204">
-        <v>229.5</v>
+        <v>95</v>
+      </c>
+      <c r="F204" s="3">
+        <v>93.2</v>
       </c>
       <c r="L204" s="4"/>
       <c r="M204" s="4"/>
@@ -9603,7 +9622,9 @@
       <c r="V204" s="4"/>
       <c r="W204" s="4"/>
       <c r="X204" s="4"/>
-      <c r="Y204" s="4"/>
+      <c r="Y204" s="4">
+        <v>93.2</v>
+      </c>
       <c r="Z204" s="9"/>
       <c r="AA204" s="4"/>
       <c r="AB204" s="4"/>
@@ -9611,16 +9632,28 @@
       <c r="AD204" s="4"/>
       <c r="AE204" s="4"/>
       <c r="AF204" s="4"/>
-    </row>
-    <row r="205" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG204" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="205" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C205">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D205" t="s">
         <v>34</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205" s="3">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>94</v>
       </c>
       <c r="L205" s="4"/>
       <c r="M205" s="4"/>
@@ -9644,24 +9677,24 @@
       <c r="AE205" s="4"/>
       <c r="AF205" s="4"/>
       <c r="AG205" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="206" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="206" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C206">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D206" t="s">
         <v>36</v>
       </c>
       <c r="E206">
-        <v>1566.27</v>
+        <v>1799.2</v>
       </c>
       <c r="F206" s="3">
-        <v>176</v>
+        <v>1696.2</v>
       </c>
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
@@ -9676,28 +9709,36 @@
       <c r="V206" s="4"/>
       <c r="W206" s="4"/>
       <c r="X206" s="4"/>
-      <c r="Y206" s="4"/>
+      <c r="Y206" s="4">
+        <v>930</v>
+      </c>
       <c r="Z206" s="9">
-        <v>42</v>
+        <v>584.20000000000005</v>
       </c>
       <c r="AA206" s="4">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="AB206" s="4"/>
       <c r="AC206" s="4"/>
       <c r="AD206" s="4"/>
       <c r="AE206" s="4"/>
       <c r="AF206" s="4"/>
-    </row>
-    <row r="207" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG206" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="207" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C207">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D207" t="s">
         <v>34</v>
+      </c>
+      <c r="I207">
+        <v>1180</v>
       </c>
       <c r="L207" s="4"/>
       <c r="M207" s="4"/>
@@ -9721,24 +9762,24 @@
       <c r="AE207" s="4"/>
       <c r="AF207" s="4"/>
       <c r="AG207" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="208" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="208" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C208">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D208" t="s">
         <v>36</v>
       </c>
       <c r="E208">
-        <v>95</v>
+        <v>382.5</v>
       </c>
       <c r="F208" s="3">
-        <v>93.2</v>
+        <v>42</v>
       </c>
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
@@ -9753,35 +9794,35 @@
       <c r="V208" s="4"/>
       <c r="W208" s="4"/>
       <c r="X208" s="4"/>
-      <c r="Y208" s="4">
-        <v>93.2</v>
-      </c>
+      <c r="Y208" s="4"/>
       <c r="Z208" s="9"/>
-      <c r="AA208" s="4"/>
+      <c r="AA208" s="4">
+        <v>42</v>
+      </c>
       <c r="AB208" s="4"/>
       <c r="AC208" s="4"/>
       <c r="AD208" s="4"/>
       <c r="AE208" s="4"/>
       <c r="AF208" s="4"/>
       <c r="AG208" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="209" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B209" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>98</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="209" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B209" t="s">
+        <v>84</v>
+      </c>
+      <c r="C209">
+        <v>75</v>
       </c>
       <c r="D209" t="s">
         <v>34</v>
       </c>
       <c r="E209">
-        <v>0</v>
-      </c>
-      <c r="F209" s="3">
-        <v>34.57</v>
+        <v>375</v>
+      </c>
+      <c r="I209">
+        <v>87</v>
       </c>
       <c r="L209" s="4"/>
       <c r="M209" s="4"/>
@@ -9793,9 +9834,7 @@
       <c r="S209" s="4"/>
       <c r="T209" s="4"/>
       <c r="U209" s="4"/>
-      <c r="V209" s="4">
-        <v>34.57</v>
-      </c>
+      <c r="V209" s="4"/>
       <c r="W209" s="4"/>
       <c r="X209" s="4"/>
       <c r="Y209" s="4"/>
@@ -9810,18 +9849,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B210" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>98</v>
+    <row r="210" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B210" t="s">
+        <v>84</v>
+      </c>
+      <c r="C210">
+        <v>75</v>
       </c>
       <c r="D210" t="s">
         <v>36</v>
       </c>
       <c r="E210">
-        <v>158</v>
+        <v>244.5</v>
       </c>
       <c r="L210" s="4"/>
       <c r="M210" s="4"/>
@@ -9848,27 +9887,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
-        <v>99</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="C211">
+        <v>76</v>
       </c>
       <c r="D211" t="s">
         <v>34</v>
-      </c>
-      <c r="E211">
-        <v>351</v>
-      </c>
-      <c r="F211" s="3">
-        <v>300.68</v>
-      </c>
-      <c r="I211">
-        <v>8</v>
-      </c>
-      <c r="J211">
-        <v>27</v>
       </c>
       <c r="L211" s="4"/>
       <c r="M211" s="4"/>
@@ -9877,9 +9904,7 @@
       <c r="P211" s="4"/>
       <c r="Q211" s="4"/>
       <c r="R211" s="4"/>
-      <c r="S211" s="4">
-        <v>300.68</v>
-      </c>
+      <c r="S211" s="4"/>
       <c r="T211" s="4"/>
       <c r="U211" s="4"/>
       <c r="V211" s="4"/>
@@ -9893,42 +9918,36 @@
       <c r="AD211" s="4"/>
       <c r="AE211" s="4"/>
       <c r="AF211" s="4"/>
-    </row>
-    <row r="212" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG211" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="212" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
-        <v>99</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="C212">
+        <v>76</v>
       </c>
       <c r="D212" t="s">
         <v>36</v>
       </c>
       <c r="E212">
-        <v>152</v>
-      </c>
-      <c r="F212" s="3">
-        <v>337.46</v>
+        <v>229.5</v>
       </c>
       <c r="L212" s="4"/>
       <c r="M212" s="4"/>
       <c r="N212" s="4"/>
       <c r="O212" s="4"/>
       <c r="P212" s="4"/>
-      <c r="Q212" s="4">
-        <v>127.69</v>
-      </c>
+      <c r="Q212" s="4"/>
       <c r="R212" s="4"/>
       <c r="S212" s="4"/>
       <c r="T212" s="4"/>
       <c r="U212" s="4"/>
       <c r="V212" s="4"/>
-      <c r="W212" s="4">
-        <v>42</v>
-      </c>
-      <c r="X212" s="4">
-        <v>167.77</v>
-      </c>
+      <c r="W212" s="4"/>
+      <c r="X212" s="4"/>
       <c r="Y212" s="4"/>
       <c r="Z212" s="9"/>
       <c r="AA212" s="4"/>
@@ -9937,19 +9956,25 @@
       <c r="AD212" s="4"/>
       <c r="AE212" s="4"/>
       <c r="AF212" s="4"/>
-    </row>
-    <row r="213" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG212" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="213" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
-        <v>101</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
+      </c>
+      <c r="C213">
+        <v>67</v>
       </c>
       <c r="D213" t="s">
         <v>34</v>
       </c>
       <c r="E213">
-        <v>100.2</v>
+        <v>772.07</v>
+      </c>
+      <c r="I213">
+        <v>785</v>
       </c>
       <c r="L213" s="4"/>
       <c r="M213" s="4"/>
@@ -9972,19 +9997,22 @@
       <c r="AD213" s="4"/>
       <c r="AE213" s="4"/>
       <c r="AF213" s="4"/>
-    </row>
-    <row r="214" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG213" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="214" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
-        <v>101</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
+      </c>
+      <c r="C214">
+        <v>67</v>
       </c>
       <c r="D214" t="s">
         <v>36</v>
       </c>
       <c r="E214">
-        <v>253.5</v>
+        <v>894.97</v>
       </c>
       <c r="L214" s="4"/>
       <c r="M214" s="4"/>
@@ -10007,19 +10035,22 @@
       <c r="AD214" s="4"/>
       <c r="AE214" s="4"/>
       <c r="AF214" s="4"/>
-    </row>
-    <row r="215" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG214" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="215" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
-        <v>103</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
+      </c>
+      <c r="C215">
+        <v>63</v>
       </c>
       <c r="D215" t="s">
         <v>34</v>
       </c>
       <c r="E215">
-        <v>89.9</v>
+        <v>418.5</v>
       </c>
       <c r="L215" s="4"/>
       <c r="M215" s="4"/>
@@ -10042,19 +10073,22 @@
       <c r="AD215" s="4"/>
       <c r="AE215" s="4"/>
       <c r="AF215" s="4"/>
-    </row>
-    <row r="216" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG215" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="216" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
-        <v>103</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
+      </c>
+      <c r="C216">
+        <v>63</v>
       </c>
       <c r="D216" t="s">
         <v>36</v>
       </c>
       <c r="E216">
-        <v>322.2</v>
+        <v>441.5</v>
       </c>
       <c r="L216" s="4"/>
       <c r="M216" s="4"/>
@@ -10077,16 +10111,25 @@
       <c r="AD216" s="4"/>
       <c r="AE216" s="4"/>
       <c r="AF216" s="4"/>
-    </row>
-    <row r="217" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG216" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="217" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
-        <v>105</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>106</v>
+        <v>39</v>
+      </c>
+      <c r="C217">
+        <v>12</v>
       </c>
       <c r="D217" t="s">
         <v>34</v>
+      </c>
+      <c r="E217">
+        <v>457</v>
+      </c>
+      <c r="I217">
+        <v>43</v>
       </c>
       <c r="L217" s="4"/>
       <c r="M217" s="4"/>
@@ -10109,19 +10152,19 @@
       <c r="AD217" s="4"/>
       <c r="AE217" s="4"/>
       <c r="AF217" s="4"/>
-    </row>
-    <row r="218" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG217" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="218" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
-        <v>105</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>106</v>
+        <v>39</v>
+      </c>
+      <c r="C218">
+        <v>12</v>
       </c>
       <c r="D218" t="s">
         <v>36</v>
-      </c>
-      <c r="E218">
-        <v>129.80000000000001</v>
       </c>
       <c r="L218" s="4"/>
       <c r="M218" s="4"/>
@@ -10144,6 +10187,9 @@
       <c r="AD218" s="4"/>
       <c r="AE218" s="4"/>
       <c r="AF218" s="4"/>
+      <c r="AG218" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="AG1:AG218" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -10172,19 +10218,19 @@
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>108</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>109</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>110</v>
-      </c>
-      <c r="F2" t="s">
-        <v>111</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -10195,7 +10241,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3">
         <v>159.15</v>
@@ -10215,7 +10261,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4">
         <v>723.7</v>
@@ -10235,7 +10281,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5">
         <v>905.99</v>
@@ -10255,7 +10301,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>1089.1400000000001</v>
@@ -10279,7 +10325,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7">
         <v>588.28</v>
@@ -10303,7 +10349,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>1227.24</v>
@@ -10327,7 +10373,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9">
         <v>1914.65</v>
@@ -10355,7 +10401,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>1749.47</v>
@@ -10383,7 +10429,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11">
         <v>1942.9</v>
@@ -10411,7 +10457,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12">
         <v>1588.61</v>
@@ -10435,7 +10481,7 @@
         <v>2026</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13">
         <v>2185.34</v>
@@ -10459,7 +10505,7 @@
         <v>2026</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14">
         <v>2340.4</v>
@@ -10483,7 +10529,7 @@
         <v>2026</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15">
         <v>2128.08</v>
@@ -10502,7 +10548,7 @@
         <v>539.41999999999985</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
@@ -10510,7 +10556,7 @@
         <v>2026</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16">
         <v>2426.84</v>
@@ -10534,7 +10580,7 @@
         <v>2026</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17">
         <v>2545.85</v>
@@ -10559,7 +10605,7 @@
         <v>2026</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18">
         <v>3108.25</v>
@@ -10576,7 +10622,7 @@
         <v>2026</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19">
         <v>3269.49</v>
@@ -10593,7 +10639,7 @@
         <v>2026</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D20">
         <v>3305.21</v>
@@ -10610,7 +10656,7 @@
         <v>2026</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D21">
         <v>3138.09</v>
@@ -10627,7 +10673,7 @@
         <v>2026</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>2251.2800000000002</v>
@@ -10644,7 +10690,7 @@
         <v>2026</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23">
         <v>1527.07</v>
@@ -10661,7 +10707,7 @@
         <v>2026</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24">
         <v>542.46</v>
@@ -10693,7 +10739,7 @@
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD004AC-E1EE-4D7E-B6E0-236C936CEFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA143249-3D47-4B4D-89D2-DB81D518D575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,13 +799,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
-  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="RCE COMUNIDADE JD. UNIÃO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF218">
     <sortCondition ref="B1:B218"/>
   </sortState>
@@ -1259,7 +1253,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>64</v>
       </c>
@@ -1316,7 +1310,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>64</v>
       </c>
@@ -1359,7 +1353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1405,7 +1399,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
@@ -1448,7 +1442,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>64</v>
       </c>
@@ -1494,7 +1488,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
@@ -1537,7 +1531,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>63</v>
       </c>
@@ -1585,7 +1579,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1628,7 +1622,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1673,7 +1667,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
@@ -1711,7 +1705,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
@@ -1754,7 +1748,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>63</v>
       </c>
@@ -1792,7 +1786,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>63</v>
       </c>
@@ -1837,7 +1831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
@@ -1875,7 +1869,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
@@ -1920,7 +1914,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1958,7 +1952,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
@@ -2001,7 +1995,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>63</v>
       </c>
@@ -2039,7 +2033,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>63</v>
       </c>
@@ -2082,7 +2076,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>63</v>
       </c>
@@ -2120,7 +2114,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>63</v>
       </c>
@@ -2163,7 +2157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>63</v>
       </c>
@@ -2201,7 +2195,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>63</v>
       </c>
@@ -2246,7 +2240,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>63</v>
       </c>
@@ -2287,7 +2281,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>62</v>
       </c>
@@ -2329,7 +2323,7 @@
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
     </row>
-    <row r="27" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>62</v>
       </c>
@@ -2371,7 +2365,7 @@
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
     </row>
-    <row r="28" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
@@ -2411,7 +2405,7 @@
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
     </row>
-    <row r="29" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>62</v>
       </c>
@@ -2446,7 +2440,7 @@
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
     </row>
-    <row r="30" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>62</v>
       </c>
@@ -2483,7 +2477,7 @@
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
     </row>
-    <row r="31" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
@@ -2518,7 +2512,7 @@
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
     </row>
-    <row r="32" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
@@ -2558,7 +2552,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>62</v>
       </c>
@@ -2596,7 +2590,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -2636,7 +2630,7 @@
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
     </row>
-    <row r="35" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>62</v>
       </c>
@@ -2671,7 +2665,7 @@
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
     </row>
-    <row r="36" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>62</v>
       </c>
@@ -2708,7 +2702,7 @@
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
     </row>
-    <row r="37" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>62</v>
       </c>
@@ -2743,7 +2737,7 @@
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
     </row>
-    <row r="38" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>62</v>
       </c>
@@ -2783,7 +2777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>62</v>
       </c>
@@ -2818,7 +2812,7 @@
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
     </row>
-    <row r="40" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>62</v>
       </c>
@@ -2855,7 +2849,7 @@
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
     </row>
-    <row r="41" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
@@ -2890,7 +2884,7 @@
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
     </row>
-    <row r="42" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>62</v>
       </c>
@@ -2927,7 +2921,7 @@
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
     </row>
-    <row r="43" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>62</v>
       </c>
@@ -2962,7 +2956,7 @@
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
     </row>
-    <row r="44" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>62</v>
       </c>
@@ -3002,7 +2996,7 @@
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
     </row>
-    <row r="45" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>62</v>
       </c>
@@ -3037,7 +3031,7 @@
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
     </row>
-    <row r="46" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>62</v>
       </c>
@@ -3079,7 +3073,7 @@
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
     </row>
-    <row r="47" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>62</v>
       </c>
@@ -3114,7 +3108,7 @@
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
     </row>
-    <row r="48" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>62</v>
       </c>
@@ -3156,7 +3150,7 @@
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
     </row>
-    <row r="49" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>62</v>
       </c>
@@ -3191,7 +3185,7 @@
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
     </row>
-    <row r="50" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>62</v>
       </c>
@@ -3231,7 +3225,7 @@
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
     </row>
-    <row r="51" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>62</v>
       </c>
@@ -3266,7 +3260,7 @@
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
     </row>
-    <row r="52" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>62</v>
       </c>
@@ -3306,7 +3300,7 @@
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
     </row>
-    <row r="53" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>62</v>
       </c>
@@ -3341,7 +3335,7 @@
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
     </row>
-    <row r="54" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>62</v>
       </c>
@@ -3386,7 +3380,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>62</v>
       </c>
@@ -3424,7 +3418,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>62</v>
       </c>
@@ -3470,7 +3464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>62</v>
       </c>
@@ -3513,7 +3507,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>62</v>
       </c>
@@ -3556,7 +3550,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>62</v>
       </c>
@@ -3594,7 +3588,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
@@ -3659,7 +3653,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>58</v>
       </c>
@@ -3702,7 +3696,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>58</v>
       </c>
@@ -3758,7 +3752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>58</v>
       </c>
@@ -3800,7 +3794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>58</v>
       </c>
@@ -3858,7 +3852,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>58</v>
       </c>
@@ -3902,7 +3896,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>59</v>
       </c>
@@ -3949,7 +3943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>59</v>
       </c>
@@ -3994,7 +3988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>59</v>
       </c>
@@ -4041,7 +4035,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>59</v>
       </c>
@@ -4085,7 +4079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>33</v>
       </c>
@@ -4131,7 +4125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>33</v>
       </c>
@@ -4174,7 +4168,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>33</v>
       </c>
@@ -4219,7 +4213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>33</v>
       </c>
@@ -4262,7 +4256,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>33</v>
       </c>
@@ -4305,7 +4299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>33</v>
       </c>
@@ -4348,7 +4342,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
         <v>33</v>
       </c>
@@ -4396,7 +4390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
         <v>33</v>
       </c>
@@ -4440,7 +4434,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>38</v>
       </c>
@@ -4495,7 +4489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
         <v>38</v>
       </c>
@@ -4538,7 +4532,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
         <v>38</v>
       </c>
@@ -4587,7 +4581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B81" s="3" t="s">
         <v>38</v>
       </c>
@@ -4630,7 +4624,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>60</v>
       </c>
@@ -4679,7 +4673,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B83" s="3" t="s">
         <v>60</v>
       </c>
@@ -4722,7 +4716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B84" s="3" t="s">
         <v>57</v>
       </c>
@@ -4778,7 +4772,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
         <v>57</v>
       </c>
@@ -4822,7 +4816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B86" s="3" t="s">
         <v>57</v>
       </c>
@@ -4872,7 +4866,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
         <v>57</v>
       </c>
@@ -4916,7 +4910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
         <v>57</v>
       </c>
@@ -4968,7 +4962,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>57</v>
       </c>
@@ -5012,7 +5006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>52</v>
       </c>
@@ -5050,7 +5044,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>52</v>
       </c>
@@ -5088,7 +5082,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
         <v>56</v>
       </c>
@@ -5140,7 +5134,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
         <v>56</v>
       </c>
@@ -5182,7 +5176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B94" s="3" t="s">
         <v>56</v>
       </c>
@@ -5234,7 +5228,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
         <v>56</v>
       </c>
@@ -5276,7 +5270,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>56</v>
       </c>
@@ -5328,7 +5322,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B97" s="3" t="s">
         <v>56</v>
       </c>
@@ -5372,7 +5366,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
         <v>56</v>
       </c>
@@ -5419,7 +5413,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B99" s="3" t="s">
         <v>56</v>
       </c>
@@ -5463,7 +5457,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B100" s="3" t="s">
         <v>55</v>
       </c>
@@ -5510,7 +5504,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B101" s="3" t="s">
         <v>37</v>
       </c>
@@ -5567,7 +5561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B102" s="3" t="s">
         <v>37</v>
       </c>
@@ -5605,7 +5599,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
         <v>37</v>
       </c>
@@ -5656,7 +5650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B104" s="3" t="s">
         <v>37</v>
       </c>
@@ -5697,7 +5691,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B105" s="3" t="s">
         <v>37</v>
       </c>
@@ -5748,7 +5742,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="2:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="3" t="s">
         <v>37</v>
       </c>
@@ -5791,7 +5785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
         <v>37</v>
       </c>
@@ -5844,7 +5838,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B108" s="3" t="s">
         <v>37</v>
       </c>
@@ -5882,7 +5876,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
         <v>37</v>
       </c>
@@ -5931,7 +5925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
         <v>37</v>
       </c>
@@ -5980,7 +5974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>89</v>
       </c>
@@ -6024,7 +6018,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>89</v>
       </c>
@@ -6062,7 +6056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B113" s="3" t="s">
         <v>77</v>
       </c>
@@ -6108,7 +6102,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B114" s="3" t="s">
         <v>77</v>
       </c>
@@ -6146,7 +6140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
         <v>77</v>
       </c>
@@ -6195,7 +6189,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B116" s="3" t="s">
         <v>77</v>
       </c>
@@ -6238,7 +6232,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
         <v>74</v>
       </c>
@@ -6299,7 +6293,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
         <v>74</v>
       </c>
@@ -6348,7 +6342,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
         <v>74</v>
       </c>
@@ -6407,7 +6401,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
         <v>74</v>
       </c>
@@ -6453,7 +6447,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
         <v>74</v>
       </c>
@@ -6502,7 +6496,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
         <v>74</v>
       </c>
@@ -6545,7 +6539,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>50</v>
       </c>
@@ -6583,7 +6577,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>50</v>
       </c>
@@ -6618,7 +6612,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>53</v>
       </c>
@@ -6656,7 +6650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>53</v>
       </c>
@@ -6694,7 +6688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>48</v>
       </c>
@@ -6732,7 +6726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>48</v>
       </c>
@@ -6767,7 +6761,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>70</v>
       </c>
@@ -6802,7 +6796,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>70</v>
       </c>
@@ -6840,7 +6834,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B131" s="3" t="s">
         <v>82</v>
       </c>
@@ -6889,7 +6883,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
         <v>82</v>
       </c>
@@ -6933,7 +6927,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>71</v>
       </c>
@@ -6971,7 +6965,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>71</v>
       </c>
@@ -7014,7 +7008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>80</v>
       </c>
@@ -7055,7 +7049,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>80</v>
       </c>
@@ -7093,7 +7087,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>51</v>
       </c>
@@ -7131,7 +7125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>51</v>
       </c>
@@ -7169,7 +7163,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>49</v>
       </c>
@@ -7207,7 +7201,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>49</v>
       </c>
@@ -7242,7 +7236,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>81</v>
       </c>
@@ -7277,7 +7271,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>81</v>
       </c>
@@ -7315,7 +7309,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>47</v>
       </c>
@@ -7350,7 +7344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>47</v>
       </c>
@@ -7395,7 +7389,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>65</v>
       </c>
@@ -7441,7 +7435,7 @@
       <c r="AE145" s="4"/>
       <c r="AF145" s="4"/>
     </row>
-    <row r="146" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>65</v>
       </c>
@@ -7479,7 +7473,7 @@
       <c r="AE146" s="4"/>
       <c r="AF146" s="4"/>
     </row>
-    <row r="147" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>65</v>
       </c>
@@ -7526,7 +7520,7 @@
       <c r="AE147" s="4"/>
       <c r="AF147" s="4"/>
     </row>
-    <row r="148" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>65</v>
       </c>
@@ -7568,7 +7562,7 @@
       <c r="AE148" s="4"/>
       <c r="AF148" s="4"/>
     </row>
-    <row r="149" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>79</v>
       </c>
@@ -7600,7 +7594,7 @@
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
     </row>
-    <row r="150" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>79</v>
       </c>
@@ -7638,7 +7632,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B151" s="3" t="s">
         <v>66</v>
       </c>
@@ -7681,7 +7675,7 @@
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
     </row>
-    <row r="152" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B152" s="3" t="s">
         <v>66</v>
       </c>
@@ -7716,7 +7710,7 @@
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
     </row>
-    <row r="153" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>67</v>
       </c>
@@ -7754,7 +7748,7 @@
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
     </row>
-    <row r="154" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>67</v>
       </c>
@@ -7789,7 +7783,7 @@
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
     </row>
-    <row r="155" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>86</v>
       </c>
@@ -7824,7 +7818,7 @@
         <v>1746.61</v>
       </c>
     </row>
-    <row r="156" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>86</v>
       </c>
@@ -7862,7 +7856,7 @@
         <v>1471.49</v>
       </c>
     </row>
-    <row r="157" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>87</v>
       </c>
@@ -7898,7 +7892,7 @@
         <v>275.11999999999989</v>
       </c>
     </row>
-    <row r="158" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>87</v>
       </c>
@@ -7933,7 +7927,7 @@
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
     </row>
-    <row r="159" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>88</v>
       </c>
@@ -7968,7 +7962,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="160" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>88</v>
       </c>
@@ -8010,7 +8004,7 @@
         <v>91.706666666666635</v>
       </c>
     </row>
-    <row r="161" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>76</v>
       </c>
@@ -8045,7 +8039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="162" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>76</v>
       </c>
@@ -8083,7 +8077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>85</v>
       </c>
@@ -8118,7 +8112,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>85</v>
       </c>
@@ -8207,7 +8201,7 @@
         <v>226.5</v>
       </c>
       <c r="F166" s="3">
-        <v>258.7</v>
+        <v>210.7</v>
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
@@ -8227,7 +8221,7 @@
         <v>100.7</v>
       </c>
       <c r="AA166" s="4">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="AB166" s="4"/>
       <c r="AC166" s="4"/>
@@ -8235,7 +8229,7 @@
       <c r="AE166" s="4"/>
       <c r="AF166" s="4"/>
     </row>
-    <row r="167" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>95</v>
       </c>
@@ -8267,7 +8261,7 @@
       <c r="AE167" s="4"/>
       <c r="AF167" s="4"/>
     </row>
-    <row r="168" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>95</v>
       </c>
@@ -8281,7 +8275,7 @@
         <v>1566.27</v>
       </c>
       <c r="F168" s="3">
-        <v>332</v>
+        <v>401</v>
       </c>
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
@@ -8301,7 +8295,7 @@
         <v>42</v>
       </c>
       <c r="AA168" s="4">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="AB168" s="4"/>
       <c r="AC168" s="4"/>
@@ -8309,7 +8303,7 @@
       <c r="AE168" s="4"/>
       <c r="AF168" s="4"/>
     </row>
-    <row r="169" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
         <v>91</v>
       </c>
@@ -8344,7 +8338,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
         <v>91</v>
       </c>
@@ -8391,7 +8385,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>42</v>
       </c>
@@ -8429,7 +8423,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
         <v>42</v>
       </c>
@@ -8464,7 +8458,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>68</v>
       </c>
@@ -8499,7 +8493,7 @@
       <c r="AE173" s="4"/>
       <c r="AF173" s="4"/>
     </row>
-    <row r="174" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>68</v>
       </c>
@@ -8534,7 +8528,7 @@
       <c r="AE174" s="4"/>
       <c r="AF174" s="4"/>
     </row>
-    <row r="175" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>98</v>
       </c>
@@ -8580,7 +8574,7 @@
       <c r="AE175" s="4"/>
       <c r="AF175" s="4"/>
     </row>
-    <row r="176" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>98</v>
       </c>
@@ -8624,7 +8618,7 @@
       <c r="AE176" s="4"/>
       <c r="AF176" s="4"/>
     </row>
-    <row r="177" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>100</v>
       </c>
@@ -8659,7 +8653,7 @@
       <c r="AE177" s="4"/>
       <c r="AF177" s="4"/>
     </row>
-    <row r="178" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>100</v>
       </c>
@@ -8694,7 +8688,7 @@
       <c r="AE178" s="4"/>
       <c r="AF178" s="4"/>
     </row>
-    <row r="179" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>102</v>
       </c>
@@ -8729,7 +8723,7 @@
       <c r="AE179" s="4"/>
       <c r="AF179" s="4"/>
     </row>
-    <row r="180" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>102</v>
       </c>
@@ -8764,7 +8758,7 @@
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
     </row>
-    <row r="181" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>104</v>
       </c>
@@ -8799,7 +8793,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>104</v>
       </c>
@@ -8837,7 +8831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>90</v>
       </c>
@@ -8872,7 +8866,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>90</v>
       </c>
@@ -8907,7 +8901,7 @@
       <c r="AE184" s="4"/>
       <c r="AF184" s="4"/>
     </row>
-    <row r="185" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>78</v>
       </c>
@@ -8945,7 +8939,7 @@
       <c r="AE185" s="4"/>
       <c r="AF185" s="4"/>
     </row>
-    <row r="186" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>78</v>
       </c>
@@ -8980,7 +8974,7 @@
       <c r="AE186" s="4"/>
       <c r="AF186" s="4"/>
     </row>
-    <row r="187" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>44</v>
       </c>
@@ -9020,7 +9014,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>44</v>
       </c>
@@ -9058,7 +9052,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>45</v>
       </c>
@@ -9090,7 +9084,7 @@
       <c r="AE189" s="4"/>
       <c r="AF189" s="4"/>
     </row>
-    <row r="190" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>45</v>
       </c>
@@ -9125,7 +9119,7 @@
       <c r="AE190" s="4"/>
       <c r="AF190" s="4"/>
     </row>
-    <row r="191" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>54</v>
       </c>
@@ -9157,7 +9151,7 @@
       <c r="AE191" s="4"/>
       <c r="AF191" s="4"/>
     </row>
-    <row r="192" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>54</v>
       </c>
@@ -9193,7 +9187,7 @@
       <c r="AE192" s="4"/>
       <c r="AF192" s="4"/>
     </row>
-    <row r="193" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>43</v>
       </c>
@@ -9225,7 +9219,7 @@
       <c r="AE193" s="4"/>
       <c r="AF193" s="4"/>
     </row>
-    <row r="194" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>43</v>
       </c>
@@ -9260,7 +9254,7 @@
       <c r="AE194" s="4"/>
       <c r="AF194" s="4"/>
     </row>
-    <row r="195" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>92</v>
       </c>
@@ -9298,7 +9292,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>92</v>
       </c>
@@ -9336,7 +9330,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>46</v>
       </c>
@@ -9371,7 +9365,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>46</v>
       </c>
@@ -9409,7 +9403,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>41</v>
       </c>
@@ -9447,7 +9441,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>41</v>
       </c>
@@ -9485,7 +9479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>61</v>
       </c>
@@ -9520,7 +9514,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="202" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>61</v>
       </c>
@@ -9558,7 +9552,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="203" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>96</v>
       </c>
@@ -9593,7 +9587,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>96</v>
       </c>
@@ -9636,7 +9630,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>69</v>
       </c>
@@ -9680,7 +9674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>69</v>
       </c>
@@ -9727,7 +9721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>72</v>
       </c>
@@ -9765,7 +9759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>72</v>
       </c>
@@ -9779,7 +9773,7 @@
         <v>382.5</v>
       </c>
       <c r="F208" s="3">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
@@ -9797,7 +9791,7 @@
       <c r="Y208" s="4"/>
       <c r="Z208" s="9"/>
       <c r="AA208" s="4">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="AB208" s="4"/>
       <c r="AC208" s="4"/>
@@ -9808,7 +9802,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="209" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>84</v>
       </c>
@@ -9849,7 +9843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>84</v>
       </c>
@@ -9887,7 +9881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>94</v>
       </c>
@@ -9922,7 +9916,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="212" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>94</v>
       </c>
@@ -9960,7 +9954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="213" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>75</v>
       </c>
@@ -10001,7 +9995,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="214" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>75</v>
       </c>
@@ -10039,7 +10033,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>73</v>
       </c>
@@ -10077,7 +10071,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="216" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>73</v>
       </c>
@@ -10115,7 +10109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>39</v>
       </c>
@@ -10156,7 +10150,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="218" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>39</v>
       </c>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA143249-3D47-4B4D-89D2-DB81D518D575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6D93DF-D2A3-4536-BFA7-4CF39D87C8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="124">
   <si>
     <t>Data</t>
   </si>
@@ -316,9 +316,6 @@
   </si>
   <si>
     <t xml:space="preserve">RCE RUA JOSÉ MILITÃO </t>
-  </si>
-  <si>
-    <t>rede existente</t>
   </si>
   <si>
     <t>RCE VIELA DA RUA INÊS SABINO</t>
@@ -799,7 +796,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
-  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="25">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF218">
     <sortCondition ref="B1:B218"/>
   </sortState>
@@ -1253,7 +1256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>64</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>64</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1399,7 +1402,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
@@ -1442,7 +1445,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>64</v>
       </c>
@@ -1488,7 +1491,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>63</v>
       </c>
@@ -1579,7 +1582,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1667,7 +1670,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
@@ -1705,7 +1708,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>63</v>
       </c>
@@ -1786,7 +1789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>63</v>
       </c>
@@ -1831,7 +1834,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
@@ -1869,7 +1872,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
@@ -1914,7 +1917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1952,7 +1955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
@@ -1995,7 +1998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>63</v>
       </c>
@@ -2033,7 +2036,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>63</v>
       </c>
@@ -2076,7 +2079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>63</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>63</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>63</v>
       </c>
@@ -2195,7 +2198,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>63</v>
       </c>
@@ -2237,10 +2240,10 @@
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
       <c r="AG24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>63</v>
       </c>
@@ -2278,10 +2281,10 @@
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
       <c r="AG25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>62</v>
       </c>
@@ -2322,8 +2325,11 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
-    </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>62</v>
       </c>
@@ -2364,8 +2370,11 @@
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
-    </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
@@ -2404,8 +2413,11 @@
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
-    </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>62</v>
       </c>
@@ -2439,8 +2451,11 @@
       <c r="AD29" s="4"/>
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
-    </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>62</v>
       </c>
@@ -2476,8 +2491,11 @@
       <c r="AD30" s="4"/>
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
-    </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
@@ -2511,8 +2529,11 @@
       <c r="AD31" s="4"/>
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
-    </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
@@ -2552,7 +2573,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>62</v>
       </c>
@@ -2587,10 +2608,10 @@
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
       <c r="AG33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -2629,8 +2650,11 @@
       <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>62</v>
       </c>
@@ -2664,8 +2688,11 @@
       <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
-    </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>62</v>
       </c>
@@ -2701,8 +2728,11 @@
       <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>62</v>
       </c>
@@ -2736,8 +2766,11 @@
       <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
-    </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>62</v>
       </c>
@@ -2774,10 +2807,10 @@
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
       <c r="AG38" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>62</v>
       </c>
@@ -2811,8 +2844,11 @@
       <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>62</v>
       </c>
@@ -2848,8 +2884,11 @@
       <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
@@ -2883,8 +2922,11 @@
       <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>62</v>
       </c>
@@ -2920,8 +2962,11 @@
       <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>62</v>
       </c>
@@ -2955,8 +3000,11 @@
       <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>62</v>
       </c>
@@ -2995,8 +3043,11 @@
       <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>62</v>
       </c>
@@ -3030,8 +3081,11 @@
       <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>62</v>
       </c>
@@ -3072,8 +3126,11 @@
       <c r="AD46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>62</v>
       </c>
@@ -3107,8 +3164,11 @@
       <c r="AD47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>62</v>
       </c>
@@ -3149,8 +3209,11 @@
       <c r="AD48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
-    </row>
-    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG48" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>62</v>
       </c>
@@ -3184,8 +3247,11 @@
       <c r="AD49" s="4"/>
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
-    </row>
-    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>62</v>
       </c>
@@ -3224,8 +3290,11 @@
       <c r="AD50" s="4"/>
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
-    </row>
-    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>62</v>
       </c>
@@ -3259,8 +3328,11 @@
       <c r="AD51" s="4"/>
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
-    </row>
-    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>62</v>
       </c>
@@ -3299,8 +3371,11 @@
       <c r="AD52" s="4"/>
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
-    </row>
-    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG52" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>62</v>
       </c>
@@ -3334,8 +3409,11 @@
       <c r="AD53" s="4"/>
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
-    </row>
-    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AG53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>62</v>
       </c>
@@ -3377,10 +3455,10 @@
       <c r="AE54" s="4"/>
       <c r="AF54" s="4"/>
       <c r="AG54" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>62</v>
       </c>
@@ -3418,7 +3496,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>62</v>
       </c>
@@ -3464,7 +3542,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>62</v>
       </c>
@@ -3507,12 +3585,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
         <v>34</v>
@@ -3550,12 +3628,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
         <v>36</v>
@@ -3588,7 +3666,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
@@ -3653,7 +3731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>58</v>
       </c>
@@ -3696,7 +3774,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>58</v>
       </c>
@@ -3752,7 +3830,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>58</v>
       </c>
@@ -3794,7 +3872,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>58</v>
       </c>
@@ -3852,7 +3930,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>58</v>
       </c>
@@ -3896,7 +3974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>59</v>
       </c>
@@ -3943,7 +4021,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>59</v>
       </c>
@@ -3988,7 +4066,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>59</v>
       </c>
@@ -4035,7 +4113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>59</v>
       </c>
@@ -4079,7 +4157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>33</v>
       </c>
@@ -4125,7 +4203,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>33</v>
       </c>
@@ -4168,7 +4246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>33</v>
       </c>
@@ -4213,7 +4291,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>33</v>
       </c>
@@ -4256,7 +4334,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>33</v>
       </c>
@@ -4299,7 +4377,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>33</v>
       </c>
@@ -4342,7 +4420,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
         <v>33</v>
       </c>
@@ -4390,7 +4468,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
         <v>33</v>
       </c>
@@ -4434,7 +4512,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>38</v>
       </c>
@@ -4489,7 +4567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
         <v>38</v>
       </c>
@@ -4532,7 +4610,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
         <v>38</v>
       </c>
@@ -4581,7 +4659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B81" s="3" t="s">
         <v>38</v>
       </c>
@@ -4624,7 +4702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>60</v>
       </c>
@@ -4673,7 +4751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B83" s="3" t="s">
         <v>60</v>
       </c>
@@ -4716,7 +4794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B84" s="3" t="s">
         <v>57</v>
       </c>
@@ -4772,7 +4850,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
         <v>57</v>
       </c>
@@ -4816,7 +4894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B86" s="3" t="s">
         <v>57</v>
       </c>
@@ -4866,7 +4944,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
         <v>57</v>
       </c>
@@ -4910,7 +4988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
         <v>57</v>
       </c>
@@ -4962,7 +5040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>57</v>
       </c>
@@ -5006,7 +5084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>52</v>
       </c>
@@ -5040,11 +5118,8 @@
       <c r="AD90" s="4"/>
       <c r="AE90" s="4"/>
       <c r="AF90" s="4"/>
-      <c r="AG90" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="91" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>52</v>
       </c>
@@ -5078,11 +5153,8 @@
       <c r="AD91" s="4"/>
       <c r="AE91" s="4"/>
       <c r="AF91" s="4"/>
-      <c r="AG91" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="92" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
         <v>56</v>
       </c>
@@ -5134,7 +5206,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
         <v>56</v>
       </c>
@@ -5176,7 +5248,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B94" s="3" t="s">
         <v>56</v>
       </c>
@@ -5228,7 +5300,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
         <v>56</v>
       </c>
@@ -5270,7 +5342,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>56</v>
       </c>
@@ -5322,7 +5394,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="3" t="s">
         <v>56</v>
       </c>
@@ -5366,7 +5438,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
         <v>56</v>
       </c>
@@ -5413,7 +5485,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" s="3" t="s">
         <v>56</v>
       </c>
@@ -5457,7 +5529,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" s="3" t="s">
         <v>55</v>
       </c>
@@ -5504,7 +5576,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" s="3" t="s">
         <v>37</v>
       </c>
@@ -5561,7 +5633,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" s="3" t="s">
         <v>37</v>
       </c>
@@ -5599,7 +5671,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
         <v>37</v>
       </c>
@@ -5650,7 +5722,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" s="3" t="s">
         <v>37</v>
       </c>
@@ -5691,7 +5763,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" s="3" t="s">
         <v>37</v>
       </c>
@@ -5742,7 +5814,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="3" t="s">
         <v>37</v>
       </c>
@@ -5785,7 +5857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
         <v>37</v>
       </c>
@@ -5838,7 +5910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" s="3" t="s">
         <v>37</v>
       </c>
@@ -5876,7 +5948,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
         <v>37</v>
       </c>
@@ -5925,7 +5997,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
         <v>37</v>
       </c>
@@ -5974,7 +6046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>89</v>
       </c>
@@ -6015,10 +6087,10 @@
       <c r="AE111" s="4"/>
       <c r="AF111" s="4"/>
       <c r="AG111" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="112" spans="2:33" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>89</v>
       </c>
@@ -6053,10 +6125,10 @@
       <c r="AE112" s="4"/>
       <c r="AF112" s="4"/>
       <c r="AG112" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="113" spans="2:33" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B113" s="3" t="s">
         <v>77</v>
       </c>
@@ -6102,7 +6174,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B114" s="3" t="s">
         <v>77</v>
       </c>
@@ -6140,7 +6212,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
         <v>77</v>
       </c>
@@ -6189,7 +6261,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" s="3" t="s">
         <v>77</v>
       </c>
@@ -6232,7 +6304,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
         <v>74</v>
       </c>
@@ -6293,7 +6365,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
         <v>74</v>
       </c>
@@ -6342,7 +6414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
         <v>74</v>
       </c>
@@ -6401,7 +6473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
         <v>74</v>
       </c>
@@ -6447,7 +6519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
         <v>74</v>
       </c>
@@ -6496,7 +6568,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
         <v>74</v>
       </c>
@@ -6539,7 +6611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>50</v>
       </c>
@@ -6573,11 +6645,8 @@
       <c r="AD123" s="4"/>
       <c r="AE123" s="4"/>
       <c r="AF123" s="4"/>
-      <c r="AG123" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="124" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>50</v>
       </c>
@@ -6608,11 +6677,8 @@
       <c r="AD124" s="4"/>
       <c r="AE124" s="4"/>
       <c r="AF124" s="4"/>
-      <c r="AG124" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="125" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>53</v>
       </c>
@@ -6646,11 +6712,8 @@
       <c r="AD125" s="4"/>
       <c r="AE125" s="4"/>
       <c r="AF125" s="4"/>
-      <c r="AG125" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="126" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>53</v>
       </c>
@@ -6684,11 +6747,8 @@
       <c r="AD126" s="4"/>
       <c r="AE126" s="4"/>
       <c r="AF126" s="4"/>
-      <c r="AG126" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="127" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>48</v>
       </c>
@@ -6722,11 +6782,8 @@
       <c r="AD127" s="4"/>
       <c r="AE127" s="4"/>
       <c r="AF127" s="4"/>
-      <c r="AG127" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>48</v>
       </c>
@@ -6757,11 +6814,8 @@
       <c r="AD128" s="4"/>
       <c r="AE128" s="4"/>
       <c r="AF128" s="4"/>
-      <c r="AG128" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="129" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>70</v>
       </c>
@@ -6792,11 +6846,8 @@
       <c r="AD129" s="4"/>
       <c r="AE129" s="4"/>
       <c r="AF129" s="4"/>
-      <c r="AG129" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="130" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>70</v>
       </c>
@@ -6830,11 +6881,8 @@
       <c r="AD130" s="4"/>
       <c r="AE130" s="4"/>
       <c r="AF130" s="4"/>
-      <c r="AG130" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="131" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" s="3" t="s">
         <v>82</v>
       </c>
@@ -6883,7 +6931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
         <v>82</v>
       </c>
@@ -6927,8 +6975,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B133" t="s">
+    <row r="133" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B133" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C133">
@@ -6965,8 +7013,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B134" t="s">
+    <row r="134" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B134" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C134">
@@ -7008,8 +7056,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B135" t="s">
+    <row r="135" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B135" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C135">
@@ -7049,8 +7097,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B136" t="s">
+    <row r="136" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C136">
@@ -7087,8 +7135,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B137" t="s">
+    <row r="137" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B137" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C137">
@@ -7121,12 +7169,9 @@
       <c r="AD137" s="4"/>
       <c r="AE137" s="4"/>
       <c r="AF137" s="4"/>
-      <c r="AG137" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="138" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B138" t="s">
+    </row>
+    <row r="138" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B138" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C138">
@@ -7159,12 +7204,9 @@
       <c r="AD138" s="4"/>
       <c r="AE138" s="4"/>
       <c r="AF138" s="4"/>
-      <c r="AG138" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="139" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B139" t="s">
+    </row>
+    <row r="139" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B139" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C139">
@@ -7197,12 +7239,9 @@
       <c r="AD139" s="4"/>
       <c r="AE139" s="4"/>
       <c r="AF139" s="4"/>
-      <c r="AG139" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="140" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B140" t="s">
+    </row>
+    <row r="140" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C140">
@@ -7232,12 +7271,9 @@
       <c r="AD140" s="4"/>
       <c r="AE140" s="4"/>
       <c r="AF140" s="4"/>
-      <c r="AG140" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="141" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B141" t="s">
+    </row>
+    <row r="141" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B141" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C141">
@@ -7267,12 +7303,9 @@
       <c r="AD141" s="4"/>
       <c r="AE141" s="4"/>
       <c r="AF141" s="4"/>
-      <c r="AG141" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="142" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B142" t="s">
+    </row>
+    <row r="142" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B142" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C142">
@@ -7305,12 +7338,9 @@
       <c r="AD142" s="4"/>
       <c r="AE142" s="4"/>
       <c r="AF142" s="4"/>
-      <c r="AG142" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="143" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B143" t="s">
+    </row>
+    <row r="143" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B143" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C143" s="1">
@@ -7345,7 +7375,7 @@
       </c>
     </row>
     <row r="144" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B144" t="s">
+      <c r="B144" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C144" s="1">
@@ -7389,8 +7419,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B145" t="s">
+    <row r="145" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B145" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C145">
@@ -7434,9 +7464,12 @@
       <c r="AD145" s="4"/>
       <c r="AE145" s="4"/>
       <c r="AF145" s="4"/>
-    </row>
-    <row r="146" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B146" t="s">
+      <c r="AG145" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="146" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B146" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C146">
@@ -7472,9 +7505,12 @@
       <c r="AD146" s="4"/>
       <c r="AE146" s="4"/>
       <c r="AF146" s="4"/>
-    </row>
-    <row r="147" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B147" t="s">
+      <c r="AG146" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="147" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B147" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C147">
@@ -7519,9 +7555,12 @@
       <c r="AD147" s="4"/>
       <c r="AE147" s="4"/>
       <c r="AF147" s="4"/>
-    </row>
-    <row r="148" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B148" t="s">
+      <c r="AG147" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="148" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B148" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C148">
@@ -7561,9 +7600,12 @@
       <c r="AD148" s="4"/>
       <c r="AE148" s="4"/>
       <c r="AF148" s="4"/>
-    </row>
-    <row r="149" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B149" t="s">
+      <c r="AG148" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="149" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B149" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C149">
@@ -7594,8 +7636,8 @@
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
     </row>
-    <row r="150" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B150" t="s">
+    <row r="150" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C150">
@@ -7628,11 +7670,8 @@
       <c r="AD150" s="4"/>
       <c r="AE150" s="4"/>
       <c r="AF150" s="4"/>
-      <c r="AG150" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="151" spans="2:38" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" s="3" t="s">
         <v>66</v>
       </c>
@@ -7675,7 +7714,7 @@
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
     </row>
-    <row r="152" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" s="3" t="s">
         <v>66</v>
       </c>
@@ -7710,8 +7749,8 @@
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
     </row>
-    <row r="153" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B153" t="s">
+    <row r="153" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B153" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C153">
@@ -7748,8 +7787,8 @@
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
     </row>
-    <row r="154" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B154" t="s">
+    <row r="154" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B154" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C154">
@@ -7783,8 +7822,8 @@
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
     </row>
-    <row r="155" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B155" t="s">
+    <row r="155" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B155" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C155">
@@ -7818,8 +7857,8 @@
         <v>1746.61</v>
       </c>
     </row>
-    <row r="156" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B156" t="s">
+    <row r="156" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B156" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C156">
@@ -7856,8 +7895,8 @@
         <v>1471.49</v>
       </c>
     </row>
-    <row r="157" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B157" t="s">
+    <row r="157" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B157" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C157">
@@ -7892,8 +7931,8 @@
         <v>275.11999999999989</v>
       </c>
     </row>
-    <row r="158" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B158" t="s">
+    <row r="158" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C158">
@@ -7927,8 +7966,8 @@
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
     </row>
-    <row r="159" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B159" t="s">
+    <row r="159" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C159">
@@ -7958,12 +7997,9 @@
       <c r="AD159" s="4"/>
       <c r="AE159" s="4"/>
       <c r="AF159" s="4"/>
-      <c r="AG159" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="160" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B160" t="s">
+    </row>
+    <row r="160" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C160">
@@ -7996,16 +8032,13 @@
       <c r="AD160" s="4"/>
       <c r="AE160" s="4"/>
       <c r="AF160" s="4"/>
-      <c r="AG160" t="s">
-        <v>35</v>
-      </c>
       <c r="AL160">
         <f>AL157/3</f>
         <v>91.706666666666635</v>
       </c>
     </row>
-    <row r="161" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B161" t="s">
+    <row r="161" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B161" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C161">
@@ -8035,12 +8068,9 @@
       <c r="AD161" s="4"/>
       <c r="AE161" s="4"/>
       <c r="AF161" s="4"/>
-      <c r="AG161" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="162" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B162" t="s">
+    </row>
+    <row r="162" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B162" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C162">
@@ -8073,12 +8103,9 @@
       <c r="AD162" s="4"/>
       <c r="AE162" s="4"/>
       <c r="AF162" s="4"/>
-      <c r="AG162" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="163" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B163" t="s">
+    </row>
+    <row r="163" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C163">
@@ -8112,8 +8139,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B164" t="s">
+    <row r="164" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B164" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C164">
@@ -8155,8 +8182,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B165" t="s">
+    <row r="165" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C165">
@@ -8186,9 +8213,12 @@
       <c r="AD165" s="4"/>
       <c r="AE165" s="4"/>
       <c r="AF165" s="4"/>
+      <c r="AG165" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="166" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B166" t="s">
+      <c r="B166" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C166">
@@ -8228,10 +8258,13 @@
       <c r="AD166" s="4"/>
       <c r="AE166" s="4"/>
       <c r="AF166" s="4"/>
-    </row>
-    <row r="167" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B167" t="s">
-        <v>95</v>
+      <c r="AG166" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="167" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C167">
         <v>76</v>
@@ -8260,10 +8293,13 @@
       <c r="AD167" s="4"/>
       <c r="AE167" s="4"/>
       <c r="AF167" s="4"/>
+      <c r="AG167" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="168" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B168" t="s">
-        <v>95</v>
+      <c r="B168" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C168">
         <v>76</v>
@@ -8275,7 +8311,7 @@
         <v>1566.27</v>
       </c>
       <c r="F168" s="3">
-        <v>401</v>
+        <v>531</v>
       </c>
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
@@ -8295,16 +8331,19 @@
         <v>42</v>
       </c>
       <c r="AA168" s="4">
-        <v>359</v>
+        <v>489</v>
       </c>
       <c r="AB168" s="4"/>
       <c r="AC168" s="4"/>
       <c r="AD168" s="4"/>
       <c r="AE168" s="4"/>
       <c r="AF168" s="4"/>
-    </row>
-    <row r="169" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B169" t="s">
+      <c r="AG168" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="169" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B169" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C169">
@@ -8339,7 +8378,7 @@
       </c>
     </row>
     <row r="170" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B170" t="s">
+      <c r="B170" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C170">
@@ -8385,8 +8424,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B171" t="s">
+    <row r="171" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B171" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C171">
@@ -8419,12 +8458,9 @@
       <c r="AD171" s="4"/>
       <c r="AE171" s="4"/>
       <c r="AF171" s="4"/>
-      <c r="AG171" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="172" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B172" t="s">
+    </row>
+    <row r="172" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B172" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C172">
@@ -8454,12 +8490,9 @@
       <c r="AD172" s="4"/>
       <c r="AE172" s="4"/>
       <c r="AF172" s="4"/>
-      <c r="AG172" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="173" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B173" t="s">
+    </row>
+    <row r="173" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B173" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C173">
@@ -8493,8 +8526,8 @@
       <c r="AE173" s="4"/>
       <c r="AF173" s="4"/>
     </row>
-    <row r="174" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B174" t="s">
+    <row r="174" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B174" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C174">
@@ -8528,12 +8561,12 @@
       <c r="AE174" s="4"/>
       <c r="AF174" s="4"/>
     </row>
-    <row r="175" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B175" t="s">
+    <row r="175" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B175" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="D175" t="s">
         <v>34</v>
@@ -8574,12 +8607,12 @@
       <c r="AE175" s="4"/>
       <c r="AF175" s="4"/>
     </row>
-    <row r="176" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B176" t="s">
+    <row r="176" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B176" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="D176" t="s">
         <v>36</v>
@@ -8618,12 +8651,12 @@
       <c r="AE176" s="4"/>
       <c r="AF176" s="4"/>
     </row>
-    <row r="177" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B177" t="s">
+    <row r="177" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B177" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="D177" t="s">
         <v>34</v>
@@ -8653,12 +8686,12 @@
       <c r="AE177" s="4"/>
       <c r="AF177" s="4"/>
     </row>
-    <row r="178" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B178" t="s">
+    <row r="178" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B178" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="D178" t="s">
         <v>36</v>
@@ -8688,12 +8721,12 @@
       <c r="AE178" s="4"/>
       <c r="AF178" s="4"/>
     </row>
-    <row r="179" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B179" t="s">
+    <row r="179" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B179" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="D179" t="s">
         <v>34</v>
@@ -8723,12 +8756,12 @@
       <c r="AE179" s="4"/>
       <c r="AF179" s="4"/>
     </row>
-    <row r="180" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B180" t="s">
+    <row r="180" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B180" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="D180" t="s">
         <v>36</v>
@@ -8758,12 +8791,12 @@
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
     </row>
-    <row r="181" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B181" t="s">
+    <row r="181" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B181" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="D181" t="s">
         <v>34</v>
@@ -8789,16 +8822,13 @@
       <c r="AD181" s="4"/>
       <c r="AE181" s="4"/>
       <c r="AF181" s="4"/>
-      <c r="AG181" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="182" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B182" t="s">
+    </row>
+    <row r="182" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B182" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="D182" t="s">
         <v>36</v>
@@ -8827,12 +8857,9 @@
       <c r="AD182" s="4"/>
       <c r="AE182" s="4"/>
       <c r="AF182" s="4"/>
-      <c r="AG182" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="183" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B183" t="s">
+    </row>
+    <row r="183" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B183" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C183">
@@ -8866,8 +8893,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B184" t="s">
+    <row r="184" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B184" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C184">
@@ -8900,9 +8927,12 @@
       <c r="AD184" s="4"/>
       <c r="AE184" s="4"/>
       <c r="AF184" s="4"/>
-    </row>
-    <row r="185" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B185" t="s">
+      <c r="AG184" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="185" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B185" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C185">
@@ -8939,8 +8969,8 @@
       <c r="AE185" s="4"/>
       <c r="AF185" s="4"/>
     </row>
-    <row r="186" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B186" t="s">
+    <row r="186" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B186" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C186">
@@ -8974,8 +9004,8 @@
       <c r="AE186" s="4"/>
       <c r="AF186" s="4"/>
     </row>
-    <row r="187" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B187" t="s">
+    <row r="187" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B187" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C187">
@@ -9011,11 +9041,11 @@
       <c r="AE187" s="4"/>
       <c r="AF187" s="4"/>
       <c r="AG187" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="188" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B188" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="188" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B188" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C188">
@@ -9049,11 +9079,11 @@
       <c r="AE188" s="4"/>
       <c r="AF188" s="4"/>
       <c r="AG188" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="189" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B189" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="189" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B189" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C189">
@@ -9084,8 +9114,8 @@
       <c r="AE189" s="4"/>
       <c r="AF189" s="4"/>
     </row>
-    <row r="190" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B190" t="s">
+    <row r="190" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B190" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C190">
@@ -9119,8 +9149,8 @@
       <c r="AE190" s="4"/>
       <c r="AF190" s="4"/>
     </row>
-    <row r="191" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B191" t="s">
+    <row r="191" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B191" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C191">
@@ -9151,8 +9181,8 @@
       <c r="AE191" s="4"/>
       <c r="AF191" s="4"/>
     </row>
-    <row r="192" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B192" t="s">
+    <row r="192" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B192" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C192">
@@ -9187,8 +9217,8 @@
       <c r="AE192" s="4"/>
       <c r="AF192" s="4"/>
     </row>
-    <row r="193" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B193" t="s">
+    <row r="193" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B193" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C193">
@@ -9218,9 +9248,12 @@
       <c r="AD193" s="4"/>
       <c r="AE193" s="4"/>
       <c r="AF193" s="4"/>
-    </row>
-    <row r="194" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B194" t="s">
+      <c r="AG193" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="194" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B194" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C194">
@@ -9253,9 +9286,12 @@
       <c r="AD194" s="4"/>
       <c r="AE194" s="4"/>
       <c r="AF194" s="4"/>
-    </row>
-    <row r="195" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B195" t="s">
+      <c r="AG194" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="195" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B195" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C195">
@@ -9288,12 +9324,9 @@
       <c r="AD195" s="4"/>
       <c r="AE195" s="4"/>
       <c r="AF195" s="4"/>
-      <c r="AG195" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="196" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B196" t="s">
+    </row>
+    <row r="196" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B196" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C196">
@@ -9326,12 +9359,9 @@
       <c r="AD196" s="4"/>
       <c r="AE196" s="4"/>
       <c r="AF196" s="4"/>
-      <c r="AG196" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="197" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B197" t="s">
+    </row>
+    <row r="197" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B197" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C197">
@@ -9361,12 +9391,9 @@
       <c r="AD197" s="4"/>
       <c r="AE197" s="4"/>
       <c r="AF197" s="4"/>
-      <c r="AG197" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="198" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B198" t="s">
+    </row>
+    <row r="198" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B198" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C198">
@@ -9399,12 +9426,9 @@
       <c r="AD198" s="4"/>
       <c r="AE198" s="4"/>
       <c r="AF198" s="4"/>
-      <c r="AG198" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="199" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B199" t="s">
+    </row>
+    <row r="199" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B199" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C199">
@@ -9437,12 +9461,9 @@
       <c r="AD199" s="4"/>
       <c r="AE199" s="4"/>
       <c r="AF199" s="4"/>
-      <c r="AG199" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="200" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B200" t="s">
+    </row>
+    <row r="200" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B200" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C200">
@@ -9475,12 +9496,9 @@
       <c r="AD200" s="4"/>
       <c r="AE200" s="4"/>
       <c r="AF200" s="4"/>
-      <c r="AG200" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="201" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B201" t="s">
+    </row>
+    <row r="201" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B201" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C201">
@@ -9510,12 +9528,9 @@
       <c r="AD201" s="4"/>
       <c r="AE201" s="4"/>
       <c r="AF201" s="4"/>
-      <c r="AG201" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="202" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B202" t="s">
+    </row>
+    <row r="202" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B202" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C202">
@@ -9548,13 +9563,10 @@
       <c r="AD202" s="4"/>
       <c r="AE202" s="4"/>
       <c r="AF202" s="4"/>
-      <c r="AG202" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="203" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B203" t="s">
-        <v>96</v>
+    </row>
+    <row r="203" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B203" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C203">
         <v>76</v>
@@ -9587,9 +9599,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B204" t="s">
-        <v>96</v>
+    <row r="204" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B204" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C204">
         <v>76</v>
@@ -9630,8 +9642,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B205" t="s">
+    <row r="205" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B205" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C205">
@@ -9675,7 +9687,7 @@
       </c>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B206" t="s">
+      <c r="B206" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C206">
@@ -9688,7 +9700,7 @@
         <v>1799.2</v>
       </c>
       <c r="F206" s="3">
-        <v>1696.2</v>
+        <v>1716.2</v>
       </c>
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
@@ -9710,7 +9722,7 @@
         <v>584.20000000000005</v>
       </c>
       <c r="AA206" s="4">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="AB206" s="4"/>
       <c r="AC206" s="4"/>
@@ -9721,7 +9733,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>72</v>
       </c>
@@ -9755,9 +9767,6 @@
       <c r="AD207" s="4"/>
       <c r="AE207" s="4"/>
       <c r="AF207" s="4"/>
-      <c r="AG207" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="208" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
@@ -9773,7 +9782,7 @@
         <v>382.5</v>
       </c>
       <c r="F208" s="3">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
@@ -9791,18 +9800,15 @@
       <c r="Y208" s="4"/>
       <c r="Z208" s="9"/>
       <c r="AA208" s="4">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="AB208" s="4"/>
       <c r="AC208" s="4"/>
       <c r="AD208" s="4"/>
       <c r="AE208" s="4"/>
       <c r="AF208" s="4"/>
-      <c r="AG208" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="209" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>84</v>
       </c>
@@ -9839,11 +9845,8 @@
       <c r="AD209" s="4"/>
       <c r="AE209" s="4"/>
       <c r="AF209" s="4"/>
-      <c r="AG209" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="210" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>84</v>
       </c>
@@ -9877,13 +9880,10 @@
       <c r="AD210" s="4"/>
       <c r="AE210" s="4"/>
       <c r="AF210" s="4"/>
-      <c r="AG210" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="211" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C211">
         <v>76</v>
@@ -9912,13 +9912,10 @@
       <c r="AD211" s="4"/>
       <c r="AE211" s="4"/>
       <c r="AF211" s="4"/>
-      <c r="AG211" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="212" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C212">
         <v>76</v>
@@ -9950,11 +9947,8 @@
       <c r="AD212" s="4"/>
       <c r="AE212" s="4"/>
       <c r="AF212" s="4"/>
-      <c r="AG212" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="213" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>75</v>
       </c>
@@ -9991,11 +9985,8 @@
       <c r="AD213" s="4"/>
       <c r="AE213" s="4"/>
       <c r="AF213" s="4"/>
-      <c r="AG213" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="214" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>75</v>
       </c>
@@ -10029,11 +10020,8 @@
       <c r="AD214" s="4"/>
       <c r="AE214" s="4"/>
       <c r="AF214" s="4"/>
-      <c r="AG214" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="215" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>73</v>
       </c>
@@ -10067,11 +10055,8 @@
       <c r="AD215" s="4"/>
       <c r="AE215" s="4"/>
       <c r="AF215" s="4"/>
-      <c r="AG215" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="216" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>73</v>
       </c>
@@ -10105,11 +10090,8 @@
       <c r="AD216" s="4"/>
       <c r="AE216" s="4"/>
       <c r="AF216" s="4"/>
-      <c r="AG216" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="217" spans="2:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>39</v>
       </c>
@@ -10147,10 +10129,10 @@
       <c r="AE217" s="4"/>
       <c r="AF217" s="4"/>
       <c r="AG217" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="218" spans="2:33" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="218" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>39</v>
       </c>
@@ -10182,15 +10164,15 @@
       <c r="AE218" s="4"/>
       <c r="AF218" s="4"/>
       <c r="AG218" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="AG1:AG218" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10212,19 +10194,19 @@
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>107</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>108</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>109</v>
-      </c>
-      <c r="F2" t="s">
-        <v>110</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -10235,7 +10217,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>159.15</v>
@@ -10255,7 +10237,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4">
         <v>723.7</v>
@@ -10275,7 +10257,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>905.99</v>
@@ -10295,7 +10277,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6">
         <v>1089.1400000000001</v>
@@ -10319,7 +10301,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>588.28</v>
@@ -10343,7 +10325,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8">
         <v>1227.24</v>
@@ -10367,7 +10349,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9">
         <v>1914.65</v>
@@ -10395,7 +10377,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10">
         <v>1749.47</v>
@@ -10423,7 +10405,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>1942.9</v>
@@ -10451,7 +10433,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12">
         <v>1588.61</v>
@@ -10475,7 +10457,7 @@
         <v>2026</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13">
         <v>2185.34</v>
@@ -10499,7 +10481,7 @@
         <v>2026</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D14">
         <v>2340.4</v>
@@ -10523,7 +10505,7 @@
         <v>2026</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15">
         <v>2128.08</v>
@@ -10542,7 +10524,7 @@
         <v>539.41999999999985</v>
       </c>
       <c r="O15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
@@ -10550,7 +10532,7 @@
         <v>2026</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16">
         <v>2426.84</v>
@@ -10574,7 +10556,7 @@
         <v>2026</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D17">
         <v>2545.85</v>
@@ -10599,7 +10581,7 @@
         <v>2026</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18">
         <v>3108.25</v>
@@ -10616,7 +10598,7 @@
         <v>2026</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19">
         <v>3269.49</v>
@@ -10633,7 +10615,7 @@
         <v>2026</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20">
         <v>3305.21</v>
@@ -10650,7 +10632,7 @@
         <v>2026</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D21">
         <v>3138.09</v>
@@ -10667,7 +10649,7 @@
         <v>2026</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D22">
         <v>2251.2800000000002</v>
@@ -10684,7 +10666,7 @@
         <v>2026</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D23">
         <v>1527.07</v>
@@ -10701,7 +10683,7 @@
         <v>2026</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D24">
         <v>542.46</v>
@@ -10733,7 +10715,7 @@
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6D93DF-D2A3-4536-BFA7-4CF39D87C8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FE1838-5364-4E8C-B508-E8192FBD5A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -796,13 +796,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tb_base_dash_extensao" displayName="tb_base_dash_extensao" ref="B1:AF218">
-  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="25">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:AF218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AF218">
     <sortCondition ref="B1:B218"/>
   </sortState>
@@ -1256,7 +1250,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>64</v>
       </c>
@@ -1313,7 +1307,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>64</v>
       </c>
@@ -1356,7 +1350,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1402,7 +1396,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
@@ -1445,7 +1439,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>64</v>
       </c>
@@ -1491,7 +1485,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
@@ -1534,7 +1528,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>63</v>
       </c>
@@ -1582,7 +1576,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1625,7 +1619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1670,7 +1664,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
@@ -1708,7 +1702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
@@ -1751,7 +1745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>63</v>
       </c>
@@ -1789,7 +1783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>63</v>
       </c>
@@ -1834,7 +1828,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
@@ -1872,7 +1866,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
@@ -1917,7 +1911,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1955,7 +1949,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
@@ -1998,7 +1992,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>63</v>
       </c>
@@ -2036,7 +2030,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>63</v>
       </c>
@@ -2079,7 +2073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>63</v>
       </c>
@@ -2117,7 +2111,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>63</v>
       </c>
@@ -2160,7 +2154,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>63</v>
       </c>
@@ -2198,7 +2192,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>63</v>
       </c>
@@ -2243,7 +2237,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>63</v>
       </c>
@@ -2284,7 +2278,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>62</v>
       </c>
@@ -2329,7 +2323,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>62</v>
       </c>
@@ -2374,7 +2368,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
@@ -2417,7 +2411,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>62</v>
       </c>
@@ -2455,7 +2449,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>62</v>
       </c>
@@ -2495,7 +2489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
@@ -2533,7 +2527,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
@@ -2573,7 +2567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>62</v>
       </c>
@@ -2611,7 +2605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>62</v>
       </c>
@@ -2654,7 +2648,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>62</v>
       </c>
@@ -2692,7 +2686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>62</v>
       </c>
@@ -2732,7 +2726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>62</v>
       </c>
@@ -2770,7 +2764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>62</v>
       </c>
@@ -2810,7 +2804,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>62</v>
       </c>
@@ -2848,7 +2842,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>62</v>
       </c>
@@ -2888,7 +2882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
@@ -2926,7 +2920,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>62</v>
       </c>
@@ -2966,7 +2960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>62</v>
       </c>
@@ -3004,7 +2998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>62</v>
       </c>
@@ -3047,7 +3041,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>62</v>
       </c>
@@ -3085,7 +3079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>62</v>
       </c>
@@ -3130,7 +3124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
         <v>62</v>
       </c>
@@ -3168,7 +3162,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>62</v>
       </c>
@@ -3213,7 +3207,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>62</v>
       </c>
@@ -3251,7 +3245,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>62</v>
       </c>
@@ -3294,7 +3288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>62</v>
       </c>
@@ -3332,7 +3326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>62</v>
       </c>
@@ -3375,7 +3369,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>62</v>
       </c>
@@ -3413,7 +3407,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>62</v>
       </c>
@@ -3458,7 +3452,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
         <v>62</v>
       </c>
@@ -3496,7 +3490,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>62</v>
       </c>
@@ -3542,7 +3536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>62</v>
       </c>
@@ -3585,7 +3579,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
         <v>62</v>
       </c>
@@ -3628,7 +3622,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
         <v>62</v>
       </c>
@@ -3666,7 +3660,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
@@ -3731,7 +3725,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>58</v>
       </c>
@@ -3774,7 +3768,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>58</v>
       </c>
@@ -3830,7 +3824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>58</v>
       </c>
@@ -3872,7 +3866,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>58</v>
       </c>
@@ -3930,7 +3924,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>58</v>
       </c>
@@ -3974,7 +3968,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>59</v>
       </c>
@@ -4021,7 +4015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>59</v>
       </c>
@@ -4066,7 +4060,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>59</v>
       </c>
@@ -4113,7 +4107,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>59</v>
       </c>
@@ -4157,7 +4151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>33</v>
       </c>
@@ -4203,7 +4197,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
         <v>33</v>
       </c>
@@ -4246,7 +4240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>33</v>
       </c>
@@ -4291,7 +4285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
         <v>33</v>
       </c>
@@ -4334,7 +4328,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>33</v>
       </c>
@@ -4377,7 +4371,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>33</v>
       </c>
@@ -4420,7 +4414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
         <v>33</v>
       </c>
@@ -4468,7 +4462,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
         <v>33</v>
       </c>
@@ -4512,7 +4506,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>38</v>
       </c>
@@ -4567,7 +4561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
         <v>38</v>
       </c>
@@ -4610,7 +4604,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
         <v>38</v>
       </c>
@@ -4659,7 +4653,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B81" s="3" t="s">
         <v>38</v>
       </c>
@@ -4702,7 +4696,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>60</v>
       </c>
@@ -4751,7 +4745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B83" s="3" t="s">
         <v>60</v>
       </c>
@@ -4794,7 +4788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B84" s="3" t="s">
         <v>57</v>
       </c>
@@ -4850,7 +4844,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
         <v>57</v>
       </c>
@@ -4894,7 +4888,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B86" s="3" t="s">
         <v>57</v>
       </c>
@@ -4944,7 +4938,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
         <v>57</v>
       </c>
@@ -4988,7 +4982,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
         <v>57</v>
       </c>
@@ -5040,7 +5034,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>57</v>
       </c>
@@ -5084,7 +5078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>52</v>
       </c>
@@ -5119,7 +5113,7 @@
       <c r="AE90" s="4"/>
       <c r="AF90" s="4"/>
     </row>
-    <row r="91" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>52</v>
       </c>
@@ -5154,7 +5148,7 @@
       <c r="AE91" s="4"/>
       <c r="AF91" s="4"/>
     </row>
-    <row r="92" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
         <v>56</v>
       </c>
@@ -5206,7 +5200,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
         <v>56</v>
       </c>
@@ -5248,7 +5242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B94" s="3" t="s">
         <v>56</v>
       </c>
@@ -5300,7 +5294,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
         <v>56</v>
       </c>
@@ -5342,7 +5336,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>56</v>
       </c>
@@ -5394,7 +5388,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B97" s="3" t="s">
         <v>56</v>
       </c>
@@ -5438,7 +5432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
         <v>56</v>
       </c>
@@ -5485,7 +5479,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B99" s="3" t="s">
         <v>56</v>
       </c>
@@ -5529,7 +5523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B100" s="3" t="s">
         <v>55</v>
       </c>
@@ -5576,7 +5570,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B101" s="3" t="s">
         <v>37</v>
       </c>
@@ -5633,7 +5627,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B102" s="3" t="s">
         <v>37</v>
       </c>
@@ -5671,7 +5665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
         <v>37</v>
       </c>
@@ -5722,7 +5716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B104" s="3" t="s">
         <v>37</v>
       </c>
@@ -5763,7 +5757,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B105" s="3" t="s">
         <v>37</v>
       </c>
@@ -5814,7 +5808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="2:33" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="3" t="s">
         <v>37</v>
       </c>
@@ -5857,7 +5851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
         <v>37</v>
       </c>
@@ -5910,7 +5904,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B108" s="3" t="s">
         <v>37</v>
       </c>
@@ -5948,7 +5942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
         <v>37</v>
       </c>
@@ -5997,7 +5991,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
         <v>37</v>
       </c>
@@ -6046,7 +6040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>89</v>
       </c>
@@ -6090,7 +6084,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>89</v>
       </c>
@@ -6128,7 +6122,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B113" s="3" t="s">
         <v>77</v>
       </c>
@@ -6174,7 +6168,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B114" s="3" t="s">
         <v>77</v>
       </c>
@@ -6212,7 +6206,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
         <v>77</v>
       </c>
@@ -6261,7 +6255,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B116" s="3" t="s">
         <v>77</v>
       </c>
@@ -6304,7 +6298,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
         <v>74</v>
       </c>
@@ -6365,7 +6359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
         <v>74</v>
       </c>
@@ -6414,7 +6408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
         <v>74</v>
       </c>
@@ -6473,7 +6467,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
         <v>74</v>
       </c>
@@ -6519,7 +6513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
         <v>74</v>
       </c>
@@ -6568,7 +6562,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
         <v>74</v>
       </c>
@@ -6611,7 +6605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>50</v>
       </c>
@@ -6646,7 +6640,7 @@
       <c r="AE123" s="4"/>
       <c r="AF123" s="4"/>
     </row>
-    <row r="124" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>50</v>
       </c>
@@ -6678,7 +6672,7 @@
       <c r="AE124" s="4"/>
       <c r="AF124" s="4"/>
     </row>
-    <row r="125" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>53</v>
       </c>
@@ -6713,7 +6707,7 @@
       <c r="AE125" s="4"/>
       <c r="AF125" s="4"/>
     </row>
-    <row r="126" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>53</v>
       </c>
@@ -6748,7 +6742,7 @@
       <c r="AE126" s="4"/>
       <c r="AF126" s="4"/>
     </row>
-    <row r="127" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>48</v>
       </c>
@@ -6783,7 +6777,7 @@
       <c r="AE127" s="4"/>
       <c r="AF127" s="4"/>
     </row>
-    <row r="128" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>48</v>
       </c>
@@ -6815,7 +6809,7 @@
       <c r="AE128" s="4"/>
       <c r="AF128" s="4"/>
     </row>
-    <row r="129" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>70</v>
       </c>
@@ -6847,7 +6841,7 @@
       <c r="AE129" s="4"/>
       <c r="AF129" s="4"/>
     </row>
-    <row r="130" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>70</v>
       </c>
@@ -6882,7 +6876,7 @@
       <c r="AE130" s="4"/>
       <c r="AF130" s="4"/>
     </row>
-    <row r="131" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B131" s="3" t="s">
         <v>82</v>
       </c>
@@ -6931,7 +6925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
         <v>82</v>
       </c>
@@ -6975,7 +6969,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B133" s="3" t="s">
         <v>71</v>
       </c>
@@ -7013,7 +7007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B134" s="3" t="s">
         <v>71</v>
       </c>
@@ -7056,7 +7050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B135" s="3" t="s">
         <v>80</v>
       </c>
@@ -7097,7 +7091,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B136" s="3" t="s">
         <v>80</v>
       </c>
@@ -7135,7 +7129,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B137" s="3" t="s">
         <v>51</v>
       </c>
@@ -7170,7 +7164,7 @@
       <c r="AE137" s="4"/>
       <c r="AF137" s="4"/>
     </row>
-    <row r="138" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B138" s="3" t="s">
         <v>51</v>
       </c>
@@ -7205,7 +7199,7 @@
       <c r="AE138" s="4"/>
       <c r="AF138" s="4"/>
     </row>
-    <row r="139" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B139" s="3" t="s">
         <v>49</v>
       </c>
@@ -7240,7 +7234,7 @@
       <c r="AE139" s="4"/>
       <c r="AF139" s="4"/>
     </row>
-    <row r="140" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B140" s="3" t="s">
         <v>49</v>
       </c>
@@ -7272,7 +7266,7 @@
       <c r="AE140" s="4"/>
       <c r="AF140" s="4"/>
     </row>
-    <row r="141" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B141" s="3" t="s">
         <v>81</v>
       </c>
@@ -7304,7 +7298,7 @@
       <c r="AE141" s="4"/>
       <c r="AF141" s="4"/>
     </row>
-    <row r="142" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B142" s="3" t="s">
         <v>81</v>
       </c>
@@ -7339,7 +7333,7 @@
       <c r="AE142" s="4"/>
       <c r="AF142" s="4"/>
     </row>
-    <row r="143" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B143" s="3" t="s">
         <v>47</v>
       </c>
@@ -7388,7 +7382,7 @@
         <v>205</v>
       </c>
       <c r="F144" s="3">
-        <v>216.1</v>
+        <v>211.95</v>
       </c>
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
@@ -7408,7 +7402,8 @@
         <v>169.1</v>
       </c>
       <c r="AA144" s="4">
-        <v>47</v>
+        <f>47-4.15</f>
+        <v>42.85</v>
       </c>
       <c r="AB144" s="4"/>
       <c r="AC144" s="4"/>
@@ -7419,7 +7414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B145" s="3" t="s">
         <v>65</v>
       </c>
@@ -7468,7 +7463,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="146" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B146" s="3" t="s">
         <v>65</v>
       </c>
@@ -7509,7 +7504,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="147" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B147" s="3" t="s">
         <v>65</v>
       </c>
@@ -7559,7 +7554,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B148" s="3" t="s">
         <v>65</v>
       </c>
@@ -7604,7 +7599,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="149" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B149" s="3" t="s">
         <v>79</v>
       </c>
@@ -7636,7 +7631,7 @@
       <c r="AE149" s="4"/>
       <c r="AF149" s="4"/>
     </row>
-    <row r="150" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B150" s="3" t="s">
         <v>79</v>
       </c>
@@ -7671,7 +7666,7 @@
       <c r="AE150" s="4"/>
       <c r="AF150" s="4"/>
     </row>
-    <row r="151" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B151" s="3" t="s">
         <v>66</v>
       </c>
@@ -7714,7 +7709,7 @@
       <c r="AE151" s="4"/>
       <c r="AF151" s="4"/>
     </row>
-    <row r="152" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B152" s="3" t="s">
         <v>66</v>
       </c>
@@ -7749,7 +7744,7 @@
       <c r="AE152" s="4"/>
       <c r="AF152" s="4"/>
     </row>
-    <row r="153" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B153" s="3" t="s">
         <v>67</v>
       </c>
@@ -7787,7 +7782,7 @@
       <c r="AE153" s="4"/>
       <c r="AF153" s="4"/>
     </row>
-    <row r="154" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B154" s="3" t="s">
         <v>67</v>
       </c>
@@ -7822,7 +7817,7 @@
       <c r="AE154" s="4"/>
       <c r="AF154" s="4"/>
     </row>
-    <row r="155" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B155" s="3" t="s">
         <v>86</v>
       </c>
@@ -7857,7 +7852,7 @@
         <v>1746.61</v>
       </c>
     </row>
-    <row r="156" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B156" s="3" t="s">
         <v>86</v>
       </c>
@@ -7895,7 +7890,7 @@
         <v>1471.49</v>
       </c>
     </row>
-    <row r="157" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B157" s="3" t="s">
         <v>87</v>
       </c>
@@ -7931,7 +7926,7 @@
         <v>275.11999999999989</v>
       </c>
     </row>
-    <row r="158" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B158" s="3" t="s">
         <v>87</v>
       </c>
@@ -7966,7 +7961,7 @@
       <c r="AE158" s="4"/>
       <c r="AF158" s="4"/>
     </row>
-    <row r="159" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B159" s="3" t="s">
         <v>88</v>
       </c>
@@ -7998,7 +7993,7 @@
       <c r="AE159" s="4"/>
       <c r="AF159" s="4"/>
     </row>
-    <row r="160" spans="2:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B160" s="3" t="s">
         <v>88</v>
       </c>
@@ -8037,7 +8032,7 @@
         <v>91.706666666666635</v>
       </c>
     </row>
-    <row r="161" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B161" s="3" t="s">
         <v>76</v>
       </c>
@@ -8069,7 +8064,7 @@
       <c r="AE161" s="4"/>
       <c r="AF161" s="4"/>
     </row>
-    <row r="162" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B162" s="3" t="s">
         <v>76</v>
       </c>
@@ -8104,7 +8099,7 @@
       <c r="AE162" s="4"/>
       <c r="AF162" s="4"/>
     </row>
-    <row r="163" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B163" s="3" t="s">
         <v>85</v>
       </c>
@@ -8139,7 +8134,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B164" s="3" t="s">
         <v>85</v>
       </c>
@@ -8153,7 +8148,7 @@
         <v>338.5</v>
       </c>
       <c r="F164" s="3">
-        <v>377.8</v>
+        <v>390.49</v>
       </c>
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
@@ -8182,7 +8177,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B165" s="3" t="s">
         <v>83</v>
       </c>
@@ -8251,7 +8246,8 @@
         <v>100.7</v>
       </c>
       <c r="AA166" s="4">
-        <v>110</v>
+        <f>12.69+110</f>
+        <v>122.69</v>
       </c>
       <c r="AB166" s="4"/>
       <c r="AC166" s="4"/>
@@ -8262,7 +8258,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="167" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B167" s="3" t="s">
         <v>94</v>
       </c>
@@ -8311,7 +8307,7 @@
         <v>1566.27</v>
       </c>
       <c r="F168" s="3">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
@@ -8331,7 +8327,7 @@
         <v>42</v>
       </c>
       <c r="AA168" s="4">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="AB168" s="4"/>
       <c r="AC168" s="4"/>
@@ -8342,7 +8338,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="169" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
         <v>91</v>
       </c>
@@ -8391,7 +8387,7 @@
         <v>180</v>
       </c>
       <c r="F170" s="3">
-        <v>167.96</v>
+        <v>201.41</v>
       </c>
       <c r="L170" s="4"/>
       <c r="M170" s="4"/>
@@ -8407,7 +8403,8 @@
       <c r="W170" s="4"/>
       <c r="X170" s="4"/>
       <c r="Y170" s="4">
-        <v>43.66</v>
+        <f>33.45+43.66</f>
+        <v>77.11</v>
       </c>
       <c r="Z170" s="9">
         <v>89.8</v>
@@ -8424,7 +8421,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B171" s="3" t="s">
         <v>42</v>
       </c>
@@ -8459,7 +8456,7 @@
       <c r="AE171" s="4"/>
       <c r="AF171" s="4"/>
     </row>
-    <row r="172" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B172" s="3" t="s">
         <v>42</v>
       </c>
@@ -8491,7 +8488,7 @@
       <c r="AE172" s="4"/>
       <c r="AF172" s="4"/>
     </row>
-    <row r="173" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B173" s="3" t="s">
         <v>68</v>
       </c>
@@ -8526,7 +8523,7 @@
       <c r="AE173" s="4"/>
       <c r="AF173" s="4"/>
     </row>
-    <row r="174" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B174" s="3" t="s">
         <v>68</v>
       </c>
@@ -8561,7 +8558,7 @@
       <c r="AE174" s="4"/>
       <c r="AF174" s="4"/>
     </row>
-    <row r="175" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B175" s="3" t="s">
         <v>97</v>
       </c>
@@ -8607,7 +8604,7 @@
       <c r="AE175" s="4"/>
       <c r="AF175" s="4"/>
     </row>
-    <row r="176" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B176" s="3" t="s">
         <v>97</v>
       </c>
@@ -8651,7 +8648,7 @@
       <c r="AE176" s="4"/>
       <c r="AF176" s="4"/>
     </row>
-    <row r="177" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B177" s="3" t="s">
         <v>99</v>
       </c>
@@ -8686,7 +8683,7 @@
       <c r="AE177" s="4"/>
       <c r="AF177" s="4"/>
     </row>
-    <row r="178" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B178" s="3" t="s">
         <v>99</v>
       </c>
@@ -8721,7 +8718,7 @@
       <c r="AE178" s="4"/>
       <c r="AF178" s="4"/>
     </row>
-    <row r="179" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B179" s="3" t="s">
         <v>101</v>
       </c>
@@ -8756,7 +8753,7 @@
       <c r="AE179" s="4"/>
       <c r="AF179" s="4"/>
     </row>
-    <row r="180" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B180" s="3" t="s">
         <v>101</v>
       </c>
@@ -8791,7 +8788,7 @@
       <c r="AE180" s="4"/>
       <c r="AF180" s="4"/>
     </row>
-    <row r="181" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B181" s="3" t="s">
         <v>103</v>
       </c>
@@ -8823,7 +8820,7 @@
       <c r="AE181" s="4"/>
       <c r="AF181" s="4"/>
     </row>
-    <row r="182" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B182" s="3" t="s">
         <v>103</v>
       </c>
@@ -8858,7 +8855,7 @@
       <c r="AE182" s="4"/>
       <c r="AF182" s="4"/>
     </row>
-    <row r="183" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B183" s="3" t="s">
         <v>90</v>
       </c>
@@ -8893,7 +8890,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B184" s="3" t="s">
         <v>90</v>
       </c>
@@ -8931,7 +8928,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B185" s="3" t="s">
         <v>78</v>
       </c>
@@ -8969,7 +8966,7 @@
       <c r="AE185" s="4"/>
       <c r="AF185" s="4"/>
     </row>
-    <row r="186" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B186" s="3" t="s">
         <v>78</v>
       </c>
@@ -9004,7 +9001,7 @@
       <c r="AE186" s="4"/>
       <c r="AF186" s="4"/>
     </row>
-    <row r="187" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B187" s="3" t="s">
         <v>44</v>
       </c>
@@ -9044,7 +9041,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B188" s="3" t="s">
         <v>44</v>
       </c>
@@ -9082,7 +9079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B189" s="3" t="s">
         <v>45</v>
       </c>
@@ -9114,7 +9111,7 @@
       <c r="AE189" s="4"/>
       <c r="AF189" s="4"/>
     </row>
-    <row r="190" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B190" s="3" t="s">
         <v>45</v>
       </c>
@@ -9149,7 +9146,7 @@
       <c r="AE190" s="4"/>
       <c r="AF190" s="4"/>
     </row>
-    <row r="191" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B191" s="3" t="s">
         <v>54</v>
       </c>
@@ -9181,7 +9178,7 @@
       <c r="AE191" s="4"/>
       <c r="AF191" s="4"/>
     </row>
-    <row r="192" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B192" s="3" t="s">
         <v>54</v>
       </c>
@@ -9217,7 +9214,7 @@
       <c r="AE192" s="4"/>
       <c r="AF192" s="4"/>
     </row>
-    <row r="193" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B193" s="3" t="s">
         <v>43</v>
       </c>
@@ -9252,7 +9249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B194" s="3" t="s">
         <v>43</v>
       </c>
@@ -9290,7 +9287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B195" s="3" t="s">
         <v>92</v>
       </c>
@@ -9325,7 +9322,7 @@
       <c r="AE195" s="4"/>
       <c r="AF195" s="4"/>
     </row>
-    <row r="196" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B196" s="3" t="s">
         <v>92</v>
       </c>
@@ -9360,7 +9357,7 @@
       <c r="AE196" s="4"/>
       <c r="AF196" s="4"/>
     </row>
-    <row r="197" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B197" s="3" t="s">
         <v>46</v>
       </c>
@@ -9392,7 +9389,7 @@
       <c r="AE197" s="4"/>
       <c r="AF197" s="4"/>
     </row>
-    <row r="198" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B198" s="3" t="s">
         <v>46</v>
       </c>
@@ -9427,7 +9424,7 @@
       <c r="AE198" s="4"/>
       <c r="AF198" s="4"/>
     </row>
-    <row r="199" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B199" s="3" t="s">
         <v>41</v>
       </c>
@@ -9462,7 +9459,7 @@
       <c r="AE199" s="4"/>
       <c r="AF199" s="4"/>
     </row>
-    <row r="200" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B200" s="3" t="s">
         <v>41</v>
       </c>
@@ -9497,7 +9494,7 @@
       <c r="AE200" s="4"/>
       <c r="AF200" s="4"/>
     </row>
-    <row r="201" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B201" s="3" t="s">
         <v>61</v>
       </c>
@@ -9529,7 +9526,7 @@
       <c r="AE201" s="4"/>
       <c r="AF201" s="4"/>
     </row>
-    <row r="202" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B202" s="3" t="s">
         <v>61</v>
       </c>
@@ -9564,7 +9561,7 @@
       <c r="AE202" s="4"/>
       <c r="AF202" s="4"/>
     </row>
-    <row r="203" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B203" s="3" t="s">
         <v>95</v>
       </c>
@@ -9599,7 +9596,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B204" s="3" t="s">
         <v>95</v>
       </c>
@@ -9613,7 +9610,7 @@
         <v>95</v>
       </c>
       <c r="F204" s="3">
-        <v>93.2</v>
+        <v>82.99</v>
       </c>
       <c r="L204" s="4"/>
       <c r="M204" s="4"/>
@@ -9629,7 +9626,7 @@
       <c r="W204" s="4"/>
       <c r="X204" s="4"/>
       <c r="Y204" s="4">
-        <v>93.2</v>
+        <v>82.99</v>
       </c>
       <c r="Z204" s="9"/>
       <c r="AA204" s="4"/>
@@ -9642,7 +9639,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" s="3" t="s">
         <v>69</v>
       </c>
@@ -9700,7 +9697,7 @@
         <v>1799.2</v>
       </c>
       <c r="F206" s="3">
-        <v>1716.2</v>
+        <v>1616.26</v>
       </c>
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
@@ -9716,7 +9713,7 @@
       <c r="W206" s="4"/>
       <c r="X206" s="4"/>
       <c r="Y206" s="4">
-        <v>930</v>
+        <v>830.06</v>
       </c>
       <c r="Z206" s="9">
         <v>584.20000000000005</v>
@@ -9733,7 +9730,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>72</v>
       </c>
@@ -9808,7 +9805,7 @@
       <c r="AE208" s="4"/>
       <c r="AF208" s="4"/>
     </row>
-    <row r="209" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>84</v>
       </c>
@@ -9846,7 +9843,7 @@
       <c r="AE209" s="4"/>
       <c r="AF209" s="4"/>
     </row>
-    <row r="210" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>84</v>
       </c>
@@ -9881,7 +9878,7 @@
       <c r="AE210" s="4"/>
       <c r="AF210" s="4"/>
     </row>
-    <row r="211" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>93</v>
       </c>
@@ -9913,7 +9910,7 @@
       <c r="AE211" s="4"/>
       <c r="AF211" s="4"/>
     </row>
-    <row r="212" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>93</v>
       </c>
@@ -9948,7 +9945,7 @@
       <c r="AE212" s="4"/>
       <c r="AF212" s="4"/>
     </row>
-    <row r="213" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>75</v>
       </c>
@@ -9986,7 +9983,7 @@
       <c r="AE213" s="4"/>
       <c r="AF213" s="4"/>
     </row>
-    <row r="214" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>75</v>
       </c>
@@ -10021,7 +10018,7 @@
       <c r="AE214" s="4"/>
       <c r="AF214" s="4"/>
     </row>
-    <row r="215" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>73</v>
       </c>
@@ -10056,7 +10053,7 @@
       <c r="AE215" s="4"/>
       <c r="AF215" s="4"/>
     </row>
-    <row r="216" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>73</v>
       </c>
@@ -10091,7 +10088,7 @@
       <c r="AE216" s="4"/>
       <c r="AF216" s="4"/>
     </row>
-    <row r="217" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>39</v>
       </c>
@@ -10132,7 +10129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="218" spans="2:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>39</v>
       </c>

--- a/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FE1838-5364-4E8C-B508-E8192FBD5A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8164927-9F47-4A8C-B1AD-701454278295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4121,7 +4121,7 @@
         <v>194.5</v>
       </c>
       <c r="F69" s="3">
-        <v>12.02</v>
+        <v>13.14</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="4"/>
@@ -4136,7 +4136,8 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
       <c r="W69" s="4">
-        <v>12.02</v>
+        <f>12.02+1.12</f>
+        <v>13.14</v>
       </c>
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
@@ -6051,7 +6052,7 @@
         <v>34</v>
       </c>
       <c r="F111" s="3">
-        <v>880.94100000000003</v>
+        <v>879.94100000000003</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -6071,8 +6072,8 @@
         <v>548.55000000000007</v>
       </c>
       <c r="Z111" s="9">
-        <f>64.57+79.57+66.725+63.68+57.846</f>
-        <v>332.39099999999996</v>
+        <f>64.57+79.57+66.725+63.68+56.846</f>
+        <v>331.39099999999996</v>
       </c>
       <c r="AA111" s="4"/>
       <c r="AB111" s="4"/>
@@ -6939,7 +6940,7 @@
         <v>83.8</v>
       </c>
       <c r="F132" s="3">
-        <v>55.83</v>
+        <v>56.52</v>
       </c>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
@@ -6954,8 +6955,8 @@
       <c r="V132" s="4"/>
       <c r="W132" s="4"/>
       <c r="X132" s="4">
-        <f>34.75+6.11+14.97</f>
-        <v>55.83</v>
+        <f>34.75+6.11+14.97+0.69</f>
+        <v>56.519999999999996</v>
       </c>
       <c r="Y132" s="4"/>
       <c r="Z132" s="9"/>
@@ -7021,7 +7022,7 @@
         <v>59.5</v>
       </c>
       <c r="F134" s="3">
-        <v>68.2</v>
+        <v>61.69</v>
       </c>
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
@@ -7038,7 +7039,8 @@
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
       <c r="Z134" s="9">
-        <v>68.2</v>
+        <f>68.2-6.51</f>
+        <v>61.690000000000005</v>
       </c>
       <c r="AA134" s="4"/>
       <c r="AB134" s="4"/>
@@ -9012,7 +9014,7 @@
         <v>34</v>
       </c>
       <c r="F187" s="3">
-        <v>38.299999999999997</v>
+        <v>37.58</v>
       </c>
       <c r="L187" s="4"/>
       <c r="M187" s="4"/>
@@ -9029,7 +9031,7 @@
       <c r="X187" s="4"/>
       <c r="Y187" s="4"/>
       <c r="Z187" s="9">
-        <v>38.299999999999997</v>
+        <v>37.58</v>
       </c>
       <c r="AA187" s="4"/>
       <c r="AB187" s="4"/>
